--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -450,52 +450,52 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Runs Rank</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Home Runs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Home Runs Rank</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>On-Base %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>On-Base % Rank</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Slugging %</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Slugging % Rank</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Batting Strikeouts</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Batting Strikeouts Rank</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Runs Rank</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Home Runs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Home Runs Rank</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>On-Base %</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>On-Base % Rank</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Slugging %</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Slugging % Rank</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -552,34 +552,34 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
+        <v>331</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3089631</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.38401255</v>
+      </c>
+      <c r="K2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2" t="n">
         <v>569</v>
       </c>
-      <c r="E2" t="n">
+      <c r="M2" t="n">
         <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>331</v>
-      </c>
-      <c r="G2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>68</v>
-      </c>
-      <c r="I2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.3089631</v>
-      </c>
-      <c r="K2" t="n">
-        <v>26</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.38401255</v>
-      </c>
-      <c r="M2" t="n">
-        <v>25</v>
       </c>
       <c r="N2" t="n">
         <v>4.3035803</v>
@@ -619,34 +619,34 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
+        <v>364</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.32978722</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.42038217</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
         <v>672</v>
       </c>
-      <c r="E3" t="n">
+      <c r="M3" t="n">
         <v>24</v>
-      </c>
-      <c r="F3" t="n">
-        <v>364</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.32978722</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.42038217</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5</v>
       </c>
       <c r="N3" t="n">
         <v>4.999048</v>
@@ -686,34 +686,34 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
+        <v>377</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>101</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.316655</v>
+      </c>
+      <c r="I4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.42109343</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
         <v>604</v>
       </c>
-      <c r="E4" t="n">
+      <c r="M4" t="n">
         <v>6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>377</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>101</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.316655</v>
-      </c>
-      <c r="K4" t="n">
-        <v>19</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.42109343</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
       </c>
       <c r="N4" t="n">
         <v>3.404926</v>
@@ -753,34 +753,34 @@
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>714</v>
+        <v>369</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>369</v>
+        <v>94</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>0.3213807</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3213807</v>
+        <v>0.4030303</v>
       </c>
       <c r="K5" t="n">
         <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4030303</v>
+        <v>714</v>
       </c>
       <c r="M5" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="N5" t="n">
         <v>4.4549356</v>
@@ -820,34 +820,34 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
+        <v>294</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>64</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.31099963</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.38061184</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27</v>
+      </c>
+      <c r="L6" t="n">
         <v>628</v>
       </c>
-      <c r="E6" t="n">
+      <c r="M6" t="n">
         <v>11</v>
-      </c>
-      <c r="F6" t="n">
-        <v>294</v>
-      </c>
-      <c r="G6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" t="n">
-        <v>64</v>
-      </c>
-      <c r="I6" t="n">
-        <v>29</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.31099963</v>
-      </c>
-      <c r="K6" t="n">
-        <v>25</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.38061184</v>
-      </c>
-      <c r="M6" t="n">
-        <v>27</v>
       </c>
       <c r="N6" t="n">
         <v>3.8513105</v>
@@ -887,34 +887,34 @@
         <v>16</v>
       </c>
       <c r="D7" t="n">
+        <v>366</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.33707866</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.40129572</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="n">
         <v>636</v>
       </c>
-      <c r="E7" t="n">
+      <c r="M7" t="n">
         <v>13</v>
-      </c>
-      <c r="F7" t="n">
-        <v>366</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>90</v>
-      </c>
-      <c r="I7" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.33707866</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.40129572</v>
-      </c>
-      <c r="M7" t="n">
-        <v>14</v>
       </c>
       <c r="N7" t="n">
         <v>4.280488</v>
@@ -954,34 +954,34 @@
         <v>23</v>
       </c>
       <c r="D8" t="n">
+        <v>353</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" t="n">
+        <v>106</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3189776</v>
+      </c>
+      <c r="I8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.40982956</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" t="n">
         <v>692</v>
       </c>
-      <c r="E8" t="n">
+      <c r="M8" t="n">
         <v>26</v>
-      </c>
-      <c r="F8" t="n">
-        <v>353</v>
-      </c>
-      <c r="G8" t="n">
-        <v>14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>106</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.3189776</v>
-      </c>
-      <c r="K8" t="n">
-        <v>16</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.40982956</v>
-      </c>
-      <c r="M8" t="n">
-        <v>9</v>
       </c>
       <c r="N8" t="n">
         <v>4.408437</v>
@@ -1021,34 +1021,34 @@
         <v>28</v>
       </c>
       <c r="D9" t="n">
+        <v>325</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>96</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.31135023</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.39498433</v>
+      </c>
+      <c r="K9" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" t="n">
         <v>712</v>
       </c>
-      <c r="E9" t="n">
+      <c r="M9" t="n">
         <v>27</v>
-      </c>
-      <c r="F9" t="n">
-        <v>325</v>
-      </c>
-      <c r="G9" t="n">
-        <v>22</v>
-      </c>
-      <c r="H9" t="n">
-        <v>96</v>
-      </c>
-      <c r="I9" t="n">
-        <v>11</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.31135023</v>
-      </c>
-      <c r="K9" t="n">
-        <v>24</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.39498433</v>
-      </c>
-      <c r="M9" t="n">
-        <v>18</v>
       </c>
       <c r="N9" t="n">
         <v>4.579646</v>
@@ -1088,34 +1088,34 @@
         <v>29</v>
       </c>
       <c r="D10" t="n">
+        <v>310</v>
+      </c>
+      <c r="E10" t="n">
+        <v>27</v>
+      </c>
+      <c r="F10" t="n">
+        <v>74</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="I10" t="n">
+        <v>22</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3702544</v>
+      </c>
+      <c r="K10" t="n">
+        <v>29</v>
+      </c>
+      <c r="L10" t="n">
         <v>627</v>
       </c>
-      <c r="E10" t="n">
+      <c r="M10" t="n">
         <v>10</v>
-      </c>
-      <c r="F10" t="n">
-        <v>310</v>
-      </c>
-      <c r="G10" t="n">
-        <v>27</v>
-      </c>
-      <c r="H10" t="n">
-        <v>74</v>
-      </c>
-      <c r="I10" t="n">
-        <v>25</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="K10" t="n">
-        <v>22</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.3702544</v>
-      </c>
-      <c r="M10" t="n">
-        <v>29</v>
       </c>
       <c r="N10" t="n">
         <v>3.7917676</v>
@@ -1155,34 +1155,34 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
+        <v>356</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>84</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3224822</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4096933</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
         <v>687</v>
       </c>
-      <c r="E11" t="n">
+      <c r="M11" t="n">
         <v>25</v>
-      </c>
-      <c r="F11" t="n">
-        <v>356</v>
-      </c>
-      <c r="G11" t="n">
-        <v>12</v>
-      </c>
-      <c r="H11" t="n">
-        <v>84</v>
-      </c>
-      <c r="I11" t="n">
-        <v>18</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.3224822</v>
-      </c>
-      <c r="K11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.4096933</v>
-      </c>
-      <c r="M11" t="n">
-        <v>10</v>
       </c>
       <c r="N11" t="n">
         <v>5.5263157</v>
@@ -1222,34 +1222,34 @@
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>664</v>
+        <v>314</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>314</v>
+        <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>86</v>
+        <v>0.31471202</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>0.31471202</v>
+        <v>0.39333335</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>0.39333335</v>
+        <v>664</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
         <v>3.8342404</v>
@@ -1289,34 +1289,34 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
+        <v>356</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>103</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.31749243</v>
+      </c>
+      <c r="I13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.41251886</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="n">
         <v>647</v>
       </c>
-      <c r="E13" t="n">
+      <c r="M13" t="n">
         <v>17</v>
-      </c>
-      <c r="F13" t="n">
-        <v>356</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12</v>
-      </c>
-      <c r="H13" t="n">
-        <v>103</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.31749243</v>
-      </c>
-      <c r="K13" t="n">
-        <v>18</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.41251886</v>
-      </c>
-      <c r="M13" t="n">
-        <v>7</v>
       </c>
       <c r="N13" t="n">
         <v>4.839866</v>
@@ -1356,34 +1356,34 @@
         <v>11</v>
       </c>
       <c r="D14" t="n">
+        <v>331</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17</v>
+      </c>
+      <c r="F14" t="n">
+        <v>77</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.32111338</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.39518902</v>
+      </c>
+      <c r="K14" t="n">
+        <v>17</v>
+      </c>
+      <c r="L14" t="n">
         <v>616</v>
       </c>
-      <c r="E14" t="n">
+      <c r="M14" t="n">
         <v>9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>331</v>
-      </c>
-      <c r="G14" t="n">
-        <v>17</v>
-      </c>
-      <c r="H14" t="n">
-        <v>77</v>
-      </c>
-      <c r="I14" t="n">
-        <v>23</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.32111338</v>
-      </c>
-      <c r="K14" t="n">
-        <v>13</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.39518902</v>
-      </c>
-      <c r="M14" t="n">
-        <v>17</v>
       </c>
       <c r="N14" t="n">
         <v>4.5760503</v>
@@ -1423,34 +1423,34 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>747</v>
+        <v>361</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>361</v>
+        <v>95</v>
       </c>
       <c r="G15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>95</v>
+        <v>0.31977326</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>0.31977326</v>
+        <v>0.40105143</v>
       </c>
       <c r="K15" t="n">
         <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>0.40105143</v>
+        <v>747</v>
       </c>
       <c r="M15" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N15" t="n">
         <v>4.6507177</v>
@@ -1490,34 +1490,34 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>405</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>105</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.34316355</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.43536633</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
         <v>615</v>
       </c>
-      <c r="E16" t="n">
+      <c r="M16" t="n">
         <v>8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>405</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>105</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.34316355</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.43536633</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>3.4568381</v>
@@ -1557,34 +1557,34 @@
         <v>15</v>
       </c>
       <c r="D17" t="n">
+        <v>336</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F17" t="n">
+        <v>69</v>
+      </c>
+      <c r="G17" t="n">
+        <v>26</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.32289156</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.38677043</v>
+      </c>
+      <c r="K17" t="n">
+        <v>24</v>
+      </c>
+      <c r="L17" t="n">
         <v>641</v>
       </c>
-      <c r="E17" t="n">
+      <c r="M17" t="n">
         <v>15</v>
-      </c>
-      <c r="F17" t="n">
-        <v>336</v>
-      </c>
-      <c r="G17" t="n">
-        <v>16</v>
-      </c>
-      <c r="H17" t="n">
-        <v>69</v>
-      </c>
-      <c r="I17" t="n">
-        <v>26</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.32289156</v>
-      </c>
-      <c r="K17" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.38677043</v>
-      </c>
-      <c r="M17" t="n">
-        <v>24</v>
       </c>
       <c r="N17" t="n">
         <v>4.072993</v>
@@ -1624,34 +1624,34 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
+        <v>397</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>68</v>
+      </c>
+      <c r="G18" t="n">
+        <v>27</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.33999312</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.39357114</v>
+      </c>
+      <c r="K18" t="n">
+        <v>19</v>
+      </c>
+      <c r="L18" t="n">
         <v>610</v>
       </c>
-      <c r="E18" t="n">
+      <c r="M18" t="n">
         <v>7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>397</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>68</v>
-      </c>
-      <c r="I18" t="n">
-        <v>27</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.33999312</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.39357114</v>
-      </c>
-      <c r="M18" t="n">
-        <v>19</v>
       </c>
       <c r="N18" t="n">
         <v>3.4488072</v>
@@ -1691,34 +1691,34 @@
         <v>12</v>
       </c>
       <c r="D19" t="n">
+        <v>388</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>97</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.32345104</v>
+      </c>
+      <c r="I19" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4117647</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="n">
         <v>657</v>
       </c>
-      <c r="E19" t="n">
+      <c r="M19" t="n">
         <v>19</v>
-      </c>
-      <c r="F19" t="n">
-        <v>388</v>
-      </c>
-      <c r="G19" t="n">
-        <v>6</v>
-      </c>
-      <c r="H19" t="n">
-        <v>97</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.32345104</v>
-      </c>
-      <c r="K19" t="n">
-        <v>9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.4117647</v>
-      </c>
-      <c r="M19" t="n">
-        <v>8</v>
       </c>
       <c r="N19" t="n">
         <v>4.78907</v>
@@ -1758,34 +1758,34 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
+        <v>311</v>
+      </c>
+      <c r="E20" t="n">
+        <v>26</v>
+      </c>
+      <c r="F20" t="n">
+        <v>82</v>
+      </c>
+      <c r="G20" t="n">
+        <v>19</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.29722124</v>
+      </c>
+      <c r="I20" t="n">
+        <v>29</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.37199378</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28</v>
+      </c>
+      <c r="L20" t="n">
         <v>638</v>
       </c>
-      <c r="E20" t="n">
+      <c r="M20" t="n">
         <v>14</v>
-      </c>
-      <c r="F20" t="n">
-        <v>311</v>
-      </c>
-      <c r="G20" t="n">
-        <v>26</v>
-      </c>
-      <c r="H20" t="n">
-        <v>82</v>
-      </c>
-      <c r="I20" t="n">
-        <v>19</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.29722124</v>
-      </c>
-      <c r="K20" t="n">
-        <v>29</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.37199378</v>
-      </c>
-      <c r="M20" t="n">
-        <v>28</v>
       </c>
       <c r="N20" t="n">
         <v>4.08932</v>
@@ -1825,34 +1825,34 @@
         <v>14</v>
       </c>
       <c r="D21" t="n">
+        <v>389</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>114</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.33159903</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.43863815</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
         <v>657</v>
       </c>
-      <c r="E21" t="n">
+      <c r="M21" t="n">
         <v>19</v>
-      </c>
-      <c r="F21" t="n">
-        <v>389</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>114</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.33159903</v>
-      </c>
-      <c r="K21" t="n">
-        <v>6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.43863815</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>3.3450148</v>
@@ -1892,34 +1892,34 @@
         <v>25</v>
       </c>
       <c r="D22" t="n">
+        <v>329</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>99</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.30031502</v>
+      </c>
+      <c r="I22" t="n">
+        <v>28</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.39643136</v>
+      </c>
+      <c r="K22" t="n">
+        <v>16</v>
+      </c>
+      <c r="L22" t="n">
         <v>660</v>
       </c>
-      <c r="E22" t="n">
+      <c r="M22" t="n">
         <v>21</v>
-      </c>
-      <c r="F22" t="n">
-        <v>329</v>
-      </c>
-      <c r="G22" t="n">
-        <v>19</v>
-      </c>
-      <c r="H22" t="n">
-        <v>99</v>
-      </c>
-      <c r="I22" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.30031502</v>
-      </c>
-      <c r="K22" t="n">
-        <v>28</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.39643136</v>
-      </c>
-      <c r="M22" t="n">
-        <v>16</v>
       </c>
       <c r="N22" t="n">
         <v>4.0578794</v>
@@ -1959,34 +1959,34 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
+        <v>391</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>94</v>
+      </c>
+      <c r="G23" t="n">
+        <v>13</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.33464438</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.40925926</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11</v>
+      </c>
+      <c r="L23" t="n">
         <v>720</v>
       </c>
-      <c r="E23" t="n">
+      <c r="M23" t="n">
         <v>29</v>
-      </c>
-      <c r="F23" t="n">
-        <v>391</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" t="n">
-        <v>94</v>
-      </c>
-      <c r="I23" t="n">
-        <v>13</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.33464438</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.40925926</v>
-      </c>
-      <c r="M23" t="n">
-        <v>11</v>
       </c>
       <c r="N23" t="n">
         <v>4.2123094</v>
@@ -2026,34 +2026,34 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>645</v>
+        <v>296</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>0.29252437</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.29252437</v>
+        <v>0.36389223</v>
       </c>
       <c r="K24" t="n">
         <v>30</v>
       </c>
       <c r="L24" t="n">
-        <v>0.36389223</v>
+        <v>645</v>
       </c>
       <c r="M24" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="N24" t="n">
         <v>3.9049034</v>
@@ -2093,34 +2093,34 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
+        <v>317</v>
+      </c>
+      <c r="E25" t="n">
+        <v>23</v>
+      </c>
+      <c r="F25" t="n">
+        <v>81</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.30878285</v>
+      </c>
+      <c r="I25" t="n">
+        <v>27</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.41857842</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" t="n">
         <v>592</v>
       </c>
-      <c r="E25" t="n">
+      <c r="M25" t="n">
         <v>5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>317</v>
-      </c>
-      <c r="G25" t="n">
-        <v>23</v>
-      </c>
-      <c r="H25" t="n">
-        <v>81</v>
-      </c>
-      <c r="I25" t="n">
-        <v>20</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.30878285</v>
-      </c>
-      <c r="K25" t="n">
-        <v>27</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.41857842</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6</v>
       </c>
       <c r="N25" t="n">
         <v>4.4624815</v>
@@ -2160,34 +2160,34 @@
         <v>27</v>
       </c>
       <c r="D26" t="n">
+        <v>326</v>
+      </c>
+      <c r="E26" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" t="n">
+        <v>98</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.31254238</v>
+      </c>
+      <c r="I26" t="n">
+        <v>21</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.38714615</v>
+      </c>
+      <c r="K26" t="n">
+        <v>22</v>
+      </c>
+      <c r="L26" t="n">
         <v>669</v>
       </c>
-      <c r="E26" t="n">
+      <c r="M26" t="n">
         <v>23</v>
-      </c>
-      <c r="F26" t="n">
-        <v>326</v>
-      </c>
-      <c r="G26" t="n">
-        <v>21</v>
-      </c>
-      <c r="H26" t="n">
-        <v>98</v>
-      </c>
-      <c r="I26" t="n">
-        <v>9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.31254238</v>
-      </c>
-      <c r="K26" t="n">
-        <v>21</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.38714615</v>
-      </c>
-      <c r="M26" t="n">
-        <v>22</v>
       </c>
       <c r="N26" t="n">
         <v>3.623044</v>
@@ -2227,34 +2227,34 @@
         <v>9</v>
       </c>
       <c r="D27" t="n">
+        <v>349</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" t="n">
+        <v>87</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.32752612</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.4016555</v>
+      </c>
+      <c r="K27" t="n">
+        <v>13</v>
+      </c>
+      <c r="L27" t="n">
         <v>587</v>
       </c>
-      <c r="E27" t="n">
+      <c r="M27" t="n">
         <v>4</v>
-      </c>
-      <c r="F27" t="n">
-        <v>349</v>
-      </c>
-      <c r="G27" t="n">
-        <v>15</v>
-      </c>
-      <c r="H27" t="n">
-        <v>87</v>
-      </c>
-      <c r="I27" t="n">
-        <v>16</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.32752612</v>
-      </c>
-      <c r="K27" t="n">
-        <v>8</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.4016555</v>
-      </c>
-      <c r="M27" t="n">
-        <v>13</v>
       </c>
       <c r="N27" t="n">
         <v>4.2942348</v>
@@ -2294,34 +2294,34 @@
         <v>3</v>
       </c>
       <c r="D28" t="n">
+        <v>327</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" t="n">
+        <v>62</v>
+      </c>
+      <c r="G28" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.33416727</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.38312474</v>
+      </c>
+      <c r="K28" t="n">
+        <v>26</v>
+      </c>
+      <c r="L28" t="n">
         <v>540</v>
       </c>
-      <c r="E28" t="n">
+      <c r="M28" t="n">
         <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>327</v>
-      </c>
-      <c r="G28" t="n">
-        <v>20</v>
-      </c>
-      <c r="H28" t="n">
-        <v>62</v>
-      </c>
-      <c r="I28" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.33416727</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.38312474</v>
-      </c>
-      <c r="M28" t="n">
-        <v>26</v>
       </c>
       <c r="N28" t="n">
         <v>3.9077156</v>
@@ -2361,34 +2361,34 @@
         <v>19</v>
       </c>
       <c r="D29" t="n">
+        <v>309</v>
+      </c>
+      <c r="E29" t="n">
+        <v>28</v>
+      </c>
+      <c r="F29" t="n">
+        <v>78</v>
+      </c>
+      <c r="G29" t="n">
+        <v>21</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.31778628</v>
+      </c>
+      <c r="I29" t="n">
+        <v>17</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3869582</v>
+      </c>
+      <c r="K29" t="n">
+        <v>23</v>
+      </c>
+      <c r="L29" t="n">
         <v>652</v>
       </c>
-      <c r="E29" t="n">
+      <c r="M29" t="n">
         <v>18</v>
-      </c>
-      <c r="F29" t="n">
-        <v>309</v>
-      </c>
-      <c r="G29" t="n">
-        <v>28</v>
-      </c>
-      <c r="H29" t="n">
-        <v>78</v>
-      </c>
-      <c r="I29" t="n">
-        <v>21</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.31778628</v>
-      </c>
-      <c r="K29" t="n">
-        <v>17</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.3869582</v>
-      </c>
-      <c r="M29" t="n">
-        <v>23</v>
       </c>
       <c r="N29" t="n">
         <v>3.9447186</v>
@@ -2428,34 +2428,34 @@
         <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>562</v>
+        <v>316</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>316</v>
+        <v>77</v>
       </c>
       <c r="G30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H30" t="n">
-        <v>77</v>
+        <v>0.31138355</v>
       </c>
       <c r="I30" t="n">
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>0.31138355</v>
+        <v>0.39133796</v>
       </c>
       <c r="K30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L30" t="n">
-        <v>0.39133796</v>
+        <v>562</v>
       </c>
       <c r="M30" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
         <v>4.1325183</v>
@@ -2495,34 +2495,34 @@
         <v>13</v>
       </c>
       <c r="D31" t="n">
+        <v>416</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>101</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3204698</v>
+      </c>
+      <c r="I31" t="n">
+        <v>14</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.42123032</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="n">
         <v>631</v>
       </c>
-      <c r="E31" t="n">
+      <c r="M31" t="n">
         <v>12</v>
-      </c>
-      <c r="F31" t="n">
-        <v>416</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>101</v>
-      </c>
-      <c r="I31" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.3204698</v>
-      </c>
-      <c r="K31" t="n">
-        <v>14</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.42123032</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3</v>
       </c>
       <c r="N31" t="n">
         <v>4.6370125</v>
@@ -2704,52 +2704,52 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Runs Rank</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Home Runs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Home Runs Rank</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>On-Base %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>On-Base % Rank</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Slugging %</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Slugging % Rank</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Batting Strikeouts</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Batting Strikeouts Rank</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Runs</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Runs Rank</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Home Runs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Home Runs Rank</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>On-Base %</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>On-Base % Rank</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Slugging %</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Slugging % Rank</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -2806,34 +2806,34 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.33777776</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.37688443</v>
+      </c>
+      <c r="K2" t="n">
+        <v>24</v>
+      </c>
+      <c r="L2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="M2" t="n">
         <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>31</v>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.33777776</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.37688443</v>
-      </c>
-      <c r="M2" t="n">
-        <v>24</v>
       </c>
       <c r="N2" t="n">
         <v>5.6666665</v>
@@ -2873,34 +2873,34 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>0.33576643</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.33576643</v>
+        <v>0.4625</v>
       </c>
       <c r="K3" t="n">
         <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4625</v>
+        <v>67</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N3" t="n">
         <v>6.46875</v>
@@ -2940,34 +2940,34 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.26704547</v>
+      </c>
+      <c r="I4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.37951806</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22</v>
+      </c>
+      <c r="L4" t="n">
         <v>48</v>
       </c>
-      <c r="E4" t="n">
+      <c r="M4" t="n">
         <v>13</v>
-      </c>
-      <c r="F4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G4" t="n">
-        <v>28</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.26704547</v>
-      </c>
-      <c r="K4" t="n">
-        <v>26</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.37951806</v>
-      </c>
-      <c r="M4" t="n">
-        <v>22</v>
       </c>
       <c r="N4" t="n">
         <v>5</v>
@@ -3007,34 +3007,34 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2882883</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.38916257</v>
+      </c>
+      <c r="K5" t="n">
+        <v>19</v>
+      </c>
+      <c r="L5" t="n">
         <v>62</v>
       </c>
-      <c r="E5" t="n">
+      <c r="M5" t="n">
         <v>27</v>
-      </c>
-      <c r="F5" t="n">
-        <v>26</v>
-      </c>
-      <c r="G5" t="n">
-        <v>14</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.2882883</v>
-      </c>
-      <c r="K5" t="n">
-        <v>23</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.38916257</v>
-      </c>
-      <c r="M5" t="n">
-        <v>19</v>
       </c>
       <c r="N5" t="n">
         <v>2.7870967</v>
@@ -3074,34 +3074,34 @@
         <v>27</v>
       </c>
       <c r="D6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" t="n">
+        <v>29</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2824074</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.34358975</v>
+      </c>
+      <c r="K6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L6" t="n">
         <v>59</v>
       </c>
-      <c r="E6" t="n">
+      <c r="M6" t="n">
         <v>25</v>
-      </c>
-      <c r="F6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G6" t="n">
-        <v>29</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>21</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.2824074</v>
-      </c>
-      <c r="K6" t="n">
-        <v>25</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.34358975</v>
-      </c>
-      <c r="M6" t="n">
-        <v>29</v>
       </c>
       <c r="N6" t="n">
         <v>3.2264152</v>
@@ -3141,34 +3141,34 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
+        <v>37</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.42465752</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5222222</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
         <v>33</v>
       </c>
-      <c r="E7" t="n">
+      <c r="M7" t="n">
         <v>3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>37</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.42465752</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5222222</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4</v>
       </c>
       <c r="N7" t="n">
         <v>5</v>
@@ -3208,31 +3208,31 @@
         <v>28</v>
       </c>
       <c r="D8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.24651162</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K8" t="n">
+        <v>21</v>
+      </c>
+      <c r="L8" t="n">
         <v>57</v>
-      </c>
-      <c r="E8" t="n">
-        <v>21</v>
-      </c>
-      <c r="F8" t="n">
-        <v>20</v>
-      </c>
-      <c r="G8" t="n">
-        <v>25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.24651162</v>
-      </c>
-      <c r="K8" t="n">
-        <v>30</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.38</v>
       </c>
       <c r="M8" t="n">
         <v>21</v>
@@ -3275,34 +3275,34 @@
         <v>24</v>
       </c>
       <c r="D9" t="n">
+        <v>32</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.30357143</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16</v>
+      </c>
+      <c r="L9" t="n">
         <v>61</v>
       </c>
-      <c r="E9" t="n">
+      <c r="M9" t="n">
         <v>26</v>
-      </c>
-      <c r="F9" t="n">
-        <v>32</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>16</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.30357143</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="M9" t="n">
-        <v>16</v>
       </c>
       <c r="N9" t="n">
         <v>3.3962264</v>
@@ -3342,34 +3342,34 @@
         <v>29</v>
       </c>
       <c r="D10" t="n">
+        <v>21</v>
+      </c>
+      <c r="E10" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.25943395</v>
+      </c>
+      <c r="I10" t="n">
+        <v>29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.34895834</v>
+      </c>
+      <c r="K10" t="n">
+        <v>28</v>
+      </c>
+      <c r="L10" t="n">
         <v>69</v>
       </c>
-      <c r="E10" t="n">
+      <c r="M10" t="n">
         <v>30</v>
-      </c>
-      <c r="F10" t="n">
-        <v>21</v>
-      </c>
-      <c r="G10" t="n">
-        <v>23</v>
-      </c>
-      <c r="H10" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>12</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.25943395</v>
-      </c>
-      <c r="K10" t="n">
-        <v>29</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.34895834</v>
-      </c>
-      <c r="M10" t="n">
-        <v>28</v>
       </c>
       <c r="N10" t="n">
         <v>4.32</v>
@@ -3409,34 +3409,34 @@
         <v>23</v>
       </c>
       <c r="D11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.32568806</v>
+      </c>
+      <c r="I11" t="n">
+        <v>13</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.41361257</v>
+      </c>
+      <c r="K11" t="n">
+        <v>17</v>
+      </c>
+      <c r="L11" t="n">
         <v>42</v>
       </c>
-      <c r="E11" t="n">
+      <c r="M11" t="n">
         <v>9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>27</v>
-      </c>
-      <c r="G11" t="n">
-        <v>12</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.32568806</v>
-      </c>
-      <c r="K11" t="n">
-        <v>13</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.41361257</v>
-      </c>
-      <c r="M11" t="n">
-        <v>17</v>
       </c>
       <c r="N11" t="n">
         <v>4.5</v>
@@ -3476,34 +3476,34 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3105023</v>
+      </c>
+      <c r="I12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4314721</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" t="n">
         <v>57</v>
       </c>
-      <c r="E12" t="n">
+      <c r="M12" t="n">
         <v>21</v>
-      </c>
-      <c r="F12" t="n">
-        <v>26</v>
-      </c>
-      <c r="G12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.3105023</v>
-      </c>
-      <c r="K12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4314721</v>
-      </c>
-      <c r="M12" t="n">
-        <v>12</v>
       </c>
       <c r="N12" t="n">
         <v>2.54717</v>
@@ -3543,34 +3543,34 @@
         <v>12</v>
       </c>
       <c r="D13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.31132075</v>
+      </c>
+      <c r="I13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.43076923</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13</v>
+      </c>
+      <c r="L13" t="n">
         <v>47</v>
       </c>
-      <c r="E13" t="n">
+      <c r="M13" t="n">
         <v>12</v>
-      </c>
-      <c r="F13" t="n">
-        <v>23</v>
-      </c>
-      <c r="G13" t="n">
-        <v>20</v>
-      </c>
-      <c r="H13" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" t="n">
-        <v>16</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.31132075</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.43076923</v>
-      </c>
-      <c r="M13" t="n">
-        <v>13</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -3610,34 +3610,34 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
+        <v>43</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>13</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.58064514</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
         <v>38</v>
       </c>
-      <c r="E14" t="n">
+      <c r="M14" t="n">
         <v>7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>43</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>13</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.58064514</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>6.230769</v>
@@ -3677,34 +3677,34 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
+        <v>38</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3321033</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5222672</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
         <v>66</v>
       </c>
-      <c r="E15" t="n">
+      <c r="M15" t="n">
         <v>28</v>
-      </c>
-      <c r="F15" t="n">
-        <v>38</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>14</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.3321033</v>
-      </c>
-      <c r="K15" t="n">
-        <v>10</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.5222672</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3</v>
       </c>
       <c r="N15" t="n">
         <v>4.922652</v>
@@ -3744,34 +3744,34 @@
         <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>0.30232558</v>
       </c>
       <c r="I16" t="n">
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>0.30232558</v>
+        <v>0.35751295</v>
       </c>
       <c r="K16" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L16" t="n">
-        <v>0.35751295</v>
+        <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="N16" t="n">
         <v>4.5</v>
@@ -3811,34 +3811,34 @@
         <v>19</v>
       </c>
       <c r="D17" t="n">
+        <v>26</v>
+      </c>
+      <c r="E17" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3196347</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.43523315</v>
+      </c>
+      <c r="K17" t="n">
+        <v>11</v>
+      </c>
+      <c r="L17" t="n">
         <v>51</v>
       </c>
-      <c r="E17" t="n">
+      <c r="M17" t="n">
         <v>18</v>
-      </c>
-      <c r="F17" t="n">
-        <v>26</v>
-      </c>
-      <c r="G17" t="n">
-        <v>14</v>
-      </c>
-      <c r="H17" t="n">
-        <v>9</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.3196347</v>
-      </c>
-      <c r="K17" t="n">
-        <v>15</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.43523315</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11</v>
       </c>
       <c r="N17" t="n">
         <v>4.1538463</v>
@@ -3878,34 +3878,34 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
+        <v>27</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3318584</v>
+      </c>
+      <c r="I18" t="n">
+        <v>11</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.37810946</v>
+      </c>
+      <c r="K18" t="n">
+        <v>23</v>
+      </c>
+      <c r="L18" t="n">
         <v>53</v>
       </c>
-      <c r="E18" t="n">
+      <c r="M18" t="n">
         <v>20</v>
-      </c>
-      <c r="F18" t="n">
-        <v>27</v>
-      </c>
-      <c r="G18" t="n">
-        <v>12</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>25</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.3318584</v>
-      </c>
-      <c r="K18" t="n">
-        <v>11</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.37810946</v>
-      </c>
-      <c r="M18" t="n">
-        <v>23</v>
       </c>
       <c r="N18" t="n">
         <v>3.4394906</v>
@@ -3945,34 +3945,34 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>0.38339922</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.38339922</v>
+        <v>0.5414847</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5414847</v>
+        <v>39</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
         <v>3.9056604</v>
@@ -4012,34 +4012,34 @@
         <v>11</v>
       </c>
       <c r="D20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>21</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.32765958</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.3809524</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20</v>
+      </c>
+      <c r="L20" t="n">
         <v>57</v>
       </c>
-      <c r="E20" t="n">
+      <c r="M20" t="n">
         <v>21</v>
-      </c>
-      <c r="F20" t="n">
-        <v>23</v>
-      </c>
-      <c r="G20" t="n">
-        <v>20</v>
-      </c>
-      <c r="H20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>21</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.32765958</v>
-      </c>
-      <c r="K20" t="n">
-        <v>12</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.3809524</v>
-      </c>
-      <c r="M20" t="n">
-        <v>20</v>
       </c>
       <c r="N20" t="n">
         <v>7.2</v>
@@ -4079,34 +4079,34 @@
         <v>7</v>
       </c>
       <c r="D21" t="n">
+        <v>31</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>12</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.35371178</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.502439</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" t="n">
         <v>50</v>
       </c>
-      <c r="E21" t="n">
+      <c r="M21" t="n">
         <v>15</v>
-      </c>
-      <c r="F21" t="n">
-        <v>31</v>
-      </c>
-      <c r="G21" t="n">
-        <v>9</v>
-      </c>
-      <c r="H21" t="n">
-        <v>12</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.35371178</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.502439</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6</v>
       </c>
       <c r="N21" t="n">
         <v>3.6666667</v>
@@ -4146,34 +4146,34 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
+        <v>44</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.34649122</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5217391</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
         <v>46</v>
       </c>
-      <c r="E22" t="n">
+      <c r="M22" t="n">
         <v>11</v>
-      </c>
-      <c r="F22" t="n">
-        <v>44</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>11</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.34649122</v>
-      </c>
-      <c r="K22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.5217391</v>
-      </c>
-      <c r="M22" t="n">
-        <v>5</v>
       </c>
       <c r="N22" t="n">
         <v>3.5</v>
@@ -4213,34 +4213,34 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>9</v>
+        <v>0.33474576</v>
       </c>
       <c r="I23" t="n">
         <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>0.33474576</v>
+        <v>0.48623854</v>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>0.48623854</v>
+        <v>50</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N23" t="n">
         <v>4.0588236</v>
@@ -4280,34 +4280,34 @@
         <v>21</v>
       </c>
       <c r="D24" t="n">
+        <v>24</v>
+      </c>
+      <c r="E24" t="n">
+        <v>17</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>25</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.28636363</v>
+      </c>
+      <c r="I24" t="n">
+        <v>24</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3546798</v>
+      </c>
+      <c r="K24" t="n">
+        <v>27</v>
+      </c>
+      <c r="L24" t="n">
         <v>57</v>
       </c>
-      <c r="E24" t="n">
+      <c r="M24" t="n">
         <v>21</v>
-      </c>
-      <c r="F24" t="n">
-        <v>24</v>
-      </c>
-      <c r="G24" t="n">
-        <v>17</v>
-      </c>
-      <c r="H24" t="n">
-        <v>5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>25</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.28636363</v>
-      </c>
-      <c r="K24" t="n">
-        <v>24</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.3546798</v>
-      </c>
-      <c r="M24" t="n">
-        <v>27</v>
       </c>
       <c r="N24" t="n">
         <v>3.8823528</v>
@@ -4347,34 +4347,34 @@
         <v>14</v>
       </c>
       <c r="D25" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" t="n">
+        <v>23</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.31016043</v>
+      </c>
+      <c r="I25" t="n">
+        <v>19</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.45238096</v>
+      </c>
+      <c r="K25" t="n">
+        <v>9</v>
+      </c>
+      <c r="L25" t="n">
         <v>33</v>
       </c>
-      <c r="E25" t="n">
+      <c r="M25" t="n">
         <v>3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>21</v>
-      </c>
-      <c r="G25" t="n">
-        <v>23</v>
-      </c>
-      <c r="H25" t="n">
-        <v>8</v>
-      </c>
-      <c r="I25" t="n">
-        <v>12</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.31016043</v>
-      </c>
-      <c r="K25" t="n">
-        <v>19</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.45238096</v>
-      </c>
-      <c r="M25" t="n">
-        <v>9</v>
       </c>
       <c r="N25" t="n">
         <v>3.642857</v>
@@ -4414,34 +4414,34 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>0.26020408</v>
       </c>
       <c r="I26" t="n">
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>0.26020408</v>
+        <v>0.24855492</v>
       </c>
       <c r="K26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L26" t="n">
-        <v>0.24855492</v>
+        <v>48</v>
       </c>
       <c r="M26" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="N26" t="n">
         <v>2.8333333</v>
@@ -4481,34 +4481,34 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>28</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.37815127</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.42364532</v>
+      </c>
+      <c r="K27" t="n">
+        <v>14</v>
+      </c>
+      <c r="L27" t="n">
         <v>27</v>
       </c>
-      <c r="E27" t="n">
+      <c r="M27" t="n">
         <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>30</v>
-      </c>
-      <c r="G27" t="n">
-        <v>11</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4</v>
-      </c>
-      <c r="I27" t="n">
-        <v>28</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.37815127</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.42364532</v>
-      </c>
-      <c r="M27" t="n">
-        <v>14</v>
       </c>
       <c r="N27" t="n">
         <v>6.0576925</v>
@@ -4548,34 +4548,34 @@
         <v>14</v>
       </c>
       <c r="D28" t="n">
+        <v>19</v>
+      </c>
+      <c r="E28" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.317757</v>
+      </c>
+      <c r="I28" t="n">
+        <v>16</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.36979166</v>
+      </c>
+      <c r="K28" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" t="n">
         <v>45</v>
       </c>
-      <c r="E28" t="n">
+      <c r="M28" t="n">
         <v>10</v>
-      </c>
-      <c r="F28" t="n">
-        <v>19</v>
-      </c>
-      <c r="G28" t="n">
-        <v>26</v>
-      </c>
-      <c r="H28" t="n">
-        <v>5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>25</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.317757</v>
-      </c>
-      <c r="K28" t="n">
-        <v>16</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.36979166</v>
-      </c>
-      <c r="M28" t="n">
-        <v>25</v>
       </c>
       <c r="N28" t="n">
         <v>3.3529413</v>
@@ -4615,34 +4615,34 @@
         <v>9</v>
       </c>
       <c r="D29" t="n">
+        <v>24</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.32286996</v>
+      </c>
+      <c r="I29" t="n">
+        <v>14</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.41747573</v>
+      </c>
+      <c r="K29" t="n">
+        <v>15</v>
+      </c>
+      <c r="L29" t="n">
         <v>52</v>
       </c>
-      <c r="E29" t="n">
+      <c r="M29" t="n">
         <v>19</v>
-      </c>
-      <c r="F29" t="n">
-        <v>24</v>
-      </c>
-      <c r="G29" t="n">
-        <v>17</v>
-      </c>
-      <c r="H29" t="n">
-        <v>7</v>
-      </c>
-      <c r="I29" t="n">
-        <v>16</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.32286996</v>
-      </c>
-      <c r="K29" t="n">
-        <v>14</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.41747573</v>
-      </c>
-      <c r="M29" t="n">
-        <v>15</v>
       </c>
       <c r="N29" t="n">
         <v>5.890909</v>
@@ -4682,34 +4682,34 @@
         <v>22</v>
       </c>
       <c r="D30" t="n">
+        <v>23</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.26256984</v>
+      </c>
+      <c r="I30" t="n">
+        <v>27</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.43786982</v>
+      </c>
+      <c r="K30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" t="n">
         <v>36</v>
       </c>
-      <c r="E30" t="n">
+      <c r="M30" t="n">
         <v>5</v>
-      </c>
-      <c r="F30" t="n">
-        <v>23</v>
-      </c>
-      <c r="G30" t="n">
-        <v>20</v>
-      </c>
-      <c r="H30" t="n">
-        <v>8</v>
-      </c>
-      <c r="I30" t="n">
-        <v>12</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.26256984</v>
-      </c>
-      <c r="K30" t="n">
-        <v>27</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.43786982</v>
-      </c>
-      <c r="M30" t="n">
-        <v>10</v>
       </c>
       <c r="N30" t="n">
         <v>4.2954545</v>
@@ -4749,34 +4749,34 @@
         <v>17</v>
       </c>
       <c r="D31" t="n">
+        <v>24</v>
+      </c>
+      <c r="E31" t="n">
+        <v>17</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.29186603</v>
+      </c>
+      <c r="I31" t="n">
+        <v>22</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="K31" t="n">
+        <v>18</v>
+      </c>
+      <c r="L31" t="n">
         <v>37</v>
       </c>
-      <c r="E31" t="n">
+      <c r="M31" t="n">
         <v>6</v>
-      </c>
-      <c r="F31" t="n">
-        <v>24</v>
-      </c>
-      <c r="G31" t="n">
-        <v>17</v>
-      </c>
-      <c r="H31" t="n">
-        <v>7</v>
-      </c>
-      <c r="I31" t="n">
-        <v>16</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.29186603</v>
-      </c>
-      <c r="K31" t="n">
-        <v>22</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.40625</v>
-      </c>
-      <c r="M31" t="n">
-        <v>18</v>
       </c>
       <c r="N31" t="n">
         <v>4.326923</v>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Last 7 Days" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Season" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Last 7 Days" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,43 +546,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23824452</v>
+        <v>0.23859242</v>
       </c>
       <c r="C2" t="n">
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3089631</v>
+        <v>0.30868056</v>
       </c>
       <c r="I2" t="n">
         <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38401255</v>
+        <v>0.38437742</v>
       </c>
       <c r="K2" t="n">
         <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3035803</v>
+        <v>4.2927775</v>
       </c>
       <c r="O2" t="n">
         <v>19</v>
@@ -594,13 +594,13 @@
         <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2976949</v>
+        <v>1.2985942</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25086573</v>
+        <v>0.250952</v>
       </c>
       <c r="U2" t="n">
         <v>21</v>
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24990633</v>
+        <v>0.24953166</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>364</v>
@@ -628,25 +628,25 @@
         <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32978722</v>
+        <v>0.32945478</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.42038217</v>
+        <v>0.4200075</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>672</v>
       </c>
       <c r="M3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N3" t="n">
         <v>4.999048</v>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25281116</v>
+        <v>0.25220054</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>377</v>
@@ -695,49 +695,49 @@
         <v>101</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.316655</v>
+        <v>0.31558937</v>
       </c>
       <c r="I4" t="n">
         <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>0.42109343</v>
+        <v>0.41829315</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.404926</v>
+        <v>3.3782864</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q4" t="n">
         <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2014778</v>
+        <v>1.2035053</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22531848</v>
+        <v>0.22449784</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -747,64 +747,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.24128787</v>
+        <v>0.242062</v>
       </c>
       <c r="C5" t="n">
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E5" t="n">
         <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3213807</v>
+        <v>0.3212041</v>
       </c>
       <c r="I5" t="n">
         <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4030303</v>
+        <v>0.4049309</v>
       </c>
       <c r="K5" t="n">
         <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4549356</v>
+        <v>4.411017</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q5" t="n">
         <v>20</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876967</v>
+        <v>1.3813559</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25687733</v>
+        <v>0.25633493</v>
       </c>
       <c r="U5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2431466</v>
+        <v>0.24224578</v>
       </c>
       <c r="C6" t="n">
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
@@ -832,25 +832,25 @@
         <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31099963</v>
+        <v>0.3109303</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38061184</v>
+        <v>0.37926972</v>
       </c>
       <c r="K6" t="n">
         <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8513105</v>
+        <v>3.8456175</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
@@ -859,16 +859,16 @@
         <v>82</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2595767</v>
+        <v>1.2624502</v>
       </c>
       <c r="S6" t="n">
         <v>11</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24271457</v>
+        <v>0.24428684</v>
       </c>
       <c r="U6" t="n">
         <v>19</v>
@@ -908,19 +908,19 @@
         <v>0.40129572</v>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
         <v>636</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
         <v>4.280488</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
         <v>113</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23701942</v>
+        <v>0.2376857</v>
       </c>
       <c r="C8" t="n">
         <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3189776</v>
+        <v>0.31904596</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40982956</v>
+        <v>0.41047692</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.408437</v>
+        <v>4.4162583</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P8" t="n">
         <v>88</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3414391</v>
+        <v>1.3442702</v>
       </c>
       <c r="S8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24228029</v>
+        <v>0.2421875</v>
       </c>
       <c r="U8" t="n">
         <v>17</v>
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22884013</v>
+        <v>0.22678019</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
         <v>96</v>
@@ -1033,28 +1033,28 @@
         <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>0.31135023</v>
+        <v>0.30861655</v>
       </c>
       <c r="I9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39498433</v>
+        <v>0.39086688</v>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="M9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.579646</v>
+        <v>4.5261626</v>
       </c>
       <c r="O9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
         <v>103</v>
@@ -1063,13 +1063,13 @@
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4646018</v>
+        <v>1.4520348</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2503864</v>
+        <v>0.24856816</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1082,16 +1082,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22818004</v>
+        <v>0.22827347</v>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
         <v>74</v>
@@ -1100,46 +1100,46 @@
         <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3125</v>
+        <v>0.3131382</v>
       </c>
       <c r="I10" t="n">
         <v>22</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3702544</v>
+        <v>0.3688683</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>627</v>
+        <v>642</v>
       </c>
       <c r="M10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7917676</v>
+        <v>3.8220947</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2595642</v>
+        <v>1.2611191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23680124</v>
+        <v>0.23745692</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2514199</v>
+        <v>0.2528048</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E11" t="n">
         <v>12</v>
@@ -1167,25 +1167,25 @@
         <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3224822</v>
+        <v>0.32293764</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4096933</v>
+        <v>0.40987286</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5263157</v>
+        <v>5.4805193</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
@@ -1197,13 +1197,13 @@
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5160819</v>
+        <v>1.5122656</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28597718</v>
+        <v>0.2846742</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,64 +1216,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23450981</v>
+        <v>0.23508908</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31471202</v>
+        <v>0.3150497</v>
       </c>
       <c r="I12" t="n">
         <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39333335</v>
+        <v>0.39465532</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="M12" t="n">
         <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8342404</v>
+        <v>3.8232422</v>
       </c>
       <c r="O12" t="n">
         <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2662048</v>
+        <v>1.2626953</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23918174</v>
+        <v>0.23874223</v>
       </c>
       <c r="U12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24321267</v>
+        <v>0.24244685</v>
       </c>
       <c r="C13" t="n">
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
         <v>103</v>
@@ -1301,46 +1301,46 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31749243</v>
+        <v>0.31745502</v>
       </c>
       <c r="I13" t="n">
         <v>18</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41251886</v>
+        <v>0.40992168</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="M13" t="n">
         <v>17</v>
       </c>
       <c r="N13" t="n">
-        <v>4.839866</v>
+        <v>4.8360114</v>
       </c>
       <c r="O13" t="n">
         <v>28</v>
       </c>
       <c r="P13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4010516</v>
+        <v>1.407845</v>
       </c>
       <c r="S13" t="n">
         <v>26</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24139251</v>
+        <v>0.24281392</v>
       </c>
       <c r="U13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24780451</v>
+        <v>0.2464151</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E14" t="n">
         <v>17</v>
@@ -1365,31 +1365,31 @@
         <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.32111338</v>
+        <v>0.31957033</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39518902</v>
+        <v>0.3928302</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5760503</v>
+        <v>4.530029</v>
       </c>
       <c r="O14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P14" t="n">
         <v>97</v>
@@ -1398,13 +1398,13 @@
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3935298</v>
+        <v>1.3870354</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25419208</v>
+        <v>0.25348398</v>
       </c>
       <c r="U14" t="n">
         <v>24</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23995493</v>
+        <v>0.23961425</v>
       </c>
       <c r="C15" t="n">
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E15" t="n">
         <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31977326</v>
+        <v>0.31882626</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>0.40105143</v>
+        <v>0.39985162</v>
       </c>
       <c r="K15" t="n">
         <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6507177</v>
+        <v>4.6679263</v>
       </c>
       <c r="O15" t="n">
         <v>26</v>
       </c>
       <c r="P15" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q15" t="n">
         <v>14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4267942</v>
+        <v>1.4270194</v>
       </c>
       <c r="S15" t="n">
         <v>27</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2377702</v>
+        <v>0.23896784</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25930187</v>
+        <v>0.2592733</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34316355</v>
+        <v>0.34281933</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.43536633</v>
+        <v>0.43565482</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="M16" t="n">
         <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4568381</v>
+        <v>3.4250839</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q16" t="n">
         <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1028129</v>
+        <v>1.0986118</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21310182</v>
+        <v>0.21177848</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,13 +1551,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24513619</v>
+        <v>0.24481168</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -1569,43 +1569,43 @@
         <v>26</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32289156</v>
+        <v>0.32210883</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>0.38677043</v>
+        <v>0.38624135</v>
       </c>
       <c r="K17" t="n">
         <v>24</v>
       </c>
       <c r="L17" t="n">
-        <v>641</v>
+        <v>654</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.072993</v>
+        <v>4.0720463</v>
       </c>
       <c r="O17" t="n">
         <v>13</v>
       </c>
       <c r="P17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2540146</v>
+        <v>1.257925</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22804973</v>
+        <v>0.22861527</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25597805</v>
+        <v>0.25406662</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
@@ -1633,28 +1633,28 @@
         <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33999312</v>
+        <v>0.337985</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39357114</v>
+        <v>0.39039505</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L18" t="n">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="M18" t="n">
         <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4488072</v>
+        <v>3.398139</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -1666,13 +1666,13 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.192843</v>
+        <v>1.1782566</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22276029</v>
+        <v>0.22071713</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24728362</v>
+        <v>0.24564654</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.32213438</v>
+      </c>
+      <c r="I19" t="n">
         <v>10</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.32345104</v>
-      </c>
-      <c r="I19" t="n">
-        <v>9</v>
-      </c>
       <c r="J19" t="n">
-        <v>0.4117647</v>
+        <v>0.4094109</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="M19" t="n">
         <v>19</v>
       </c>
       <c r="N19" t="n">
-        <v>4.78907</v>
+        <v>4.7534313</v>
       </c>
       <c r="O19" t="n">
         <v>27</v>
       </c>
       <c r="P19" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3907</v>
+        <v>1.389967</v>
       </c>
       <c r="S19" t="n">
         <v>24</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25326857</v>
+        <v>0.25331858</v>
       </c>
       <c r="U19" t="n">
         <v>23</v>
@@ -1755,13 +1755,13 @@
         <v>0.23196276</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
         <v>311</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F20" t="n">
         <v>82</v>
@@ -1785,10 +1785,10 @@
         <v>638</v>
       </c>
       <c r="M20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.08932</v>
+        <v>4.0762134</v>
       </c>
       <c r="O20" t="n">
         <v>14</v>
@@ -1800,13 +1800,13 @@
         <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2815534</v>
+        <v>1.280097</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23364127</v>
+        <v>0.23325635</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -1819,64 +1819,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.24544735</v>
+        <v>0.24492188</v>
       </c>
       <c r="C21" t="n">
         <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.33159903</v>
+        <v>0.33082193</v>
       </c>
       <c r="I21" t="n">
         <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.43863815</v>
+        <v>0.43710938</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="M21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3450148</v>
+        <v>3.3717072</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.180158</v>
+        <v>1.1839025</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22474144</v>
+        <v>0.2254517</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1886,64 +1886,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23273855</v>
+        <v>0.23141763</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E22" t="n">
         <v>19</v>
       </c>
       <c r="F22" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
         <v>8</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30031502</v>
+        <v>0.29837313</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39643136</v>
+        <v>0.394636</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.0578794</v>
+        <v>4.0629807</v>
       </c>
       <c r="O22" t="n">
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2986382</v>
+        <v>1.3024039</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25613904</v>
+        <v>0.25707898</v>
       </c>
       <c r="U22" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -1956,19 +1956,19 @@
         <v>0.2548148</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>391</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
         <v>94</v>
       </c>
       <c r="G23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
         <v>0.33464438</v>
@@ -1986,10 +1986,10 @@
         <v>720</v>
       </c>
       <c r="M23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2123094</v>
+        <v>4.173664</v>
       </c>
       <c r="O23" t="n">
         <v>16</v>
@@ -1998,16 +1998,16 @@
         <v>75</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3067747</v>
+        <v>1.3053435</v>
       </c>
       <c r="S23" t="n">
         <v>18</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2363156</v>
+        <v>0.23593809</v>
       </c>
       <c r="U23" t="n">
         <v>7</v>
@@ -2020,43 +2020,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2199437</v>
+        <v>0.21917263</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E24" t="n">
         <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" t="n">
         <v>21</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29252437</v>
+        <v>0.29290047</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.36389223</v>
+        <v>0.36316627</v>
       </c>
       <c r="K24" t="n">
         <v>30</v>
       </c>
       <c r="L24" t="n">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="M24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9049034</v>
+        <v>3.8533723</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
@@ -2068,16 +2068,16 @@
         <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3016344</v>
+        <v>1.2961876</v>
       </c>
       <c r="S24" t="n">
+        <v>14</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.24213837</v>
+      </c>
+      <c r="U24" t="n">
         <v>16</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.24262948</v>
-      </c>
-      <c r="U24" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -2096,7 +2096,7 @@
         <v>317</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F25" t="n">
         <v>81</v>
@@ -2108,13 +2108,13 @@
         <v>0.30878285</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
         <v>0.41857842</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
         <v>592</v>
@@ -2138,7 +2138,7 @@
         <v>1.3903874</v>
       </c>
       <c r="S25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T25" t="n">
         <v>0.25203568</v>
@@ -2157,7 +2157,7 @@
         <v>0.23182862</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
         <v>326</v>
@@ -2175,19 +2175,19 @@
         <v>0.31254238</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
         <v>0.38714615</v>
       </c>
       <c r="K26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
         <v>669</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N26" t="n">
         <v>3.623044</v>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24911313</v>
+        <v>0.24921997</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
@@ -2239,46 +2239,46 @@
         <v>16</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32752612</v>
+        <v>0.32793662</v>
       </c>
       <c r="I27" t="n">
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4016555</v>
+        <v>0.40015602</v>
       </c>
       <c r="K27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2942348</v>
+        <v>4.263855</v>
       </c>
       <c r="O27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P27" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q27" t="n">
         <v>15</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3464215</v>
+        <v>1.3403629</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25585938</v>
+        <v>0.2555898</v>
       </c>
       <c r="U27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2563585</v>
+        <v>0.25558212</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E28" t="n">
         <v>20</v>
@@ -2306,25 +2306,25 @@
         <v>30</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33416727</v>
+        <v>0.33309785</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.38312474</v>
+        <v>0.38197768</v>
       </c>
       <c r="K28" t="n">
         <v>26</v>
       </c>
       <c r="L28" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9077156</v>
+        <v>3.8820896</v>
       </c>
       <c r="O28" t="n">
         <v>10</v>
@@ -2333,19 +2333,19 @@
         <v>89</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2314675</v>
+        <v>1.2238806</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23828594</v>
+        <v>0.2369462</v>
       </c>
       <c r="U28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -2355,43 +2355,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24170247</v>
+        <v>0.24209715</v>
       </c>
       <c r="C29" t="n">
         <v>19</v>
       </c>
       <c r="D29" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F29" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" t="n">
         <v>21</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31778628</v>
+        <v>0.31833792</v>
       </c>
       <c r="I29" t="n">
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3869582</v>
+        <v>0.38743255</v>
       </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="M29" t="n">
         <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9447186</v>
+        <v>3.9322941</v>
       </c>
       <c r="O29" t="n">
         <v>11</v>
@@ -2400,19 +2400,19 @@
         <v>91</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2482725</v>
+        <v>1.2450074</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23698524</v>
+        <v>0.23676132</v>
       </c>
       <c r="U29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -2422,43 +2422,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24864656</v>
+        <v>0.25</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G30" t="n">
         <v>23</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31138355</v>
+        <v>0.3132988</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>0.39133796</v>
+        <v>0.3925841</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L30" t="n">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1325183</v>
+        <v>4.1047297</v>
       </c>
       <c r="O30" t="n">
         <v>15</v>
@@ -2470,16 +2470,16 @@
         <v>13</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3056234</v>
+        <v>1.3045367</v>
       </c>
       <c r="S30" t="n">
         <v>17</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24214202</v>
+        <v>0.24136607</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -2489,64 +2489,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24643661</v>
+        <v>0.24750277</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3204698</v>
+        <v>0.3209672</v>
       </c>
       <c r="I31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42123032</v>
+        <v>0.42323345</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="M31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6370125</v>
+        <v>4.5908875</v>
       </c>
       <c r="O31" t="n">
         <v>25</v>
       </c>
       <c r="P31" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3901047</v>
+        <v>1.3795209</v>
       </c>
       <c r="S31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2567418</v>
+        <v>0.25556773</v>
       </c>
       <c r="U31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2800,61 +2800,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2512563</v>
+        <v>0.25247526</v>
       </c>
       <c r="C2" t="n">
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.33777776</v>
+        <v>0.3288889</v>
       </c>
       <c r="I2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.38118812</v>
+      </c>
+      <c r="K2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L2" t="n">
+        <v>31</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.773585</v>
+      </c>
+      <c r="O2" t="n">
+        <v>26</v>
+      </c>
+      <c r="P2" t="n">
         <v>7</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.37688443</v>
-      </c>
-      <c r="K2" t="n">
-        <v>24</v>
-      </c>
-      <c r="L2" t="n">
-        <v>32</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5.6666665</v>
-      </c>
-      <c r="O2" t="n">
-        <v>24</v>
-      </c>
-      <c r="P2" t="n">
-        <v>9</v>
-      </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6111112</v>
+        <v>1.6603774</v>
       </c>
       <c r="S2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3167421</v>
+        <v>0.31455398</v>
       </c>
       <c r="U2" t="n">
         <v>30</v>
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.25</v>
+        <v>0.2238806</v>
       </c>
       <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.32188842</v>
+      </c>
+      <c r="I3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.41791046</v>
+      </c>
+      <c r="K3" t="n">
         <v>14</v>
       </c>
-      <c r="D3" t="n">
-        <v>44</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>13</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.33576643</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.4625</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8</v>
-      </c>
       <c r="L3" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="M3" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>6.46875</v>
+        <v>7.3636365</v>
       </c>
       <c r="O3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5625</v>
+        <v>1.6181818</v>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2890625</v>
+        <v>0.29864255</v>
       </c>
       <c r="U3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.23493975</v>
+        <v>0.23</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>0.26704547</v>
+        <v>0.2606635</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.37951806</v>
+        <v>0.35</v>
       </c>
       <c r="K4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L4" t="n">
+        <v>57</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.4150944</v>
+      </c>
+      <c r="O4" t="n">
+        <v>20</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.4339622</v>
+      </c>
+      <c r="S4" t="n">
         <v>22</v>
       </c>
-      <c r="L4" t="n">
-        <v>48</v>
-      </c>
-      <c r="M4" t="n">
-        <v>13</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>22</v>
-      </c>
-      <c r="P4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.4444444</v>
-      </c>
-      <c r="S4" t="n">
-        <v>20</v>
-      </c>
       <c r="T4" t="n">
-        <v>0.28651685</v>
+        <v>0.2682927</v>
       </c>
       <c r="U4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.22167487</v>
+        <v>0.23333333</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2882883</v>
+        <v>0.29118773</v>
       </c>
       <c r="I5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5" t="n">
-        <v>0.38916257</v>
+        <v>0.4125</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="M5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7870967</v>
+        <v>2.5219781</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1999999</v>
+        <v>1.1538461</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
       </c>
       <c r="T5" t="n">
-        <v>0.20744681</v>
+        <v>0.2081448</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.21025641</v>
+        <v>0.20444444</v>
       </c>
       <c r="C6" t="n">
         <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2824074</v>
+        <v>0.2857143</v>
       </c>
       <c r="I6" t="n">
         <v>25</v>
       </c>
       <c r="J6" t="n">
-        <v>0.34358975</v>
+        <v>0.33333334</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2264152</v>
+        <v>3.2459016</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
         <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9245283</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1861702</v>
+        <v>0.21266969</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.31111112</v>
+        <v>0.31292516</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="n">
-        <v>7</v>
-      </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
-        <v>0.42465752</v>
+        <v>0.41714287</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5222222</v>
+        <v>0.5170068</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="n">
         <v>18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0888889</v>
+        <v>1.0555556</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>0.21556886</v>
+        <v>0.21641791</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.195</v>
+        <v>0.20851064</v>
       </c>
       <c r="C8" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2579365</v>
+      </c>
+      <c r="I8" t="n">
+        <v>29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.39148936</v>
+      </c>
+      <c r="K8" t="n">
+        <v>18</v>
+      </c>
+      <c r="L8" t="n">
+        <v>70</v>
+      </c>
+      <c r="M8" t="n">
         <v>28</v>
       </c>
-      <c r="D8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E8" t="n">
-        <v>25</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.24651162</v>
-      </c>
-      <c r="I8" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K8" t="n">
-        <v>21</v>
-      </c>
-      <c r="L8" t="n">
-        <v>57</v>
-      </c>
-      <c r="M8" t="n">
-        <v>21</v>
-      </c>
       <c r="N8" t="n">
-        <v>5.94</v>
+        <v>5.7966104</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P8" t="n">
         <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.66</v>
+        <v>1.6440678</v>
       </c>
       <c r="S8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3043478</v>
+        <v>0.29460582</v>
       </c>
       <c r="U8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.23</v>
+        <v>0.1959799</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30357143</v>
+        <v>0.25345623</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.415</v>
+        <v>0.3316583</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="M9" t="n">
         <v>26</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3962264</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
         <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4716982</v>
+        <v>1.3333334</v>
       </c>
       <c r="S9" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25123152</v>
+        <v>0.23880596</v>
       </c>
       <c r="U9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.18229167</v>
+        <v>0.19026549</v>
       </c>
       <c r="C10" t="n">
         <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>0.25943395</v>
+        <v>0.27559054</v>
       </c>
       <c r="I10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J10" t="n">
-        <v>0.34895834</v>
+        <v>0.33628318</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>4.32</v>
+        <v>4.6022725</v>
       </c>
       <c r="O10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.278409</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23404256</v>
+        <v>0.24215247</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2303665</v>
+        <v>0.2565445</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32568806</v>
+        <v>0.33333334</v>
       </c>
       <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.43455496</v>
+      </c>
+      <c r="K11" t="n">
         <v>13</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.41361257</v>
-      </c>
-      <c r="K11" t="n">
-        <v>17</v>
       </c>
       <c r="L11" t="n">
         <v>42</v>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4.075472</v>
       </c>
       <c r="O11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q11" t="n">
         <v>7</v>
       </c>
-      <c r="Q11" t="n">
-        <v>9</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.4423077</v>
+        <v>1.264151</v>
       </c>
       <c r="S11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>0.26960784</v>
+        <v>0.24875621</v>
       </c>
       <c r="U11" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23857868</v>
+        <v>0.2356021</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3105023</v>
+        <v>0.3</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4314721</v>
+        <v>0.38219896</v>
       </c>
       <c r="K12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="N12" t="n">
         <v>2.54717</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q12" t="n">
         <v>7</v>
       </c>
-      <c r="Q12" t="n">
-        <v>9</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.1132076</v>
+        <v>1.0943396</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2160804</v>
+        <v>0.215</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.25128207</v>
+        <v>0.2460733</v>
       </c>
       <c r="C13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.31428573</v>
+      </c>
+      <c r="I13" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.38743454</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" t="n">
+        <v>46</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.3962264</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>23</v>
-      </c>
-      <c r="E13" t="n">
-        <v>20</v>
-      </c>
-      <c r="F13" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>16</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.31132075</v>
-      </c>
-      <c r="I13" t="n">
-        <v>17</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.43076923</v>
-      </c>
-      <c r="K13" t="n">
-        <v>13</v>
-      </c>
-      <c r="L13" t="n">
-        <v>47</v>
-      </c>
-      <c r="M13" t="n">
-        <v>12</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>13</v>
-      </c>
-      <c r="P13" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>25</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.9259259</v>
+        <v>0.9622642</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>0.20408164</v>
+        <v>0.21276596</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.31336406</v>
+        <v>0.2990654</v>
       </c>
       <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>42</v>
+      </c>
+      <c r="E14" t="n">
         <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>43</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.375</v>
+        <v>0.3601695</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>0.58064514</v>
+        <v>0.57009345</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>6.230769</v>
+        <v>5.09434</v>
       </c>
       <c r="O14" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5961539</v>
+        <v>1.490566</v>
       </c>
       <c r="S14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2961165</v>
+        <v>0.28640777</v>
       </c>
       <c r="U14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.27530363</v>
+        <v>0.26530612</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3321033</v>
+        <v>0.32342008</v>
       </c>
       <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.49387756</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>69</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.2826085</v>
+      </c>
+      <c r="O15" t="n">
+        <v>24</v>
+      </c>
+      <c r="P15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>0.5222672</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>66</v>
-      </c>
-      <c r="M15" t="n">
-        <v>28</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.922652</v>
-      </c>
-      <c r="O15" t="n">
-        <v>21</v>
-      </c>
-      <c r="P15" t="n">
-        <v>9</v>
-      </c>
       <c r="Q15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3591161</v>
+        <v>1.3695652</v>
       </c>
       <c r="S15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U15" t="n">
         <v>16</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.23913044</v>
-      </c>
-      <c r="U15" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.22279793</v>
+        <v>0.2284264</v>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>0.30232558</v>
+        <v>0.3090909</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>0.35751295</v>
+        <v>0.35532996</v>
       </c>
       <c r="K16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>4.1666665</v>
       </c>
       <c r="O16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P16" t="n">
         <v>7</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2592592</v>
+        <v>1.1851852</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>0.23880596</v>
+        <v>0.215</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -3805,16 +3805,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.23834197</v>
+        <v>0.24870466</v>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
         <v>9</v>
@@ -3823,46 +3823,46 @@
         <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3196347</v>
+        <v>0.3242009</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>0.43523315</v>
+        <v>0.4611399</v>
       </c>
       <c r="K17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L17" t="n">
         <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1538463</v>
+        <v>3.5660377</v>
       </c>
       <c r="O17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q17" t="n">
         <v>7</v>
       </c>
-      <c r="Q17" t="n">
-        <v>9</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.2692307</v>
+        <v>1.245283</v>
       </c>
       <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.24120604</v>
+      </c>
+      <c r="U17" t="n">
         <v>13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.24623115</v>
-      </c>
-      <c r="U17" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -3872,61 +3872,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25870648</v>
+        <v>0.23706897</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
       </c>
       <c r="G18" t="n">
+        <v>24</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.31034482</v>
+      </c>
+      <c r="I18" t="n">
+        <v>16</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3448276</v>
+      </c>
+      <c r="K18" t="n">
+        <v>26</v>
+      </c>
+      <c r="L18" t="n">
+        <v>64</v>
+      </c>
+      <c r="M18" t="n">
         <v>25</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.3318584</v>
-      </c>
-      <c r="I18" t="n">
-        <v>11</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.37810946</v>
-      </c>
-      <c r="K18" t="n">
-        <v>23</v>
-      </c>
-      <c r="L18" t="n">
-        <v>53</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20</v>
-      </c>
       <c r="N18" t="n">
-        <v>3.4394906</v>
+        <v>2.8877006</v>
       </c>
       <c r="O18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
         <v>8</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9936306</v>
+        <v>0.8663102</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.18181819</v>
+        <v>0.16438356</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3231441</v>
+        <v>0.32017544</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
         <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>0.38339922</v>
+        <v>0.38582677</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5414847</v>
+        <v>0.5219298</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
         <v>3.9056604</v>
       </c>
       <c r="O19" t="n">
+        <v>13</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" t="n">
         <v>12</v>
       </c>
-      <c r="P19" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.3396226</v>
+        <v>1.4716982</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24878049</v>
+        <v>0.2631579</v>
       </c>
       <c r="U19" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.25238097</v>
+        <v>0.26553673</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>23</v>
@@ -4021,46 +4021,46 @@
         <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>0.32765958</v>
+        <v>0.33163264</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3809524</v>
+        <v>0.40677965</v>
       </c>
       <c r="K20" t="n">
+        <v>17</v>
+      </c>
+      <c r="L20" t="n">
+        <v>46</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.785714</v>
+      </c>
+      <c r="O20" t="n">
+        <v>27</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>18</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3809524</v>
+      </c>
+      <c r="S20" t="n">
         <v>20</v>
       </c>
-      <c r="L20" t="n">
-        <v>57</v>
-      </c>
-      <c r="M20" t="n">
-        <v>21</v>
-      </c>
-      <c r="N20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>30</v>
-      </c>
-      <c r="P20" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>25</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S20" t="n">
-        <v>23</v>
-      </c>
       <c r="T20" t="n">
-        <v>0.26865673</v>
+        <v>0.26190478</v>
       </c>
       <c r="U20" t="n">
         <v>20</v>
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.28292683</v>
+        <v>0.27196652</v>
       </c>
       <c r="C21" t="n">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.34210527</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.47698745</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>62</v>
+      </c>
+      <c r="M21" t="n">
+        <v>24</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.919355</v>
+      </c>
+      <c r="O21" t="n">
+        <v>15</v>
+      </c>
+      <c r="P21" t="n">
         <v>9</v>
       </c>
-      <c r="F21" t="n">
-        <v>12</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.35371178</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.502439</v>
-      </c>
-      <c r="K21" t="n">
-        <v>6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>50</v>
-      </c>
-      <c r="M21" t="n">
-        <v>15</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.6666667</v>
-      </c>
-      <c r="O21" t="n">
-        <v>10</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
+        <v>22</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.1451613</v>
+      </c>
+      <c r="S21" t="n">
         <v>8</v>
       </c>
-      <c r="Q21" t="n">
-        <v>15</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.0925926</v>
-      </c>
-      <c r="S21" t="n">
-        <v>6</v>
-      </c>
       <c r="T21" t="n">
-        <v>0.22815534</v>
+        <v>0.23529412</v>
       </c>
       <c r="U21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.28985506</v>
+        <v>0.26213592</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
         <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.34649122</v>
+        <v>0.3090909</v>
       </c>
       <c r="I22" t="n">
+        <v>18</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.48058254</v>
+      </c>
+      <c r="K22" t="n">
         <v>6</v>
       </c>
-      <c r="J22" t="n">
-        <v>0.5217391</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5</v>
-      </c>
       <c r="L22" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>4.245283</v>
       </c>
       <c r="O22" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="P22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2222222</v>
+        <v>1.3396226</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.23809524</v>
+        <v>0.26511627</v>
       </c>
       <c r="U22" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.28440368</v>
+        <v>0.29508197</v>
       </c>
       <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>30</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.34343433</v>
+      </c>
+      <c r="I23" t="n">
         <v>6</v>
       </c>
-      <c r="D23" t="n">
-        <v>32</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="J23" t="n">
+        <v>0.5136612</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>44</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.139535</v>
+      </c>
+      <c r="O23" t="n">
+        <v>6</v>
+      </c>
+      <c r="P23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" t="n">
-        <v>9</v>
-      </c>
-      <c r="G23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.33474576</v>
-      </c>
-      <c r="I23" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.48623854</v>
-      </c>
-      <c r="K23" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" t="n">
-        <v>50</v>
-      </c>
-      <c r="M23" t="n">
-        <v>15</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.0588236</v>
-      </c>
-      <c r="O23" t="n">
-        <v>14</v>
-      </c>
-      <c r="P23" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>18</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.372549</v>
+        <v>1.2325581</v>
       </c>
       <c r="S23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2538071</v>
+        <v>0.221519</v>
       </c>
       <c r="U23" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -4274,46 +4274,46 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23152709</v>
+        <v>0.24630542</v>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
+        <v>19</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" t="n">
         <v>17</v>
       </c>
-      <c r="F24" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>25</v>
-      </c>
       <c r="H24" t="n">
-        <v>0.28636363</v>
+        <v>0.31858408</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3546798</v>
+        <v>0.38916257</v>
       </c>
       <c r="K24" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L24" t="n">
         <v>57</v>
       </c>
       <c r="M24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8823528</v>
+        <v>3.2884614</v>
       </c>
       <c r="O24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
@@ -4322,16 +4322,16 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4509804</v>
+        <v>1.3653846</v>
       </c>
       <c r="S24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2717949</v>
+        <v>0.26130652</v>
       </c>
       <c r="U24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -4344,7 +4344,7 @@
         <v>0.25</v>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
         <v>21</v>
@@ -4356,13 +4356,13 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H25" t="n">
         <v>0.31016043</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
         <v>0.45238096</v>
@@ -4374,25 +4374,25 @@
         <v>33</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
         <v>3.642857</v>
       </c>
       <c r="O25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P25" t="n">
         <v>5</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>1.3095238</v>
       </c>
       <c r="S25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T25" t="n">
         <v>0.25</v>
@@ -4423,7 +4423,7 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H26" t="n">
         <v>0.26020408</v>
@@ -4441,7 +4441,7 @@
         <v>48</v>
       </c>
       <c r="M26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N26" t="n">
         <v>2.8333333</v>
@@ -4453,19 +4453,19 @@
         <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
         <v>0.9074074</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
         <v>0.19371727</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.29064038</v>
+        <v>0.29</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
         <v>30</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H27" t="n">
-        <v>0.37815127</v>
+        <v>0.38235295</v>
       </c>
       <c r="I27" t="n">
         <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>0.42364532</v>
+        <v>0.415</v>
       </c>
       <c r="K27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L27" t="n">
         <v>27</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>6.0576925</v>
+        <v>6.4038463</v>
       </c>
       <c r="O27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3653846</v>
+        <v>1.4807693</v>
       </c>
       <c r="S27" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2753623</v>
+        <v>0.2990654</v>
       </c>
       <c r="U27" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25</v>
+        <v>0.23958333</v>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
+        <v>28</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
         <v>26</v>
       </c>
-      <c r="F28" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>25</v>
-      </c>
       <c r="H28" t="n">
-        <v>0.317757</v>
+        <v>0.3018868</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>0.36979166</v>
+        <v>0.35416666</v>
       </c>
       <c r="K28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L28" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3529413</v>
+        <v>2.9423077</v>
       </c>
       <c r="O28" t="n">
         <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.117647</v>
+        <v>1.0384616</v>
       </c>
       <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.21578947</v>
+      </c>
+      <c r="U28" t="n">
         <v>8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.23157895</v>
-      </c>
-      <c r="U28" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -4609,16 +4609,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2669903</v>
+        <v>0.28365386</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
@@ -4627,46 +4627,46 @@
         <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>0.32286996</v>
+        <v>0.3478261</v>
       </c>
       <c r="I29" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>0.41747573</v>
+        <v>0.44230768</v>
       </c>
       <c r="K29" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L29" t="n">
         <v>52</v>
       </c>
       <c r="M29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>5.890909</v>
+        <v>5.7272725</v>
       </c>
       <c r="O29" t="n">
         <v>25</v>
       </c>
       <c r="P29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4545455</v>
+        <v>1.5090909</v>
       </c>
       <c r="S29" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="T29" t="n">
-        <v>0.280543</v>
+        <v>0.2927928</v>
       </c>
       <c r="U29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.23076923</v>
+        <v>0.2512563</v>
       </c>
       <c r="C30" t="n">
+        <v>14</v>
+      </c>
+      <c r="D30" t="n">
+        <v>27</v>
+      </c>
+      <c r="E30" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.29680365</v>
+      </c>
+      <c r="I30" t="n">
         <v>22</v>
       </c>
-      <c r="D30" t="n">
-        <v>23</v>
-      </c>
-      <c r="E30" t="n">
-        <v>20</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G30" t="n">
-        <v>12</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.26256984</v>
-      </c>
-      <c r="I30" t="n">
-        <v>27</v>
-      </c>
       <c r="J30" t="n">
-        <v>0.43786982</v>
+        <v>0.44723618</v>
       </c>
       <c r="K30" t="n">
         <v>10</v>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2954545</v>
+        <v>3.9056604</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P30" t="n">
         <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.7727273</v>
+        <v>1.6792452</v>
       </c>
       <c r="S30" t="n">
         <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>0.26256984</v>
+        <v>0.25</v>
       </c>
       <c r="U30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.23958333</v>
+        <v>0.25252524</v>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
+        <v>21</v>
+      </c>
+      <c r="E31" t="n">
+        <v>23</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>11</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.29577464</v>
+      </c>
+      <c r="I31" t="n">
+        <v>23</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.43939394</v>
+      </c>
+      <c r="K31" t="n">
+        <v>12</v>
+      </c>
+      <c r="L31" t="n">
+        <v>42</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.9807692</v>
+      </c>
+      <c r="O31" t="n">
+        <v>16</v>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4038461</v>
+      </c>
+      <c r="S31" t="n">
+        <v>21</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.27722773</v>
+      </c>
+      <c r="U31" t="n">
         <v>24</v>
-      </c>
-      <c r="E31" t="n">
-        <v>17</v>
-      </c>
-      <c r="F31" t="n">
-        <v>7</v>
-      </c>
-      <c r="G31" t="n">
-        <v>16</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.29186603</v>
-      </c>
-      <c r="I31" t="n">
-        <v>22</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.40625</v>
-      </c>
-      <c r="K31" t="n">
-        <v>18</v>
-      </c>
-      <c r="L31" t="n">
-        <v>37</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.326923</v>
-      </c>
-      <c r="O31" t="n">
-        <v>18</v>
-      </c>
-      <c r="P31" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>18</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.5192307</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.28921568</v>
-      </c>
-      <c r="U31" t="n">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Season" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Last 7 Days" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Last 7 Days" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23859242</v>
+        <v>0.23796791</v>
       </c>
       <c r="C2" t="n">
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
         <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30868056</v>
+        <v>0.30877313</v>
       </c>
       <c r="I2" t="n">
         <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38437742</v>
+        <v>0.38349885</v>
       </c>
       <c r="K2" t="n">
         <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2927775</v>
+        <v>4.2760763</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>93</v>
       </c>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2985942</v>
+        <v>1.2976077</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
       </c>
       <c r="T2" t="n">
-        <v>0.250952</v>
+        <v>0.25056434</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24953166</v>
+        <v>0.24796145</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
         <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32945478</v>
+        <v>0.32840237</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4200075</v>
+        <v>0.4166049</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="M3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>4.999048</v>
+        <v>4.9807057</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.447882</v>
+        <v>1.4498824</v>
       </c>
       <c r="S3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26346862</v>
+        <v>0.26377234</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25220054</v>
+        <v>0.25179043</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31558937</v>
+        <v>0.31552076</v>
       </c>
       <c r="I4" t="n">
         <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41829315</v>
+        <v>0.41764042</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3782864</v>
+        <v>3.3993273</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q4" t="n">
         <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2035053</v>
+        <v>1.2066314</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22449784</v>
+        <v>0.22494173</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.242062</v>
+        <v>0.24057649</v>
       </c>
       <c r="C5" t="n">
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E5" t="n">
         <v>8</v>
@@ -762,49 +762,49 @@
         <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3212041</v>
+        <v>0.31958088</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4049309</v>
+        <v>0.40169993</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>726</v>
+        <v>739</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.411017</v>
+        <v>4.424581</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3813559</v>
+        <v>1.3798883</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25633493</v>
+        <v>0.25644752</v>
       </c>
       <c r="U5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24224578</v>
+        <v>0.24312815</v>
       </c>
       <c r="C6" t="n">
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
         <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3109303</v>
+        <v>0.31230393</v>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.37926972</v>
+        <v>0.3809524</v>
       </c>
       <c r="K6" t="n">
         <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8456175</v>
+        <v>3.8211303</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2624502</v>
+        <v>1.2619165</v>
       </c>
       <c r="S6" t="n">
         <v>11</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24428684</v>
+        <v>0.24416797</v>
       </c>
       <c r="U6" t="n">
         <v>19</v>
@@ -881,64 +881,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24352135</v>
+        <v>0.2435994</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="E7" t="n">
         <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G7" t="n">
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33707866</v>
+        <v>0.33778936</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40129572</v>
+        <v>0.40286145</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="M7" t="n">
         <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>4.280488</v>
+        <v>4.3028407</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P7" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2380488</v>
+        <v>1.2407318</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23957928</v>
+        <v>0.23893805</v>
       </c>
       <c r="U7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2376857</v>
+        <v>0.23636363</v>
       </c>
       <c r="C8" t="n">
         <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31904596</v>
+        <v>0.31735706</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41047692</v>
+        <v>0.4088975</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4162583</v>
+        <v>4.371677</v>
       </c>
       <c r="O8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q8" t="n">
         <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3442702</v>
+        <v>1.3383276</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2421875</v>
+        <v>0.24160556</v>
       </c>
       <c r="U8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22678019</v>
+        <v>0.22520107</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
@@ -1024,34 +1024,34 @@
         <v>326</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
         <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30861655</v>
+        <v>0.3066984</v>
       </c>
       <c r="I9" t="n">
         <v>27</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39086688</v>
+        <v>0.38759097</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>726</v>
+        <v>739</v>
       </c>
       <c r="M9" t="n">
         <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5261626</v>
+        <v>4.4935436</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
@@ -1060,16 +1060,16 @@
         <v>103</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4520348</v>
+        <v>1.446198</v>
       </c>
       <c r="S9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24856816</v>
+        <v>0.24764062</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22827347</v>
+        <v>0.2278626</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" t="n">
         <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3131382</v>
+        <v>0.31258413</v>
       </c>
       <c r="I10" t="n">
         <v>22</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3688683</v>
+        <v>0.3687023</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="M10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8220947</v>
+        <v>3.8042552</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2611191</v>
+        <v>1.2524823</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23745692</v>
+        <v>0.23616377</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2528048</v>
+        <v>0.25258493</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G11" t="n">
         <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32293764</v>
+        <v>0.32262337</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>0.40987286</v>
+        <v>0.4102659</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4805193</v>
+        <v>5.474359</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5122656</v>
+        <v>1.517094</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2846742</v>
+        <v>0.2849443</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23508908</v>
+        <v>0.23527162</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E12" t="n">
         <v>24</v>
@@ -1234,46 +1234,46 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3150497</v>
+        <v>0.31504065</v>
       </c>
       <c r="I12" t="n">
         <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39465532</v>
+        <v>0.39364958</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L12" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8232422</v>
+        <v>3.8255422</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2626953</v>
+        <v>1.2621686</v>
       </c>
       <c r="S12" t="n">
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23874223</v>
+        <v>0.23898889</v>
       </c>
       <c r="U12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24244685</v>
+        <v>0.24394718</v>
       </c>
       <c r="C13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>367</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>107</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.31825632</v>
+      </c>
+      <c r="I13" t="n">
         <v>17</v>
       </c>
-      <c r="D13" t="n">
-        <v>358</v>
-      </c>
-      <c r="E13" t="n">
-        <v>14</v>
-      </c>
-      <c r="F13" t="n">
-        <v>103</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.31745502</v>
-      </c>
-      <c r="I13" t="n">
-        <v>18</v>
-      </c>
       <c r="J13" t="n">
-        <v>0.40992168</v>
+        <v>0.41379312</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="M13" t="n">
         <v>17</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8360114</v>
+        <v>4.8120055</v>
       </c>
       <c r="O13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.407845</v>
+        <v>1.4099581</v>
       </c>
       <c r="S13" t="n">
         <v>26</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24281392</v>
+        <v>0.24349442</v>
       </c>
       <c r="U13" t="n">
         <v>18</v>
@@ -1350,64 +1350,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2464151</v>
+        <v>0.24832714</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="E14" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" t="n">
+        <v>80</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3204237</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.39739776</v>
+      </c>
+      <c r="K14" t="n">
         <v>17</v>
       </c>
-      <c r="F14" t="n">
-        <v>77</v>
-      </c>
-      <c r="G14" t="n">
-        <v>24</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.31957033</v>
-      </c>
-      <c r="I14" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.3928302</v>
-      </c>
-      <c r="K14" t="n">
-        <v>18</v>
-      </c>
       <c r="L14" t="n">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.530029</v>
+        <v>4.536</v>
       </c>
       <c r="O14" t="n">
         <v>24</v>
       </c>
       <c r="P14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3870354</v>
+        <v>1.3905883</v>
       </c>
       <c r="S14" t="n">
         <v>23</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25348398</v>
+        <v>0.25362587</v>
       </c>
       <c r="U14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23961425</v>
+        <v>0.23991196</v>
       </c>
       <c r="C15" t="n">
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G15" t="n">
         <v>11</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31882626</v>
+        <v>0.31865624</v>
       </c>
       <c r="I15" t="n">
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39985162</v>
+        <v>0.39985326</v>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L15" t="n">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6679263</v>
+        <v>4.621735</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>86</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4270194</v>
+        <v>1.4160447</v>
       </c>
       <c r="S15" t="n">
         <v>27</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23896784</v>
+        <v>0.23751387</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2592733</v>
+        <v>0.26145253</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34281933</v>
+        <v>0.3449398</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.43565482</v>
+        <v>0.43761638</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>623</v>
+        <v>633</v>
       </c>
       <c r="M16" t="n">
         <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4250839</v>
+        <v>3.4196599</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0986118</v>
+        <v>1.0973536</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21177848</v>
+        <v>0.2117013</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24481168</v>
+        <v>0.2460197</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
         <v>26</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32210883</v>
+        <v>0.32292715</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>0.38624135</v>
+        <v>0.39006823</v>
       </c>
       <c r="K17" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L17" t="n">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="M17" t="n">
         <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.0720463</v>
+        <v>4.0711236</v>
       </c>
       <c r="O17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.257925</v>
+        <v>1.2603129</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22861527</v>
+        <v>0.2292849</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25406662</v>
+        <v>0.25306278</v>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
@@ -1636,28 +1636,28 @@
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.337985</v>
+        <v>0.3370333</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39039505</v>
+        <v>0.3885911</v>
       </c>
       <c r="K18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L18" t="n">
-        <v>621</v>
+        <v>635</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>3.398139</v>
+        <v>3.353794</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
         <v>72</v>
@@ -1666,13 +1666,13 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1782566</v>
+        <v>1.1657805</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22071713</v>
+        <v>0.21915649</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,64 +1685,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24564654</v>
+        <v>0.24515185</v>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32213438</v>
+        <v>0.32128906</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4094109</v>
+        <v>0.4094402</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="M19" t="n">
         <v>19</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7534313</v>
+        <v>4.832243</v>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P19" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.389967</v>
+        <v>1.4060748</v>
       </c>
       <c r="S19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25331858</v>
+        <v>0.2555354</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23196276</v>
+        <v>0.23141763</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F20" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29722124</v>
+        <v>0.2977099</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37199378</v>
+        <v>0.37203065</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="M20" t="n">
         <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.0762134</v>
+        <v>4.1399136</v>
       </c>
       <c r="O20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q20" t="n">
         <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.280097</v>
+        <v>1.2850982</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23325635</v>
+        <v>0.23346007</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -1819,46 +1819,46 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.24492188</v>
+        <v>0.2450867</v>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.33082193</v>
+        <v>0.33040243</v>
       </c>
       <c r="I21" t="n">
         <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.43710938</v>
+        <v>0.43660885</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3717072</v>
+        <v>3.3668754</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
         <v>70</v>
@@ -1867,13 +1867,13 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1839025</v>
+        <v>1.1844006</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2254517</v>
+        <v>0.2257564</v>
       </c>
       <c r="U21" t="n">
         <v>4</v>
@@ -1886,64 +1886,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23141763</v>
+        <v>0.23407464</v>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>0.29837313</v>
+        <v>0.30074933</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.394636</v>
+        <v>0.3995477</v>
       </c>
       <c r="K22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" t="n">
+        <v>684</v>
+      </c>
+      <c r="M22" t="n">
+        <v>24</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.126246</v>
+      </c>
+      <c r="O22" t="n">
+        <v>13</v>
+      </c>
+      <c r="P22" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q22" t="n">
         <v>17</v>
       </c>
-      <c r="L22" t="n">
-        <v>672</v>
-      </c>
-      <c r="M22" t="n">
-        <v>23</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.0629807</v>
-      </c>
-      <c r="O22" t="n">
-        <v>12</v>
-      </c>
-      <c r="P22" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>16</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.3024039</v>
+        <v>1.304224</v>
       </c>
       <c r="S22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25707898</v>
+        <v>0.2570798</v>
       </c>
       <c r="U22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -1953,13 +1953,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2548148</v>
+        <v>0.2548446</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
@@ -1971,43 +1971,43 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33464438</v>
+        <v>0.33441243</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40925926</v>
+        <v>0.40804386</v>
       </c>
       <c r="K23" t="n">
         <v>11</v>
       </c>
       <c r="L23" t="n">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.173664</v>
+        <v>4.1587377</v>
       </c>
       <c r="O23" t="n">
         <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3053435</v>
+        <v>1.3028733</v>
       </c>
       <c r="S23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23593809</v>
+        <v>0.23584203</v>
       </c>
       <c r="U23" t="n">
         <v>7</v>
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.21917263</v>
+        <v>0.219694</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="E24" t="n">
         <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29290047</v>
+        <v>0.2934553</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.36316627</v>
+        <v>0.36367202</v>
       </c>
       <c r="K24" t="n">
         <v>30</v>
       </c>
       <c r="L24" t="n">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="M24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8533723</v>
+        <v>3.8757226</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q24" t="n">
         <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2961876</v>
+        <v>1.2962428</v>
       </c>
       <c r="S24" t="n">
         <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24213837</v>
+        <v>0.24187307</v>
       </c>
       <c r="U24" t="n">
         <v>16</v>
@@ -2087,64 +2087,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25723955</v>
+        <v>0.2576208</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E25" t="n">
         <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G25" t="n">
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30878285</v>
+        <v>0.30976775</v>
       </c>
       <c r="I25" t="n">
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41857842</v>
+        <v>0.41858736</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4624815</v>
+        <v>4.4041624</v>
       </c>
       <c r="O25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P25" t="n">
         <v>80</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3903874</v>
+        <v>1.3838334</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25203568</v>
+        <v>0.25038344</v>
       </c>
       <c r="U25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23182862</v>
+        <v>0.23178558</v>
       </c>
       <c r="C26" t="n">
         <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E26" t="n">
         <v>21</v>
       </c>
       <c r="F26" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
         <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31254238</v>
+        <v>0.31201875</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38714615</v>
+        <v>0.38769346</v>
       </c>
       <c r="K26" t="n">
         <v>23</v>
       </c>
       <c r="L26" t="n">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="M26" t="n">
         <v>20</v>
       </c>
       <c r="N26" t="n">
-        <v>3.623044</v>
+        <v>3.5898876</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -2199,19 +2199,19 @@
         <v>77</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1778094</v>
+        <v>1.1797752</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23884013</v>
+        <v>0.23908132</v>
       </c>
       <c r="U26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24921997</v>
+        <v>0.24884437</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
@@ -2239,25 +2239,25 @@
         <v>16</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32793662</v>
+        <v>0.327551</v>
       </c>
       <c r="I27" t="n">
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.40015602</v>
+        <v>0.39869028</v>
       </c>
       <c r="K27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L27" t="n">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.263855</v>
+        <v>4.247338</v>
       </c>
       <c r="O27" t="n">
         <v>17</v>
@@ -2266,19 +2266,19 @@
         <v>87</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3403629</v>
+        <v>1.340271</v>
       </c>
       <c r="S27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2555898</v>
+        <v>0.2547601</v>
       </c>
       <c r="U27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -2288,64 +2288,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25558212</v>
+        <v>0.25570416</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E28" t="n">
         <v>20</v>
       </c>
       <c r="F28" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33309785</v>
+        <v>0.33391365</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.38197768</v>
+        <v>0.3815893</v>
       </c>
       <c r="K28" t="n">
         <v>26</v>
       </c>
       <c r="L28" t="n">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8820896</v>
+        <v>3.9366715</v>
       </c>
       <c r="O28" t="n">
         <v>10</v>
       </c>
       <c r="P28" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2238806</v>
+        <v>1.2297497</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2369462</v>
+        <v>0.23880015</v>
       </c>
       <c r="U28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -2355,64 +2355,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24209715</v>
+        <v>0.24258555</v>
       </c>
       <c r="C29" t="n">
         <v>19</v>
       </c>
       <c r="D29" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G29" t="n">
         <v>21</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31833792</v>
+        <v>0.31876695</v>
       </c>
       <c r="I29" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.38897339</v>
+      </c>
+      <c r="K29" t="n">
+        <v>21</v>
+      </c>
+      <c r="L29" t="n">
+        <v>666</v>
+      </c>
+      <c r="M29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" t="n">
-        <v>0.38743255</v>
-      </c>
-      <c r="K29" t="n">
-        <v>22</v>
-      </c>
-      <c r="L29" t="n">
-        <v>659</v>
-      </c>
-      <c r="M29" t="n">
-        <v>18</v>
-      </c>
       <c r="N29" t="n">
-        <v>3.9322941</v>
+        <v>3.964853</v>
       </c>
       <c r="O29" t="n">
         <v>11</v>
       </c>
       <c r="P29" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2450074</v>
+        <v>1.252287</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23676132</v>
+        <v>0.23807721</v>
       </c>
       <c r="U29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -2422,64 +2422,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.25</v>
+        <v>0.25056347</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3132988</v>
+        <v>0.3137521</v>
       </c>
       <c r="I30" t="n">
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3925841</v>
+        <v>0.3940646</v>
       </c>
       <c r="K30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L30" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1047297</v>
+        <v>4.130166</v>
       </c>
       <c r="O30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P30" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3045367</v>
+        <v>1.3097386</v>
       </c>
       <c r="S30" t="n">
+        <v>18</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.2429272</v>
+      </c>
+      <c r="U30" t="n">
         <v>17</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.24136607</v>
-      </c>
-      <c r="U30" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -2489,64 +2489,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24750277</v>
+        <v>0.247626</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G31" t="n">
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3209672</v>
+        <v>0.32134685</v>
       </c>
       <c r="I31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42323345</v>
+        <v>0.42366692</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>639</v>
+        <v>656</v>
       </c>
       <c r="M31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N31" t="n">
-        <v>4.5908875</v>
+        <v>4.7087197</v>
       </c>
       <c r="O31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3795209</v>
+        <v>1.3914657</v>
       </c>
       <c r="S31" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25556773</v>
+        <v>0.25799498</v>
       </c>
       <c r="U31" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.25247526</v>
+        <v>0.25615764</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
       </c>
       <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.34632036</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4039409</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.09434</v>
+      </c>
+      <c r="O2" t="n">
+        <v>21</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.5849056</v>
+      </c>
+      <c r="S2" t="n">
         <v>26</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.3288889</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.38118812</v>
-      </c>
-      <c r="K2" t="n">
-        <v>22</v>
-      </c>
-      <c r="L2" t="n">
-        <v>31</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5.773585</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="T2" t="n">
+        <v>0.29268292</v>
+      </c>
+      <c r="U2" t="n">
         <v>26</v>
-      </c>
-      <c r="P2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>12</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.6603774</v>
-      </c>
-      <c r="S2" t="n">
-        <v>29</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.31455398</v>
-      </c>
-      <c r="U2" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2238806</v>
+        <v>0.20918368</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32188842</v>
+        <v>0.30837005</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>0.41791046</v>
+        <v>0.38265306</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>7.3636365</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
         <v>30</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6181818</v>
+        <v>1.6111112</v>
       </c>
       <c r="S3" t="n">
         <v>27</v>
       </c>
       <c r="T3" t="n">
-        <v>0.29864255</v>
+        <v>0.29302326</v>
       </c>
       <c r="U3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2934,52 +2934,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.23</v>
+        <v>0.23300971</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2606635</v>
+        <v>0.26605505</v>
       </c>
       <c r="I4" t="n">
         <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.35</v>
+        <v>0.3592233</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4150944</v>
+        <v>4.075472</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="P4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="n">
         <v>8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>18</v>
       </c>
       <c r="R4" t="n">
         <v>1.4339622</v>
@@ -2988,10 +2988,10 @@
         <v>22</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2682927</v>
+        <v>0.26341462</v>
       </c>
       <c r="U4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -3001,16 +3001,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23333333</v>
+        <v>0.23430963</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -3019,46 +3019,46 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.29118773</v>
+        <v>0.2923077</v>
       </c>
       <c r="I5" t="n">
         <v>24</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4125</v>
+        <v>0.41004184</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M5" t="n">
         <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5219781</v>
+        <v>2.8186812</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.120879</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.21333334</v>
+      </c>
+      <c r="U5" t="n">
         <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.1538461</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.2081448</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.20444444</v>
+        <v>0.21681416</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
         <v>6</v>
       </c>
       <c r="G6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2964427</v>
+      </c>
+      <c r="I6" t="n">
+        <v>23</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.35840708</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27</v>
+      </c>
+      <c r="L6" t="n">
+        <v>53</v>
+      </c>
+      <c r="M6" t="n">
         <v>17</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.2857143</v>
-      </c>
-      <c r="I6" t="n">
-        <v>25</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="K6" t="n">
-        <v>28</v>
-      </c>
-      <c r="L6" t="n">
-        <v>61</v>
-      </c>
-      <c r="M6" t="n">
-        <v>23</v>
-      </c>
       <c r="N6" t="n">
-        <v>3.2459016</v>
+        <v>2.6557376</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>0.21266969</v>
+        <v>0.21621622</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.31292516</v>
+        <v>0.32413793</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
         <v>7</v>
       </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>0.41714287</v>
+        <v>0.43820226</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5170068</v>
+        <v>0.5586207</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0555556</v>
+        <v>1.0833334</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>0.21641791</v>
+        <v>0.21481481</v>
       </c>
       <c r="U7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20851064</v>
+        <v>0.20779221</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2579365</v>
+        <v>0.25506073</v>
       </c>
       <c r="I8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J8" t="n">
-        <v>0.39148936</v>
+        <v>0.3982684</v>
       </c>
       <c r="K8" t="n">
+        <v>21</v>
+      </c>
+      <c r="L8" t="n">
+        <v>72</v>
+      </c>
+      <c r="M8" t="n">
+        <v>27</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>14</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3833333</v>
+      </c>
+      <c r="S8" t="n">
+        <v>19</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.26180258</v>
+      </c>
+      <c r="U8" t="n">
         <v>18</v>
-      </c>
-      <c r="L8" t="n">
-        <v>70</v>
-      </c>
-      <c r="M8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.7966104</v>
-      </c>
-      <c r="O8" t="n">
-        <v>28</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>28</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.6440678</v>
-      </c>
-      <c r="S8" t="n">
-        <v>28</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.29460582</v>
-      </c>
-      <c r="U8" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -3269,34 +3269,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1959799</v>
+        <v>0.17676768</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>0.25345623</v>
+        <v>0.22169812</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3316583</v>
+        <v>0.2777778</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
         <v>69</v>
@@ -3305,28 +3305,28 @@
         <v>26</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>3.3333333</v>
       </c>
       <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2592592</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.23232323</v>
+      </c>
+      <c r="U9" t="n">
         <v>10</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3333334</v>
-      </c>
-      <c r="S9" t="n">
-        <v>16</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.23880596</v>
-      </c>
-      <c r="U9" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.19026549</v>
+        <v>0.19823788</v>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>0.27559054</v>
+        <v>0.27667984</v>
       </c>
       <c r="I10" t="n">
         <v>26</v>
       </c>
       <c r="J10" t="n">
-        <v>0.33628318</v>
+        <v>0.36123347</v>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M10" t="n">
         <v>30</v>
@@ -3375,25 +3375,25 @@
         <v>4.6022725</v>
       </c>
       <c r="O10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.278409</v>
+        <v>1.2443181</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>0.24215247</v>
+        <v>0.23873875</v>
       </c>
       <c r="U10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2565445</v>
+        <v>0.26288658</v>
       </c>
       <c r="C11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" t="n">
+        <v>23</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3286385</v>
+      </c>
+      <c r="I11" t="n">
+        <v>13</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.45360824</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>46</v>
+      </c>
+      <c r="M11" t="n">
         <v>11</v>
       </c>
-      <c r="D11" t="n">
-        <v>26</v>
-      </c>
-      <c r="E11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F11" t="n">
-        <v>8</v>
-      </c>
-      <c r="G11" t="n">
-        <v>11</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.43455496</v>
-      </c>
-      <c r="K11" t="n">
-        <v>13</v>
-      </c>
-      <c r="L11" t="n">
-        <v>42</v>
-      </c>
-      <c r="M11" t="n">
-        <v>7</v>
-      </c>
       <c r="N11" t="n">
-        <v>4.075472</v>
+        <v>4.5849056</v>
       </c>
       <c r="O11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P11" t="n">
         <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.264151</v>
+        <v>1.3773584</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="T11" t="n">
-        <v>0.24875621</v>
+        <v>0.26600984</v>
       </c>
       <c r="U11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2356021</v>
+        <v>0.24742268</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3</v>
+        <v>0.30805686</v>
       </c>
       <c r="I12" t="n">
         <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>0.38219896</v>
+        <v>0.3969072</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.54717</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0943396</v>
+        <v>1.037037</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0.215</v>
+        <v>0.21393035</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2460733</v>
+        <v>0.26237625</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.32126698</v>
+      </c>
+      <c r="I13" t="n">
+        <v>16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.45544556</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>48</v>
+      </c>
+      <c r="M13" t="n">
+        <v>14</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>10</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>20</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.0727273</v>
+      </c>
+      <c r="S13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" t="n">
-        <v>24</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.31428573</v>
-      </c>
-      <c r="I13" t="n">
-        <v>15</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.38743454</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="n">
-        <v>46</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="T13" t="n">
+        <v>0.23414634</v>
+      </c>
+      <c r="U13" t="n">
         <v>11</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.3962264</v>
-      </c>
-      <c r="O13" t="n">
-        <v>9</v>
-      </c>
-      <c r="P13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>12</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.9622642</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.21276596</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2990654</v>
+        <v>0.31506848</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3601695</v>
+        <v>0.36134455</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>0.57009345</v>
+        <v>0.6210046</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>5.09434</v>
+        <v>4.8333335</v>
       </c>
       <c r="O14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.490566</v>
+        <v>1.4814814</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T14" t="n">
-        <v>0.28640777</v>
+        <v>0.27884614</v>
       </c>
       <c r="U14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -3671,46 +3671,46 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.26530612</v>
+        <v>0.25106382</v>
       </c>
       <c r="C15" t="n">
+        <v>17</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.31417623</v>
+      </c>
+      <c r="I15" t="n">
+        <v>17</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.45531914</v>
+      </c>
+      <c r="K15" t="n">
         <v>9</v>
       </c>
-      <c r="D15" t="n">
-        <v>36</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>13</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.32342008</v>
-      </c>
-      <c r="I15" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.49387756</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5</v>
-      </c>
       <c r="L15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2826085</v>
+        <v>5.429348</v>
       </c>
       <c r="O15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P15" t="n">
         <v>10</v>
@@ -3719,16 +3719,16 @@
         <v>25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3695652</v>
+        <v>1.3532609</v>
       </c>
       <c r="S15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
-        <v>0.25</v>
+        <v>0.24358974</v>
       </c>
       <c r="U15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2284264</v>
+        <v>0.26540285</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3090909</v>
+        <v>0.3553719</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.35532996</v>
+        <v>0.4028436</v>
       </c>
       <c r="K16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1666665</v>
+        <v>4.6666665</v>
       </c>
       <c r="O16" t="n">
         <v>18</v>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1851852</v>
+        <v>1.2777778</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T16" t="n">
-        <v>0.215</v>
+        <v>0.2292683</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24870466</v>
+        <v>0.2717949</v>
       </c>
       <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>33</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.34684685</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.51794875</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>45</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.8333333</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.2777778</v>
+      </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.25365853</v>
+      </c>
+      <c r="U17" t="n">
         <v>16</v>
-      </c>
-      <c r="D17" t="n">
-        <v>29</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11</v>
-      </c>
-      <c r="F17" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" t="n">
-        <v>9</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.3242009</v>
-      </c>
-      <c r="I17" t="n">
-        <v>11</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.4611399</v>
-      </c>
-      <c r="K17" t="n">
-        <v>8</v>
-      </c>
-      <c r="L17" t="n">
-        <v>51</v>
-      </c>
-      <c r="M17" t="n">
-        <v>17</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.5660377</v>
-      </c>
-      <c r="O17" t="n">
-        <v>11</v>
-      </c>
-      <c r="P17" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.245283</v>
-      </c>
-      <c r="S17" t="n">
-        <v>12</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.24120604</v>
-      </c>
-      <c r="U17" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.23706897</v>
+        <v>0.23931624</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
         <v>29</v>
@@ -3884,49 +3884,49 @@
         <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H18" t="n">
-        <v>0.31034482</v>
+        <v>0.31320754</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3448276</v>
+        <v>0.32905984</v>
       </c>
       <c r="K18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L18" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8877006</v>
+        <v>2.7433155</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
         <v>8</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8663102</v>
+        <v>0.75401074</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.16438356</v>
+        <v>0.1574074</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.32017544</v>
+        <v>0.28767124</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -3957,46 +3957,46 @@
         <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>0.38582677</v>
+        <v>0.3553719</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5219298</v>
+        <v>0.47488585</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9056604</v>
+        <v>5.4339623</v>
       </c>
       <c r="O19" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4716982</v>
+        <v>1.754717</v>
       </c>
       <c r="S19" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2631579</v>
+        <v>0.29357797</v>
       </c>
       <c r="U19" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.26553673</v>
+        <v>0.26136363</v>
       </c>
       <c r="C20" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.32474226</v>
+      </c>
+      <c r="I20" t="n">
+        <v>14</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.42045453</v>
+      </c>
+      <c r="K20" t="n">
+        <v>16</v>
+      </c>
+      <c r="L20" t="n">
+        <v>45</v>
+      </c>
+      <c r="M20" t="n">
         <v>8</v>
       </c>
-      <c r="D20" t="n">
-        <v>23</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>17</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.33163264</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.40677965</v>
-      </c>
-      <c r="K20" t="n">
-        <v>17</v>
-      </c>
-      <c r="L20" t="n">
-        <v>46</v>
-      </c>
-      <c r="M20" t="n">
-        <v>11</v>
-      </c>
       <c r="N20" t="n">
-        <v>5.785714</v>
+        <v>6.4883723</v>
       </c>
       <c r="O20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P20" t="n">
         <v>8</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3809524</v>
+        <v>1.4418604</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T20" t="n">
-        <v>0.26190478</v>
+        <v>0.26744187</v>
       </c>
       <c r="U20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.27196652</v>
+        <v>0.24680851</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>5</v>
       </c>
-      <c r="F21" t="n">
-        <v>13</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.34210527</v>
+        <v>0.31128404</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>0.47698745</v>
+        <v>0.4212766</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L21" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M21" t="n">
         <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.919355</v>
+        <v>4.064516</v>
       </c>
       <c r="O21" t="n">
+        <v>12</v>
+      </c>
+      <c r="P21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>14</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2258065</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.25104603</v>
+      </c>
+      <c r="U21" t="n">
         <v>15</v>
-      </c>
-      <c r="P21" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>22</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.1451613</v>
-      </c>
-      <c r="S21" t="n">
-        <v>8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.23529412</v>
-      </c>
-      <c r="U21" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -4140,16 +4140,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.26213592</v>
+        <v>0.29680365</v>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
@@ -4158,46 +4158,46 @@
         <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3090909</v>
+        <v>0.3390558</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J22" t="n">
-        <v>0.48058254</v>
+        <v>0.51141554</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.245283</v>
+        <v>5.4339623</v>
       </c>
       <c r="O22" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3396226</v>
+        <v>1.4150944</v>
       </c>
       <c r="S22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T22" t="n">
-        <v>0.26511627</v>
+        <v>0.27314815</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.29508197</v>
+        <v>0.28176796</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
+        <v>17</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>25</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.33163264</v>
+      </c>
+      <c r="I23" t="n">
+        <v>12</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.45856354</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.5581396</v>
+      </c>
+      <c r="O23" t="n">
         <v>9</v>
       </c>
-      <c r="F23" t="n">
+      <c r="P23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>12</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.1627907</v>
+      </c>
+      <c r="S23" t="n">
         <v>8</v>
       </c>
-      <c r="G23" t="n">
-        <v>11</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.34343433</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.5136612</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" t="n">
-        <v>44</v>
-      </c>
-      <c r="M23" t="n">
-        <v>9</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.139535</v>
-      </c>
-      <c r="O23" t="n">
-        <v>6</v>
-      </c>
-      <c r="P23" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="T23" t="n">
+        <v>0.2264151</v>
+      </c>
+      <c r="U23" t="n">
         <v>7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.2325581</v>
-      </c>
-      <c r="S23" t="n">
-        <v>11</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.221519</v>
-      </c>
-      <c r="U23" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24630542</v>
+        <v>0.26442307</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H24" t="n">
-        <v>0.31858408</v>
+        <v>0.34188035</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38916257</v>
+        <v>0.42307693</v>
       </c>
       <c r="K24" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L24" t="n">
         <v>57</v>
       </c>
       <c r="M24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2884614</v>
+        <v>3.6666667</v>
       </c>
       <c r="O24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3653846</v>
+        <v>1.3148148</v>
       </c>
       <c r="S24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T24" t="n">
-        <v>0.26130652</v>
+        <v>0.25480768</v>
       </c>
       <c r="U24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -4344,61 +4344,61 @@
         <v>0.25</v>
       </c>
       <c r="C25" t="n">
+        <v>18</v>
+      </c>
+      <c r="D25" t="n">
+        <v>17</v>
+      </c>
+      <c r="E25" t="n">
+        <v>28</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.32240438</v>
+      </c>
+      <c r="I25" t="n">
         <v>15</v>
       </c>
-      <c r="D25" t="n">
-        <v>21</v>
-      </c>
-      <c r="E25" t="n">
-        <v>23</v>
-      </c>
-      <c r="F25" t="n">
-        <v>8</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="J25" t="n">
+        <v>0.4207317</v>
+      </c>
+      <c r="K25" t="n">
+        <v>15</v>
+      </c>
+      <c r="L25" t="n">
+        <v>40</v>
+      </c>
+      <c r="M25" t="n">
+        <v>6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.2142856</v>
+      </c>
+      <c r="O25" t="n">
+        <v>7</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2380953</v>
+      </c>
+      <c r="S25" t="n">
         <v>11</v>
       </c>
-      <c r="H25" t="n">
-        <v>0.31016043</v>
-      </c>
-      <c r="I25" t="n">
-        <v>17</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.45238096</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="T25" t="n">
+        <v>0.23225807</v>
+      </c>
+      <c r="U25" t="n">
         <v>9</v>
-      </c>
-      <c r="L25" t="n">
-        <v>33</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.642857</v>
-      </c>
-      <c r="O25" t="n">
-        <v>12</v>
-      </c>
-      <c r="P25" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.3095238</v>
-      </c>
-      <c r="S25" t="n">
-        <v>15</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U25" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1618497</v>
+        <v>0.16483517</v>
       </c>
       <c r="C26" t="n">
         <v>30</v>
@@ -4420,52 +4420,52 @@
         <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H26" t="n">
-        <v>0.26020408</v>
+        <v>0.24378109</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>0.24855492</v>
+        <v>0.2857143</v>
       </c>
       <c r="K26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L26" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M26" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N26" t="n">
         <v>2.8333333</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
         <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9074074</v>
+        <v>1.0555556</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.19371727</v>
+        <v>0.21938775</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.29</v>
+        <v>0.2835821</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
         <v>30</v>
@@ -4490,28 +4490,28 @@
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H27" t="n">
-        <v>0.38235295</v>
+        <v>0.36864406</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.415</v>
+        <v>0.41293532</v>
       </c>
       <c r="K27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>6.4038463</v>
+        <v>6.576923</v>
       </c>
       <c r="O27" t="n">
         <v>29</v>
@@ -4523,16 +4523,16 @@
         <v>25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4807693</v>
+        <v>1.6153846</v>
       </c>
       <c r="S27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2990654</v>
+        <v>0.30555555</v>
       </c>
       <c r="U27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.23958333</v>
+        <v>0.26395938</v>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3018868</v>
+        <v>0.34080717</v>
       </c>
       <c r="I28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.39086294</v>
+      </c>
+      <c r="K28" t="n">
+        <v>23</v>
+      </c>
+      <c r="L28" t="n">
+        <v>47</v>
+      </c>
+      <c r="M28" t="n">
+        <v>12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.075472</v>
+      </c>
+      <c r="O28" t="n">
+        <v>13</v>
+      </c>
+      <c r="P28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" t="n">
         <v>20</v>
       </c>
-      <c r="J28" t="n">
-        <v>0.35416666</v>
-      </c>
-      <c r="K28" t="n">
-        <v>24</v>
-      </c>
-      <c r="L28" t="n">
-        <v>46</v>
-      </c>
-      <c r="M28" t="n">
-        <v>11</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.9423077</v>
-      </c>
-      <c r="O28" t="n">
-        <v>5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>12</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.0384616</v>
+        <v>1.1886792</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T28" t="n">
-        <v>0.21578947</v>
+        <v>0.245</v>
       </c>
       <c r="U28" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.28365386</v>
+        <v>0.2904762</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
+        <v>13</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3617021</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.47619048</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>51</v>
+      </c>
+      <c r="M29" t="n">
         <v>15</v>
       </c>
-      <c r="F29" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" t="n">
-        <v>16</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.3478261</v>
-      </c>
-      <c r="I29" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.44230768</v>
-      </c>
-      <c r="K29" t="n">
-        <v>11</v>
-      </c>
-      <c r="L29" t="n">
-        <v>52</v>
-      </c>
-      <c r="M29" t="n">
-        <v>18</v>
-      </c>
       <c r="N29" t="n">
-        <v>5.7272725</v>
+        <v>5.3333335</v>
       </c>
       <c r="O29" t="n">
+        <v>22</v>
+      </c>
+      <c r="P29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="n">
         <v>25</v>
       </c>
-      <c r="P29" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>22</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.5090909</v>
+        <v>1.425926</v>
       </c>
       <c r="S29" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2927928</v>
+        <v>0.27906978</v>
       </c>
       <c r="U29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2512563</v>
+        <v>0.26415095</v>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H30" t="n">
-        <v>0.29680365</v>
+        <v>0.3073593</v>
       </c>
       <c r="I30" t="n">
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>0.44723618</v>
+        <v>0.43867925</v>
       </c>
       <c r="K30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L30" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M30" t="n">
+        <v>12</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.7454543</v>
+      </c>
+      <c r="O30" t="n">
+        <v>19</v>
+      </c>
+      <c r="P30" t="n">
         <v>9</v>
       </c>
-      <c r="N30" t="n">
-        <v>3.9056604</v>
-      </c>
-      <c r="O30" t="n">
-        <v>13</v>
-      </c>
-      <c r="P30" t="n">
-        <v>6</v>
-      </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
-        <v>1.6792452</v>
+        <v>1.6909091</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T30" t="n">
-        <v>0.25</v>
+        <v>0.2706422</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.25252524</v>
+        <v>0.24378109</v>
       </c>
       <c r="C31" t="n">
+        <v>21</v>
+      </c>
+      <c r="D31" t="n">
+        <v>24</v>
+      </c>
+      <c r="E31" t="n">
+        <v>22</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2883721</v>
+      </c>
+      <c r="I31" t="n">
+        <v>25</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.42288557</v>
+      </c>
+      <c r="K31" t="n">
+        <v>13</v>
+      </c>
+      <c r="L31" t="n">
+        <v>55</v>
+      </c>
+      <c r="M31" t="n">
+        <v>19</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.7115383</v>
+      </c>
+      <c r="O31" t="n">
+        <v>27</v>
+      </c>
+      <c r="P31" t="n">
         <v>12</v>
       </c>
-      <c r="D31" t="n">
-        <v>21</v>
-      </c>
-      <c r="E31" t="n">
-        <v>23</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
-      </c>
-      <c r="G31" t="n">
-        <v>11</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.29577464</v>
-      </c>
-      <c r="I31" t="n">
-        <v>23</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.43939394</v>
-      </c>
-      <c r="K31" t="n">
-        <v>12</v>
-      </c>
-      <c r="L31" t="n">
-        <v>42</v>
-      </c>
-      <c r="M31" t="n">
-        <v>7</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.9807692</v>
-      </c>
-      <c r="O31" t="n">
-        <v>16</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
       <c r="Q31" t="n">
+        <v>28</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.5384616</v>
+      </c>
+      <c r="S31" t="n">
         <v>25</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.4038461</v>
-      </c>
-      <c r="S31" t="n">
-        <v>21</v>
-      </c>
       <c r="T31" t="n">
-        <v>0.27722773</v>
+        <v>0.30331755</v>
       </c>
       <c r="U31" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Last 7 Days" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Season" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Last 7 Days" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23796791</v>
+        <v>0.23899135</v>
       </c>
       <c r="C2" t="n">
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="E2" t="n">
         <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
         <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30877313</v>
+        <v>0.30982113</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38349885</v>
+        <v>0.3861498</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L2" t="n">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2760763</v>
+        <v>4.2853093</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q2" t="n">
         <v>21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2976077</v>
+        <v>1.2966461</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25056434</v>
+        <v>0.25074294</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24796145</v>
+        <v>0.24651504</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32840237</v>
+        <v>0.3272609</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4166049</v>
+        <v>0.41489363</v>
       </c>
       <c r="K3" t="n">
         <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9807057</v>
+        <v>4.9456067</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4498824</v>
+        <v>1.4449093</v>
       </c>
       <c r="S3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26377234</v>
+        <v>0.2630819</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25179043</v>
+        <v>0.25083736</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G4" t="n">
         <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31552076</v>
+        <v>0.3143914</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41764042</v>
+        <v>0.4160774</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3993273</v>
+        <v>3.4247031</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q4" t="n">
         <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2066314</v>
+        <v>1.2114013</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22494173</v>
+        <v>0.22521138</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -747,64 +747,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.24057649</v>
+        <v>0.24061246</v>
       </c>
       <c r="C5" t="n">
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31958088</v>
+        <v>0.31954765</v>
       </c>
       <c r="I5" t="n">
         <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>0.40169993</v>
+        <v>0.40247902</v>
       </c>
       <c r="K5" t="n">
         <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="M5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>4.424581</v>
+        <v>4.427653</v>
       </c>
       <c r="O5" t="n">
         <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3798883</v>
+        <v>1.3821772</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25644752</v>
+        <v>0.2556391</v>
       </c>
       <c r="U5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -814,43 +814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24312815</v>
+        <v>0.24389313</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
         <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31230393</v>
+        <v>0.3123495</v>
       </c>
       <c r="I6" t="n">
         <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3809524</v>
+        <v>0.3847328</v>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8211303</v>
+        <v>3.8159301</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -859,16 +859,16 @@
         <v>84</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2619165</v>
+        <v>1.2690626</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24416797</v>
+        <v>0.24597701</v>
       </c>
       <c r="U6" t="n">
         <v>19</v>
@@ -881,64 +881,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2435994</v>
+        <v>0.24414349</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33778936</v>
+        <v>0.33830056</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40286145</v>
+        <v>0.4059297</v>
       </c>
       <c r="K7" t="n">
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3028407</v>
+        <v>4.2951665</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2407318</v>
+        <v>1.2402629</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23893805</v>
+        <v>0.23864916</v>
       </c>
       <c r="U7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -948,43 +948,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23636363</v>
+        <v>0.23693247</v>
       </c>
       <c r="C8" t="n">
         <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31735706</v>
+        <v>0.317921</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4088975</v>
+        <v>0.40976727</v>
       </c>
       <c r="K8" t="n">
         <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.371677</v>
+        <v>4.3349214</v>
       </c>
       <c r="O8" t="n">
         <v>20</v>
@@ -993,16 +993,16 @@
         <v>89</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3383276</v>
+        <v>1.3392091</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24160556</v>
+        <v>0.24115634</v>
       </c>
       <c r="U8" t="n">
         <v>15</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22520107</v>
+        <v>0.22629392</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3066984</v>
+        <v>0.30946806</v>
       </c>
       <c r="I9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" t="n">
-        <v>0.38759097</v>
+        <v>0.38911974</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="M9" t="n">
         <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4935436</v>
+        <v>4.512748</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.446198</v>
+        <v>1.4490085</v>
       </c>
       <c r="S9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24764062</v>
+        <v>0.24823223</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1082,16 +1082,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2278626</v>
+        <v>0.22761475</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
         <v>75</v>
@@ -1100,43 +1100,43 @@
         <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31258413</v>
+        <v>0.3126658</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3687023</v>
+        <v>0.36644092</v>
       </c>
       <c r="K10" t="n">
         <v>29</v>
       </c>
       <c r="L10" t="n">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="M10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8042552</v>
+        <v>3.7888112</v>
       </c>
       <c r="O10" t="n">
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2524823</v>
+        <v>1.2545455</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23616377</v>
+        <v>0.236724</v>
       </c>
       <c r="U10" t="n">
         <v>8</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25258493</v>
+        <v>0.2541879</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
         <v>86</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32262337</v>
+        <v>0.32352942</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4102659</v>
+        <v>0.41041514</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.474359</v>
+        <v>5.481013</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.517094</v>
+        <v>1.5147679</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2849443</v>
+        <v>0.2851064</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,64 +1216,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23527162</v>
+        <v>0.2352719</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
         <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31504065</v>
+        <v>0.3147157</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39364958</v>
+        <v>0.3923716</v>
       </c>
       <c r="K12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8255422</v>
+        <v>3.827783</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2621686</v>
+        <v>1.2545195</v>
       </c>
       <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.2383655</v>
+      </c>
+      <c r="U12" t="n">
         <v>12</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.23898889</v>
-      </c>
-      <c r="U12" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24394718</v>
+        <v>0.24265505</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
         <v>107</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31825632</v>
+        <v>0.31812298</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41379312</v>
+        <v>0.41167936</v>
       </c>
       <c r="K13" t="n">
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="M13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8120055</v>
+        <v>4.7647057</v>
       </c>
       <c r="O13" t="n">
         <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4099581</v>
+        <v>1.4007354</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24349442</v>
+        <v>0.24227941</v>
       </c>
       <c r="U13" t="n">
         <v>18</v>
@@ -1350,43 +1350,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24832714</v>
+        <v>0.24770643</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3204237</v>
+        <v>0.3197123</v>
       </c>
       <c r="I14" t="n">
         <v>13</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39739776</v>
+        <v>0.39669725</v>
       </c>
       <c r="K14" t="n">
         <v>17</v>
       </c>
       <c r="L14" t="n">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="M14" t="n">
         <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.536</v>
+        <v>4.548162</v>
       </c>
       <c r="O14" t="n">
         <v>24</v>
@@ -1398,13 +1398,13 @@
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3905883</v>
+        <v>1.3946022</v>
       </c>
       <c r="S14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25362587</v>
+        <v>0.25441176</v>
       </c>
       <c r="U14" t="n">
         <v>23</v>
@@ -1417,61 +1417,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23991196</v>
+        <v>0.23933478</v>
       </c>
       <c r="C15" t="n">
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G15" t="n">
         <v>11</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31865624</v>
+        <v>0.31866366</v>
       </c>
       <c r="I15" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.39840925</v>
+      </c>
+      <c r="K15" t="n">
         <v>16</v>
       </c>
-      <c r="J15" t="n">
-        <v>0.39985326</v>
-      </c>
-      <c r="K15" t="n">
-        <v>14</v>
-      </c>
       <c r="L15" t="n">
-        <v>765</v>
+        <v>782</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.621735</v>
+        <v>4.632475</v>
       </c>
       <c r="O15" t="n">
         <v>25</v>
       </c>
       <c r="P15" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4160447</v>
+        <v>1.4130634</v>
       </c>
       <c r="S15" t="n">
         <v>27</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23751387</v>
+        <v>0.23759124</v>
       </c>
       <c r="U15" t="n">
         <v>9</v>
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26145253</v>
+        <v>0.2617647</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3449398</v>
+        <v>0.34458375</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.43761638</v>
+        <v>0.4375</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4196599</v>
+        <v>3.4017732</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
         <v>84</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0973536</v>
+        <v>1.1003267</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2117013</v>
+        <v>0.21200608</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2460197</v>
+        <v>0.24568643</v>
       </c>
       <c r="C17" t="n">
         <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
         <v>26</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32292715</v>
+        <v>0.32259136</v>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39006823</v>
+        <v>0.39047262</v>
       </c>
       <c r="K17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L17" t="n">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>4.0711236</v>
+        <v>4.044944</v>
       </c>
       <c r="O17" t="n">
         <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2603129</v>
+        <v>1.252809</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2292849</v>
+        <v>0.2288706</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25306278</v>
+        <v>0.2535849</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G18" t="n">
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3370333</v>
+        <v>0.33753315</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3885911</v>
+        <v>0.39132077</v>
       </c>
       <c r="K18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L18" t="n">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="M18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>3.353794</v>
+        <v>3.375</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1657805</v>
+        <v>1.1822519</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21915649</v>
+        <v>0.22036533</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24515185</v>
+        <v>0.24539213</v>
       </c>
       <c r="C19" t="n">
         <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
@@ -1703,46 +1703,46 @@
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32128906</v>
+        <v>0.3215434</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4094402</v>
+        <v>0.40838453</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>667</v>
+        <v>681</v>
       </c>
       <c r="M19" t="n">
         <v>19</v>
       </c>
       <c r="N19" t="n">
-        <v>4.832243</v>
+        <v>4.8218737</v>
       </c>
       <c r="O19" t="n">
         <v>28</v>
       </c>
       <c r="P19" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4060748</v>
+        <v>1.403784</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2555354</v>
+        <v>0.25591397</v>
       </c>
       <c r="U19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23141763</v>
+        <v>0.23131539</v>
       </c>
       <c r="C20" t="n">
         <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2977099</v>
+        <v>0.29780033</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37203065</v>
+        <v>0.37630793</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="M20" t="n">
         <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1399136</v>
+        <v>4.2246614</v>
       </c>
       <c r="O20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2850982</v>
+        <v>1.2919196</v>
       </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23346007</v>
+        <v>0.23429416</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -1819,46 +1819,46 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2450867</v>
+        <v>0.24438523</v>
       </c>
       <c r="C21" t="n">
         <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.33040243</v>
+        <v>0.329097</v>
       </c>
       <c r="I21" t="n">
         <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.43660885</v>
+        <v>0.43738103</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="M21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3668754</v>
+        <v>3.3365018</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
         <v>70</v>
@@ -1867,13 +1867,13 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1844006</v>
+        <v>1.184886</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2257564</v>
+        <v>0.22588055</v>
       </c>
       <c r="U21" t="n">
         <v>4</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23407464</v>
+        <v>0.23409006</v>
       </c>
       <c r="C22" t="n">
         <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G22" t="n">
         <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30074933</v>
+        <v>0.30037</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3995477</v>
+        <v>0.3993301</v>
       </c>
       <c r="K22" t="n">
+        <v>14</v>
+      </c>
+      <c r="L22" t="n">
+        <v>690</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.1246486</v>
+      </c>
+      <c r="O22" t="n">
         <v>15</v>
       </c>
-      <c r="L22" t="n">
-        <v>684</v>
-      </c>
-      <c r="M22" t="n">
-        <v>24</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.126246</v>
-      </c>
-      <c r="O22" t="n">
-        <v>13</v>
-      </c>
       <c r="P22" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.304224</v>
+        <v>1.3003749</v>
       </c>
       <c r="S22" t="n">
         <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2570798</v>
+        <v>0.25617734</v>
       </c>
       <c r="U22" t="n">
         <v>27</v>
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2548446</v>
+        <v>0.25676164</v>
       </c>
       <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>404</v>
+      </c>
+      <c r="E23" t="n">
         <v>4</v>
-      </c>
-      <c r="D23" t="n">
-        <v>393</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5</v>
       </c>
       <c r="F23" t="n">
         <v>94</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33441243</v>
+        <v>0.3356755</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.40804386</v>
+        <v>0.41074648</v>
       </c>
       <c r="K23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="M23" t="n">
         <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1587377</v>
+        <v>4.1190696</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
         <v>77</v>
@@ -2001,13 +2001,13 @@
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3028733</v>
+        <v>1.2962791</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23584203</v>
+        <v>0.23546726</v>
       </c>
       <c r="U23" t="n">
         <v>7</v>
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.219694</v>
+        <v>0.22002329</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E24" t="n">
         <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2934553</v>
+        <v>0.29440388</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.36367202</v>
+        <v>0.36437717</v>
       </c>
       <c r="K24" t="n">
         <v>30</v>
       </c>
       <c r="L24" t="n">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="M24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8757226</v>
+        <v>3.8516405</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q24" t="n">
         <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2962428</v>
+        <v>1.2910129</v>
       </c>
       <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.24102369</v>
+      </c>
+      <c r="U24" t="n">
         <v>14</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.24187307</v>
-      </c>
-      <c r="U24" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2576208</v>
+        <v>0.2569853</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G25" t="n">
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30976775</v>
+        <v>0.30935496</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41858736</v>
+        <v>0.41875</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4041624</v>
+        <v>4.3602486</v>
       </c>
       <c r="O25" t="n">
         <v>21</v>
       </c>
       <c r="P25" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q25" t="n">
         <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3838334</v>
+        <v>1.3745819</v>
       </c>
       <c r="S25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25038344</v>
+        <v>0.24886191</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,16 +2154,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23178558</v>
+        <v>0.23145732</v>
       </c>
       <c r="C26" t="n">
         <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
         <v>100</v>
@@ -2172,25 +2172,25 @@
         <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31201875</v>
+        <v>0.31082425</v>
       </c>
       <c r="I26" t="n">
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38769346</v>
+        <v>0.38613492</v>
       </c>
       <c r="K26" t="n">
+        <v>25</v>
+      </c>
+      <c r="L26" t="n">
+        <v>691</v>
+      </c>
+      <c r="M26" t="n">
         <v>23</v>
       </c>
-      <c r="L26" t="n">
-        <v>678</v>
-      </c>
-      <c r="M26" t="n">
-        <v>20</v>
-      </c>
       <c r="N26" t="n">
-        <v>3.5898876</v>
+        <v>3.6875</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -2202,16 +2202,16 @@
         <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1797752</v>
+        <v>1.1916667</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23908132</v>
+        <v>0.2412769</v>
       </c>
       <c r="U26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24884437</v>
+        <v>0.2486692</v>
       </c>
       <c r="C27" t="n">
         <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" t="n">
-        <v>0.327551</v>
+        <v>0.3268391</v>
       </c>
       <c r="I27" t="n">
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39869028</v>
+        <v>0.39885932</v>
       </c>
       <c r="K27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L27" t="n">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.247338</v>
+        <v>4.2957478</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P27" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R27" t="n">
-        <v>1.340271</v>
+        <v>1.3473482</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2547601</v>
+        <v>0.2555347</v>
       </c>
       <c r="U27" t="n">
         <v>24</v>
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25570416</v>
+        <v>0.2565099</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E28" t="n">
         <v>20</v>
@@ -2306,43 +2306,43 @@
         <v>30</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33391365</v>
+        <v>0.3349381</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3815893</v>
+        <v>0.38204432</v>
       </c>
       <c r="K28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L28" t="n">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9366715</v>
+        <v>3.8982558</v>
       </c>
       <c r="O28" t="n">
         <v>10</v>
       </c>
       <c r="P28" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2297497</v>
+        <v>1.2267442</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23880015</v>
+        <v>0.23827825</v>
       </c>
       <c r="U28" t="n">
         <v>11</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24258555</v>
+        <v>0.24201427</v>
       </c>
       <c r="C29" t="n">
         <v>19</v>
       </c>
       <c r="D29" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F29" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G29" t="n">
         <v>21</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31876695</v>
+        <v>0.31746563</v>
       </c>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>0.38897339</v>
+        <v>0.3889515</v>
       </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="M29" t="n">
         <v>17</v>
       </c>
       <c r="N29" t="n">
-        <v>3.964853</v>
+        <v>3.970966</v>
       </c>
       <c r="O29" t="n">
         <v>11</v>
       </c>
       <c r="P29" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.252287</v>
+        <v>1.2508329</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23807721</v>
+        <v>0.23782772</v>
       </c>
       <c r="U29" t="n">
         <v>10</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.25056347</v>
+        <v>0.24925706</v>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="n">
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3137521</v>
+        <v>0.31239504</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3940646</v>
+        <v>0.3922734</v>
       </c>
       <c r="K30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L30" t="n">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.130166</v>
+        <v>4.1031895</v>
       </c>
       <c r="O30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P30" t="n">
         <v>87</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3097386</v>
+        <v>1.3100375</v>
       </c>
       <c r="S30" t="n">
         <v>18</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2429272</v>
+        <v>0.24161074</v>
       </c>
       <c r="U30" t="n">
         <v>17</v>
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.247626</v>
+        <v>0.2468423</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32134685</v>
+        <v>0.32095575</v>
       </c>
       <c r="I31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42366692</v>
+        <v>0.42511728</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="M31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7087197</v>
+        <v>4.687586</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3914657</v>
+        <v>1.3879981</v>
       </c>
       <c r="S31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25799498</v>
+        <v>0.25772098</v>
       </c>
       <c r="U31" t="n">
         <v>28</v>
@@ -2800,46 +2800,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.25615764</v>
+        <v>0.25480768</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.34632036</v>
+        <v>0.34177214</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4039409</v>
+        <v>0.40865386</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>5.09434</v>
+        <v>5.773585</v>
       </c>
       <c r="O2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
@@ -2848,16 +2848,16 @@
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5849056</v>
+        <v>1.6226416</v>
       </c>
       <c r="S2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T2" t="n">
-        <v>0.29268292</v>
+        <v>0.3014354</v>
       </c>
       <c r="U2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.20918368</v>
+        <v>0.19895288</v>
       </c>
       <c r="C3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D3" t="n">
         <v>26</v>
       </c>
-      <c r="D3" t="n">
-        <v>29</v>
-      </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>0.30837005</v>
+        <v>0.30493274</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>0.38265306</v>
+        <v>0.36649215</v>
       </c>
       <c r="K3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>5.36646</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P3" t="n">
         <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6111112</v>
+        <v>1.416149</v>
       </c>
       <c r="S3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="T3" t="n">
-        <v>0.29302326</v>
+        <v>0.26108375</v>
       </c>
       <c r="U3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.23300971</v>
+        <v>0.20792079</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -2952,46 +2952,46 @@
         <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>0.26605505</v>
+        <v>0.24413146</v>
       </c>
       <c r="I4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.33663365</v>
+      </c>
+      <c r="K4" t="n">
         <v>27</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.3592233</v>
-      </c>
-      <c r="K4" t="n">
-        <v>26</v>
-      </c>
       <c r="L4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>4.075472</v>
+        <v>3.8076923</v>
       </c>
       <c r="O4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4339622</v>
+        <v>1.4807693</v>
       </c>
       <c r="S4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T4" t="n">
-        <v>0.26341462</v>
+        <v>0.26130652</v>
       </c>
       <c r="U4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23430963</v>
+        <v>0.22821577</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2923077</v>
+        <v>0.29166666</v>
       </c>
       <c r="I5" t="n">
         <v>24</v>
       </c>
       <c r="J5" t="n">
-        <v>0.41004184</v>
+        <v>0.40248963</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8186812</v>
+        <v>3.0815217</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.120879</v>
+        <v>1.1902174</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>0.21333334</v>
+        <v>0.21030043</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.21681416</v>
+        <v>0.23043478</v>
       </c>
       <c r="C6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.29083666</v>
+      </c>
+      <c r="I6" t="n">
         <v>25</v>
       </c>
-      <c r="D6" t="n">
-        <v>22</v>
-      </c>
-      <c r="E6" t="n">
-        <v>25</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>19</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.2964427</v>
-      </c>
-      <c r="I6" t="n">
-        <v>23</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.35840708</v>
+        <v>0.42173913</v>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M6" t="n">
         <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6557376</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>6</v>
       </c>
       <c r="Q6" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1333333</v>
+      </c>
+      <c r="S6" t="n">
         <v>8</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.21621622</v>
+        <v>0.24</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.32413793</v>
+        <v>0.2925532</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>0.43820226</v>
+        <v>0.40969163</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5586207</v>
+        <v>0.5159575</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0833334</v>
+        <v>1.1111112</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>0.21481481</v>
+        <v>0.21212122</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20779221</v>
+        <v>0.20434782</v>
       </c>
       <c r="C8" t="n">
         <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.25506073</v>
+        <v>0.26</v>
       </c>
       <c r="I8" t="n">
         <v>28</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3982684</v>
+        <v>0.37826088</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>2.903226</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3064516</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.24034335</v>
+      </c>
+      <c r="U8" t="n">
         <v>14</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.3833333</v>
-      </c>
-      <c r="S8" t="n">
-        <v>19</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.26180258</v>
-      </c>
-      <c r="U8" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.17676768</v>
+        <v>0.2039801</v>
       </c>
       <c r="C9" t="n">
+        <v>28</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>28</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2780269</v>
+      </c>
+      <c r="I9" t="n">
+        <v>27</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.31840795</v>
+      </c>
+      <c r="K9" t="n">
         <v>29</v>
       </c>
-      <c r="D9" t="n">
-        <v>16</v>
-      </c>
-      <c r="E9" t="n">
-        <v>29</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.22169812</v>
-      </c>
-      <c r="I9" t="n">
-        <v>30</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.2777778</v>
-      </c>
-      <c r="K9" t="n">
-        <v>30</v>
-      </c>
       <c r="L9" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3333333</v>
+        <v>2.8333333</v>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2592592</v>
+        <v>1.2037038</v>
       </c>
       <c r="S9" t="n">
         <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>0.23232323</v>
+        <v>0.21319798</v>
       </c>
       <c r="U9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.19823788</v>
+        <v>0.21276596</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>0.27667984</v>
+        <v>0.29545453</v>
       </c>
       <c r="I10" t="n">
+        <v>22</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3531915</v>
+      </c>
+      <c r="K10" t="n">
         <v>26</v>
       </c>
-      <c r="J10" t="n">
-        <v>0.36123347</v>
-      </c>
-      <c r="K10" t="n">
-        <v>25</v>
-      </c>
       <c r="L10" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M10" t="n">
         <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6022725</v>
+        <v>3.5604396</v>
       </c>
       <c r="O10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="P10" t="n">
         <v>8</v>
       </c>
       <c r="Q10" t="n">
+        <v>15</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2197802</v>
+      </c>
+      <c r="S10" t="n">
         <v>14</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.2443181</v>
-      </c>
-      <c r="S10" t="n">
-        <v>12</v>
-      </c>
       <c r="T10" t="n">
-        <v>0.23873875</v>
+        <v>0.23214285</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -3403,61 +3403,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.26288658</v>
+        <v>0.2857143</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3286385</v>
+        <v>0.3472222</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.45360824</v>
+        <v>0.41836736</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5849056</v>
+        <v>4.1666665</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P11" t="n">
         <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3773584</v>
+        <v>1.2777778</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T11" t="n">
-        <v>0.26600984</v>
+        <v>0.25603864</v>
       </c>
       <c r="U11" t="n">
         <v>20</v>
@@ -3470,61 +3470,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24742268</v>
+        <v>0.26767677</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>23</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H12" t="n">
-        <v>0.30805686</v>
+        <v>0.33027524</v>
       </c>
       <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3939394</v>
+      </c>
+      <c r="K12" t="n">
         <v>21</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.3969072</v>
-      </c>
-      <c r="K12" t="n">
-        <v>22</v>
-      </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
         <v>7</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2.9454546</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.037037</v>
+        <v>0.90909094</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.21393035</v>
+        <v>0.19900498</v>
       </c>
       <c r="U12" t="n">
         <v>3</v>
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.26237625</v>
+        <v>0.23880596</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>0.32126698</v>
+        <v>0.31555554</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.45544556</v>
+        <v>0.4079602</v>
       </c>
       <c r="K13" t="n">
+        <v>17</v>
+      </c>
+      <c r="L13" t="n">
+        <v>52</v>
+      </c>
+      <c r="M13" t="n">
+        <v>13</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.4363637</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11</v>
+      </c>
+      <c r="P13" t="n">
         <v>8</v>
       </c>
-      <c r="L13" t="n">
-        <v>48</v>
-      </c>
-      <c r="M13" t="n">
-        <v>14</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>10</v>
-      </c>
-      <c r="P13" t="n">
-        <v>9</v>
-      </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0727273</v>
+        <v>1.1272727</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23414634</v>
+        <v>0.23902439</v>
       </c>
       <c r="U13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -3604,46 +3604,46 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.31506848</v>
+        <v>0.29032257</v>
       </c>
       <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>47</v>
+      </c>
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="n">
-        <v>50</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36134455</v>
+        <v>0.33617023</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6210046</v>
+        <v>0.5529954</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8333335</v>
+        <v>5.4339623</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
@@ -3652,16 +3652,16 @@
         <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4814814</v>
+        <v>1.6415094</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T14" t="n">
-        <v>0.27884614</v>
+        <v>0.29807693</v>
       </c>
       <c r="U14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.25106382</v>
+        <v>0.2489796</v>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
@@ -3689,46 +3689,46 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31417623</v>
+        <v>0.32</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>0.45531914</v>
+        <v>0.4408163</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>5.429348</v>
+        <v>4.9736843</v>
       </c>
       <c r="O15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>24</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.263158</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.23206751</v>
+      </c>
+      <c r="U15" t="n">
         <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>25</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3532609</v>
-      </c>
-      <c r="S15" t="n">
-        <v>17</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.24358974</v>
-      </c>
-      <c r="U15" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -3738,16 +3738,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26540285</v>
+        <v>0.26635513</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
@@ -3756,25 +3756,25 @@
         <v>19</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3553719</v>
+        <v>0.3375</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4028436</v>
+        <v>0.40186915</v>
       </c>
       <c r="K16" t="n">
         <v>20</v>
       </c>
       <c r="L16" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6666665</v>
+        <v>4.3333335</v>
       </c>
       <c r="O16" t="n">
         <v>18</v>
@@ -3783,19 +3783,19 @@
         <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R16" t="n">
         <v>1.2777778</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2292683</v>
+        <v>0.22815534</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2717949</v>
+        <v>0.25</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H17" t="n">
-        <v>0.34684685</v>
+        <v>0.32692307</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>0.51794875</v>
+        <v>0.4456522</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
         <v>2.8333333</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2777778</v>
+        <v>1.1851852</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.25365853</v>
+        <v>0.24120604</v>
       </c>
       <c r="U17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.23931624</v>
+        <v>0.23529412</v>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.31320754</v>
+        <v>0.31617647</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>0.32905984</v>
+        <v>0.33193278</v>
       </c>
       <c r="K18" t="n">
         <v>28</v>
       </c>
       <c r="L18" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7433155</v>
+        <v>2.8877006</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
         <v>8</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
-        <v>0.75401074</v>
+        <v>1.0106952</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1574074</v>
+        <v>0.1891892</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.28767124</v>
+        <v>0.28458497</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E19" t="n">
         <v>4</v>
@@ -3954,49 +3954,49 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3553719</v>
+        <v>0.35357141</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>0.47488585</v>
+        <v>0.45454547</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4339623</v>
+        <v>5.225806</v>
       </c>
       <c r="O19" t="n">
         <v>24</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.754717</v>
+        <v>1.6774193</v>
       </c>
       <c r="S19" t="n">
         <v>30</v>
       </c>
       <c r="T19" t="n">
-        <v>0.29357797</v>
+        <v>0.29249012</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.26136363</v>
+        <v>0.22660099</v>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D20" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" t="n">
+        <v>13</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.29910713</v>
+      </c>
+      <c r="I20" t="n">
+        <v>21</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.44827586</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>58</v>
+      </c>
+      <c r="M20" t="n">
+        <v>21</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7.9615383</v>
+      </c>
+      <c r="O20" t="n">
+        <v>30</v>
+      </c>
+      <c r="P20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>24</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.5961539</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.28372094</v>
+      </c>
+      <c r="U20" t="n">
         <v>26</v>
-      </c>
-      <c r="E20" t="n">
-        <v>17</v>
-      </c>
-      <c r="F20" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" t="n">
-        <v>16</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.32474226</v>
-      </c>
-      <c r="I20" t="n">
-        <v>14</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.42045453</v>
-      </c>
-      <c r="K20" t="n">
-        <v>16</v>
-      </c>
-      <c r="L20" t="n">
-        <v>45</v>
-      </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>6.4883723</v>
-      </c>
-      <c r="O20" t="n">
-        <v>28</v>
-      </c>
-      <c r="P20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>14</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4418604</v>
-      </c>
-      <c r="S20" t="n">
-        <v>23</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.26744187</v>
-      </c>
-      <c r="U20" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.24680851</v>
+        <v>0.22270742</v>
       </c>
       <c r="C21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>26</v>
-      </c>
-      <c r="E21" t="n">
-        <v>17</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31128404</v>
+        <v>0.28225806</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4212766</v>
+        <v>0.3842795</v>
       </c>
       <c r="K21" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="L21" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="M21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>4.064516</v>
+        <v>3.483871</v>
       </c>
       <c r="O21" t="n">
         <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2258065</v>
+        <v>1.1935484</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T21" t="n">
-        <v>0.25104603</v>
+        <v>0.24152543</v>
       </c>
       <c r="U21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.29680365</v>
+        <v>0.29166666</v>
       </c>
       <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>45</v>
+      </c>
+      <c r="E22" t="n">
         <v>3</v>
       </c>
-      <c r="D22" t="n">
-        <v>44</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
         <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3390558</v>
+        <v>0.33620688</v>
       </c>
       <c r="I22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.51141554</v>
+        <v>0.5277778</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>5.4339623</v>
+        <v>4.5849056</v>
       </c>
       <c r="O22" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4150944</v>
+        <v>1.264151</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T22" t="n">
-        <v>0.27314815</v>
+        <v>0.24761905</v>
       </c>
       <c r="U22" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.28176796</v>
+        <v>0.28248587</v>
       </c>
       <c r="C23" t="n">
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33163264</v>
+        <v>0.3227513</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>0.45856354</v>
+        <v>0.4463277</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5581396</v>
+        <v>3.139535</v>
       </c>
       <c r="O23" t="n">
         <v>9</v>
       </c>
       <c r="P23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1627907</v>
+        <v>1.1162791</v>
       </c>
       <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.23125</v>
+      </c>
+      <c r="U23" t="n">
         <v>8</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.2264151</v>
-      </c>
-      <c r="U23" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.26442307</v>
+        <v>0.24242425</v>
       </c>
       <c r="C24" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" t="n">
+        <v>29</v>
+      </c>
+      <c r="E24" t="n">
         <v>10</v>
-      </c>
-      <c r="D24" t="n">
-        <v>30</v>
-      </c>
-      <c r="E24" t="n">
-        <v>9</v>
       </c>
       <c r="F24" t="n">
         <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>0.34188035</v>
+        <v>0.3318584</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J24" t="n">
-        <v>0.42307693</v>
+        <v>0.4040404</v>
       </c>
       <c r="K24" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L24" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N24" t="n">
-        <v>3.6666667</v>
+        <v>3.8333333</v>
       </c>
       <c r="O24" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.3148148</v>
+        <v>1.2962962</v>
       </c>
       <c r="S24" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="T24" t="n">
-        <v>0.25480768</v>
+        <v>0.25</v>
       </c>
       <c r="U24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25</v>
+        <v>0.2375</v>
       </c>
       <c r="C25" t="n">
+        <v>19</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="n">
+        <v>30</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>21</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.30898875</v>
+      </c>
+      <c r="I25" t="n">
         <v>18</v>
       </c>
-      <c r="D25" t="n">
-        <v>17</v>
-      </c>
-      <c r="E25" t="n">
-        <v>28</v>
-      </c>
-      <c r="F25" t="n">
-        <v>6</v>
-      </c>
-      <c r="G25" t="n">
-        <v>19</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.32240438</v>
-      </c>
-      <c r="I25" t="n">
-        <v>15</v>
-      </c>
       <c r="J25" t="n">
-        <v>0.4207317</v>
+        <v>0.3875</v>
       </c>
       <c r="K25" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L25" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2142856</v>
+        <v>2.357143</v>
       </c>
       <c r="O25" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>4</v>
       </c>
       <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.0476191</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.18620689</v>
+      </c>
+      <c r="U25" t="n">
         <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.2380953</v>
-      </c>
-      <c r="S25" t="n">
-        <v>11</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.23225807</v>
-      </c>
-      <c r="U25" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.16483517</v>
+        <v>0.16304348</v>
       </c>
       <c r="C26" t="n">
         <v>30</v>
       </c>
       <c r="D26" t="n">
+        <v>13</v>
+      </c>
+      <c r="E26" t="n">
+        <v>29</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>26</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I26" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.25543478</v>
+      </c>
+      <c r="K26" t="n">
+        <v>30</v>
+      </c>
+      <c r="L26" t="n">
+        <v>54</v>
+      </c>
+      <c r="M26" t="n">
         <v>15</v>
       </c>
-      <c r="E26" t="n">
-        <v>30</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6</v>
-      </c>
-      <c r="G26" t="n">
-        <v>19</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.24378109</v>
-      </c>
-      <c r="I26" t="n">
-        <v>29</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.2857143</v>
-      </c>
-      <c r="K26" t="n">
-        <v>29</v>
-      </c>
-      <c r="L26" t="n">
-        <v>55</v>
-      </c>
-      <c r="M26" t="n">
-        <v>19</v>
-      </c>
       <c r="N26" t="n">
-        <v>2.8333333</v>
+        <v>3.9056604</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.0555556</v>
+        <v>1.1886792</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>0.21938775</v>
+        <v>0.24120604</v>
       </c>
       <c r="U26" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2835821</v>
+        <v>0.28780487</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.36864406</v>
+        <v>0.36401674</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.41293532</v>
+        <v>0.44390243</v>
       </c>
       <c r="K27" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L27" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>6.576923</v>
+        <v>6.923077</v>
       </c>
       <c r="O27" t="n">
         <v>29</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R27" t="n">
         <v>1.6153846</v>
       </c>
       <c r="S27" t="n">
+        <v>26</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.29493088</v>
+      </c>
+      <c r="U27" t="n">
         <v>28</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.30555555</v>
-      </c>
-      <c r="U27" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26395938</v>
+        <v>0.2769231</v>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H28" t="n">
-        <v>0.34080717</v>
+        <v>0.35454544</v>
       </c>
       <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.41538462</v>
+      </c>
+      <c r="K28" t="n">
+        <v>15</v>
+      </c>
+      <c r="L28" t="n">
+        <v>46</v>
+      </c>
+      <c r="M28" t="n">
+        <v>7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.3333333</v>
+      </c>
+      <c r="O28" t="n">
         <v>10</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.39086294</v>
-      </c>
-      <c r="K28" t="n">
-        <v>23</v>
-      </c>
-      <c r="L28" t="n">
-        <v>47</v>
-      </c>
-      <c r="M28" t="n">
-        <v>12</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.075472</v>
-      </c>
-      <c r="O28" t="n">
-        <v>13</v>
       </c>
       <c r="P28" t="n">
         <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1886792</v>
+        <v>1.0185186</v>
       </c>
       <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.23152709</v>
+      </c>
+      <c r="U28" t="n">
         <v>9</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="U28" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2904762</v>
+        <v>0.2780083</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E29" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3617021</v>
+        <v>0.34210527</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>0.47619048</v>
+        <v>0.4647303</v>
       </c>
       <c r="K29" t="n">
         <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="M29" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3333335</v>
+        <v>5.225806</v>
       </c>
       <c r="O29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R29" t="n">
-        <v>1.425926</v>
+        <v>1.3870968</v>
       </c>
       <c r="S29" t="n">
         <v>21</v>
       </c>
       <c r="T29" t="n">
-        <v>0.27906978</v>
+        <v>0.27160493</v>
       </c>
       <c r="U29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.26415095</v>
+        <v>0.25120774</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E30" t="n">
         <v>13</v>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3073593</v>
+        <v>0.29955947</v>
       </c>
       <c r="I30" t="n">
+        <v>20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.4299517</v>
+      </c>
+      <c r="K30" t="n">
+        <v>12</v>
+      </c>
+      <c r="L30" t="n">
+        <v>43</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5.072727</v>
+      </c>
+      <c r="O30" t="n">
         <v>22</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.43867925</v>
-      </c>
-      <c r="K30" t="n">
-        <v>11</v>
-      </c>
-      <c r="L30" t="n">
-        <v>47</v>
-      </c>
-      <c r="M30" t="n">
-        <v>12</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.7454543</v>
-      </c>
-      <c r="O30" t="n">
-        <v>19</v>
       </c>
       <c r="P30" t="n">
         <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R30" t="n">
-        <v>1.6909091</v>
+        <v>1.6545454</v>
       </c>
       <c r="S30" t="n">
         <v>29</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2706422</v>
+        <v>0.25925925</v>
       </c>
       <c r="U30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24378109</v>
+        <v>0.2413793</v>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E31" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.29545453</v>
+      </c>
+      <c r="I31" t="n">
         <v>22</v>
       </c>
-      <c r="F31" t="n">
+      <c r="J31" t="n">
+        <v>0.4729064</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>59</v>
+      </c>
+      <c r="M31" t="n">
+        <v>23</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.1923075</v>
+      </c>
+      <c r="O31" t="n">
+        <v>23</v>
+      </c>
+      <c r="P31" t="n">
         <v>9</v>
       </c>
-      <c r="G31" t="n">
-        <v>9</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.2883721</v>
-      </c>
-      <c r="I31" t="n">
+      <c r="Q31" t="n">
+        <v>18</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4038461</v>
+      </c>
+      <c r="S31" t="n">
+        <v>22</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.28365386</v>
+      </c>
+      <c r="U31" t="n">
         <v>25</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.42288557</v>
-      </c>
-      <c r="K31" t="n">
-        <v>13</v>
-      </c>
-      <c r="L31" t="n">
-        <v>55</v>
-      </c>
-      <c r="M31" t="n">
-        <v>19</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5.7115383</v>
-      </c>
-      <c r="O31" t="n">
-        <v>27</v>
-      </c>
-      <c r="P31" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>28</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.5384616</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.30331755</v>
-      </c>
-      <c r="U31" t="n">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -555,7 +555,7 @@
         <v>346</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>71</v>
@@ -573,7 +573,7 @@
         <v>0.3861498</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
         <v>581</v>
@@ -585,13 +585,13 @@
         <v>4.2853093</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>94</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
         <v>1.2966461</v>
@@ -603,7 +603,7 @@
         <v>0.25074294</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24651504</v>
+        <v>0.2483731</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>106</v>
       </c>
       <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.32873636</v>
+      </c>
+      <c r="I3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.3272609</v>
-      </c>
-      <c r="I3" t="n">
-        <v>7</v>
-      </c>
       <c r="J3" t="n">
-        <v>0.41489363</v>
+        <v>0.41503978</v>
       </c>
       <c r="K3" t="n">
         <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9456067</v>
+        <v>4.958678</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4449093</v>
+        <v>1.439394</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2630819</v>
+        <v>0.26186228</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -701,7 +701,7 @@
         <v>0.3143914</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
         <v>0.4160774</v>
@@ -768,7 +768,7 @@
         <v>0.31954765</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
         <v>0.40247902</v>
@@ -780,7 +780,7 @@
         <v>749</v>
       </c>
       <c r="M5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N5" t="n">
         <v>4.427653</v>
@@ -798,13 +798,13 @@
         <v>1.3821772</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
         <v>0.2556391</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24389313</v>
+        <v>0.24368162</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
         <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3123495</v>
+        <v>0.3125</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3847328</v>
+        <v>0.38438326</v>
       </c>
       <c r="K6" t="n">
         <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>642</v>
+        <v>652</v>
       </c>
       <c r="M6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.8053691</v>
+      </c>
+      <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="N6" t="n">
-        <v>3.8159301</v>
-      </c>
-      <c r="O6" t="n">
-        <v>7</v>
-      </c>
       <c r="P6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2690626</v>
+        <v>1.2684565</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24597701</v>
+        <v>0.24574669</v>
       </c>
       <c r="U6" t="n">
         <v>19</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24414349</v>
+        <v>0.24304803</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -896,46 +896,46 @@
         <v>95</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33830056</v>
+        <v>0.33667397</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4059297</v>
+        <v>0.40339473</v>
       </c>
       <c r="K7" t="n">
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2951665</v>
+        <v>4.2730217</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2402629</v>
+        <v>1.2438686</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23864916</v>
+        <v>0.23853551</v>
       </c>
       <c r="U7" t="n">
         <v>13</v>
@@ -969,7 +969,7 @@
         <v>0.317921</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
         <v>0.40976727</v>
@@ -993,7 +993,7 @@
         <v>89</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
         <v>1.3392091</v>
@@ -1024,7 +1024,7 @@
         <v>331</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
         <v>97</v>
@@ -1042,13 +1042,13 @@
         <v>0.38911974</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>745</v>
       </c>
       <c r="M9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N9" t="n">
         <v>4.512748</v>
@@ -1091,7 +1091,7 @@
         <v>320</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
         <v>75</v>
@@ -1139,7 +1139,7 @@
         <v>0.236724</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1158,7 +1158,7 @@
         <v>369</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
         <v>86</v>
@@ -1176,7 +1176,7 @@
         <v>0.41041514</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>719</v>
@@ -1216,64 +1216,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2352719</v>
+        <v>0.23441583</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3147157</v>
+        <v>0.31336862</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3923716</v>
+        <v>0.39081746</v>
       </c>
       <c r="K12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>689</v>
+        <v>702</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>3.827783</v>
+        <v>3.804603</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2545195</v>
+        <v>1.2456552</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2383655</v>
+        <v>0.23747195</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1283,64 +1283,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24265505</v>
+        <v>0.24175036</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31812298</v>
+        <v>0.3164638</v>
       </c>
       <c r="I13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4099713</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>681</v>
+      </c>
+      <c r="M13" t="n">
+        <v>17</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.7185655</v>
+      </c>
+      <c r="O13" t="n">
+        <v>26</v>
+      </c>
+      <c r="P13" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>26</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3917385</v>
+      </c>
+      <c r="S13" t="n">
+        <v>23</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.24136677</v>
+      </c>
+      <c r="U13" t="n">
         <v>16</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.41167936</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" t="n">
-        <v>674</v>
-      </c>
-      <c r="M13" t="n">
-        <v>18</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.7647057</v>
-      </c>
-      <c r="O13" t="n">
-        <v>27</v>
-      </c>
-      <c r="P13" t="n">
-        <v>105</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4007354</v>
-      </c>
-      <c r="S13" t="n">
-        <v>25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.24227941</v>
-      </c>
-      <c r="U13" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -1350,64 +1350,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24770643</v>
+        <v>0.2455503</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E14" t="n">
         <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3197123</v>
+        <v>0.3175785</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39669725</v>
+        <v>0.3941155</v>
       </c>
       <c r="K14" t="n">
         <v>17</v>
       </c>
       <c r="L14" t="n">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.548162</v>
+        <v>4.659457</v>
       </c>
       <c r="O14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3946022</v>
+        <v>1.4026692</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25441176</v>
+        <v>0.25625226</v>
       </c>
       <c r="U14" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -1426,7 +1426,7 @@
         <v>374</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
         <v>98</v>
@@ -1438,7 +1438,7 @@
         <v>0.31866366</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
         <v>0.39840925</v>
@@ -1456,13 +1456,13 @@
         <v>4.632475</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P15" t="n">
         <v>88</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
         <v>1.4130634</v>
@@ -1474,7 +1474,7 @@
         <v>0.23759124</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1517,7 +1517,7 @@
         <v>644</v>
       </c>
       <c r="M16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N16" t="n">
         <v>3.4017732</v>
@@ -1554,13 +1554,13 @@
         <v>0.24568643</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>349</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
         <v>73</v>
@@ -1578,13 +1578,13 @@
         <v>0.39047262</v>
       </c>
       <c r="K17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17" t="n">
         <v>671</v>
       </c>
       <c r="M17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N17" t="n">
         <v>4.044944</v>
@@ -1596,13 +1596,13 @@
         <v>79</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
         <v>1.252809</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
         <v>0.2288706</v>
@@ -1627,7 +1627,7 @@
         <v>407</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>70</v>
@@ -1639,19 +1639,19 @@
         <v>0.33753315</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0.39132077</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L18" t="n">
         <v>643</v>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
         <v>3.375</v>
@@ -1694,7 +1694,7 @@
         <v>395</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>100</v>
@@ -1718,7 +1718,7 @@
         <v>681</v>
       </c>
       <c r="M19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
         <v>4.8218737</v>
@@ -1752,43 +1752,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23131539</v>
+        <v>0.23130755</v>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E20" t="n">
         <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G20" t="n">
         <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29780033</v>
+        <v>0.29856715</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37630793</v>
+        <v>0.3767956</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2246614</v>
+        <v>4.1662827</v>
       </c>
       <c r="O20" t="n">
         <v>16</v>
@@ -1800,13 +1800,13 @@
         <v>9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2919196</v>
+        <v>1.285122</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23429416</v>
+        <v>0.23332117</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.24438523</v>
+        <v>0.24417731</v>
       </c>
       <c r="C21" t="n">
         <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.329097</v>
+        <v>0.32859972</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.43738103</v>
+        <v>0.43613824</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="M21" t="n">
         <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3365018</v>
+        <v>3.2988722</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.184886</v>
+        <v>1.1856203</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22588055</v>
+        <v>0.22587968</v>
       </c>
       <c r="U21" t="n">
         <v>4</v>
@@ -1886,64 +1886,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23409006</v>
+        <v>0.2355099</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30037</v>
+        <v>0.30218688</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3993301</v>
+        <v>0.40205428</v>
       </c>
       <c r="K22" t="n">
         <v>14</v>
       </c>
       <c r="L22" t="n">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="M22" t="n">
         <v>22</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1246486</v>
+        <v>4.1355853</v>
       </c>
       <c r="O22" t="n">
         <v>15</v>
       </c>
       <c r="P22" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3003749</v>
+        <v>1.2966219</v>
       </c>
       <c r="S22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25617734</v>
+        <v>0.25573888</v>
       </c>
       <c r="U22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25676164</v>
+        <v>0.25668448</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3356755</v>
+        <v>0.33501896</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.41074648</v>
+        <v>0.4114082</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="M23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1190696</v>
+        <v>4.0803857</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P23" t="n">
         <v>77</v>
@@ -2001,13 +2001,13 @@
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2962791</v>
+        <v>1.2967386</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23546726</v>
+        <v>0.23490909</v>
       </c>
       <c r="U23" t="n">
         <v>7</v>
@@ -2029,13 +2029,13 @@
         <v>309</v>
       </c>
       <c r="E24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24" t="n">
         <v>81</v>
       </c>
       <c r="G24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H24" t="n">
         <v>0.29440388</v>
@@ -2053,7 +2053,7 @@
         <v>670</v>
       </c>
       <c r="M24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N24" t="n">
         <v>3.8516405</v>
@@ -2071,7 +2071,7 @@
         <v>1.2910129</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T24" t="n">
         <v>0.24102369</v>
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2569853</v>
+        <v>0.25581396</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30935496</v>
+        <v>0.30864197</v>
       </c>
       <c r="I25" t="n">
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41875</v>
+        <v>0.41860464</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3602486</v>
+        <v>4.4193397</v>
       </c>
       <c r="O25" t="n">
         <v>21</v>
@@ -2132,19 +2132,19 @@
         <v>81</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3745819</v>
+        <v>1.3825471</v>
       </c>
       <c r="S25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24886191</v>
+        <v>0.25074738</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23145732</v>
+        <v>0.23093922</v>
       </c>
       <c r="C26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E26" t="n">
         <v>22</v>
@@ -2172,46 +2172,46 @@
         <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31082425</v>
+        <v>0.31111112</v>
       </c>
       <c r="I26" t="n">
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38613492</v>
+        <v>0.38416207</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6875</v>
+        <v>3.7087913</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1916667</v>
+        <v>1.1909341</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2412769</v>
+        <v>0.2413793</v>
       </c>
       <c r="U26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -2224,7 +2224,7 @@
         <v>0.2486692</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
         <v>359</v>
@@ -2266,7 +2266,7 @@
         <v>89</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R27" t="n">
         <v>1.3473482</v>
@@ -2278,7 +2278,7 @@
         <v>0.2555347</v>
       </c>
       <c r="U27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -2288,64 +2288,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2565099</v>
+        <v>0.25842267</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3349381</v>
+        <v>0.33604613</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.38204432</v>
+        <v>0.38782543</v>
       </c>
       <c r="K28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L28" t="n">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8982558</v>
+        <v>3.8737447</v>
       </c>
       <c r="O28" t="n">
         <v>10</v>
       </c>
       <c r="P28" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2267442</v>
+        <v>1.215208</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23827825</v>
+        <v>0.23612167</v>
       </c>
       <c r="U28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24201427</v>
+        <v>0.24276169</v>
       </c>
       <c r="C29" t="n">
+        <v>18</v>
+      </c>
+      <c r="D29" t="n">
+        <v>325</v>
+      </c>
+      <c r="E29" t="n">
+        <v>26</v>
+      </c>
+      <c r="F29" t="n">
+        <v>86</v>
+      </c>
+      <c r="G29" t="n">
         <v>19</v>
       </c>
-      <c r="D29" t="n">
-        <v>319</v>
-      </c>
-      <c r="E29" t="n">
-        <v>28</v>
-      </c>
-      <c r="F29" t="n">
-        <v>83</v>
-      </c>
-      <c r="G29" t="n">
-        <v>21</v>
-      </c>
       <c r="H29" t="n">
-        <v>0.31746563</v>
+        <v>0.31866315</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3889515</v>
+        <v>0.3912398</v>
       </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="M29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N29" t="n">
-        <v>3.970966</v>
+        <v>3.9840226</v>
       </c>
       <c r="O29" t="n">
         <v>11</v>
       </c>
       <c r="P29" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2508329</v>
+        <v>1.2448308</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23782772</v>
+        <v>0.23731951</v>
       </c>
       <c r="U29" t="n">
         <v>10</v>
@@ -2422,64 +2422,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24925706</v>
+        <v>0.24862285</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G30" t="n">
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31239504</v>
+        <v>0.3112957</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3922734</v>
+        <v>0.39148</v>
       </c>
       <c r="K30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L30" t="n">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1031895</v>
+        <v>4.1269107</v>
       </c>
       <c r="O30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P30" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3100375</v>
+        <v>1.315887</v>
       </c>
       <c r="S30" t="n">
         <v>18</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24161074</v>
+        <v>0.24235727</v>
       </c>
       <c r="U30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2468423</v>
+        <v>0.24652654</v>
       </c>
       <c r="C31" t="n">
         <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32095575</v>
+        <v>0.3202552</v>
       </c>
       <c r="I31" t="n">
         <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42511728</v>
+        <v>0.4235839</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="M31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>4.687586</v>
+        <v>4.7524886</v>
       </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3879981</v>
+        <v>1.395475</v>
       </c>
       <c r="S31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25772098</v>
+        <v>0.2587535</v>
       </c>
       <c r="U31" t="n">
         <v>28</v>
@@ -2803,7 +2803,7 @@
         <v>0.25480768</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>34</v>
@@ -2815,13 +2815,13 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
         <v>0.34177214</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
         <v>0.40865386</v>
@@ -2833,19 +2833,19 @@
         <v>32</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>5.773585</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
         <v>1.6226416</v>
@@ -2857,7 +2857,7 @@
         <v>0.3014354</v>
       </c>
       <c r="U2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -2867,61 +2867,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.19895288</v>
+        <v>0.22613065</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.32900432</v>
+      </c>
+      <c r="I3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.30493274</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19</v>
-      </c>
       <c r="J3" t="n">
-        <v>0.36649215</v>
+        <v>0.36180905</v>
       </c>
       <c r="K3" t="n">
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>5.36646</v>
+        <v>6.3726707</v>
       </c>
       <c r="O3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.416149</v>
+        <v>1.4347826</v>
       </c>
       <c r="S3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26108375</v>
+        <v>0.26341462</v>
       </c>
       <c r="U3" t="n">
         <v>22</v>
@@ -2937,13 +2937,13 @@
         <v>0.20792079</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -2955,7 +2955,7 @@
         <v>0.24413146</v>
       </c>
       <c r="I4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
         <v>0.33663365</v>
@@ -2967,19 +2967,19 @@
         <v>57</v>
       </c>
       <c r="M4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N4" t="n">
         <v>3.8076923</v>
       </c>
       <c r="O4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P4" t="n">
         <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>1.4807693</v>
@@ -2991,7 +2991,7 @@
         <v>0.26130652</v>
       </c>
       <c r="U4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.22821577</v>
+        <v>0.24644549</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>33</v>
@@ -3016,28 +3016,28 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.29166666</v>
+        <v>0.3073593</v>
       </c>
       <c r="I5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
-        <v>0.40248963</v>
+        <v>0.4407583</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="M5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0815217</v>
+        <v>3.0375</v>
       </c>
       <c r="O5" t="n">
         <v>8</v>
@@ -3046,19 +3046,19 @@
         <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1902174</v>
+        <v>1.2375001</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>0.21030043</v>
+        <v>0.21568628</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.23043478</v>
+        <v>0.23913044</v>
       </c>
       <c r="C6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" t="n">
+        <v>31</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.31128404</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.41304347</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L6" t="n">
+        <v>59</v>
+      </c>
+      <c r="M6" t="n">
         <v>21</v>
       </c>
-      <c r="D6" t="n">
-        <v>28</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.29083666</v>
-      </c>
-      <c r="I6" t="n">
-        <v>25</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.42173913</v>
-      </c>
-      <c r="K6" t="n">
-        <v>13</v>
-      </c>
-      <c r="L6" t="n">
-        <v>55</v>
-      </c>
-      <c r="M6" t="n">
-        <v>17</v>
-      </c>
       <c r="N6" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
         <v>1.1333333</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24</v>
+        <v>0.2300885</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2925532</v>
+        <v>0.2711111</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3150,46 +3150,46 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7" t="n">
-        <v>0.40969163</v>
+        <v>0.37969926</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5159575</v>
+        <v>0.46666667</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.418182</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1111112</v>
+        <v>1.1818181</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>0.21212122</v>
+        <v>0.21568628</v>
       </c>
       <c r="U7" t="n">
         <v>5</v>
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20434782</v>
+        <v>0.20707071</v>
       </c>
       <c r="C8" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="n">
         <v>27</v>
       </c>
-      <c r="D8" t="n">
-        <v>24</v>
-      </c>
-      <c r="E8" t="n">
-        <v>23</v>
-      </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>0.26</v>
+        <v>0.26046512</v>
       </c>
       <c r="I8" t="n">
         <v>28</v>
       </c>
       <c r="J8" t="n">
-        <v>0.37826088</v>
+        <v>0.37373737</v>
       </c>
       <c r="K8" t="n">
         <v>24</v>
       </c>
       <c r="L8" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="M8" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.903226</v>
+        <v>3.2264152</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3064516</v>
+        <v>1.3962264</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24034335</v>
+        <v>0.24630542</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -3272,7 +3272,7 @@
         <v>0.2039801</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
         <v>20</v>
@@ -3284,7 +3284,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
         <v>0.2780269</v>
@@ -3302,31 +3302,31 @@
         <v>66</v>
       </c>
       <c r="M9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N9" t="n">
         <v>2.8333333</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
         <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R9" t="n">
         <v>1.2037038</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
         <v>0.21319798</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.21276596</v>
+        <v>0.21287128</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2792793</v>
+      </c>
+      <c r="I10" t="n">
         <v>26</v>
       </c>
-      <c r="E10" t="n">
-        <v>13</v>
-      </c>
-      <c r="F10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>12</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.29545453</v>
-      </c>
-      <c r="I10" t="n">
-        <v>22</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.3531915</v>
+        <v>0.32673267</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L10" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5604396</v>
+        <v>3.832258</v>
       </c>
       <c r="O10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P10" t="n">
         <v>8</v>
       </c>
       <c r="Q10" t="n">
+        <v>16</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.1612903</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.24226804</v>
+      </c>
+      <c r="U10" t="n">
         <v>15</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.2197802</v>
-      </c>
-      <c r="S10" t="n">
-        <v>14</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.23214285</v>
-      </c>
-      <c r="U10" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -3406,7 +3406,7 @@
         <v>0.2857143</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>25</v>
@@ -3418,13 +3418,13 @@
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
         <v>0.3472222</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>0.41836736</v>
@@ -3436,25 +3436,25 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N11" t="n">
         <v>4.1666665</v>
       </c>
       <c r="O11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P11" t="n">
         <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
         <v>1.2777778</v>
       </c>
       <c r="S11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T11" t="n">
         <v>0.25603864</v>
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.26767677</v>
+        <v>0.2532751</v>
       </c>
       <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24</v>
+      </c>
+      <c r="E12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.37554586</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L12" t="n">
+        <v>59</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.8125</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
         <v>10</v>
       </c>
-      <c r="D12" t="n">
+      <c r="Q12" t="n">
         <v>23</v>
       </c>
-      <c r="E12" t="n">
-        <v>24</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>26</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.33027524</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.3939394</v>
-      </c>
-      <c r="K12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M12" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.9454546</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>18</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.90909094</v>
+        <v>0.859375</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.19900498</v>
+        <v>0.19396552</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23880596</v>
+        <v>0.22844827</v>
       </c>
       <c r="C13" t="n">
+        <v>21</v>
+      </c>
+      <c r="D13" t="n">
+        <v>28</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.29571983</v>
+      </c>
+      <c r="I13" t="n">
+        <v>21</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.38793105</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" t="n">
+        <v>59</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.09375</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q13" t="n">
         <v>18</v>
       </c>
-      <c r="D13" t="n">
-        <v>26</v>
-      </c>
-      <c r="E13" t="n">
-        <v>13</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.31555554</v>
-      </c>
-      <c r="I13" t="n">
-        <v>17</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.4079602</v>
-      </c>
-      <c r="K13" t="n">
-        <v>17</v>
-      </c>
-      <c r="L13" t="n">
-        <v>52</v>
-      </c>
-      <c r="M13" t="n">
-        <v>13</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.4363637</v>
-      </c>
-      <c r="O13" t="n">
-        <v>11</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>15</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.1272727</v>
+        <v>1.0625</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23902439</v>
+        <v>0.22881356</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.29032257</v>
+        <v>0.23152709</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.33617023</v>
+        <v>0.2850679</v>
       </c>
       <c r="I14" t="n">
+        <v>25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.44334975</v>
+      </c>
+      <c r="K14" t="n">
         <v>10</v>
       </c>
-      <c r="J14" t="n">
-        <v>0.5529954</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
       <c r="L14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4339623</v>
+        <v>6.923077</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6415094</v>
+        <v>1.6346154</v>
       </c>
       <c r="S14" t="n">
         <v>28</v>
       </c>
       <c r="T14" t="n">
-        <v>0.29807693</v>
+        <v>0.30769232</v>
       </c>
       <c r="U14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2489796</v>
+        <v>0.26511627</v>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>40</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
       </c>
       <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.33195022</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.47906977</v>
+      </c>
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I15" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.4408163</v>
-      </c>
-      <c r="K15" t="n">
-        <v>11</v>
-      </c>
       <c r="L15" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9736843</v>
+        <v>4.879518</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.263158</v>
+        <v>1.2469879</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23206751</v>
+        <v>0.2292683</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -3741,13 +3741,13 @@
         <v>0.26635513</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
@@ -3759,25 +3759,25 @@
         <v>0.3375</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" t="n">
         <v>0.40186915</v>
       </c>
       <c r="K16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L16" t="n">
         <v>57</v>
       </c>
       <c r="M16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
         <v>4.3333335</v>
       </c>
       <c r="O16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P16" t="n">
         <v>9</v>
@@ -3789,13 +3789,13 @@
         <v>1.2777778</v>
       </c>
       <c r="S16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T16" t="n">
         <v>0.22815534</v>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3808,7 +3808,7 @@
         <v>0.25</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -3820,7 +3820,7 @@
         <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H17" t="n">
         <v>0.32692307</v>
@@ -3838,31 +3838,31 @@
         <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
         <v>2.8333333</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
         <v>7</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
         <v>1.1851852</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
         <v>0.24120604</v>
       </c>
       <c r="U17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.23529412</v>
+        <v>0.2451923</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18" t="n">
-        <v>0.31617647</v>
+        <v>0.3073593</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>0.33193278</v>
+        <v>0.34615386</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L18" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="M18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8877006</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
         <v>5</v>
       </c>
-      <c r="P18" t="n">
-        <v>8</v>
-      </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0106952</v>
+        <v>0.90000004</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1891892</v>
+        <v>0.18518518</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.28458497</v>
+        <v>0.27570093</v>
       </c>
       <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>32</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3487395</v>
+      </c>
+      <c r="I19" t="n">
         <v>6</v>
       </c>
-      <c r="D19" t="n">
-        <v>41</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.35357141</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4</v>
-      </c>
       <c r="J19" t="n">
-        <v>0.45454547</v>
+        <v>0.43457943</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>5.225806</v>
+        <v>5.6037736</v>
       </c>
       <c r="O19" t="n">
         <v>24</v>
       </c>
       <c r="P19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6774193</v>
+        <v>1.6981132</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T19" t="n">
-        <v>0.29249012</v>
+        <v>0.29166666</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -4006,43 +4006,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.22660099</v>
+        <v>0.21568628</v>
       </c>
       <c r="C20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>22</v>
+      </c>
+      <c r="E20" t="n">
         <v>23</v>
-      </c>
-      <c r="D20" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" t="n">
-        <v>19</v>
       </c>
       <c r="F20" t="n">
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29910713</v>
+        <v>0.30131003</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>0.44827586</v>
+        <v>0.42647058</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M20" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>7.9615383</v>
+        <v>7.4716983</v>
       </c>
       <c r="O20" t="n">
         <v>30</v>
@@ -4051,19 +4051,19 @@
         <v>11</v>
       </c>
       <c r="Q20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5961539</v>
+        <v>1.5283018</v>
       </c>
       <c r="S20" t="n">
+        <v>26</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.27522936</v>
+      </c>
+      <c r="U20" t="n">
         <v>25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.28372094</v>
-      </c>
-      <c r="U20" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -4073,61 +4073,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.22270742</v>
+        <v>0.22649573</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>0.28225806</v>
+        <v>0.2901961</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3842795</v>
+        <v>0.3803419</v>
       </c>
       <c r="K21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L21" t="n">
         <v>72</v>
       </c>
       <c r="M21" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N21" t="n">
-        <v>3.483871</v>
+        <v>2.8032787</v>
       </c>
       <c r="O21" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1935484</v>
+        <v>1.2622951</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T21" t="n">
-        <v>0.24152543</v>
+        <v>0.24680851</v>
       </c>
       <c r="U21" t="n">
         <v>17</v>
@@ -4140,40 +4140,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.29166666</v>
+        <v>0.3122172</v>
       </c>
       <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>51</v>
+      </c>
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
-        <v>45</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
+        <v>14</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.35983264</v>
+      </c>
+      <c r="I22" t="n">
         <v>3</v>
       </c>
-      <c r="F22" t="n">
-        <v>11</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.33620688</v>
-      </c>
-      <c r="I22" t="n">
-        <v>9</v>
-      </c>
       <c r="J22" t="n">
-        <v>0.5277778</v>
+        <v>0.57466066</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>53</v>
       </c>
       <c r="M22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N22" t="n">
         <v>4.5849056</v>
@@ -4182,22 +4182,22 @@
         <v>19</v>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.264151</v>
+        <v>1.1698114</v>
       </c>
       <c r="S22" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>0.24761905</v>
+        <v>0.23557693</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.28248587</v>
+        <v>0.27751195</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E23" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3227513</v>
+        <v>0.3153153</v>
       </c>
       <c r="I23" t="n">
         <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4463277</v>
+        <v>0.44976076</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="M23" t="n">
+        <v>13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.7692308</v>
+      </c>
+      <c r="O23" t="n">
         <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.139535</v>
-      </c>
-      <c r="O23" t="n">
-        <v>9</v>
       </c>
       <c r="P23" t="n">
         <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1162791</v>
+        <v>1.1538461</v>
       </c>
       <c r="S23" t="n">
         <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23125</v>
+        <v>0.22395833</v>
       </c>
       <c r="U23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -4283,13 +4283,13 @@
         <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F24" t="n">
         <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
         <v>0.3318584</v>
@@ -4301,13 +4301,13 @@
         <v>0.4040404</v>
       </c>
       <c r="K24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L24" t="n">
         <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N24" t="n">
         <v>3.8333333</v>
@@ -4319,19 +4319,19 @@
         <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
         <v>1.2962962</v>
       </c>
       <c r="S24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T24" t="n">
         <v>0.25</v>
       </c>
       <c r="U24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2375</v>
+        <v>0.22395833</v>
       </c>
       <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" t="n">
+        <v>29</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2990654</v>
+      </c>
+      <c r="I25" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="K25" t="n">
         <v>19</v>
       </c>
-      <c r="D25" t="n">
+      <c r="L25" t="n">
+        <v>57</v>
+      </c>
+      <c r="M25" t="n">
+        <v>16</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.5294118</v>
+      </c>
+      <c r="O25" t="n">
         <v>12</v>
-      </c>
-      <c r="E25" t="n">
-        <v>30</v>
-      </c>
-      <c r="F25" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>21</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.30898875</v>
-      </c>
-      <c r="I25" t="n">
-        <v>18</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.3875</v>
-      </c>
-      <c r="K25" t="n">
-        <v>22</v>
-      </c>
-      <c r="L25" t="n">
-        <v>47</v>
-      </c>
-      <c r="M25" t="n">
-        <v>10</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.357143</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0476191</v>
+        <v>1.2156863</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>0.18620689</v>
+        <v>0.22702703</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.16304348</v>
+        <v>0.1657754</v>
       </c>
       <c r="C26" t="n">
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H26" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>0.25543478</v>
+        <v>0.25668448</v>
       </c>
       <c r="K26" t="n">
         <v>30</v>
       </c>
       <c r="L26" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M26" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9056604</v>
+        <v>4.8461537</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1886792</v>
+        <v>1.2692307</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24120604</v>
+        <v>0.2636816</v>
       </c>
       <c r="U26" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.28780487</v>
+        <v>0.27710843</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>0.36401674</v>
+        <v>0.35078534</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>0.44390243</v>
+        <v>0.44578314</v>
       </c>
       <c r="K27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>6.923077</v>
+        <v>5.931818</v>
       </c>
       <c r="O27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q27" t="n">
+        <v>16</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.4772727</v>
+      </c>
+      <c r="S27" t="n">
+        <v>23</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.26857144</v>
+      </c>
+      <c r="U27" t="n">
         <v>24</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.6153846</v>
-      </c>
-      <c r="S27" t="n">
-        <v>26</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.29493088</v>
-      </c>
-      <c r="U27" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2769231</v>
+        <v>0.2948718</v>
       </c>
       <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>36</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
         <v>9</v>
       </c>
-      <c r="D28" t="n">
-        <v>23</v>
-      </c>
-      <c r="E28" t="n">
-        <v>24</v>
-      </c>
-      <c r="F28" t="n">
-        <v>5</v>
-      </c>
       <c r="G28" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.35454544</v>
+        <v>0.36398467</v>
       </c>
       <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.47435898</v>
+      </c>
+      <c r="K28" t="n">
         <v>3</v>
       </c>
-      <c r="J28" t="n">
-        <v>0.41538462</v>
-      </c>
-      <c r="K28" t="n">
-        <v>15</v>
-      </c>
       <c r="L28" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M28" t="n">
         <v>7</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3333333</v>
+        <v>3.142857</v>
       </c>
       <c r="O28" t="n">
         <v>10</v>
       </c>
       <c r="P28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.0185186</v>
+        <v>0.9206349</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23152709</v>
+        <v>0.20779221</v>
       </c>
       <c r="U28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4609,16 +4609,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2780083</v>
+        <v>0.278481</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
@@ -4627,46 +4627,46 @@
         <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.34210527</v>
+        <v>0.3509434</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4647303</v>
+        <v>0.46413502</v>
       </c>
       <c r="K29" t="n">
         <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M29" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>5.225806</v>
+        <v>4.645161</v>
       </c>
       <c r="O29" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3870968</v>
+        <v>1.2419355</v>
       </c>
       <c r="S29" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T29" t="n">
-        <v>0.27160493</v>
+        <v>0.25106382</v>
       </c>
       <c r="U29" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.25120774</v>
+        <v>0.23529412</v>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
         <v>11</v>
       </c>
       <c r="H30" t="n">
-        <v>0.29955947</v>
+        <v>0.2857143</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4299517</v>
+        <v>0.3872549</v>
       </c>
       <c r="K30" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L30" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>5.072727</v>
+        <v>5.5636363</v>
       </c>
       <c r="O30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R30" t="n">
-        <v>1.6545454</v>
+        <v>1.8545455</v>
       </c>
       <c r="S30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>0.25925925</v>
+        <v>0.2798165</v>
       </c>
       <c r="U30" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2413793</v>
+        <v>0.23849373</v>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
         <v>13</v>
-      </c>
-      <c r="F31" t="n">
-        <v>12</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.29545453</v>
+        <v>0.29069766</v>
       </c>
       <c r="I31" t="n">
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4729064</v>
+        <v>0.44769874</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L31" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="M31" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="N31" t="n">
-        <v>5.1923075</v>
+        <v>5.9016395</v>
       </c>
       <c r="O31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4038461</v>
+        <v>1.4918033</v>
       </c>
       <c r="S31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T31" t="n">
-        <v>0.28365386</v>
+        <v>0.29149798</v>
       </c>
       <c r="U31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23899135</v>
+        <v>0.23894463</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
         <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30982113</v>
+        <v>0.30920613</v>
       </c>
       <c r="I2" t="n">
         <v>25</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861498</v>
+        <v>0.3861018</v>
       </c>
       <c r="K2" t="n">
         <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2853093</v>
+        <v>4.3129377</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2966461</v>
+        <v>1.2933209</v>
       </c>
       <c r="S2" t="n">
         <v>16</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25074294</v>
+        <v>0.2501837</v>
       </c>
       <c r="U2" t="n">
         <v>21</v>
@@ -613,16 +613,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2483731</v>
+        <v>0.2487509</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>106</v>
@@ -631,43 +631,43 @@
         <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32873636</v>
+        <v>0.32858047</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.41503978</v>
+        <v>0.4136331</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>4.958678</v>
+        <v>4.934694</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.439394</v>
+        <v>1.4394557</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26186228</v>
+        <v>0.26180407</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25083736</v>
+        <v>0.25055107</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
@@ -698,28 +698,28 @@
         <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3143914</v>
+        <v>0.31374502</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4160774</v>
+        <v>0.4140338</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4247031</v>
+        <v>3.3939962</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
         <v>84</v>
@@ -728,13 +728,13 @@
         <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2114013</v>
+        <v>1.2115384</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22521138</v>
+        <v>0.22513288</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -747,64 +747,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.24061246</v>
+        <v>0.2408075</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>98</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31954765</v>
+        <v>0.32045963</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>0.40247902</v>
+        <v>0.40194663</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="M5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>4.427653</v>
+        <v>4.3856626</v>
       </c>
       <c r="O5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
         <v>93</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3821772</v>
+        <v>1.3720508</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2556391</v>
+        <v>0.25451326</v>
       </c>
       <c r="U5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24368162</v>
+        <v>0.24422073</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E6" t="n">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
         <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3125</v>
+        <v>0.31308725</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38438326</v>
+        <v>0.38590604</v>
       </c>
       <c r="K6" t="n">
         <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8053691</v>
+        <v>3.769522</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
         <v>85</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2684565</v>
+        <v>1.259347</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24574669</v>
+        <v>0.24411215</v>
       </c>
       <c r="U6" t="n">
         <v>19</v>
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24304803</v>
+        <v>0.24168752</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G7" t="n">
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33667397</v>
+        <v>0.33601734</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40339473</v>
+        <v>0.4015016</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="M7" t="n">
         <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2730217</v>
+        <v>4.3002286</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2438686</v>
+        <v>1.2521739</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23853551</v>
+        <v>0.23967849</v>
       </c>
       <c r="U7" t="n">
         <v>13</v>
@@ -948,46 +948,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23693247</v>
+        <v>0.24146982</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.317921</v>
+        <v>0.32228118</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40976727</v>
+        <v>0.41807273</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3349214</v>
+        <v>4.292568</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P8" t="n">
         <v>89</v>
@@ -996,16 +996,16 @@
         <v>14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3392091</v>
+        <v>1.3320789</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24115634</v>
+        <v>0.2400301</v>
       </c>
       <c r="U8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22629392</v>
+        <v>0.22649254</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G9" t="n">
         <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30946806</v>
+        <v>0.30898875</v>
       </c>
       <c r="I9" t="n">
         <v>26</v>
       </c>
       <c r="J9" t="n">
-        <v>0.38911974</v>
+        <v>0.38880596</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="M9" t="n">
         <v>27</v>
       </c>
       <c r="N9" t="n">
-        <v>4.512748</v>
+        <v>4.493706</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4490085</v>
+        <v>1.4461539</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24823223</v>
+        <v>0.2483468</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22761475</v>
+        <v>0.2265625</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E10" t="n">
         <v>28</v>
@@ -1100,43 +1100,43 @@
         <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3126658</v>
+        <v>0.3111257</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36644092</v>
+        <v>0.36421132</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7888112</v>
+        <v>3.7790055</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2545455</v>
+        <v>1.2555249</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.236724</v>
+        <v>0.23631656</v>
       </c>
       <c r="U10" t="n">
         <v>9</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2541879</v>
+        <v>0.2544867</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32352942</v>
+        <v>0.3236715</v>
       </c>
       <c r="I11" t="n">
         <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41041514</v>
+        <v>0.41241923</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.481013</v>
+        <v>5.5125</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q11" t="n">
         <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5147679</v>
+        <v>1.5180556</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2851064</v>
+        <v>0.286014</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,46 +1216,46 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23441583</v>
+        <v>0.23420762</v>
       </c>
       <c r="C12" t="n">
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G12" t="n">
         <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31336862</v>
+        <v>0.31403336</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39081746</v>
+        <v>0.39231622</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L12" t="n">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="M12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.804603</v>
+        <v>3.7569573</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
         <v>81</v>
@@ -1264,16 +1264,16 @@
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2456552</v>
+        <v>1.2397959</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23747195</v>
+        <v>0.2365989</v>
       </c>
       <c r="U12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24175036</v>
+        <v>0.24086556</v>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
         <v>372</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
         <v>108</v>
@@ -1301,46 +1301,46 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3164638</v>
+        <v>0.31537244</v>
       </c>
       <c r="I13" t="n">
         <v>18</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4099713</v>
+        <v>0.40759134</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="M13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7185655</v>
+        <v>4.7647057</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
       </c>
       <c r="P13" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q13" t="n">
         <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3917385</v>
+        <v>1.3942524</v>
       </c>
       <c r="S13" t="n">
         <v>23</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24136677</v>
+        <v>0.24109392</v>
       </c>
       <c r="U13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -1350,64 +1350,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2455503</v>
+        <v>0.24442847</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
         <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3175785</v>
+        <v>0.31656522</v>
       </c>
       <c r="I14" t="n">
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3941155</v>
+        <v>0.39252338</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L14" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>4.659457</v>
+        <v>4.8666363</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4026692</v>
+        <v>1.4283113</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.25625226</v>
+        <v>0.26024956</v>
       </c>
       <c r="U14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -1417,43 +1417,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23933478</v>
+        <v>0.2395573</v>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
         <v>11</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31866366</v>
+        <v>0.31884518</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39840925</v>
+        <v>0.39842913</v>
       </c>
       <c r="K15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.632475</v>
+        <v>4.6737847</v>
       </c>
       <c r="O15" t="n">
         <v>24</v>
@@ -1465,13 +1465,13 @@
         <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4130634</v>
+        <v>1.4120854</v>
       </c>
       <c r="S15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23759124</v>
+        <v>0.23811239</v>
       </c>
       <c r="U15" t="n">
         <v>12</v>
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2617647</v>
+        <v>0.26145455</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34458375</v>
+        <v>0.34435612</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4375</v>
+        <v>0.4367273</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4017732</v>
+        <v>3.4513152</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1003267</v>
+        <v>1.1102908</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21200608</v>
+        <v>0.21240601</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24568643</v>
+        <v>0.24564654</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
         <v>73</v>
@@ -1569,25 +1569,25 @@
         <v>26</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32259136</v>
+        <v>0.32283464</v>
       </c>
       <c r="I17" t="n">
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39047262</v>
+        <v>0.389033</v>
       </c>
       <c r="K17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L17" t="n">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="M17" t="n">
         <v>13</v>
       </c>
       <c r="N17" t="n">
-        <v>4.044944</v>
+        <v>3.9944522</v>
       </c>
       <c r="O17" t="n">
         <v>12</v>
@@ -1599,13 +1599,13 @@
         <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.252809</v>
+        <v>1.2441055</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2288706</v>
+        <v>0.22752497</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2535849</v>
+        <v>0.25456578</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33753315</v>
+        <v>0.33857235</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39132077</v>
+        <v>0.3947074</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L18" t="n">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.375</v>
+        <v>3.357513</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1822519</v>
+        <v>1.1813471</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22036533</v>
+        <v>0.21914648</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24539213</v>
+        <v>0.2468828</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G19" t="n">
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3215434</v>
+        <v>0.32233503</v>
       </c>
       <c r="I19" t="n">
         <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40838453</v>
+        <v>0.41111508</v>
       </c>
       <c r="K19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8218737</v>
+        <v>4.8543468</v>
       </c>
       <c r="O19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P19" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.403784</v>
+        <v>1.4050978</v>
       </c>
       <c r="S19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25591397</v>
+        <v>0.25618374</v>
       </c>
       <c r="U19" t="n">
         <v>26</v>
@@ -1752,16 +1752,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23130755</v>
+        <v>0.23051712</v>
       </c>
       <c r="C20" t="n">
+        <v>27</v>
+      </c>
+      <c r="D20" t="n">
+        <v>329</v>
+      </c>
+      <c r="E20" t="n">
         <v>26</v>
-      </c>
-      <c r="D20" t="n">
-        <v>328</v>
-      </c>
-      <c r="E20" t="n">
-        <v>24</v>
       </c>
       <c r="F20" t="n">
         <v>92</v>
@@ -1770,25 +1770,25 @@
         <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29856715</v>
+        <v>0.29739532</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3767956</v>
+        <v>0.37472686</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="M20" t="n">
         <v>14</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1662827</v>
+        <v>4.1396723</v>
       </c>
       <c r="O20" t="n">
         <v>16</v>
@@ -1800,13 +1800,13 @@
         <v>9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.285122</v>
+        <v>1.2843493</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23332117</v>
+        <v>0.23370543</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.24417731</v>
+        <v>0.24257058</v>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
@@ -1837,43 +1837,43 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.32859972</v>
+        <v>0.3267974</v>
       </c>
       <c r="I21" t="n">
         <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.43613824</v>
+        <v>0.4331352</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="M21" t="n">
         <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2988722</v>
+        <v>3.3373606</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1856203</v>
+        <v>1.1905205</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22587968</v>
+        <v>0.22662678</v>
       </c>
       <c r="U21" t="n">
         <v>4</v>
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2355099</v>
+        <v>0.23586957</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E22" t="n">
         <v>15</v>
@@ -1904,46 +1904,46 @@
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30218688</v>
+        <v>0.30222657</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40205428</v>
+        <v>0.40108696</v>
       </c>
       <c r="K22" t="n">
         <v>14</v>
       </c>
       <c r="L22" t="n">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="M22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1355853</v>
+        <v>4.0968924</v>
       </c>
       <c r="O22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P22" t="n">
         <v>94</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2966219</v>
+        <v>1.2888483</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25573888</v>
+        <v>0.25470024</v>
       </c>
       <c r="U22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25668448</v>
+        <v>0.25669014</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33501896</v>
+        <v>0.33468622</v>
       </c>
       <c r="I23" t="n">
         <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4114082</v>
+        <v>0.41267607</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="M23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N23" t="n">
-        <v>4.0803857</v>
+        <v>4.103902</v>
       </c>
       <c r="O23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2967386</v>
+        <v>1.2944646</v>
       </c>
       <c r="S23" t="n">
         <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23490909</v>
+        <v>0.2349982</v>
       </c>
       <c r="U23" t="n">
         <v>7</v>
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22002329</v>
+        <v>0.22034548</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29440388</v>
+        <v>0.29639795</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.36437717</v>
+        <v>0.36545107</v>
       </c>
       <c r="K24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="M24" t="n">
         <v>12</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8516405</v>
+        <v>3.8154929</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q24" t="n">
         <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2910129</v>
+        <v>1.2901409</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24102369</v>
+        <v>0.24093656</v>
       </c>
       <c r="U24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -2087,46 +2087,46 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25581396</v>
+        <v>0.25538793</v>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
         <v>86</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30864197</v>
+        <v>0.30860534</v>
       </c>
       <c r="I25" t="n">
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41860464</v>
+        <v>0.41774425</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4193397</v>
+        <v>4.4014907</v>
       </c>
       <c r="O25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P25" t="n">
         <v>81</v>
@@ -2135,13 +2135,13 @@
         <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3825471</v>
+        <v>1.3791336</v>
       </c>
       <c r="S25" t="n">
         <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25074738</v>
+        <v>0.25046107</v>
       </c>
       <c r="U25" t="n">
         <v>22</v>
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23093922</v>
+        <v>0.23060109</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E26" t="n">
+        <v>23</v>
+      </c>
+      <c r="F26" t="n">
+        <v>101</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3113695</v>
+      </c>
+      <c r="I26" t="n">
         <v>22</v>
       </c>
-      <c r="F26" t="n">
-        <v>100</v>
-      </c>
-      <c r="G26" t="n">
-        <v>9</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.31111112</v>
-      </c>
-      <c r="I26" t="n">
-        <v>24</v>
-      </c>
       <c r="J26" t="n">
-        <v>0.38416207</v>
+        <v>0.38360655</v>
       </c>
       <c r="K26" t="n">
         <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="M26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>3.7087913</v>
+        <v>3.6757123</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -2202,16 +2202,16 @@
         <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1909341</v>
+        <v>1.1831751</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2413793</v>
+        <v>0.24020319</v>
       </c>
       <c r="U26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -2221,46 +2221,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2486692</v>
+        <v>0.24708538</v>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
         <v>359</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
         <v>88</v>
       </c>
       <c r="G27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3268391</v>
+        <v>0.32535726</v>
       </c>
       <c r="I27" t="n">
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39885932</v>
+        <v>0.39601353</v>
       </c>
       <c r="K27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L27" t="n">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2957478</v>
+        <v>4.291981</v>
       </c>
       <c r="O27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P27" t="n">
         <v>89</v>
@@ -2269,16 +2269,16 @@
         <v>14</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3473482</v>
+        <v>1.3485849</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2555347</v>
+        <v>0.25537434</v>
       </c>
       <c r="U27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -2288,34 +2288,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25842267</v>
+        <v>0.25775927</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33604613</v>
+        <v>0.33534542</v>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.38782543</v>
+        <v>0.38909918</v>
       </c>
       <c r="K28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L28" t="n">
         <v>568</v>
@@ -2324,25 +2324,25 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8737447</v>
+        <v>3.8371105</v>
       </c>
       <c r="O28" t="n">
         <v>10</v>
       </c>
       <c r="P28" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
-        <v>1.215208</v>
+        <v>1.2124646</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23612167</v>
+        <v>0.2361111</v>
       </c>
       <c r="U28" t="n">
         <v>8</v>
@@ -2355,64 +2355,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24276169</v>
+        <v>0.24294613</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31866315</v>
+        <v>0.31885004</v>
       </c>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3912398</v>
+        <v>0.39135215</v>
       </c>
       <c r="K29" t="n">
         <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="M29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9840226</v>
+        <v>3.9842227</v>
       </c>
       <c r="O29" t="n">
         <v>11</v>
       </c>
       <c r="P29" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q29" t="n">
         <v>23</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2448308</v>
+        <v>1.2459397</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23731951</v>
+        <v>0.2375731</v>
       </c>
       <c r="U29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24862285</v>
+        <v>0.24873096</v>
       </c>
       <c r="C30" t="n">
         <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E30" t="n">
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" t="n">
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3112957</v>
+        <v>0.31135172</v>
       </c>
       <c r="I30" t="n">
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>0.39148</v>
+        <v>0.39122552</v>
       </c>
       <c r="K30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L30" t="n">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1269107</v>
+        <v>4.1376944</v>
       </c>
       <c r="O30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P30" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q30" t="n">
         <v>16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.315887</v>
+        <v>1.3161024</v>
       </c>
       <c r="S30" t="n">
         <v>18</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24235727</v>
+        <v>0.24254546</v>
       </c>
       <c r="U30" t="n">
         <v>18</v>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24652654</v>
+        <v>0.24550898</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -2504,31 +2504,31 @@
         <v>109</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3202552</v>
+        <v>0.31859803</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4235839</v>
+        <v>0.42162734</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7524886</v>
+        <v>4.7376904</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P31" t="n">
         <v>119</v>
@@ -2537,16 +2537,16 @@
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.395475</v>
+        <v>1.4006267</v>
       </c>
       <c r="S31" t="n">
         <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2587535</v>
+        <v>0.25874612</v>
       </c>
       <c r="U31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.25480768</v>
+        <v>0.23414634</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -2818,43 +2818,43 @@
         <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>0.34177214</v>
+        <v>0.31601733</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J2" t="n">
-        <v>0.40865386</v>
+        <v>0.3804878</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>5.773585</v>
+        <v>6.0576925</v>
       </c>
       <c r="O2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6226416</v>
+        <v>1.5192307</v>
       </c>
       <c r="S2" t="n">
         <v>27</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3014354</v>
+        <v>0.28780487</v>
       </c>
       <c r="U2" t="n">
         <v>29</v>
@@ -2867,61 +2867,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.22613065</v>
+        <v>0.21717171</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
         <v>30</v>
       </c>
-      <c r="E3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>19</v>
-      </c>
       <c r="H3" t="n">
-        <v>0.32900432</v>
+        <v>0.2972973</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>0.36180905</v>
+        <v>0.28282827</v>
       </c>
       <c r="K3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
         <v>52</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>6.3726707</v>
+        <v>5.126582</v>
       </c>
       <c r="O3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4347826</v>
+        <v>1.4050633</v>
       </c>
       <c r="S3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26341462</v>
+        <v>0.25742576</v>
       </c>
       <c r="U3" t="n">
         <v>22</v>
@@ -2934,43 +2934,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.20792079</v>
+        <v>0.20873787</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>0.24413146</v>
+        <v>0.24657534</v>
       </c>
       <c r="I4" t="n">
         <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>0.33663365</v>
+        <v>0.32038835</v>
       </c>
       <c r="K4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8076923</v>
+        <v>3.6346154</v>
       </c>
       <c r="O4" t="n">
         <v>13</v>
@@ -2979,19 +2979,19 @@
         <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4807693</v>
+        <v>1.4038461</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="T4" t="n">
-        <v>0.26130652</v>
+        <v>0.24615385</v>
       </c>
       <c r="U4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.24644549</v>
+        <v>0.25238097</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3073593</v>
+        <v>0.32765958</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4407583</v>
+        <v>0.43333334</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>3.0375</v>
+        <v>2.347826</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2375001</v>
+        <v>0.9875776000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>0.21568628</v>
+        <v>0.18686868</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3068,16 +3068,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.23913044</v>
+        <v>0.23788546</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
         <v>31</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
@@ -3086,46 +3086,46 @@
         <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31128404</v>
+        <v>0.32170543</v>
       </c>
       <c r="I6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4185022</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1166667</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.23348017</v>
+      </c>
+      <c r="U6" t="n">
         <v>16</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.41304347</v>
-      </c>
-      <c r="K6" t="n">
-        <v>15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>59</v>
-      </c>
-      <c r="M6" t="n">
-        <v>21</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.1333333</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.2300885</v>
-      </c>
-      <c r="U6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2711111</v>
+        <v>0.2200957</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.37969926</v>
+        <v>0.3319838</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.46666667</v>
+        <v>0.41148326</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N7" t="n">
-        <v>4.418182</v>
+        <v>5.1666665</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1818181</v>
+        <v>1.4074074</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T7" t="n">
-        <v>0.21568628</v>
+        <v>0.24390244</v>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20707071</v>
+        <v>0.26666668</v>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3275862</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.47142857</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>52</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.6666667</v>
+      </c>
+      <c r="O8" t="n">
         <v>8</v>
       </c>
-      <c r="G8" t="n">
-        <v>11</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.26046512</v>
-      </c>
-      <c r="I8" t="n">
-        <v>28</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.37373737</v>
-      </c>
-      <c r="K8" t="n">
-        <v>24</v>
-      </c>
-      <c r="L8" t="n">
-        <v>55</v>
-      </c>
-      <c r="M8" t="n">
-        <v>13</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.2264152</v>
-      </c>
-      <c r="O8" t="n">
-        <v>11</v>
-      </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3962264</v>
+        <v>1.3333334</v>
       </c>
       <c r="S8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24630542</v>
+        <v>0.22772278</v>
       </c>
       <c r="U8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2039801</v>
+        <v>0.22167487</v>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2780269</v>
+        <v>0.2907489</v>
       </c>
       <c r="I9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J9" t="n">
-        <v>0.31840795</v>
+        <v>0.3497537</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8333333</v>
+        <v>2.4545455</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
+        <v>15</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.1454545</v>
+      </c>
+      <c r="S9" t="n">
         <v>12</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.2037038</v>
-      </c>
-      <c r="S9" t="n">
-        <v>11</v>
-      </c>
       <c r="T9" t="n">
-        <v>0.21319798</v>
+        <v>0.21393035</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.21287128</v>
+        <v>0.2020202</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2792793</v>
+        <v>0.2739726</v>
       </c>
       <c r="I10" t="n">
         <v>26</v>
       </c>
       <c r="J10" t="n">
-        <v>0.32673267</v>
+        <v>0.2929293</v>
       </c>
       <c r="K10" t="n">
         <v>28</v>
       </c>
       <c r="L10" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="M10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
-        <v>3.832258</v>
+        <v>2.9050634</v>
       </c>
       <c r="O10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1612903</v>
+        <v>1.0822785</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>0.24226804</v>
+        <v>0.21808511</v>
       </c>
       <c r="U10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2857143</v>
+        <v>0.28292683</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.34070796</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.43414634</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>60</v>
+      </c>
+      <c r="M11" t="n">
         <v>19</v>
       </c>
-      <c r="F11" t="n">
+      <c r="N11" t="n">
         <v>5</v>
       </c>
-      <c r="G11" t="n">
+      <c r="O11" t="n">
         <v>22</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.3472222</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.41836736</v>
-      </c>
-      <c r="K11" t="n">
-        <v>14</v>
-      </c>
-      <c r="L11" t="n">
-        <v>54</v>
-      </c>
-      <c r="M11" t="n">
-        <v>12</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.1666665</v>
-      </c>
-      <c r="O11" t="n">
-        <v>16</v>
-      </c>
       <c r="P11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2777778</v>
+        <v>1.425926</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="T11" t="n">
-        <v>0.25603864</v>
+        <v>0.28037384</v>
       </c>
       <c r="U11" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -3470,61 +3470,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2532751</v>
+        <v>0.24669604</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>0.312</v>
+        <v>0.32283464</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>0.37554586</v>
+        <v>0.3876652</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M12" t="n">
         <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8125</v>
+        <v>2.390625</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R12" t="n">
-        <v>0.859375</v>
+        <v>0.8125</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.19396552</v>
+        <v>0.18340611</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.22844827</v>
+        <v>0.20264317</v>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
+        <v>26</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.27091634</v>
+      </c>
+      <c r="I13" t="n">
+        <v>27</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.31277534</v>
+      </c>
+      <c r="K13" t="n">
+        <v>27</v>
+      </c>
+      <c r="L13" t="n">
+        <v>53</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.857143</v>
+      </c>
+      <c r="O13" t="n">
         <v>15</v>
       </c>
-      <c r="F13" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.29571983</v>
-      </c>
-      <c r="I13" t="n">
-        <v>21</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.38793105</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" t="n">
-        <v>59</v>
-      </c>
-      <c r="M13" t="n">
-        <v>21</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.09375</v>
-      </c>
-      <c r="O13" t="n">
-        <v>9</v>
-      </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0625</v>
+        <v>1.1746032</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T13" t="n">
-        <v>0.22881356</v>
+        <v>0.23043478</v>
       </c>
       <c r="U13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.23152709</v>
+        <v>0.20895523</v>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
         <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2850679</v>
+        <v>0.26605505</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>0.44334975</v>
+        <v>0.39800996</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L14" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N14" t="n">
-        <v>6.923077</v>
+        <v>10.058824</v>
       </c>
       <c r="O14" t="n">
+        <v>30</v>
+      </c>
+      <c r="P14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q14" t="n">
         <v>29</v>
       </c>
-      <c r="P14" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>18</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.6346154</v>
+        <v>2.0196078</v>
       </c>
       <c r="S14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>0.30769232</v>
+        <v>0.3542601</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.26511627</v>
+        <v>0.25943395</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
-        <v>0.33195022</v>
+        <v>0.32627118</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>0.47906977</v>
+        <v>0.4198113</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N15" t="n">
-        <v>4.879518</v>
+        <v>4.418182</v>
       </c>
       <c r="O15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2469879</v>
+        <v>1.0909091</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2292683</v>
+        <v>0.22058824</v>
       </c>
       <c r="U15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26635513</v>
+        <v>0.2524272</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
       </c>
       <c r="G16" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.32173914</v>
+      </c>
+      <c r="I16" t="n">
+        <v>14</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.38349515</v>
+      </c>
+      <c r="K16" t="n">
+        <v>22</v>
+      </c>
+      <c r="L16" t="n">
+        <v>50</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.754717</v>
+      </c>
+      <c r="O16" t="n">
+        <v>21</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q16" t="n">
         <v>19</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.3375</v>
-      </c>
-      <c r="I16" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.40186915</v>
-      </c>
-      <c r="K16" t="n">
-        <v>18</v>
-      </c>
-      <c r="L16" t="n">
-        <v>57</v>
-      </c>
-      <c r="M16" t="n">
-        <v>16</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.3333335</v>
-      </c>
-      <c r="O16" t="n">
-        <v>17</v>
-      </c>
-      <c r="P16" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>18</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.2777778</v>
+        <v>1.4339622</v>
       </c>
       <c r="S16" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="T16" t="n">
-        <v>0.22815534</v>
+        <v>0.23267327</v>
       </c>
       <c r="U16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25</v>
+        <v>0.23783784</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.32057416</v>
+      </c>
+      <c r="I17" t="n">
+        <v>16</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.4054054</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13</v>
+      </c>
+      <c r="L17" t="n">
+        <v>43</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.3333333</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>13</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.074074</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.21649484</v>
+      </c>
+      <c r="U17" t="n">
         <v>7</v>
-      </c>
-      <c r="G17" t="n">
-        <v>14</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.32692307</v>
-      </c>
-      <c r="I17" t="n">
-        <v>13</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.4456522</v>
-      </c>
-      <c r="K17" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>47</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.8333333</v>
-      </c>
-      <c r="O17" t="n">
-        <v>6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>15</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.1851852</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.24120604</v>
-      </c>
-      <c r="U17" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -3872,61 +3872,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2451923</v>
+        <v>0.24878049</v>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3073593</v>
+        <v>0.31441048</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>0.34615386</v>
+        <v>0.39512196</v>
       </c>
       <c r="K18" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>2.4846625</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
         <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R18" t="n">
-        <v>0.90000004</v>
+        <v>0.9202454</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.18518518</v>
+        <v>0.16666667</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.27570093</v>
+        <v>0.28636363</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3487395</v>
+        <v>0.34854773</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>0.43457943</v>
+        <v>0.4409091</v>
       </c>
       <c r="K19" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>5.6037736</v>
+        <v>5.7272725</v>
       </c>
       <c r="O19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6981132</v>
+        <v>1.6</v>
       </c>
       <c r="S19" t="n">
         <v>29</v>
       </c>
       <c r="T19" t="n">
-        <v>0.29166666</v>
+        <v>0.27853882</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -4006,16 +4006,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.21568628</v>
+        <v>0.20851064</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" t="n">
         <v>22</v>
-      </c>
-      <c r="E20" t="n">
-        <v>23</v>
       </c>
       <c r="F20" t="n">
         <v>13</v>
@@ -4024,28 +4024,28 @@
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30131003</v>
+        <v>0.28735632</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>0.42647058</v>
+        <v>0.39574468</v>
       </c>
       <c r="K20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L20" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M20" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N20" t="n">
-        <v>7.4716983</v>
+        <v>6.677419</v>
       </c>
       <c r="O20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P20" t="n">
         <v>11</v>
@@ -4054,13 +4054,13 @@
         <v>26</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5283018</v>
+        <v>1.483871</v>
       </c>
       <c r="S20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T20" t="n">
-        <v>0.27522936</v>
+        <v>0.27380952</v>
       </c>
       <c r="U20" t="n">
         <v>25</v>
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.22649573</v>
+        <v>0.20600858</v>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2901961</v>
+        <v>0.26294822</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3803419</v>
+        <v>0.3390558</v>
       </c>
       <c r="K21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L21" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8032787</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2622951</v>
+        <v>1.4166666</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T21" t="n">
-        <v>0.24680851</v>
+        <v>0.2680851</v>
       </c>
       <c r="U21" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -4140,16 +4140,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3122172</v>
+        <v>0.30588236</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>14</v>
@@ -4158,28 +4158,28 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.35983264</v>
+        <v>0.35272726</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>0.57466066</v>
+        <v>0.5411764999999999</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5849056</v>
+        <v>4.064516</v>
       </c>
       <c r="O22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
         <v>11</v>
@@ -4188,16 +4188,16 @@
         <v>26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1698114</v>
+        <v>1.0967742</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>0.23557693</v>
+        <v>0.22594142</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -4207,61 +4207,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.27751195</v>
+        <v>0.2843602</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.32300884</v>
+      </c>
+      <c r="I23" t="n">
         <v>12</v>
       </c>
-      <c r="F23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>22</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.3153153</v>
-      </c>
-      <c r="I23" t="n">
-        <v>14</v>
-      </c>
       <c r="J23" t="n">
-        <v>0.44976076</v>
+        <v>0.47393364</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7692308</v>
+        <v>3.0566037</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P23" t="n">
         <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1538461</v>
+        <v>1.1132076</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T23" t="n">
-        <v>0.22395833</v>
+        <v>0.21649484</v>
       </c>
       <c r="U23" t="n">
         <v>7</v>
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24242425</v>
+        <v>0.23809524</v>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
         <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.35267857</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.38624337</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20</v>
+      </c>
+      <c r="L24" t="n">
+        <v>50</v>
+      </c>
+      <c r="M24" t="n">
         <v>7</v>
       </c>
-      <c r="G24" t="n">
-        <v>14</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.3318584</v>
-      </c>
-      <c r="I24" t="n">
-        <v>11</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.4040404</v>
-      </c>
-      <c r="K24" t="n">
-        <v>17</v>
-      </c>
-      <c r="L24" t="n">
-        <v>56</v>
-      </c>
-      <c r="M24" t="n">
-        <v>15</v>
-      </c>
       <c r="N24" t="n">
-        <v>3.8333333</v>
+        <v>2.6181817</v>
       </c>
       <c r="O24" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="P24" t="n">
         <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2962962</v>
+        <v>1.1454545</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T24" t="n">
-        <v>0.25</v>
+        <v>0.2292683</v>
       </c>
       <c r="U24" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.22395833</v>
+        <v>0.21578947</v>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2990654</v>
+        <v>0.3004695</v>
       </c>
       <c r="I25" t="n">
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>0.390625</v>
+        <v>0.38421053</v>
       </c>
       <c r="K25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L25" t="n">
         <v>57</v>
       </c>
       <c r="M25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5294118</v>
+        <v>3.2884614</v>
       </c>
       <c r="O25" t="n">
         <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2156863</v>
+        <v>1.1346154</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T25" t="n">
-        <v>0.22702703</v>
+        <v>0.21276596</v>
       </c>
       <c r="U25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1657754</v>
+        <v>0.1861702</v>
       </c>
       <c r="C26" t="n">
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
@@ -4423,49 +4423,49 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H26" t="n">
-        <v>0.25</v>
+        <v>0.2748815</v>
       </c>
       <c r="I26" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>0.25668448</v>
+        <v>0.27659574</v>
       </c>
       <c r="K26" t="n">
         <v>30</v>
       </c>
       <c r="L26" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8461537</v>
+        <v>4.1538463</v>
       </c>
       <c r="O26" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2692307</v>
+        <v>1.1730769</v>
       </c>
       <c r="S26" t="n">
+        <v>14</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.23857868</v>
+      </c>
+      <c r="U26" t="n">
         <v>17</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.2636816</v>
-      </c>
-      <c r="U26" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -4475,16 +4475,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.27710843</v>
+        <v>0.25</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -4493,46 +4493,46 @@
         <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>0.35078534</v>
+        <v>0.3262032</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>0.44578314</v>
+        <v>0.40243903</v>
       </c>
       <c r="K27" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>5.931818</v>
+        <v>5.4</v>
       </c>
       <c r="O27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4772727</v>
+        <v>1.4666667</v>
       </c>
       <c r="S27" t="n">
+        <v>24</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.259887</v>
+      </c>
+      <c r="U27" t="n">
         <v>23</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.26857144</v>
-      </c>
-      <c r="U27" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2948718</v>
+        <v>0.2801724</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
@@ -4557,49 +4557,49 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>0.36398467</v>
+        <v>0.35632184</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.47435898</v>
+        <v>0.4698276</v>
       </c>
       <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>48</v>
+      </c>
+      <c r="M28" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" t="n">
         <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>51</v>
-      </c>
-      <c r="M28" t="n">
-        <v>7</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.142857</v>
       </c>
       <c r="O28" t="n">
         <v>10</v>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9206349</v>
+        <v>0.96825397</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0.20779221</v>
+        <v>0.21459228</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.278481</v>
+        <v>0.2638298</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3509434</v>
+        <v>0.33587787</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>0.46413502</v>
+        <v>0.43829787</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>4.645161</v>
+        <v>4.209677</v>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2419355</v>
+        <v>1.2258065</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T29" t="n">
-        <v>0.25106382</v>
+        <v>0.24892704</v>
       </c>
       <c r="U29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
@@ -4676,46 +4676,46 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.23529412</v>
+        <v>0.25120774</v>
       </c>
       <c r="C30" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2857143</v>
+        <v>0.30869564</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3872549</v>
+        <v>0.39613527</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L30" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>5.5636363</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
         <v>10</v>
@@ -4724,16 +4724,16 @@
         <v>23</v>
       </c>
       <c r="R30" t="n">
-        <v>1.8545455</v>
+        <v>1.5178572</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2798165</v>
+        <v>0.24880382</v>
       </c>
       <c r="U30" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.23849373</v>
+        <v>0.23430963</v>
       </c>
       <c r="C31" t="n">
         <v>18</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" t="n">
         <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>0.29069766</v>
+        <v>0.2868217</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>0.44769874</v>
+        <v>0.43096235</v>
       </c>
       <c r="K31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L31" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N31" t="n">
-        <v>5.9016395</v>
+        <v>5.6065574</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
+        <v>23</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.5573771</v>
+      </c>
+      <c r="S31" t="n">
         <v>28</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.4918033</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
       <c r="T31" t="n">
-        <v>0.29149798</v>
+        <v>0.28455284</v>
       </c>
       <c r="U31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23894463</v>
+        <v>0.2387073</v>
       </c>
       <c r="C2" t="n">
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30920613</v>
+        <v>0.3082508</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861018</v>
+        <v>0.38597137</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3129377</v>
+        <v>4.3150115</v>
       </c>
       <c r="O2" t="n">
         <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q2" t="n">
         <v>21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2933209</v>
+        <v>1.295612</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2501837</v>
+        <v>0.25054544</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2487509</v>
+        <v>0.24770643</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E3" t="n">
         <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G3" t="n">
         <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32858047</v>
+        <v>0.3279048</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4136331</v>
+        <v>0.41178545</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>4.934694</v>
+        <v>4.9300137</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
@@ -661,13 +661,13 @@
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4394557</v>
+        <v>1.4374158</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26180407</v>
+        <v>0.26192963</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25055107</v>
+        <v>0.24836363</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>388</v>
@@ -698,43 +698,43 @@
         <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31374502</v>
+        <v>0.3118633</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4140338</v>
+        <v>0.41054547</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3939962</v>
+        <v>3.418831</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q4" t="n">
         <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2115384</v>
+        <v>1.2077922</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22513288</v>
+        <v>0.22501878</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -747,64 +747,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2408075</v>
+        <v>0.24012807</v>
       </c>
       <c r="C5" t="n">
         <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
         <v>98</v>
       </c>
       <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.31957138</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.39950195</v>
+      </c>
+      <c r="K5" t="n">
         <v>13</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.32045963</v>
-      </c>
-      <c r="I5" t="n">
-        <v>13</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.40194663</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
       <c r="L5" t="n">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="M5" t="n">
         <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3856626</v>
+        <v>4.35094</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q5" t="n">
         <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3720508</v>
+        <v>1.3751118</v>
       </c>
       <c r="S5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25451326</v>
+        <v>0.25523013</v>
       </c>
       <c r="U5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -814,64 +814,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24422073</v>
+        <v>0.24401031</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E6" t="n">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
         <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31308725</v>
+        <v>0.3126452</v>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38590604</v>
+        <v>0.38665685</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="M6" t="n">
         <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.769522</v>
+        <v>3.7345793</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="n">
+        <v>10</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.2518692</v>
+      </c>
+      <c r="S6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.259347</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.24411215</v>
+        <v>0.24260356</v>
       </c>
       <c r="U6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24168752</v>
+        <v>0.24196397</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33601734</v>
+        <v>0.33618844</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4015016</v>
+        <v>0.40374425</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3002286</v>
+        <v>4.272152</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2521739</v>
+        <v>1.2450272</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23967849</v>
+        <v>0.23888688</v>
       </c>
       <c r="U7" t="n">
         <v>13</v>
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24146982</v>
+        <v>0.24213254</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
         <v>115</v>
@@ -966,43 +966,43 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32228118</v>
+        <v>0.32218945</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41807273</v>
+        <v>0.4165124</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.292568</v>
+        <v>4.2512774</v>
       </c>
       <c r="O8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P8" t="n">
         <v>89</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3320789</v>
+        <v>1.3279145</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2400301</v>
+        <v>0.23949423</v>
       </c>
       <c r="U8" t="n">
         <v>14</v>
@@ -1015,64 +1015,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22649254</v>
+        <v>0.22725599</v>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="E9" t="n">
         <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30898875</v>
+        <v>0.30984998</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>0.38880596</v>
+        <v>0.39005524</v>
       </c>
       <c r="K9" t="n">
         <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="M9" t="n">
         <v>27</v>
       </c>
       <c r="N9" t="n">
-        <v>4.493706</v>
+        <v>4.512431</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4461539</v>
+        <v>1.4461325</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2483468</v>
+        <v>0.2486408</v>
       </c>
       <c r="U9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2265625</v>
+        <v>0.22655389</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E10" t="n">
         <v>28</v>
@@ -1100,43 +1100,43 @@
         <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3111257</v>
+        <v>0.3102664</v>
       </c>
       <c r="I10" t="n">
         <v>24</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36421132</v>
+        <v>0.3633689</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7790055</v>
+        <v>3.7694407</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2555249</v>
+        <v>1.255116</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23631656</v>
+        <v>0.23613138</v>
       </c>
       <c r="U10" t="n">
         <v>9</v>
@@ -1149,43 +1149,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2544867</v>
+        <v>0.2553116</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E11" t="n">
         <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3236715</v>
+        <v>0.32443598</v>
       </c>
       <c r="I11" t="n">
         <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41241923</v>
+        <v>0.4167847</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5125</v>
+        <v>5.5061727</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
@@ -1194,16 +1194,16 @@
         <v>111</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5180556</v>
+        <v>1.5144033</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.286014</v>
+        <v>0.2859116</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,64 +1216,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23420762</v>
+        <v>0.23488711</v>
       </c>
       <c r="C12" t="n">
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31403336</v>
+        <v>0.31429493</v>
       </c>
       <c r="I12" t="n">
         <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39231622</v>
+        <v>0.39402768</v>
       </c>
       <c r="K12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7569573</v>
+        <v>3.7970684</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2397959</v>
+        <v>1.2478241</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2365989</v>
+        <v>0.23852877</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1283,64 +1283,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24086556</v>
+        <v>0.24265735</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="E13" t="n">
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31537244</v>
+        <v>0.3164478</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40759134</v>
+        <v>0.4090909</v>
       </c>
       <c r="K13" t="n">
         <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="M13" t="n">
         <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7647057</v>
+        <v>4.7675242</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
       </c>
       <c r="P13" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q13" t="n">
         <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3942524</v>
+        <v>1.3948536</v>
       </c>
       <c r="S13" t="n">
         <v>23</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24109392</v>
+        <v>0.24166076</v>
       </c>
       <c r="U13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24442847</v>
+        <v>0.24386775</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E14" t="n">
         <v>19</v>
@@ -1365,31 +1365,31 @@
         <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31656522</v>
+        <v>0.31600633</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39252338</v>
+        <v>0.3910416</v>
       </c>
       <c r="K14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L14" t="n">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="M14" t="n">
         <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8666363</v>
+        <v>4.8361835</v>
       </c>
       <c r="O14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P14" t="n">
         <v>107</v>
@@ -1398,13 +1398,13 @@
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4283113</v>
+        <v>1.4270927</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26024956</v>
+        <v>0.26065516</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2395573</v>
+        <v>0.23994355</v>
       </c>
       <c r="C15" t="n">
         <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
         <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31884518</v>
+        <v>0.3190088</v>
       </c>
       <c r="I15" t="n">
         <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39842913</v>
+        <v>0.39837685</v>
       </c>
       <c r="K15" t="n">
         <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6737847</v>
+        <v>4.629264</v>
       </c>
       <c r="O15" t="n">
         <v>24</v>
       </c>
       <c r="P15" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q15" t="n">
         <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4120854</v>
+        <v>1.408438</v>
       </c>
       <c r="S15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23811239</v>
+        <v>0.23717949</v>
       </c>
       <c r="U15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26145455</v>
+        <v>0.26342162</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34435612</v>
+        <v>0.34596118</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4367273</v>
+        <v>0.4416607</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4513152</v>
+        <v>3.4457612</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1102908</v>
+        <v>1.1144029</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21240601</v>
+        <v>0.212987</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,13 +1551,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24564654</v>
+        <v>0.24716637</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E17" t="n">
         <v>18</v>
@@ -1569,43 +1569,43 @@
         <v>26</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32283464</v>
+        <v>0.32372004</v>
       </c>
       <c r="I17" t="n">
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>0.389033</v>
+        <v>0.39012796</v>
       </c>
       <c r="K17" t="n">
         <v>23</v>
       </c>
       <c r="L17" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="M17" t="n">
         <v>13</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9944522</v>
+        <v>3.9575343</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P17" t="n">
         <v>79</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2441055</v>
+        <v>1.2410959</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22752497</v>
+        <v>0.22733918</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25456578</v>
+        <v>0.2532252</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33857235</v>
+        <v>0.33679092</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3947074</v>
+        <v>0.39329156</v>
       </c>
       <c r="K18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>3.357513</v>
+        <v>3.415814</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1813471</v>
+        <v>1.1860465</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21914648</v>
+        <v>0.21973434</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2468828</v>
+        <v>0.24727401</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
@@ -1703,43 +1703,43 @@
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32233503</v>
+        <v>0.32215607</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>0.41111508</v>
+        <v>0.41083363</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="M19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8543468</v>
+        <v>4.892536</v>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P19" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4050978</v>
+        <v>1.4096223</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25618374</v>
+        <v>0.2569735</v>
       </c>
       <c r="U19" t="n">
         <v>26</v>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23051712</v>
+        <v>0.23082463</v>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E20" t="n">
         <v>26</v>
@@ -1767,46 +1767,46 @@
         <v>92</v>
       </c>
       <c r="G20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29739532</v>
+        <v>0.2980456</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37472686</v>
+        <v>0.37486497</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="M20" t="n">
         <v>14</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1396723</v>
+        <v>4.113708</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P20" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q20" t="n">
         <v>9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2843493</v>
+        <v>1.2795506</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23370543</v>
+        <v>0.23290598</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.24257058</v>
+        <v>0.24108784</v>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3267974</v>
+        <v>0.32535577</v>
       </c>
       <c r="I21" t="n">
         <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4331352</v>
+        <v>0.430724</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="M21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3373606</v>
+        <v>3.3377757</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1905205</v>
+        <v>1.1897979</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22662678</v>
+        <v>0.22661738</v>
       </c>
       <c r="U21" t="n">
         <v>4</v>
@@ -1886,43 +1886,43 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23586957</v>
+        <v>0.2350412</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E22" t="n">
         <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30222657</v>
+        <v>0.30148965</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40108696</v>
+        <v>0.39949837</v>
       </c>
       <c r="K22" t="n">
         <v>14</v>
       </c>
       <c r="L22" t="n">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.0968924</v>
+        <v>4.0768538</v>
       </c>
       <c r="O22" t="n">
         <v>13</v>
@@ -1931,19 +1931,19 @@
         <v>94</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2888483</v>
+        <v>1.2911392</v>
       </c>
       <c r="S22" t="n">
         <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25470024</v>
+        <v>0.25438598</v>
       </c>
       <c r="U22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25669014</v>
+        <v>0.25755996</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G23" t="n">
         <v>11</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33468622</v>
+        <v>0.33508015</v>
       </c>
       <c r="I23" t="n">
         <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.41267607</v>
+        <v>0.41432047</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="M23" t="n">
         <v>28</v>
       </c>
       <c r="N23" t="n">
-        <v>4.103902</v>
+        <v>4.1510534</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P23" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2944646</v>
+        <v>1.2976243</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2349982</v>
+        <v>0.2356281</v>
       </c>
       <c r="U23" t="n">
         <v>7</v>
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22034548</v>
+        <v>0.22083333</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29639795</v>
+        <v>0.29688558</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.36545107</v>
+        <v>0.3655303</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="M24" t="n">
         <v>12</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8154929</v>
+        <v>3.905424</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2901409</v>
+        <v>1.3045897</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24093656</v>
+        <v>0.24331352</v>
       </c>
       <c r="U24" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -2087,46 +2087,46 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25538793</v>
+        <v>0.25497866</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F25" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30860534</v>
+        <v>0.3078681</v>
       </c>
       <c r="I25" t="n">
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41774425</v>
+        <v>0.41820768</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4014907</v>
+        <v>4.346826</v>
       </c>
       <c r="O25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P25" t="n">
         <v>81</v>
@@ -2135,16 +2135,16 @@
         <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3791336</v>
+        <v>1.3675252</v>
       </c>
       <c r="S25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25046107</v>
+        <v>0.24826579</v>
       </c>
       <c r="U25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23060109</v>
+        <v>0.23049262</v>
       </c>
       <c r="C26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3113695</v>
+        <v>0.31144404</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38360655</v>
+        <v>0.38295576</v>
       </c>
       <c r="K26" t="n">
         <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="M26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6757123</v>
+        <v>3.6845639</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -2199,16 +2199,16 @@
         <v>79</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1831751</v>
+        <v>1.181208</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24020319</v>
+        <v>0.24040186</v>
       </c>
       <c r="U26" t="n">
         <v>15</v>
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24708538</v>
+        <v>0.24665676</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F27" t="n">
         <v>88</v>
       </c>
       <c r="G27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32535726</v>
+        <v>0.32479474</v>
       </c>
       <c r="I27" t="n">
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39601353</v>
+        <v>0.39375928</v>
       </c>
       <c r="K27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L27" t="n">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.291981</v>
+        <v>4.3008847</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P27" t="n">
         <v>89</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3485849</v>
+        <v>1.352585</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25537434</v>
+        <v>0.25676665</v>
       </c>
       <c r="U27" t="n">
         <v>25</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25775927</v>
+        <v>0.25842696</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G28" t="n">
         <v>29</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33534542</v>
+        <v>0.33598673</v>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.38909918</v>
+        <v>0.39101124</v>
       </c>
       <c r="K28" t="n">
         <v>22</v>
       </c>
       <c r="L28" t="n">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8371105</v>
+        <v>3.813986</v>
       </c>
       <c r="O28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P28" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2124646</v>
+        <v>1.206993</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2361111</v>
+        <v>0.23590505</v>
       </c>
       <c r="U28" t="n">
         <v>8</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24294613</v>
+        <v>0.24358511</v>
       </c>
       <c r="C29" t="n">
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31885004</v>
+        <v>0.31980675</v>
       </c>
       <c r="I29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39135215</v>
+        <v>0.39176002</v>
       </c>
       <c r="K29" t="n">
         <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>688</v>
+        <v>701</v>
       </c>
       <c r="M29" t="n">
         <v>17</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9842227</v>
+        <v>3.984418</v>
       </c>
       <c r="O29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q29" t="n">
         <v>23</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2459397</v>
+        <v>1.2456462</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2375731</v>
+        <v>0.23800938</v>
       </c>
       <c r="U29" t="n">
         <v>11</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24873096</v>
+        <v>0.2490161</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G30" t="n">
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31135172</v>
+        <v>0.3110823</v>
       </c>
       <c r="I30" t="n">
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>0.39122552</v>
+        <v>0.3921288</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L30" t="n">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1376944</v>
+        <v>4.1726165</v>
       </c>
       <c r="O30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q30" t="n">
         <v>16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3161024</v>
+        <v>1.3230908</v>
       </c>
       <c r="S30" t="n">
         <v>18</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24254546</v>
+        <v>0.24318507</v>
       </c>
       <c r="U30" t="n">
         <v>18</v>
@@ -2489,43 +2489,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24550898</v>
+        <v>0.24600972</v>
       </c>
       <c r="C31" t="n">
         <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G31" t="n">
         <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>0.31859803</v>
+        <v>0.31870526</v>
       </c>
       <c r="I31" t="n">
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42162734</v>
+        <v>0.42158222</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="M31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7376904</v>
+        <v>4.6987634</v>
       </c>
       <c r="O31" t="n">
         <v>25</v>
@@ -2537,13 +2537,13 @@
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4006267</v>
+        <v>1.396643</v>
       </c>
       <c r="S31" t="n">
         <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25874612</v>
+        <v>0.25820795</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,34 +2800,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23414634</v>
+        <v>0.23267327</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
       </c>
       <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.29411766</v>
+      </c>
+      <c r="I2" t="n">
         <v>22</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.31601733</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17</v>
-      </c>
       <c r="J2" t="n">
-        <v>0.3804878</v>
+        <v>0.38118812</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
         <v>28</v>
@@ -2836,28 +2836,28 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>6.0576925</v>
+        <v>4.0588236</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5192307</v>
+        <v>1.254902</v>
       </c>
       <c r="S2" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T2" t="n">
-        <v>0.28780487</v>
+        <v>0.2513369</v>
       </c>
       <c r="U2" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -2873,58 +2873,58 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.30357143</v>
+      </c>
+      <c r="I3" t="n">
         <v>18</v>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.2972973</v>
-      </c>
-      <c r="I3" t="n">
-        <v>21</v>
-      </c>
       <c r="J3" t="n">
-        <v>0.28282827</v>
+        <v>0.28787878</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L3" t="n">
         <v>52</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>5.126582</v>
+        <v>4.8774195</v>
       </c>
       <c r="O3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4050633</v>
+        <v>1.316129</v>
       </c>
       <c r="S3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T3" t="n">
-        <v>0.25742576</v>
+        <v>0.25</v>
       </c>
       <c r="U3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.20873787</v>
+        <v>0.18719211</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>0.24657534</v>
+        <v>0.23744293</v>
       </c>
       <c r="I4" t="n">
         <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>0.32038835</v>
+        <v>0.27093595</v>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6346154</v>
+        <v>4.4117646</v>
       </c>
       <c r="O4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4038461</v>
+        <v>1.3921568</v>
       </c>
       <c r="S4" t="n">
+        <v>23</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.24338624</v>
+      </c>
+      <c r="U4" t="n">
         <v>18</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.24615385</v>
-      </c>
-      <c r="U4" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.25238097</v>
+        <v>0.2488263</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32765958</v>
+        <v>0.3206751</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.43333334</v>
+        <v>0.42723006</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>2.347826</v>
+        <v>2.4695122</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9875776000000001</v>
+        <v>1.1341463</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>0.18686868</v>
+        <v>0.21904762</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3068,61 +3068,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.23788546</v>
+        <v>0.24336283</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.31889763</v>
+      </c>
+      <c r="I6" t="n">
         <v>14</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.32170543</v>
-      </c>
-      <c r="I6" t="n">
-        <v>15</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.4185022</v>
+        <v>0.44247788</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
         <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1166667</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>0.23348017</v>
+        <v>0.23684211</v>
       </c>
       <c r="U6" t="n">
         <v>16</v>
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2200957</v>
+        <v>0.22222222</v>
       </c>
       <c r="C7" t="n">
         <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3319838</v>
+        <v>0.3251029</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41148326</v>
+        <v>0.4347826</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N7" t="n">
-        <v>5.1666665</v>
+        <v>4.1666665</v>
       </c>
       <c r="O7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4074074</v>
+        <v>1.3333334</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24390244</v>
+        <v>0.23</v>
       </c>
       <c r="U7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.26666668</v>
+        <v>0.29107982</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3275862</v>
+        <v>0.33766234</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.47142857</v>
+        <v>0.4741784</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6666667</v>
+        <v>2.290909</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3333334</v>
+        <v>1.2545455</v>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T8" t="n">
-        <v>0.22772278</v>
+        <v>0.22277227</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22167487</v>
+        <v>0.20408164</v>
       </c>
       <c r="C9" t="n">
+        <v>26</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" t="n">
         <v>20</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2850679</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.32142857</v>
+      </c>
+      <c r="K9" t="n">
         <v>26</v>
       </c>
-      <c r="E9" t="n">
-        <v>19</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>27</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.2907489</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
+        <v>61</v>
+      </c>
+      <c r="M9" t="n">
         <v>22</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.3497537</v>
-      </c>
-      <c r="K9" t="n">
-        <v>24</v>
-      </c>
-      <c r="L9" t="n">
-        <v>62</v>
-      </c>
-      <c r="M9" t="n">
-        <v>23</v>
-      </c>
       <c r="N9" t="n">
-        <v>2.4545455</v>
+        <v>3.1090908</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1454545</v>
+        <v>1.1818181</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>0.21393035</v>
+        <v>0.22167487</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2020202</v>
+        <v>0.1897436</v>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2739726</v>
+        <v>0.26046512</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2929293</v>
+        <v>0.24615385</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M10" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9050634</v>
+        <v>3.2468355</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
         <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0822785</v>
+        <v>1.1772152</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.21808511</v>
+        <v>0.22797927</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.28292683</v>
+        <v>0.30092594</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34070796</v>
+        <v>0.3516949</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.43414634</v>
+        <v>0.49537036</v>
       </c>
       <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>54</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.6666665</v>
+      </c>
+      <c r="O11" t="n">
+        <v>28</v>
+      </c>
+      <c r="P11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" t="n">
-        <v>60</v>
-      </c>
-      <c r="M11" t="n">
-        <v>19</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8</v>
-      </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>1.425926</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28037384</v>
+        <v>0.29357797</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24669604</v>
+        <v>0.25531915</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>0.32283464</v>
+        <v>0.32307693</v>
       </c>
       <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.41276595</v>
+      </c>
+      <c r="K12" t="n">
         <v>13</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.3876652</v>
-      </c>
-      <c r="K12" t="n">
-        <v>19</v>
-      </c>
       <c r="L12" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>2.390625</v>
+        <v>3.234375</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
         <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8125</v>
+        <v>0.953125</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0.18340611</v>
+        <v>0.22175732</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.20264317</v>
+        <v>0.23628692</v>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>17</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.30152673</v>
+      </c>
+      <c r="I13" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.36708862</v>
+      </c>
+      <c r="K13" t="n">
+        <v>24</v>
+      </c>
+      <c r="L13" t="n">
+        <v>47</v>
+      </c>
+      <c r="M13" t="n">
         <v>6</v>
       </c>
-      <c r="G13" t="n">
-        <v>16</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.27091634</v>
-      </c>
-      <c r="I13" t="n">
-        <v>27</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.31277534</v>
-      </c>
-      <c r="K13" t="n">
-        <v>27</v>
-      </c>
-      <c r="L13" t="n">
-        <v>53</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>3.4285715</v>
+      </c>
+      <c r="O13" t="n">
         <v>12</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.857143</v>
-      </c>
-      <c r="O13" t="n">
-        <v>15</v>
-      </c>
       <c r="P13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
         <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1746032</v>
+        <v>1.2222222</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23043478</v>
+        <v>0.22978723</v>
       </c>
       <c r="U13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -3604,43 +3604,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.20895523</v>
+        <v>0.20689656</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>0.26605505</v>
+        <v>0.26587301</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39800996</v>
+        <v>0.37931034</v>
       </c>
       <c r="K14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L14" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M14" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N14" t="n">
-        <v>10.058824</v>
+        <v>8.949438000000001</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
@@ -3649,16 +3649,16 @@
         <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0196078</v>
+        <v>1.9213483</v>
       </c>
       <c r="S14" t="n">
         <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3542601</v>
+        <v>0.3463035</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
@@ -3671,55 +3671,55 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.25943395</v>
+        <v>0.2524272</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>17</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.32017544</v>
+      </c>
+      <c r="I15" t="n">
+        <v>13</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.39320388</v>
+      </c>
+      <c r="K15" t="n">
+        <v>17</v>
+      </c>
+      <c r="L15" t="n">
+        <v>66</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.7454543</v>
+      </c>
+      <c r="O15" t="n">
+        <v>23</v>
+      </c>
+      <c r="P15" t="n">
         <v>6</v>
-      </c>
-      <c r="F15" t="n">
-        <v>8</v>
-      </c>
-      <c r="G15" t="n">
-        <v>8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.32627118</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.4198113</v>
-      </c>
-      <c r="K15" t="n">
-        <v>10</v>
-      </c>
-      <c r="L15" t="n">
-        <v>65</v>
-      </c>
-      <c r="M15" t="n">
-        <v>27</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.418182</v>
-      </c>
-      <c r="O15" t="n">
-        <v>19</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5</v>
       </c>
       <c r="Q15" t="n">
         <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0909091</v>
+        <v>1.1454545</v>
       </c>
       <c r="S15" t="n">
         <v>7</v>
@@ -3728,7 +3728,7 @@
         <v>0.22058824</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2524272</v>
+        <v>0.29680365</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3632653</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.47945204</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>47</v>
+      </c>
+      <c r="M16" t="n">
         <v>6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>16</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.32173914</v>
-      </c>
-      <c r="I16" t="n">
-        <v>14</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.38349515</v>
-      </c>
-      <c r="K16" t="n">
-        <v>22</v>
-      </c>
-      <c r="L16" t="n">
-        <v>50</v>
-      </c>
-      <c r="M16" t="n">
-        <v>7</v>
       </c>
       <c r="N16" t="n">
         <v>4.754717</v>
       </c>
       <c r="O16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4339622</v>
+        <v>1.4716982</v>
       </c>
       <c r="S16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T16" t="n">
-        <v>0.23267327</v>
+        <v>0.2413793</v>
       </c>
       <c r="U16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.23783784</v>
+        <v>0.265625</v>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
         <v>21</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>16</v>
       </c>
       <c r="H17" t="n">
         <v>0.32057416</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4054054</v>
+        <v>0.42708334</v>
       </c>
       <c r="K17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.3333333</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.074074</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>0.21649484</v>
+        <v>0.20418848</v>
       </c>
       <c r="U17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -3872,61 +3872,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.24878049</v>
+        <v>0.23383084</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>0.31441048</v>
+        <v>0.30357143</v>
       </c>
       <c r="I18" t="n">
         <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39512196</v>
+        <v>0.40298507</v>
       </c>
       <c r="K18" t="n">
+        <v>14</v>
+      </c>
+      <c r="L18" t="n">
+        <v>55</v>
+      </c>
+      <c r="M18" t="n">
         <v>18</v>
       </c>
-      <c r="L18" t="n">
-        <v>60</v>
-      </c>
-      <c r="M18" t="n">
-        <v>19</v>
-      </c>
       <c r="N18" t="n">
-        <v>2.4846625</v>
+        <v>3.1090908</v>
       </c>
       <c r="O18" t="n">
+        <v>7</v>
+      </c>
+      <c r="P18" t="n">
         <v>6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>8</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9202454</v>
+        <v>1.0545454</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>0.16666667</v>
+        <v>0.17989418</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.28636363</v>
+        <v>0.25238097</v>
       </c>
       <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>21</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.30396476</v>
+      </c>
+      <c r="I19" t="n">
+        <v>17</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3809524</v>
+      </c>
+      <c r="K19" t="n">
+        <v>19</v>
+      </c>
+      <c r="L19" t="n">
+        <v>37</v>
+      </c>
+      <c r="M19" t="n">
         <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" t="n">
-        <v>16</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.34854773</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.4409091</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>36</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3</v>
       </c>
       <c r="N19" t="n">
         <v>5.7272725</v>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6</v>
+        <v>1.6181818</v>
       </c>
       <c r="S19" t="n">
         <v>29</v>
       </c>
       <c r="T19" t="n">
-        <v>0.27853882</v>
+        <v>0.2927928</v>
       </c>
       <c r="U19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.20851064</v>
+        <v>0.21212122</v>
       </c>
       <c r="C20" t="n">
+        <v>23</v>
+      </c>
+      <c r="D20" t="n">
         <v>26</v>
       </c>
-      <c r="D20" t="n">
-        <v>23</v>
-      </c>
       <c r="E20" t="n">
+        <v>17</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.30152673</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.3939394</v>
+      </c>
+      <c r="K20" t="n">
+        <v>16</v>
+      </c>
+      <c r="L20" t="n">
+        <v>65</v>
+      </c>
+      <c r="M20" t="n">
+        <v>24</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.714286</v>
+      </c>
+      <c r="O20" t="n">
         <v>22</v>
       </c>
-      <c r="F20" t="n">
-        <v>13</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.28735632</v>
-      </c>
-      <c r="I20" t="n">
-        <v>23</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.39574468</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="P20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q20" t="n">
         <v>17</v>
       </c>
-      <c r="L20" t="n">
-        <v>64</v>
-      </c>
-      <c r="M20" t="n">
-        <v>26</v>
-      </c>
-      <c r="N20" t="n">
-        <v>6.677419</v>
-      </c>
-      <c r="O20" t="n">
-        <v>29</v>
-      </c>
-      <c r="P20" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>26</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.483871</v>
+        <v>1.3015873</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T20" t="n">
-        <v>0.27380952</v>
+        <v>0.23553719</v>
       </c>
       <c r="U20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.20600858</v>
+        <v>0.18942732</v>
       </c>
       <c r="C21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D21" t="n">
+        <v>17</v>
+      </c>
+      <c r="E21" t="n">
         <v>27</v>
-      </c>
-      <c r="D21" t="n">
-        <v>18</v>
-      </c>
-      <c r="E21" t="n">
-        <v>28</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H21" t="n">
-        <v>0.26294822</v>
+        <v>0.2489796</v>
       </c>
       <c r="I21" t="n">
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3390558</v>
+        <v>0.32599118</v>
       </c>
       <c r="K21" t="n">
         <v>25</v>
       </c>
       <c r="L21" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M21" t="n">
         <v>29</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>3.3559322</v>
       </c>
       <c r="O21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q21" t="n">
         <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4166666</v>
+        <v>1.2881356</v>
       </c>
       <c r="S21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2680851</v>
+        <v>0.24553572</v>
       </c>
       <c r="U21" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.30588236</v>
+        <v>0.26938775</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.35272726</v>
+        <v>0.3258427</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5411764999999999</v>
+        <v>0.4489796</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N22" t="n">
-        <v>4.064516</v>
+        <v>3.9836066</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0967742</v>
+        <v>1.1639345</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>0.22594142</v>
+        <v>0.22553192</v>
       </c>
       <c r="U22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2843602</v>
+        <v>0.30555555</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9</v>
+      </c>
+      <c r="G23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" t="n">
-        <v>8</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.32300884</v>
+        <v>0.34334764</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>0.47393364</v>
+        <v>0.5046296</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M23" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
-        <v>3.0566037</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
         <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1132076</v>
+        <v>1.2037038</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>0.21649484</v>
+        <v>0.23267327</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23809524</v>
+        <v>0.24064171</v>
       </c>
       <c r="C24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H24" t="n">
-        <v>0.35267857</v>
+        <v>0.3529412</v>
       </c>
       <c r="I24" t="n">
         <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38624337</v>
+        <v>0.37967914</v>
       </c>
       <c r="K24" t="n">
         <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M24" t="n">
+        <v>6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>14</v>
+      </c>
+      <c r="P24" t="n">
         <v>7</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.6181817</v>
-      </c>
-      <c r="O24" t="n">
-        <v>7</v>
-      </c>
-      <c r="P24" t="n">
-        <v>5</v>
-      </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1454545</v>
+        <v>1.3888888</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2292683</v>
+        <v>0.2606635</v>
       </c>
       <c r="U24" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.21578947</v>
+        <v>0.2032967</v>
       </c>
       <c r="C25" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3004695</v>
+        <v>0.28431374</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>0.38421053</v>
+        <v>0.37362638</v>
       </c>
       <c r="K25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L25" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M25" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2884614</v>
+        <v>2.54717</v>
       </c>
       <c r="O25" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1346154</v>
+        <v>0.9811321</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>0.21276596</v>
+        <v>0.18716578</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1861702</v>
+        <v>0.20918368</v>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
+        <v>21</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.29223743</v>
+      </c>
+      <c r="I26" t="n">
+        <v>23</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.31632653</v>
+      </c>
+      <c r="K26" t="n">
         <v>27</v>
       </c>
-      <c r="H26" t="n">
-        <v>0.2748815</v>
-      </c>
-      <c r="I26" t="n">
-        <v>25</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.27659574</v>
-      </c>
-      <c r="K26" t="n">
-        <v>30</v>
-      </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1538463</v>
+        <v>4.0588236</v>
       </c>
       <c r="O26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1730769</v>
+        <v>1.1568627</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23857868</v>
+        <v>0.25</v>
       </c>
       <c r="U26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.25</v>
+        <v>0.24365482</v>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3262032</v>
+        <v>0.31838566</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J27" t="n">
-        <v>0.40243903</v>
+        <v>0.37055838</v>
       </c>
       <c r="K27" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="L27" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>5.4</v>
+        <v>5.3333335</v>
       </c>
       <c r="O27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P27" t="n">
         <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4666667</v>
+        <v>1.5</v>
       </c>
       <c r="S27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T27" t="n">
-        <v>0.259887</v>
+        <v>0.2769953</v>
       </c>
       <c r="U27" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2801724</v>
+        <v>0.2819383</v>
       </c>
       <c r="C28" t="n">
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.35177866</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.50220263</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>45</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.7142856</v>
+      </c>
+      <c r="O28" t="n">
         <v>6</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.35632184</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="P28" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>17</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.9206349</v>
+      </c>
+      <c r="S28" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="n">
-        <v>0.4698276</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="T28" t="n">
+        <v>0.20524018</v>
+      </c>
+      <c r="U28" t="n">
         <v>4</v>
-      </c>
-      <c r="L28" t="n">
-        <v>48</v>
-      </c>
-      <c r="M28" t="n">
-        <v>5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>10</v>
-      </c>
-      <c r="P28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>22</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.96825397</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.21459228</v>
-      </c>
-      <c r="U28" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2638298</v>
+        <v>0.27234042</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.33587787</v>
+        <v>0.35338345</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0.43829787</v>
+        <v>0.44680852</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M29" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N29" t="n">
-        <v>4.209677</v>
+        <v>4.2786884</v>
       </c>
       <c r="O29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2258065</v>
+        <v>1.2131147</v>
       </c>
       <c r="S29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24892704</v>
+        <v>0.2532189</v>
       </c>
       <c r="U29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.25120774</v>
+        <v>0.25358853</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30869564</v>
+        <v>0.3073593</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>0.39613527</v>
+        <v>0.40191388</v>
       </c>
       <c r="K30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L30" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5</v>
+        <v>4.660714</v>
       </c>
       <c r="O30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5178572</v>
+        <v>1.5357143</v>
       </c>
       <c r="S30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24880382</v>
+        <v>0.25592417</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.23430963</v>
+        <v>0.23577236</v>
       </c>
       <c r="C31" t="n">
         <v>18</v>
@@ -4752,55 +4752,55 @@
         <v>30</v>
       </c>
       <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="n">
         <v>10</v>
       </c>
-      <c r="F31" t="n">
-        <v>11</v>
-      </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2868217</v>
+        <v>0.29213482</v>
       </c>
       <c r="I31" t="n">
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>0.43096235</v>
+        <v>0.41869918</v>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L31" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M31" t="n">
         <v>30</v>
       </c>
       <c r="N31" t="n">
-        <v>5.6065574</v>
+        <v>5.370968</v>
       </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
         <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5573771</v>
+        <v>1.451613</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.28455284</v>
+        <v>0.272</v>
       </c>
       <c r="U31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2387073</v>
+        <v>0.23774955</v>
       </c>
       <c r="C2" t="n">
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G2" t="n">
         <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3082508</v>
+        <v>0.30734095</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38597137</v>
+        <v>0.384755</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3150115</v>
+        <v>4.3293743</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.295612</v>
+        <v>1.2978529</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25054544</v>
+        <v>0.25134844</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24770643</v>
+        <v>0.24703419</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E3" t="n">
         <v>11</v>
@@ -631,43 +631,43 @@
         <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3279048</v>
+        <v>0.32703623</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.41178545</v>
+        <v>0.40928122</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9300137</v>
+        <v>4.9254327</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4374158</v>
+        <v>1.4327563</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26192963</v>
+        <v>0.26163393</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,46 +680,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24836363</v>
+        <v>0.24757455</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>103</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3118633</v>
+        <v>0.31059128</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41054547</v>
+        <v>0.40855193</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.418831</v>
+        <v>3.4059634</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
         <v>86</v>
@@ -728,13 +728,13 @@
         <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2077922</v>
+        <v>1.2110091</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22501878</v>
+        <v>0.2260579</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.24012807</v>
+        <v>0.23926812</v>
       </c>
       <c r="C5" t="n">
         <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E5" t="n">
         <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31957138</v>
+        <v>0.31889027</v>
       </c>
       <c r="I5" t="n">
         <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39950195</v>
+        <v>0.39901477</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="M5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.35094</v>
+        <v>4.3586907</v>
       </c>
       <c r="O5" t="n">
         <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3751118</v>
+        <v>1.3746129</v>
       </c>
       <c r="S5" t="n">
         <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25523013</v>
+        <v>0.25473973</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24401031</v>
+        <v>0.24335155</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E6" t="n">
         <v>29</v>
@@ -829,31 +829,31 @@
         <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3126452</v>
+        <v>0.31213114</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38665685</v>
+        <v>0.38469946</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="M6" t="n">
         <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7345793</v>
+        <v>3.6953917</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
         <v>86</v>
@@ -862,16 +862,16 @@
         <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2518692</v>
+        <v>1.2414747</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24260356</v>
+        <v>0.24068663</v>
       </c>
       <c r="U6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24196397</v>
+        <v>0.24048866</v>
       </c>
       <c r="C7" t="n">
         <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -896,46 +896,46 @@
         <v>99</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33618844</v>
+        <v>0.33534744</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40374425</v>
+        <v>0.40069807</v>
       </c>
       <c r="K7" t="n">
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="M7" t="n">
+        <v>19</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.2390723</v>
+      </c>
+      <c r="O7" t="n">
         <v>17</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.272152</v>
-      </c>
-      <c r="O7" t="n">
-        <v>18</v>
-      </c>
       <c r="P7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2450272</v>
+        <v>1.2471008</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23888688</v>
+        <v>0.23921569</v>
       </c>
       <c r="U7" t="n">
         <v>13</v>
@@ -948,46 +948,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24213254</v>
+        <v>0.24185877</v>
       </c>
       <c r="C8" t="n">
         <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E8" t="n">
         <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32218945</v>
+        <v>0.32221502</v>
       </c>
       <c r="I8" t="n">
         <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4165124</v>
+        <v>0.41566044</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2512774</v>
+        <v>4.248165</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P8" t="n">
         <v>89</v>
@@ -996,13 +996,13 @@
         <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3279145</v>
+        <v>1.3293577</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23949423</v>
+        <v>0.2402788</v>
       </c>
       <c r="U8" t="n">
         <v>14</v>
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22725599</v>
+        <v>0.22743814</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
         <v>100</v>
@@ -1033,43 +1033,43 @@
         <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30984998</v>
+        <v>0.31024486</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39005524</v>
+        <v>0.3890102</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="M9" t="n">
         <v>27</v>
       </c>
       <c r="N9" t="n">
-        <v>4.512431</v>
+        <v>4.5737705</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4461325</v>
+        <v>1.4562842</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2486408</v>
+        <v>0.24946314</v>
       </c>
       <c r="U9" t="n">
         <v>21</v>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22655389</v>
+        <v>0.22811478</v>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E10" t="n">
         <v>28</v>
@@ -1100,25 +1100,25 @@
         <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3102664</v>
+        <v>0.31195897</v>
       </c>
       <c r="I10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3633689</v>
+        <v>0.36396658</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7694407</v>
+        <v>3.7601078</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
@@ -1127,19 +1127,19 @@
         <v>97</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R10" t="n">
-        <v>1.255116</v>
+        <v>1.2628032</v>
       </c>
       <c r="S10" t="n">
         <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23613138</v>
+        <v>0.2373247</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2553116</v>
+        <v>0.25481275</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
         <v>92</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32443598</v>
+        <v>0.3241206</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4167847</v>
+        <v>0.41477075</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>731</v>
+        <v>745</v>
       </c>
       <c r="M11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5061727</v>
+        <v>5.4708276</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5144033</v>
+        <v>1.5088196</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2859116</v>
+        <v>0.28561667</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23488711</v>
+        <v>0.2349982</v>
       </c>
       <c r="C12" t="n">
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G12" t="n">
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31429493</v>
+        <v>0.3149857</v>
       </c>
       <c r="I12" t="n">
         <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39402768</v>
+        <v>0.39453825</v>
       </c>
       <c r="K12" t="n">
         <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7970684</v>
+        <v>3.7943966</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q12" t="n">
         <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2478241</v>
+        <v>1.2471757</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23852877</v>
+        <v>0.23778735</v>
       </c>
       <c r="U12" t="n">
         <v>12</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24265735</v>
+        <v>0.24189095</v>
       </c>
       <c r="C13" t="n">
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3164478</v>
+        <v>0.31595185</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4090909</v>
+        <v>0.40959284</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>691</v>
+        <v>704</v>
       </c>
       <c r="M13" t="n">
         <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7675242</v>
+        <v>4.740368</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
       </c>
       <c r="P13" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3948536</v>
+        <v>1.3975482</v>
       </c>
       <c r="S13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24166076</v>
+        <v>0.24168126</v>
       </c>
       <c r="U13" t="n">
         <v>16</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24386775</v>
+        <v>0.2445614</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E14" t="n">
         <v>19</v>
@@ -1368,43 +1368,43 @@
         <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31600633</v>
+        <v>0.3163329</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3910416</v>
+        <v>0.39052632</v>
       </c>
       <c r="K14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L14" t="n">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="M14" t="n">
         <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8361835</v>
+        <v>4.826145</v>
       </c>
       <c r="O14" t="n">
         <v>27</v>
       </c>
       <c r="P14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4270927</v>
+        <v>1.4259671</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26065516</v>
+        <v>0.26018807</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,43 +1417,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23994355</v>
+        <v>0.2398743</v>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3190088</v>
+        <v>0.31842187</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39837685</v>
+        <v>0.39769554</v>
       </c>
       <c r="K15" t="n">
         <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.629264</v>
+        <v>4.585809</v>
       </c>
       <c r="O15" t="n">
         <v>24</v>
@@ -1465,16 +1465,16 @@
         <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.408438</v>
+        <v>1.4035476</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23717949</v>
+        <v>0.23661971</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26342162</v>
+        <v>0.26230088</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -1502,43 +1502,43 @@
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34596118</v>
+        <v>0.3454039</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4416607</v>
+        <v>0.43858406</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4457612</v>
+        <v>3.4281855</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1144029</v>
+        <v>1.1130122</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.212987</v>
+        <v>0.21284404</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,13 +1551,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24716637</v>
+        <v>0.24602026</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E17" t="n">
         <v>18</v>
@@ -1566,46 +1566,46 @@
         <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32372004</v>
+        <v>0.3226427</v>
       </c>
       <c r="I17" t="n">
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39012796</v>
+        <v>0.3882055</v>
       </c>
       <c r="K17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L17" t="n">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="M17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9575343</v>
+        <v>3.9390244</v>
       </c>
       <c r="O17" t="n">
         <v>11</v>
       </c>
       <c r="P17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2410959</v>
+        <v>1.2357724</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22733918</v>
+        <v>0.22720695</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2532252</v>
+        <v>0.25336242</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18" t="n">
         <v>26</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33679092</v>
+        <v>0.3367445</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39329156</v>
+        <v>0.39331153</v>
       </c>
       <c r="K18" t="n">
         <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.415814</v>
+        <v>3.4059634</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
@@ -1666,13 +1666,13 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1860465</v>
+        <v>1.1834862</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21973434</v>
+        <v>0.21843387</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,43 +1685,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24727401</v>
+        <v>0.24739039</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G19" t="n">
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32215607</v>
+        <v>0.3215394</v>
       </c>
       <c r="I19" t="n">
         <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>0.41083363</v>
+        <v>0.4119694</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N19" t="n">
-        <v>4.892536</v>
+        <v>4.857841</v>
       </c>
       <c r="O19" t="n">
         <v>28</v>
@@ -1733,13 +1733,13 @@
         <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4096223</v>
+        <v>1.4033763</v>
       </c>
       <c r="S19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2569735</v>
+        <v>0.2564633</v>
       </c>
       <c r="U19" t="n">
         <v>26</v>
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23082463</v>
+        <v>0.23107003</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E20" t="n">
         <v>26</v>
       </c>
       <c r="F20" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G20" t="n">
         <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2980456</v>
+        <v>0.29951847</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37486497</v>
+        <v>0.37468895</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="M20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N20" t="n">
-        <v>4.113708</v>
+        <v>4.124334</v>
       </c>
       <c r="O20" t="n">
         <v>14</v>
       </c>
       <c r="P20" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2795506</v>
+        <v>1.2788632</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23290598</v>
+        <v>0.23347399</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.24108784</v>
+        <v>0.23920146</v>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
@@ -1837,25 +1837,25 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.32535577</v>
+        <v>0.32320973</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.430724</v>
+        <v>0.42649728</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="M21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3377757</v>
+        <v>3.3198729</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1867,13 +1867,13 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1897979</v>
+        <v>1.1882939</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22661738</v>
+        <v>0.22616003</v>
       </c>
       <c r="U21" t="n">
         <v>4</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2350412</v>
+        <v>0.23558542</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E22" t="n">
         <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30148965</v>
+        <v>0.30134356</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39949837</v>
+        <v>0.399717</v>
       </c>
       <c r="K22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L22" t="n">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N22" t="n">
-        <v>4.0768538</v>
+        <v>4.075927</v>
       </c>
       <c r="O22" t="n">
         <v>13</v>
       </c>
       <c r="P22" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q22" t="n">
         <v>17</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2911392</v>
+        <v>1.2983475</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25438598</v>
+        <v>0.25433126</v>
       </c>
       <c r="U22" t="n">
         <v>23</v>
@@ -1953,43 +1953,43 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25755996</v>
+        <v>0.25824177</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33508015</v>
+        <v>0.33667883</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.41432047</v>
+        <v>0.41758242</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="M23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1510534</v>
+        <v>4.1372895</v>
       </c>
       <c r="O23" t="n">
         <v>15</v>
@@ -1998,19 +1998,19 @@
         <v>80</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2976243</v>
+        <v>1.2980514</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2356281</v>
+        <v>0.23570678</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -2020,43 +2020,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22083333</v>
+        <v>0.22059925</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G24" t="n">
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29688558</v>
+        <v>0.29732442</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3655303</v>
+        <v>0.36516854</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="M24" t="n">
         <v>12</v>
       </c>
       <c r="N24" t="n">
-        <v>3.905424</v>
+        <v>3.8942308</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
@@ -2065,19 +2065,19 @@
         <v>80</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3045897</v>
+        <v>1.3008242</v>
       </c>
       <c r="S24" t="n">
         <v>17</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24331352</v>
+        <v>0.24237972</v>
       </c>
       <c r="U24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25497866</v>
+        <v>0.25562587</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E25" t="n">
         <v>27</v>
@@ -2102,31 +2102,31 @@
         <v>88</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3078681</v>
+        <v>0.3082634</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41820768</v>
+        <v>0.4173699</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>4.346826</v>
+        <v>4.30577</v>
       </c>
       <c r="O25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P25" t="n">
         <v>81</v>
@@ -2135,13 +2135,13 @@
         <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3675252</v>
+        <v>1.3602908</v>
       </c>
       <c r="S25" t="n">
         <v>21</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24826579</v>
+        <v>0.24747474</v>
       </c>
       <c r="U25" t="n">
         <v>20</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23049262</v>
+        <v>0.23175053</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E26" t="n">
         <v>24</v>
@@ -2169,31 +2169,31 @@
         <v>102</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31144404</v>
+        <v>0.31259817</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38295576</v>
+        <v>0.38235295</v>
       </c>
       <c r="K26" t="n">
         <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6845639</v>
+        <v>3.7171314</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
         <v>79</v>
@@ -2202,16 +2202,16 @@
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.181208</v>
+        <v>1.192563</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24040186</v>
+        <v>0.24175824</v>
       </c>
       <c r="U26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -2221,43 +2221,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24665676</v>
+        <v>0.24632353</v>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E27" t="n">
         <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G27" t="n">
         <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32479474</v>
+        <v>0.32378784</v>
       </c>
       <c r="I27" t="n">
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39375928</v>
+        <v>0.3930147</v>
       </c>
       <c r="K27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L27" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3008847</v>
+        <v>4.2598896</v>
       </c>
       <c r="O27" t="n">
         <v>19</v>
@@ -2269,13 +2269,13 @@
         <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>1.352585</v>
+        <v>1.3454461</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25676665</v>
+        <v>0.25551936</v>
       </c>
       <c r="U27" t="n">
         <v>25</v>
@@ -2288,64 +2288,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25842696</v>
+        <v>0.25916326</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G28" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33598673</v>
+        <v>0.3361758</v>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39101124</v>
+        <v>0.39392817</v>
       </c>
       <c r="K28" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L28" t="n">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.813986</v>
+        <v>3.7790055</v>
       </c>
       <c r="O28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q28" t="n">
         <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>1.206993</v>
+        <v>1.2002763</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23590505</v>
+        <v>0.23497067</v>
       </c>
       <c r="U28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24358511</v>
+        <v>0.24357143</v>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G29" t="n">
         <v>19</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31980675</v>
+        <v>0.32029262</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39176002</v>
+        <v>0.39142856</v>
       </c>
       <c r="K29" t="n">
         <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="M29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>3.984418</v>
+        <v>3.9601629</v>
       </c>
       <c r="O29" t="n">
         <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2456462</v>
+        <v>1.2399276</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23800938</v>
+        <v>0.23734854</v>
       </c>
       <c r="U29" t="n">
         <v>11</v>
@@ -2422,64 +2422,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2490161</v>
+        <v>0.24823196</v>
       </c>
       <c r="C30" t="n">
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G30" t="n">
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3110823</v>
+        <v>0.3099359</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3921288</v>
+        <v>0.3907355</v>
       </c>
       <c r="K30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L30" t="n">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1726165</v>
+        <v>4.158482</v>
       </c>
       <c r="O30" t="n">
         <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q30" t="n">
         <v>16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3230908</v>
+        <v>1.3258928</v>
       </c>
       <c r="S30" t="n">
         <v>18</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24318507</v>
+        <v>0.24317618</v>
       </c>
       <c r="U30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24600972</v>
+        <v>0.24562608</v>
       </c>
       <c r="C31" t="n">
         <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G31" t="n">
         <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>0.31870526</v>
+        <v>0.31867117</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42158222</v>
+        <v>0.4219554</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="M31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6987634</v>
+        <v>4.690528</v>
       </c>
       <c r="O31" t="n">
         <v>25</v>
       </c>
       <c r="P31" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.396643</v>
+        <v>1.3919685</v>
       </c>
       <c r="S31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25820795</v>
+        <v>0.2571912</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23267327</v>
+        <v>0.22660099</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>0.29411766</v>
+        <v>0.28181818</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38118812</v>
+        <v>0.38916257</v>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>4.0588236</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>1.254902</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2513369</v>
+        <v>0.25274727</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.21717171</v>
+        <v>0.21319798</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.29411766</v>
+      </c>
+      <c r="I3" t="n">
+        <v>23</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.26395938</v>
+      </c>
+      <c r="K3" t="n">
         <v>29</v>
       </c>
-      <c r="E3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>28</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.30357143</v>
-      </c>
-      <c r="I3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.28787878</v>
-      </c>
-      <c r="K3" t="n">
-        <v>28</v>
-      </c>
       <c r="L3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8774195</v>
+        <v>4.0855265</v>
       </c>
       <c r="O3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.316129</v>
+        <v>1.2434211</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T3" t="n">
-        <v>0.25</v>
+        <v>0.2408377</v>
       </c>
       <c r="U3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.18719211</v>
+        <v>0.18137255</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>0.23744293</v>
+        <v>0.23181818</v>
       </c>
       <c r="I4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K4" t="n">
         <v>30</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.27093595</v>
-      </c>
-      <c r="K4" t="n">
-        <v>29</v>
-      </c>
       <c r="L4" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4117646</v>
+        <v>3.42</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="n">
         <v>6</v>
       </c>
-      <c r="Q4" t="n">
-        <v>8</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.3921568</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T4" t="n">
-        <v>0.24338624</v>
+        <v>0.23626374</v>
       </c>
       <c r="U4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2488263</v>
+        <v>0.21287128</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2857143</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.34653464</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L5" t="n">
+        <v>64</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.128049</v>
+      </c>
+      <c r="O5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" t="n">
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
         <v>11</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.3206751</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="R5" t="n">
+        <v>1.207317</v>
+      </c>
+      <c r="S5" t="n">
         <v>11</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.42723006</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="T5" t="n">
+        <v>0.22748815</v>
+      </c>
+      <c r="U5" t="n">
         <v>10</v>
-      </c>
-      <c r="L5" t="n">
-        <v>68</v>
-      </c>
-      <c r="M5" t="n">
-        <v>28</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.4695122</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.1341463</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.21904762</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24336283</v>
+        <v>0.24561404</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3243243</v>
+      </c>
+      <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" t="n">
-        <v>11</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.31889763</v>
-      </c>
-      <c r="I6" t="n">
-        <v>14</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.44247788</v>
+        <v>0.42982456</v>
       </c>
       <c r="K6" t="n">
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>2.032258</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>1.048387</v>
       </c>
       <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.21888413</v>
+      </c>
+      <c r="U6" t="n">
         <v>8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.23684211</v>
-      </c>
-      <c r="U6" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.22222222</v>
+        <v>0.20746888</v>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3150,46 +3150,46 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3251029</v>
+        <v>0.31690142</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4347826</v>
+        <v>0.39419088</v>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="M7" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1666665</v>
+        <v>3.796875</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3333334</v>
+        <v>1.34375</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23</v>
+        <v>0.23529412</v>
       </c>
       <c r="U7" t="n">
         <v>13</v>
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.29107982</v>
+        <v>0.3</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>39</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.33766234</v>
+        <v>0.36206895</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4741784</v>
+        <v>0.4857143</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
         <v>2.290909</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2545455</v>
+        <v>1.1818181</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>0.22277227</v>
+        <v>0.215</v>
       </c>
       <c r="U8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.20408164</v>
+        <v>0.20918368</v>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
         <v>25</v>
       </c>
       <c r="E9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.29596412</v>
+      </c>
+      <c r="I9" t="n">
         <v>20</v>
       </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>21</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.2850679</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
+        <v>0.31632653</v>
+      </c>
+      <c r="K9" t="n">
         <v>25</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.32142857</v>
-      </c>
-      <c r="K9" t="n">
-        <v>26</v>
       </c>
       <c r="L9" t="n">
         <v>61</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1090908</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1818181</v>
+        <v>1.3518518</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T9" t="n">
-        <v>0.22167487</v>
+        <v>0.23786408</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -3336,16 +3336,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1897436</v>
+        <v>0.22727273</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -3354,46 +3354,46 @@
         <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>0.26046512</v>
+        <v>0.30493274</v>
       </c>
       <c r="I10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J10" t="n">
-        <v>0.24615385</v>
+        <v>0.28282827</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2468355</v>
+        <v>3.3540373</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1772152</v>
+        <v>1.3043478</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="T10" t="n">
-        <v>0.22797927</v>
+        <v>0.24390244</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.30092594</v>
+        <v>0.2962963</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.34468085</v>
+      </c>
+      <c r="I11" t="n">
         <v>7</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.3516949</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
+        <v>0.47685185</v>
+      </c>
+      <c r="K11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.49537036</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M11" t="n">
         <v>14</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6666665</v>
+        <v>4.754717</v>
       </c>
       <c r="O11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P11" t="n">
         <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.4150944</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T11" t="n">
-        <v>0.29357797</v>
+        <v>0.2809524</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.25531915</v>
+        <v>0.24034335</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>30</v>
       </c>
       <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.31800765</v>
+      </c>
+      <c r="I12" t="n">
         <v>11</v>
       </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.32307693</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
+        <v>0.40772533</v>
+      </c>
+      <c r="K12" t="n">
         <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.41276595</v>
-      </c>
-      <c r="K12" t="n">
-        <v>13</v>
       </c>
       <c r="L12" t="n">
         <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N12" t="n">
-        <v>3.234375</v>
+        <v>3.375</v>
       </c>
       <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>23</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.046875</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.2231405</v>
+      </c>
+      <c r="U12" t="n">
         <v>9</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>17</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.953125</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.22175732</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23628692</v>
+        <v>0.22764228</v>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>0.30152673</v>
+        <v>0.29927006</v>
       </c>
       <c r="I13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.37804878</v>
+      </c>
+      <c r="K13" t="n">
         <v>20</v>
       </c>
-      <c r="J13" t="n">
-        <v>0.36708862</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>57</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.65625</v>
+      </c>
+      <c r="O13" t="n">
+        <v>13</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>29</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.359375</v>
+      </c>
+      <c r="S13" t="n">
         <v>24</v>
       </c>
-      <c r="L13" t="n">
-        <v>47</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.4285715</v>
-      </c>
-      <c r="O13" t="n">
-        <v>12</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>26</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.2222222</v>
-      </c>
-      <c r="S13" t="n">
-        <v>15</v>
-      </c>
       <c r="T13" t="n">
-        <v>0.22978723</v>
+        <v>0.24481328</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.20689656</v>
+        <v>0.20434782</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.26587301</v>
+        <v>0.2570281</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>0.37931034</v>
+        <v>0.3347826</v>
       </c>
       <c r="K14" t="n">
+        <v>23</v>
+      </c>
+      <c r="L14" t="n">
+        <v>61</v>
+      </c>
+      <c r="M14" t="n">
         <v>21</v>
       </c>
-      <c r="L14" t="n">
-        <v>62</v>
-      </c>
-      <c r="M14" t="n">
-        <v>23</v>
-      </c>
       <c r="N14" t="n">
-        <v>8.949438000000001</v>
+        <v>7.735955</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9213483</v>
+        <v>1.8033708</v>
       </c>
       <c r="S14" t="n">
         <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3463035</v>
+        <v>0.32388663</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2524272</v>
+        <v>0.24378109</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>0.32017544</v>
+        <v>0.30454546</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39320388</v>
+        <v>0.35820895</v>
       </c>
       <c r="K15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L15" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7454543</v>
+        <v>3.9272728</v>
       </c>
       <c r="O15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="P15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" t="n">
         <v>6</v>
       </c>
-      <c r="Q15" t="n">
-        <v>8</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.1454545</v>
+        <v>1.0909091</v>
       </c>
       <c r="S15" t="n">
         <v>7</v>
       </c>
       <c r="T15" t="n">
-        <v>0.22058824</v>
+        <v>0.21674877</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.29680365</v>
+        <v>0.29816514</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3632653</v>
+        <v>0.37246963</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.47945204</v>
+        <v>0.47706422</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M16" t="n">
+        <v>9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.0566037</v>
+      </c>
+      <c r="O16" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" t="n">
         <v>6</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.754717</v>
-      </c>
-      <c r="O16" t="n">
-        <v>24</v>
-      </c>
-      <c r="P16" t="n">
-        <v>9</v>
-      </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4716982</v>
+        <v>1.245283</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2413793</v>
+        <v>0.20942408</v>
       </c>
       <c r="U16" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.265625</v>
+        <v>0.25773194</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
         <v>24</v>
       </c>
-      <c r="E17" t="n">
-        <v>23</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>21</v>
-      </c>
       <c r="H17" t="n">
-        <v>0.32057416</v>
+        <v>0.31924883</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>0.42708334</v>
+        <v>0.4072165</v>
       </c>
       <c r="K17" t="n">
         <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N17" t="n">
+        <v>2.2075472</v>
+      </c>
+      <c r="O17" t="n">
         <v>2</v>
       </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0.20418848</v>
+        <v>0.21578947</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -3872,61 +3872,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.23383084</v>
+        <v>0.22</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H18" t="n">
-        <v>0.30357143</v>
+        <v>0.29464287</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40298507</v>
+        <v>0.39</v>
       </c>
       <c r="K18" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" t="n">
+        <v>58</v>
+      </c>
+      <c r="M18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" t="n">
-        <v>55</v>
-      </c>
-      <c r="M18" t="n">
-        <v>18</v>
-      </c>
       <c r="N18" t="n">
-        <v>3.1090908</v>
+        <v>2.892857</v>
       </c>
       <c r="O18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="Q18" t="n">
-        <v>8</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.0545454</v>
+        <v>1.0714285</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>0.17989418</v>
+        <v>0.16230367</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
@@ -3939,40 +3939,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25238097</v>
+        <v>0.24390244</v>
       </c>
       <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24</v>
+      </c>
+      <c r="E19" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.29090908</v>
+      </c>
+      <c r="I19" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.40487805</v>
+      </c>
+      <c r="K19" t="n">
         <v>12</v>
       </c>
-      <c r="D19" t="n">
-        <v>25</v>
-      </c>
-      <c r="E19" t="n">
-        <v>20</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>21</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.30396476</v>
-      </c>
-      <c r="I19" t="n">
-        <v>17</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.3809524</v>
-      </c>
-      <c r="K19" t="n">
-        <v>19</v>
-      </c>
       <c r="L19" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>5.7272725</v>
@@ -3984,19 +3984,19 @@
         <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6181818</v>
+        <v>1.5636364</v>
       </c>
       <c r="S19" t="n">
         <v>29</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2927928</v>
+        <v>0.29464287</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.21212122</v>
+        <v>0.2212766</v>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30152673</v>
+        <v>0.32352942</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3939394</v>
+        <v>0.40425533</v>
       </c>
       <c r="K20" t="n">
+        <v>13</v>
+      </c>
+      <c r="L20" t="n">
+        <v>61</v>
+      </c>
+      <c r="M20" t="n">
+        <v>21</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.640625</v>
+      </c>
+      <c r="O20" t="n">
+        <v>25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q20" t="n">
         <v>16</v>
       </c>
-      <c r="L20" t="n">
-        <v>65</v>
-      </c>
-      <c r="M20" t="n">
-        <v>24</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.714286</v>
-      </c>
-      <c r="O20" t="n">
-        <v>22</v>
-      </c>
-      <c r="P20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>17</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.3015873</v>
+        <v>1.265625</v>
       </c>
       <c r="S20" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23553719</v>
+        <v>0.23577236</v>
       </c>
       <c r="U20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.18942732</v>
+        <v>0.17030568</v>
       </c>
       <c r="C21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2489796</v>
+        <v>0.2244898</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>0.32599118</v>
+        <v>0.29257643</v>
       </c>
       <c r="K21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L21" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3559322</v>
+        <v>3.1853933</v>
       </c>
       <c r="O21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q21" t="n">
         <v>6</v>
       </c>
-      <c r="Q21" t="n">
-        <v>8</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.2881356</v>
+        <v>1.2808989</v>
       </c>
       <c r="S21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T21" t="n">
-        <v>0.24553572</v>
+        <v>0.24215247</v>
       </c>
       <c r="U21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.26938775</v>
+        <v>0.26907632</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3258427</v>
+        <v>0.31598514</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4489796</v>
+        <v>0.437751</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L22" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9836066</v>
+        <v>4.2786884</v>
       </c>
       <c r="O22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
         <v>9</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1639345</v>
+        <v>1.295082</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T22" t="n">
-        <v>0.22553192</v>
+        <v>0.23430963</v>
       </c>
       <c r="U22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.30555555</v>
+        <v>0.3018868</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0.34334764</v>
+        <v>0.3628692</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5046296</v>
+        <v>0.5235849</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M23" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.6666667</v>
       </c>
       <c r="O23" t="n">
         <v>14</v>
       </c>
       <c r="P23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="n">
         <v>6</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8</v>
       </c>
       <c r="R23" t="n">
         <v>1.2037038</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T23" t="n">
         <v>0.23267327</v>
       </c>
       <c r="U23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24064171</v>
+        <v>0.22950819</v>
       </c>
       <c r="C24" t="n">
+        <v>17</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" t="n">
         <v>16</v>
       </c>
-      <c r="D24" t="n">
-        <v>26</v>
-      </c>
-      <c r="E24" t="n">
-        <v>17</v>
-      </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3529412</v>
+        <v>0.35746607</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37967914</v>
+        <v>0.38251367</v>
       </c>
       <c r="K24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L24" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M24" t="n">
         <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>3.7636364</v>
       </c>
       <c r="O24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3888888</v>
+        <v>1.290909</v>
       </c>
       <c r="S24" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2606635</v>
+        <v>0.23943663</v>
       </c>
       <c r="U24" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -4341,61 +4341,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2032967</v>
+        <v>0.23243243</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" t="n">
         <v>7</v>
       </c>
       <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.30097088</v>
+      </c>
+      <c r="I25" t="n">
         <v>17</v>
       </c>
-      <c r="H25" t="n">
-        <v>0.28431374</v>
-      </c>
-      <c r="I25" t="n">
-        <v>26</v>
-      </c>
       <c r="J25" t="n">
-        <v>0.37362638</v>
+        <v>0.4</v>
       </c>
       <c r="K25" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N25" t="n">
-        <v>2.54717</v>
+        <v>2.3333333</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9811321</v>
+        <v>0.9814815</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>0.18716578</v>
+        <v>0.1865285</v>
       </c>
       <c r="U25" t="n">
         <v>2</v>
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.20918368</v>
+        <v>0.23076923</v>
       </c>
       <c r="C26" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16</v>
+      </c>
+      <c r="E26" t="n">
+        <v>28</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
         <v>24</v>
       </c>
-      <c r="D26" t="n">
+      <c r="H26" t="n">
+        <v>0.31330472</v>
+      </c>
+      <c r="I26" t="n">
         <v>14</v>
       </c>
-      <c r="E26" t="n">
-        <v>30</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>21</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.29223743</v>
-      </c>
-      <c r="I26" t="n">
-        <v>23</v>
-      </c>
       <c r="J26" t="n">
-        <v>0.31632653</v>
+        <v>0.3221154</v>
       </c>
       <c r="K26" t="n">
+        <v>24</v>
+      </c>
+      <c r="L26" t="n">
+        <v>59</v>
+      </c>
+      <c r="M26" t="n">
+        <v>16</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="O26" t="n">
         <v>27</v>
       </c>
-      <c r="L26" t="n">
-        <v>54</v>
-      </c>
-      <c r="M26" t="n">
-        <v>14</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.0588236</v>
-      </c>
-      <c r="O26" t="n">
-        <v>16</v>
-      </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1568627</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="U26" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24365482</v>
+        <v>0.20765027</v>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31838566</v>
+        <v>0.27093595</v>
       </c>
       <c r="I27" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>0.37055838</v>
+        <v>0.27322406</v>
       </c>
       <c r="K27" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L27" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3333335</v>
+        <v>3.8333333</v>
       </c>
       <c r="O27" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.3333334</v>
       </c>
       <c r="S27" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2769953</v>
+        <v>0.25123152</v>
       </c>
       <c r="U27" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2819383</v>
+        <v>0.2857143</v>
       </c>
       <c r="C28" t="n">
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.35177866</v>
+        <v>0.35458168</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.50220263</v>
+        <v>0.5089286</v>
       </c>
       <c r="K28" t="n">
         <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M28" t="n">
         <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7142856</v>
+        <v>2.4285715</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
         <v>8</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9206349</v>
+        <v>0.8730159</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.20524018</v>
+        <v>0.1991342</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.27234042</v>
+        <v>0.26359832</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0.35338345</v>
+        <v>0.34686348</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>0.44680852</v>
+        <v>0.43933055</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2786884</v>
+        <v>4.1311474</v>
       </c>
       <c r="O29" t="n">
+        <v>20</v>
+      </c>
+      <c r="P29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>21</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.1475409</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.2413793</v>
+      </c>
+      <c r="U29" t="n">
         <v>19</v>
-      </c>
-      <c r="P29" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>17</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.2131147</v>
-      </c>
-      <c r="S29" t="n">
-        <v>14</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.2532189</v>
-      </c>
-      <c r="U29" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.25358853</v>
+        <v>0.24380165</v>
       </c>
       <c r="C30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" t="n">
+        <v>27</v>
+      </c>
+      <c r="E30" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.29433963</v>
+      </c>
+      <c r="I30" t="n">
+        <v>22</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.38429752</v>
+      </c>
+      <c r="K30" t="n">
+        <v>18</v>
+      </c>
+      <c r="L30" t="n">
+        <v>62</v>
+      </c>
+      <c r="M30" t="n">
+        <v>24</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.4307694</v>
+      </c>
+      <c r="O30" t="n">
+        <v>22</v>
+      </c>
+      <c r="P30" t="n">
         <v>10</v>
       </c>
-      <c r="D30" t="n">
-        <v>25</v>
-      </c>
-      <c r="E30" t="n">
-        <v>20</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G30" t="n">
-        <v>11</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.3073593</v>
-      </c>
-      <c r="I30" t="n">
-        <v>16</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.40191388</v>
-      </c>
-      <c r="K30" t="n">
-        <v>15</v>
-      </c>
-      <c r="L30" t="n">
-        <v>54</v>
-      </c>
-      <c r="M30" t="n">
-        <v>14</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.660714</v>
-      </c>
-      <c r="O30" t="n">
-        <v>21</v>
-      </c>
-      <c r="P30" t="n">
-        <v>9</v>
-      </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5357143</v>
+        <v>1.5384616</v>
       </c>
       <c r="S30" t="n">
         <v>28</v>
       </c>
       <c r="T30" t="n">
-        <v>0.25592417</v>
+        <v>0.25409836</v>
       </c>
       <c r="U30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -4743,61 +4743,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.23577236</v>
+        <v>0.23694779</v>
       </c>
       <c r="C31" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="n">
         <v>11</v>
       </c>
-      <c r="F31" t="n">
-        <v>10</v>
-      </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.29213482</v>
+        <v>0.29889297</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>0.41869918</v>
+        <v>0.42971888</v>
       </c>
       <c r="K31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L31" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N31" t="n">
-        <v>5.370968</v>
+        <v>5.285714</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P31" t="n">
         <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R31" t="n">
-        <v>1.451613</v>
+        <v>1.3809524</v>
       </c>
       <c r="S31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T31" t="n">
-        <v>0.272</v>
+        <v>0.25506073</v>
       </c>
       <c r="U31" t="n">
         <v>26</v>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23774955</v>
+        <v>0.23759885</v>
       </c>
       <c r="C2" t="n">
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3079406</v>
+      </c>
+      <c r="I2" t="n">
         <v>26</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.30734095</v>
-      </c>
-      <c r="I2" t="n">
-        <v>27</v>
-      </c>
       <c r="J2" t="n">
-        <v>0.384755</v>
+        <v>0.3860532</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3293743</v>
+        <v>4.325361</v>
       </c>
       <c r="O2" t="n">
         <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q2" t="n">
         <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2978529</v>
+        <v>1.2955775</v>
       </c>
       <c r="S2" t="n">
         <v>14</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25134844</v>
+        <v>0.25150976</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24703419</v>
+        <v>0.24758953</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E3" t="n">
         <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
         <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32703623</v>
+        <v>0.32721713</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40928122</v>
+        <v>0.4090909</v>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9254327</v>
+        <v>4.9736843</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4327563</v>
+        <v>1.4407895</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26163393</v>
+        <v>0.26358697</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -689,13 +689,13 @@
         <v>390</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
         <v>103</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
         <v>0.31059128</v>
@@ -719,13 +719,13 @@
         <v>3.4059634</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
         <v>86</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
         <v>1.2110091</v>
@@ -747,43 +747,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23926812</v>
+        <v>0.23824452</v>
       </c>
       <c r="C5" t="n">
         <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31889027</v>
+        <v>0.3179155</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39901477</v>
+        <v>0.3967259</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>778</v>
+        <v>791</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3586907</v>
+        <v>4.3780594</v>
       </c>
       <c r="O5" t="n">
         <v>22</v>
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3746129</v>
+        <v>1.3767482</v>
       </c>
       <c r="S5" t="n">
         <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25473973</v>
+        <v>0.25502214</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24335155</v>
+        <v>0.24396396</v>
       </c>
       <c r="C6" t="n">
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31213114</v>
+        <v>0.31203374</v>
       </c>
       <c r="I6" t="n">
         <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38469946</v>
+        <v>0.38630632</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6953917</v>
+        <v>3.6868458</v>
       </c>
       <c r="O6" t="n">
         <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2414747</v>
+        <v>1.238507</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24068663</v>
+        <v>0.24034645</v>
       </c>
       <c r="U6" t="n">
         <v>15</v>
@@ -881,16 +881,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24048866</v>
+        <v>0.24111763</v>
       </c>
       <c r="C7" t="n">
         <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>99</v>
@@ -899,25 +899,25 @@
         <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33534744</v>
+        <v>0.33582088</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40069807</v>
+        <v>0.400138</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="M7" t="n">
         <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2390723</v>
+        <v>4.2124286</v>
       </c>
       <c r="O7" t="n">
         <v>17</v>
@@ -929,16 +929,16 @@
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2471008</v>
+        <v>1.2494491</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23921569</v>
+        <v>0.24014084</v>
       </c>
       <c r="U7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24185877</v>
+        <v>0.24232575</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="E8" t="n">
         <v>8</v>
@@ -966,25 +966,25 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32221502</v>
+        <v>0.32278684</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41566044</v>
+        <v>0.41603467</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.248165</v>
+        <v>4.2206616</v>
       </c>
       <c r="O8" t="n">
         <v>18</v>
@@ -996,16 +996,16 @@
         <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3293577</v>
+        <v>1.3239691</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2402788</v>
+        <v>0.23920146</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22743814</v>
+        <v>0.22781171</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G9" t="n">
         <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0.31024486</v>
+        <v>0.3098726</v>
       </c>
       <c r="I9" t="n">
         <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3890102</v>
+        <v>0.3891484</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="M9" t="n">
         <v>27</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5737705</v>
+        <v>4.585135</v>
       </c>
       <c r="O9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P9" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4562842</v>
+        <v>1.4581081</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24946314</v>
+        <v>0.2493801</v>
       </c>
       <c r="U9" t="n">
         <v>21</v>
@@ -1082,43 +1082,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22811478</v>
+        <v>0.22867383</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E10" t="n">
         <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
         <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31195897</v>
+        <v>0.3116883</v>
       </c>
       <c r="I10" t="n">
         <v>22</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36396658</v>
+        <v>0.3641577</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7601078</v>
+        <v>3.7749667</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
@@ -1127,19 +1127,19 @@
         <v>97</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2628032</v>
+        <v>1.2636485</v>
       </c>
       <c r="S10" t="n">
         <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2373247</v>
+        <v>0.23819666</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25481275</v>
+        <v>0.25527498</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" t="n">
         <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3241206</v>
+        <v>0.32475185</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41477075</v>
+        <v>0.41611898</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="M11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4708276</v>
+        <v>5.5254693</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q11" t="n">
         <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5088196</v>
+        <v>1.5134048</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28561667</v>
+        <v>0.2862441</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2349982</v>
+        <v>0.23564848</v>
       </c>
       <c r="C12" t="n">
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E12" t="n">
         <v>22</v>
@@ -1234,46 +1234,46 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3149857</v>
+        <v>0.31512868</v>
       </c>
       <c r="I12" t="n">
         <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39453825</v>
+        <v>0.39404678</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7943966</v>
+        <v>3.7848215</v>
       </c>
       <c r="O12" t="n">
         <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2471757</v>
+        <v>1.2375</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23778735</v>
+        <v>0.23631841</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24189095</v>
+        <v>0.2413793</v>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E13" t="n">
         <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31595185</v>
+        <v>0.31541985</v>
       </c>
       <c r="I13" t="n">
         <v>18</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40959284</v>
+        <v>0.41037896</v>
       </c>
       <c r="K13" t="n">
         <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="M13" t="n">
         <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>4.740368</v>
+        <v>4.743401</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
       </c>
       <c r="P13" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3975482</v>
+        <v>1.396798</v>
       </c>
       <c r="S13" t="n">
         <v>24</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24168126</v>
+        <v>0.24152249</v>
       </c>
       <c r="U13" t="n">
         <v>16</v>
@@ -1417,61 +1417,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2398743</v>
+        <v>0.23998618</v>
       </c>
       <c r="C15" t="n">
         <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G15" t="n">
         <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31842187</v>
+        <v>0.31816784</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39769554</v>
+        <v>0.39813536</v>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L15" t="n">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.585809</v>
+        <v>4.5849056</v>
       </c>
       <c r="O15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P15" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4035476</v>
+        <v>1.399298</v>
       </c>
       <c r="S15" t="n">
         <v>26</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23661971</v>
+        <v>0.23623693</v>
       </c>
       <c r="U15" t="n">
         <v>9</v>
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26230088</v>
+        <v>0.26429567</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>116</v>
+      </c>
+      <c r="G16" t="n">
         <v>2</v>
       </c>
-      <c r="F16" t="n">
-        <v>113</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.3454039</v>
+        <v>0.3464591</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.43858406</v>
+        <v>0.44142258</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4281855</v>
+        <v>3.4350533</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q16" t="n">
         <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1130122</v>
+        <v>1.1183274</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21284404</v>
+        <v>0.21389794</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24602026</v>
+        <v>0.2472351</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3226427</v>
+        <v>0.32384565</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3882055</v>
+        <v>0.39207992</v>
       </c>
       <c r="K17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L17" t="n">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="M17" t="n">
         <v>12</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9390244</v>
+        <v>3.9759035</v>
       </c>
       <c r="O17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2357724</v>
+        <v>1.2409638</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22720695</v>
+        <v>0.22802001</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25336242</v>
+        <v>0.2532374</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3367445</v>
+        <v>0.33733797</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39331153</v>
+        <v>0.39460433</v>
       </c>
       <c r="K18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4059634</v>
+        <v>3.400997</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1834862</v>
+        <v>1.1826007</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21843387</v>
+        <v>0.21893491</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24739039</v>
+        <v>0.24716398</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G19" t="n">
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3215394</v>
+        <v>0.32137382</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4119694</v>
+        <v>0.41285664</v>
       </c>
       <c r="K19" t="n">
         <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="M19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N19" t="n">
-        <v>4.857841</v>
+        <v>4.8476734</v>
       </c>
       <c r="O19" t="n">
         <v>28</v>
       </c>
       <c r="P19" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q19" t="n">
         <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4033763</v>
+        <v>1.3985953</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2564633</v>
+        <v>0.2557981</v>
       </c>
       <c r="U19" t="n">
         <v>26</v>
@@ -1752,46 +1752,46 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23107003</v>
+        <v>0.23022847</v>
       </c>
       <c r="C20" t="n">
         <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G20" t="n">
         <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29951847</v>
+        <v>0.29873016</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37468895</v>
+        <v>0.37398946</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="M20" t="n">
         <v>15</v>
       </c>
       <c r="N20" t="n">
-        <v>4.124334</v>
+        <v>4.1045694</v>
       </c>
       <c r="O20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P20" t="n">
         <v>85</v>
@@ -1800,13 +1800,13 @@
         <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2788632</v>
+        <v>1.2759227</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23347399</v>
+        <v>0.23267154</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -1819,43 +1819,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23920146</v>
+        <v>0.23770198</v>
       </c>
       <c r="C21" t="n">
         <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.32320973</v>
+        <v>0.3213042</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>0.42649728</v>
+        <v>0.42477557</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>730</v>
+        <v>743</v>
       </c>
       <c r="M21" t="n">
         <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3198729</v>
+        <v>3.3038995</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1867,13 +1867,13 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1882939</v>
+        <v>1.191394</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22616003</v>
+        <v>0.22694525</v>
       </c>
       <c r="U21" t="n">
         <v>4</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23558542</v>
+        <v>0.23593149</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E22" t="n">
         <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30134356</v>
+        <v>0.30173776</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.399717</v>
+        <v>0.40230688</v>
       </c>
       <c r="K22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L22" t="n">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="M22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.075927</v>
+        <v>4.1465135</v>
       </c>
       <c r="O22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P22" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Q22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2983475</v>
+        <v>1.3040601</v>
       </c>
       <c r="S22" t="n">
         <v>16</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25433126</v>
+        <v>0.25487512</v>
       </c>
       <c r="U22" t="n">
         <v>23</v>
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25824177</v>
+        <v>0.25873178</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33667883</v>
+        <v>0.337136</v>
       </c>
       <c r="I23" t="n">
         <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.41758242</v>
+        <v>0.42048153</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="M23" t="n">
         <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1372895</v>
+        <v>4.171116</v>
       </c>
       <c r="O23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2980514</v>
+        <v>1.2984682</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23570678</v>
+        <v>0.23604852</v>
       </c>
       <c r="U23" t="n">
         <v>8</v>
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22059925</v>
+        <v>0.22181146</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
@@ -2038,25 +2038,25 @@
         <v>23</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29732442</v>
+        <v>0.2979848</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.36516854</v>
+        <v>0.36524954</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="M24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8942308</v>
+        <v>3.885068</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
@@ -2065,19 +2065,19 @@
         <v>80</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3008242</v>
+        <v>1.3045249</v>
       </c>
       <c r="S24" t="n">
         <v>17</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24237972</v>
+        <v>0.24301778</v>
       </c>
       <c r="U24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25562587</v>
+        <v>0.25573316</v>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E25" t="n">
+        <v>26</v>
+      </c>
+      <c r="F25" t="n">
+        <v>89</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3079132</v>
+      </c>
+      <c r="I25" t="n">
         <v>27</v>
       </c>
-      <c r="F25" t="n">
-        <v>88</v>
-      </c>
-      <c r="G25" t="n">
-        <v>21</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.3082634</v>
-      </c>
-      <c r="I25" t="n">
-        <v>26</v>
-      </c>
       <c r="J25" t="n">
-        <v>0.4173699</v>
+        <v>0.41730368</v>
       </c>
       <c r="K25" t="n">
         <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="M25" t="n">
         <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>4.30577</v>
+        <v>4.32</v>
       </c>
       <c r="O25" t="n">
         <v>20</v>
       </c>
       <c r="P25" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3602908</v>
+        <v>1.3617977</v>
       </c>
       <c r="S25" t="n">
         <v>21</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24747474</v>
+        <v>0.24723116</v>
       </c>
       <c r="U25" t="n">
         <v>20</v>
@@ -2154,61 +2154,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23175053</v>
+        <v>0.23141655</v>
       </c>
       <c r="C26" t="n">
         <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31259817</v>
+        <v>0.31218904</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38235295</v>
+        <v>0.38359046</v>
       </c>
       <c r="K26" t="n">
         <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="M26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N26" t="n">
-        <v>3.7171314</v>
+        <v>3.6968503</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q26" t="n">
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.192563</v>
+        <v>1.191601</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24175824</v>
+        <v>0.24185069</v>
       </c>
       <c r="U26" t="n">
         <v>17</v>
@@ -2224,13 +2224,13 @@
         <v>0.24632353</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
         <v>362</v>
       </c>
       <c r="E27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
         <v>89</v>
@@ -2242,7 +2242,7 @@
         <v>0.32378784</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
         <v>0.3930147</v>
@@ -2254,7 +2254,7 @@
         <v>625</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
         <v>4.2598896</v>
@@ -2297,13 +2297,13 @@
         <v>366</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F28" t="n">
         <v>74</v>
       </c>
       <c r="G28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H28" t="n">
         <v>0.3361758</v>
@@ -2315,7 +2315,7 @@
         <v>0.39392817</v>
       </c>
       <c r="K28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L28" t="n">
         <v>580</v>
@@ -2333,7 +2333,7 @@
         <v>97</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R28" t="n">
         <v>1.2002763</v>
@@ -2355,16 +2355,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24357143</v>
+        <v>0.24435826</v>
       </c>
       <c r="C29" t="n">
         <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>89</v>
@@ -2373,43 +2373,43 @@
         <v>19</v>
       </c>
       <c r="H29" t="n">
-        <v>0.32029262</v>
+        <v>0.32033953</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39142856</v>
+        <v>0.39210156</v>
       </c>
       <c r="K29" t="n">
         <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="M29" t="n">
         <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9601629</v>
+        <v>3.9485688</v>
       </c>
       <c r="O29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P29" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2399276</v>
+        <v>1.2397138</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23734854</v>
+        <v>0.237777</v>
       </c>
       <c r="U29" t="n">
         <v>11</v>
@@ -2422,16 +2422,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24823196</v>
+        <v>0.24728547</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
         <v>86</v>
@@ -2440,46 +2440,46 @@
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3099359</v>
+        <v>0.30954647</v>
       </c>
       <c r="I30" t="n">
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3907355</v>
+        <v>0.38949212</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L30" t="n">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.158482</v>
+        <v>4.1208644</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P30" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q30" t="n">
         <v>16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3258928</v>
+        <v>1.3193648</v>
       </c>
       <c r="S30" t="n">
         <v>18</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24317618</v>
+        <v>0.2422012</v>
       </c>
       <c r="U30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24562608</v>
+        <v>0.24525101</v>
       </c>
       <c r="C31" t="n">
         <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.31867117</v>
+        <v>0.3180158</v>
       </c>
       <c r="I31" t="n">
         <v>15</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4219554</v>
+        <v>0.42096338</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="M31" t="n">
         <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>4.690528</v>
+        <v>4.7118793</v>
       </c>
       <c r="O31" t="n">
         <v>25</v>
       </c>
       <c r="P31" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3919685</v>
+        <v>1.3904967</v>
       </c>
       <c r="S31" t="n">
         <v>23</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2571912</v>
+        <v>0.25762144</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.22660099</v>
+        <v>0.2244898</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>0.28181818</v>
+        <v>0.29816514</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38916257</v>
+        <v>0.40816328</v>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4.5882354</v>
       </c>
       <c r="O2" t="n">
         <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.2352941</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25274727</v>
+        <v>0.25396827</v>
       </c>
       <c r="U2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.21319798</v>
+        <v>0.22553192</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>0.29411766</v>
+        <v>0.30152673</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>0.26395938</v>
+        <v>0.2851064</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>4.0855265</v>
+        <v>4.8268156</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2434211</v>
+        <v>1.3743017</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2408377</v>
+        <v>0.26923078</v>
       </c>
       <c r="U3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.18137255</v>
+        <v>0.1764706</v>
       </c>
       <c r="C4" t="n">
         <v>29</v>
@@ -2949,49 +2949,49 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>0.23181818</v>
+        <v>0.23243243</v>
       </c>
       <c r="I4" t="n">
         <v>29</v>
       </c>
       <c r="J4" t="n">
-        <v>0.25</v>
+        <v>0.25882354</v>
       </c>
       <c r="K4" t="n">
         <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.42</v>
+        <v>3.857143</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>6</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.3333334</v>
       </c>
       <c r="S4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23626374</v>
+        <v>0.2516129</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21287128</v>
+        <v>0.185567</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2857143</v>
+        <v>0.27272728</v>
       </c>
       <c r="I5" t="n">
         <v>25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.34653464</v>
+        <v>0.28350514</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N5" t="n">
-        <v>3.128049</v>
+        <v>3.9512196</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.207317</v>
+        <v>1.3170731</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T5" t="n">
-        <v>0.22748815</v>
+        <v>0.23831776</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24561404</v>
+        <v>0.2631579</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3243243</v>
+        <v>0.32421875</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>0.42982456</v>
+        <v>0.4649123</v>
       </c>
       <c r="K6" t="n">
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
         <v>5</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.032258</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4</v>
-      </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.048387</v>
+        <v>0.984127</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0.21888413</v>
+        <v>0.19742489</v>
       </c>
       <c r="U6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.20746888</v>
+        <v>0.21818182</v>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3153,46 +3153,46 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.31690142</v>
+        <v>0.32407406</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>0.39419088</v>
+        <v>0.3890909</v>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L7" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N7" t="n">
-        <v>3.796875</v>
+        <v>3.5753424</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P7" t="n">
         <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34375</v>
+        <v>1.3561643</v>
       </c>
       <c r="S7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T7" t="n">
-        <v>0.23529412</v>
+        <v>0.24542125</v>
       </c>
       <c r="U7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -3202,46 +3202,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3</v>
+        <v>0.2985782</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>0.36206895</v>
+        <v>0.36864406</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4857143</v>
+        <v>0.48341233</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.290909</v>
+        <v>1.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -3250,13 +3250,13 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1818181</v>
+        <v>1.0727273</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>0.215</v>
+        <v>0.2</v>
       </c>
       <c r="U8" t="n">
         <v>5</v>
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.20918368</v>
+        <v>0.24120604</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
         <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
+        <v>22</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.32599118</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.37185928</v>
+      </c>
+      <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
+        <v>57</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.3653846</v>
+      </c>
+      <c r="O9" t="n">
+        <v>26</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>28</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5384616</v>
+      </c>
+      <c r="S9" t="n">
+        <v>29</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.25980392</v>
+      </c>
+      <c r="U9" t="n">
         <v>24</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.29596412</v>
-      </c>
-      <c r="I9" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.31632653</v>
-      </c>
-      <c r="K9" t="n">
-        <v>25</v>
-      </c>
-      <c r="L9" t="n">
-        <v>61</v>
-      </c>
-      <c r="M9" t="n">
-        <v>21</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>23</v>
-      </c>
-      <c r="P9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>27</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3518518</v>
-      </c>
-      <c r="S9" t="n">
-        <v>23</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.23786408</v>
-      </c>
-      <c r="U9" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22727273</v>
+        <v>0.23383084</v>
       </c>
       <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
         <v>19</v>
       </c>
-      <c r="D10" t="n">
-        <v>21</v>
-      </c>
       <c r="E10" t="n">
+        <v>27</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.29223743</v>
+      </c>
+      <c r="I10" t="n">
         <v>23</v>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.30493274</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
+        <v>0.3034826</v>
+      </c>
+      <c r="K10" t="n">
+        <v>25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>47</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.1666667</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2962962</v>
+      </c>
+      <c r="S10" t="n">
         <v>15</v>
       </c>
-      <c r="J10" t="n">
-        <v>0.28282827</v>
-      </c>
-      <c r="K10" t="n">
-        <v>27</v>
-      </c>
-      <c r="L10" t="n">
-        <v>57</v>
-      </c>
-      <c r="M10" t="n">
-        <v>12</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.3540373</v>
-      </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>11</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3043478</v>
-      </c>
-      <c r="S10" t="n">
-        <v>19</v>
-      </c>
       <c r="T10" t="n">
-        <v>0.24390244</v>
+        <v>0.24757281</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2962963</v>
+        <v>0.2857143</v>
       </c>
       <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.34710744</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.49308756</v>
+      </c>
+      <c r="K11" t="n">
         <v>4</v>
       </c>
-      <c r="D11" t="n">
-        <v>31</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="L11" t="n">
+        <v>54</v>
+      </c>
+      <c r="M11" t="n">
+        <v>13</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.1132073</v>
+      </c>
+      <c r="O11" t="n">
+        <v>29</v>
+      </c>
+      <c r="P11" t="n">
         <v>9</v>
       </c>
-      <c r="F11" t="n">
-        <v>8</v>
-      </c>
-      <c r="G11" t="n">
-        <v>12</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.34468085</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.47685185</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>58</v>
-      </c>
-      <c r="M11" t="n">
-        <v>14</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.754717</v>
-      </c>
-      <c r="O11" t="n">
-        <v>26</v>
-      </c>
-      <c r="P11" t="n">
-        <v>7</v>
-      </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4150944</v>
+        <v>1.5283018</v>
       </c>
       <c r="S11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2809524</v>
+        <v>0.30593607</v>
       </c>
       <c r="U11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24034335</v>
+        <v>0.24166666</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31800765</v>
+        <v>0.31598514</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>0.40772533</v>
+        <v>0.3875</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N12" t="n">
         <v>3.375</v>
       </c>
       <c r="O12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
         <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>1.046875</v>
+        <v>0.96875</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2231405</v>
+        <v>0.21008404</v>
       </c>
       <c r="U12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.22764228</v>
+        <v>0.22983871</v>
       </c>
       <c r="C13" t="n">
         <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
         <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.29927006</v>
+        <v>0.2930403</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J13" t="n">
-        <v>0.37804878</v>
+        <v>0.41532257</v>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65625</v>
+        <v>3.7384615</v>
       </c>
       <c r="O13" t="n">
         <v>13</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="n">
         <v>29</v>
       </c>
       <c r="R13" t="n">
-        <v>1.359375</v>
+        <v>1.2769231</v>
       </c>
       <c r="S13" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24481328</v>
+        <v>0.22764228</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -3604,16 +3604,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.20434782</v>
+        <v>0.2160804</v>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -3622,25 +3622,25 @@
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2570281</v>
+        <v>0.2685185</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3347826</v>
+        <v>0.35678393</v>
       </c>
       <c r="K14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M14" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N14" t="n">
-        <v>7.735955</v>
+        <v>8.940397000000001</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
@@ -3649,16 +3649,16 @@
         <v>11</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8033708</v>
+        <v>1.9668875</v>
       </c>
       <c r="S14" t="n">
         <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>0.32388663</v>
+        <v>0.3425926</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
@@ -3671,16 +3671,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.24378109</v>
+        <v>0.25</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -3689,46 +3689,46 @@
         <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30454546</v>
+        <v>0.31363636</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>0.35820895</v>
+        <v>0.38</v>
       </c>
       <c r="K15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M15" t="n">
         <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9272728</v>
+        <v>3.6666667</v>
       </c>
       <c r="O15" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>10</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.037037</v>
+      </c>
+      <c r="S15" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.0909091</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
       <c r="T15" t="n">
-        <v>0.21674877</v>
+        <v>0.19897959</v>
       </c>
       <c r="U15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.29816514</v>
+        <v>0.32300884</v>
       </c>
       <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="D16" t="n">
-        <v>38</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5</v>
-      </c>
       <c r="F16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
         <v>8</v>
       </c>
-      <c r="G16" t="n">
-        <v>12</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.37246963</v>
+        <v>0.38976377</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.47706422</v>
+        <v>0.50884956</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N16" t="n">
-        <v>3.0566037</v>
+        <v>3.5660377</v>
       </c>
       <c r="O16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P16" t="n">
         <v>6</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>1.245283</v>
+        <v>1.3773584</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T16" t="n">
-        <v>0.20942408</v>
+        <v>0.24120604</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25773194</v>
+        <v>0.27860695</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H17" t="n">
-        <v>0.31924883</v>
+        <v>0.34684685</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4072165</v>
+        <v>0.46766168</v>
       </c>
       <c r="K17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2075472</v>
+        <v>2.7169812</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
         <v>6</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>1.018868</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>0.21578947</v>
+        <v>0.21989529</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.22</v>
+        <v>0.24242425</v>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
+        <v>24</v>
+      </c>
+      <c r="E18" t="n">
         <v>21</v>
       </c>
-      <c r="E18" t="n">
-        <v>23</v>
-      </c>
       <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3288889</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.44949496</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>53</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.4363637</v>
+      </c>
+      <c r="O18" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" t="n">
         <v>6</v>
       </c>
-      <c r="G18" t="n">
-        <v>18</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.29464287</v>
-      </c>
-      <c r="I18" t="n">
-        <v>21</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K18" t="n">
-        <v>16</v>
-      </c>
-      <c r="L18" t="n">
-        <v>58</v>
-      </c>
-      <c r="M18" t="n">
-        <v>14</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.892857</v>
-      </c>
-      <c r="O18" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5</v>
-      </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0714285</v>
+        <v>1.2363636</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T18" t="n">
-        <v>0.16230367</v>
+        <v>0.19587629</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24390244</v>
+        <v>0.26190478</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.30666667</v>
+      </c>
+      <c r="I19" t="n">
+        <v>18</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.44761905</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" t="n">
+        <v>36</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.0545454</v>
+      </c>
+      <c r="O19" t="n">
+        <v>27</v>
+      </c>
+      <c r="P19" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q19" t="n">
         <v>24</v>
       </c>
-      <c r="E19" t="n">
-        <v>19</v>
-      </c>
-      <c r="F19" t="n">
-        <v>7</v>
-      </c>
-      <c r="G19" t="n">
-        <v>14</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.29090908</v>
-      </c>
-      <c r="I19" t="n">
-        <v>24</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.40487805</v>
-      </c>
-      <c r="K19" t="n">
-        <v>12</v>
-      </c>
-      <c r="L19" t="n">
-        <v>33</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5.7272725</v>
-      </c>
-      <c r="O19" t="n">
-        <v>29</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>23</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.5636364</v>
+        <v>1.5090909</v>
       </c>
       <c r="S19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T19" t="n">
-        <v>0.29464287</v>
+        <v>0.28636363</v>
       </c>
       <c r="U19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2212766</v>
+        <v>0.21348314</v>
       </c>
       <c r="C20" t="n">
+        <v>26</v>
+      </c>
+      <c r="D20" t="n">
+        <v>29</v>
+      </c>
+      <c r="E20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.31270358</v>
+      </c>
+      <c r="I20" t="n">
+        <v>16</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.39325842</v>
+      </c>
+      <c r="K20" t="n">
+        <v>16</v>
+      </c>
+      <c r="L20" t="n">
+        <v>66</v>
+      </c>
+      <c r="M20" t="n">
+        <v>25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="O20" t="n">
         <v>21</v>
-      </c>
-      <c r="D20" t="n">
-        <v>28</v>
-      </c>
-      <c r="E20" t="n">
-        <v>13</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.32352942</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.40425533</v>
-      </c>
-      <c r="K20" t="n">
-        <v>13</v>
-      </c>
-      <c r="L20" t="n">
-        <v>61</v>
-      </c>
-      <c r="M20" t="n">
-        <v>21</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.640625</v>
-      </c>
-      <c r="O20" t="n">
-        <v>25</v>
       </c>
       <c r="P20" t="n">
         <v>7</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.265625</v>
+        <v>1.2361112</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23577236</v>
+        <v>0.22710623</v>
       </c>
       <c r="U20" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.17030568</v>
+        <v>0.15555556</v>
       </c>
       <c r="C21" t="n">
         <v>30</v>
@@ -4082,55 +4082,55 @@
         <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" t="n">
         <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2244898</v>
+        <v>0.20502092</v>
       </c>
       <c r="I21" t="n">
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>0.29257643</v>
+        <v>0.28444445</v>
       </c>
       <c r="K21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L21" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1853933</v>
+        <v>2.685083</v>
       </c>
       <c r="O21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" t="n">
         <v>5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>6</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.2808989</v>
+        <v>1.2762431</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>0.24215247</v>
+        <v>0.24347825</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.26907632</v>
+        <v>0.28286853</v>
       </c>
       <c r="C22" t="n">
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>13</v>
+      </c>
+      <c r="G22" t="n">
         <v>2</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
+        <v>0.33695653</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.48207173</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>69</v>
+      </c>
+      <c r="M22" t="n">
+        <v>26</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.080645</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25</v>
+      </c>
+      <c r="P22" t="n">
         <v>10</v>
       </c>
-      <c r="G22" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.31598514</v>
-      </c>
-      <c r="I22" t="n">
-        <v>13</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.437751</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>68</v>
-      </c>
-      <c r="M22" t="n">
-        <v>27</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.2786884</v>
-      </c>
-      <c r="O22" t="n">
-        <v>21</v>
-      </c>
-      <c r="P22" t="n">
-        <v>9</v>
-      </c>
       <c r="Q22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.295082</v>
+        <v>1.3225807</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.23430963</v>
+        <v>0.23012552</v>
       </c>
       <c r="U22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3018868</v>
+        <v>0.30120483</v>
       </c>
       <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>49</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>14</v>
+      </c>
+      <c r="G23" t="n">
         <v>1</v>
       </c>
-      <c r="D23" t="n">
-        <v>38</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" t="n">
-        <v>11</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
+        <v>0.3642857</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5421686999999999</v>
+      </c>
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="n">
-        <v>0.3628692</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.5235849</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
       <c r="L23" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="M23" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6666667</v>
+        <v>4.142857</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2037038</v>
+        <v>1.2222222</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23267327</v>
+        <v>0.23728813</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22950819</v>
+        <v>0.2565445</v>
       </c>
       <c r="C24" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" t="n">
+        <v>26</v>
+      </c>
+      <c r="E24" t="n">
+        <v>18</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.36160713</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.39267015</v>
+      </c>
+      <c r="K24" t="n">
         <v>17</v>
       </c>
-      <c r="D24" t="n">
-        <v>25</v>
-      </c>
-      <c r="E24" t="n">
-        <v>16</v>
-      </c>
-      <c r="F24" t="n">
-        <v>6</v>
-      </c>
-      <c r="G24" t="n">
-        <v>18</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.35746607</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.38251367</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
+        <v>43</v>
+      </c>
+      <c r="M24" t="n">
+        <v>7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.280488</v>
+      </c>
+      <c r="O24" t="n">
         <v>19</v>
-      </c>
-      <c r="L24" t="n">
-        <v>45</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.7636364</v>
-      </c>
-      <c r="O24" t="n">
-        <v>15</v>
       </c>
       <c r="P24" t="n">
         <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>1.290909</v>
+        <v>1.4085366</v>
       </c>
       <c r="S24" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="T24" t="n">
-        <v>0.23943663</v>
+        <v>0.2535211</v>
       </c>
       <c r="U24" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.23243243</v>
+        <v>0.23744293</v>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30097088</v>
+        <v>0.29752067</v>
       </c>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4</v>
+        <v>0.40182647</v>
       </c>
       <c r="K25" t="n">
         <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3333333</v>
+        <v>2.7580645</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.048387</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.19090909</v>
+      </c>
+      <c r="U25" t="n">
         <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.9814815</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.1865285</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -4408,61 +4408,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23076923</v>
+        <v>0.22689076</v>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31330472</v>
+        <v>0.30827066</v>
       </c>
       <c r="I26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3221154</v>
+        <v>0.34453782</v>
       </c>
       <c r="K26" t="n">
         <v>24</v>
       </c>
       <c r="L26" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="M26" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>5.04</v>
+        <v>4.576271</v>
       </c>
       <c r="O26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.3559322</v>
       </c>
       <c r="S26" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28</v>
+        <v>0.27586207</v>
       </c>
       <c r="U26" t="n">
         <v>27</v>
@@ -4475,61 +4475,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.20765027</v>
+        <v>0.19871795</v>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F27" t="n">
         <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H27" t="n">
-        <v>0.27093595</v>
+        <v>0.2529412</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>0.27322406</v>
+        <v>0.27564102</v>
       </c>
       <c r="K27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L27" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8333333</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3333334</v>
+        <v>1.4222223</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25123152</v>
+        <v>0.25443786</v>
       </c>
       <c r="U27" t="n">
         <v>23</v>
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2857143</v>
+        <v>0.30051813</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
         <v>12</v>
       </c>
       <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.37155962</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.54404145</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.35458168</v>
-      </c>
-      <c r="I28" t="n">
-        <v>5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.5089286</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
-      </c>
       <c r="L28" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4285715</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
         <v>8</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8730159</v>
+        <v>0.9074074</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1991342</v>
+        <v>0.21</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.26359832</v>
+        <v>0.26859504</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
         <v>9</v>
       </c>
       <c r="F29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.34200743</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.44214877</v>
+      </c>
+      <c r="K29" t="n">
         <v>11</v>
       </c>
-      <c r="G29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.34686348</v>
-      </c>
-      <c r="I29" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.43933055</v>
-      </c>
-      <c r="K29" t="n">
-        <v>6</v>
-      </c>
       <c r="L29" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N29" t="n">
         <v>4.1311474</v>
       </c>
       <c r="O29" t="n">
+        <v>16</v>
+      </c>
+      <c r="P29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="n">
         <v>20</v>
       </c>
-      <c r="P29" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>21</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.1475409</v>
+        <v>1.1803279</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2413793</v>
+        <v>0.24894515</v>
       </c>
       <c r="U29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24380165</v>
+        <v>0.21757323</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
+        <v>25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.26744187</v>
+      </c>
+      <c r="I30" t="n">
         <v>27</v>
       </c>
-      <c r="E30" t="n">
-        <v>14</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9</v>
-      </c>
-      <c r="G30" t="n">
-        <v>8</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.29433963</v>
-      </c>
-      <c r="I30" t="n">
-        <v>22</v>
-      </c>
       <c r="J30" t="n">
-        <v>0.38429752</v>
+        <v>0.35564855</v>
       </c>
       <c r="K30" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L30" t="n">
         <v>62</v>
       </c>
       <c r="M30" t="n">
+        <v>19</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.292308</v>
+      </c>
+      <c r="O30" t="n">
+        <v>20</v>
+      </c>
+      <c r="P30" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q30" t="n">
         <v>24</v>
       </c>
-      <c r="N30" t="n">
-        <v>4.4307694</v>
-      </c>
-      <c r="O30" t="n">
-        <v>22</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>23</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.5384616</v>
+        <v>1.4769231</v>
       </c>
       <c r="S30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T30" t="n">
-        <v>0.25409836</v>
+        <v>0.25101215</v>
       </c>
       <c r="U30" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -4743,61 +4743,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.23694779</v>
+        <v>0.22040816</v>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>0.29889297</v>
+        <v>0.2846442</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42971888</v>
+        <v>0.39591837</v>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L31" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="M31" t="n">
         <v>29</v>
       </c>
       <c r="N31" t="n">
-        <v>5.285714</v>
+        <v>6.096774</v>
       </c>
       <c r="O31" t="n">
         <v>28</v>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3809524</v>
+        <v>1.483871</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25506073</v>
+        <v>0.2734694</v>
       </c>
       <c r="U31" t="n">
         <v>26</v>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23759885</v>
+        <v>0.23828125</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3079406</v>
+        <v>0.3093342</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3860532</v>
+        <v>0.3877841</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L2" t="n">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.325361</v>
+        <v>4.2973695</v>
       </c>
       <c r="O2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q2" t="n">
         <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2955775</v>
+        <v>1.2880071</v>
       </c>
       <c r="S2" t="n">
         <v>14</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25150976</v>
+        <v>0.25026363</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24758953</v>
+        <v>0.24719101</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G3" t="n">
         <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32721713</v>
+        <v>0.32627118</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4090909</v>
+        <v>0.4082397</v>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9736843</v>
+        <v>5.0208063</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4407895</v>
+        <v>1.4486346</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26358697</v>
+        <v>0.26492286</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24757455</v>
+        <v>0.24689165</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E4" t="n">
         <v>13</v>
@@ -695,46 +695,46 @@
         <v>103</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31059128</v>
+        <v>0.31099713</v>
       </c>
       <c r="I4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40855193</v>
+        <v>0.4063943</v>
       </c>
       <c r="K4" t="n">
         <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4059634</v>
+        <v>3.4254644</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2110091</v>
+        <v>1.2111464</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2260579</v>
+        <v>0.22560528</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23824452</v>
+        <v>0.23847213</v>
       </c>
       <c r="C5" t="n">
         <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
@@ -762,49 +762,49 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3179155</v>
+        <v>0.31789088</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3967259</v>
+        <v>0.39573297</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3780594</v>
+        <v>4.4319654</v>
       </c>
       <c r="O5" t="n">
         <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q5" t="n">
         <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3767482</v>
+        <v>1.3840172</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25502214</v>
+        <v>0.2557983</v>
       </c>
       <c r="U5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -814,16 +814,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24396396</v>
+        <v>0.24269423</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
         <v>73</v>
@@ -832,46 +832,46 @@
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31203374</v>
+        <v>0.31021196</v>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38630632</v>
+        <v>0.38382038</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>675</v>
+        <v>688</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6868458</v>
+        <v>3.7392087</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>1.238507</v>
+        <v>1.2464029</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24034645</v>
+        <v>0.24153902</v>
       </c>
       <c r="U6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -881,64 +881,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24111763</v>
+        <v>0.24293016</v>
       </c>
       <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>425</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>104</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.33755895</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.40511075</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="n">
+        <v>727</v>
+      </c>
+      <c r="M7" t="n">
+        <v>18</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.245209</v>
+      </c>
+      <c r="O7" t="n">
         <v>19</v>
       </c>
-      <c r="D7" t="n">
-        <v>416</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="n">
-        <v>99</v>
-      </c>
-      <c r="G7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.33582088</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.400138</v>
-      </c>
-      <c r="K7" t="n">
-        <v>13</v>
-      </c>
-      <c r="L7" t="n">
-        <v>722</v>
-      </c>
-      <c r="M7" t="n">
-        <v>19</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.2124286</v>
-      </c>
-      <c r="O7" t="n">
-        <v>17</v>
-      </c>
       <c r="P7" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2494491</v>
+        <v>1.2543554</v>
       </c>
       <c r="S7" t="n">
         <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24014084</v>
+        <v>0.24140327</v>
       </c>
       <c r="U7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24232575</v>
+        <v>0.24296401</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="E8" t="n">
         <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32278684</v>
+        <v>0.32366845</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41603467</v>
+        <v>0.41752762</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2206616</v>
+        <v>4.205909</v>
       </c>
       <c r="O8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
         <v>89</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3239691</v>
+        <v>1.3240824</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23920146</v>
+        <v>0.23942652</v>
       </c>
       <c r="U8" t="n">
         <v>13</v>
@@ -1015,64 +1015,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22781171</v>
+        <v>0.22743426</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3098726</v>
+        <v>0.30917114</v>
       </c>
       <c r="I9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3891484</v>
+        <v>0.3891258</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="M9" t="n">
         <v>27</v>
       </c>
       <c r="N9" t="n">
-        <v>4.585135</v>
+        <v>4.620321</v>
       </c>
       <c r="O9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q9" t="n">
         <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4581081</v>
+        <v>1.4639038</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2493801</v>
+        <v>0.25113675</v>
       </c>
       <c r="U9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22867383</v>
+        <v>0.22785258</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E10" t="n">
         <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3116883</v>
+        <v>0.31012857</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3641577</v>
+        <v>0.36321756</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7749667</v>
+        <v>3.7657895</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2636485</v>
+        <v>1.2565789</v>
       </c>
       <c r="S10" t="n">
         <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23819666</v>
+        <v>0.23754387</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25527498</v>
+        <v>0.25427788</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E11" t="n">
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" t="n">
         <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32475185</v>
+        <v>0.32464746</v>
       </c>
       <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.41546887</v>
+      </c>
+      <c r="K11" t="n">
         <v>7</v>
       </c>
-      <c r="J11" t="n">
-        <v>0.41611898</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
       <c r="L11" t="n">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5254693</v>
+        <v>5.62649</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5134048</v>
+        <v>1.5258278</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2862441</v>
+        <v>0.28874874</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,64 +1216,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23564848</v>
+        <v>0.23636363</v>
       </c>
       <c r="C12" t="n">
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31512868</v>
+        <v>0.31503877</v>
       </c>
       <c r="I12" t="n">
         <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39404678</v>
+        <v>0.39825174</v>
       </c>
       <c r="K12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L12" t="n">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7848215</v>
+        <v>3.763564</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q12" t="n">
         <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2375</v>
+        <v>1.229378</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23631841</v>
+        <v>0.23514938</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2413793</v>
+        <v>0.24147248</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31541985</v>
+        <v>0.3156146</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41037896</v>
+        <v>0.40999663</v>
       </c>
       <c r="K13" t="n">
         <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="M13" t="n">
         <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>4.743401</v>
+        <v>4.734816</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
@@ -1328,19 +1328,19 @@
         <v>116</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.396798</v>
+        <v>1.3909324</v>
       </c>
       <c r="S13" t="n">
         <v>24</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24152249</v>
+        <v>0.24093087</v>
       </c>
       <c r="U13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2445614</v>
+        <v>0.24392782</v>
       </c>
       <c r="C14" t="n">
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G14" t="n">
         <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3163329</v>
+        <v>0.3152679</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39052632</v>
+        <v>0.39208883</v>
       </c>
       <c r="K14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L14" t="n">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
-        <v>4.826145</v>
+        <v>4.875659</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4259671</v>
+        <v>1.4380492</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26018807</v>
+        <v>0.2611092</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23998618</v>
+        <v>0.23967224</v>
       </c>
       <c r="C15" t="n">
         <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -1432,31 +1432,31 @@
         <v>101</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31816784</v>
+        <v>0.31772575</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39813536</v>
+        <v>0.3960396</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L15" t="n">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5849056</v>
+        <v>4.630916</v>
       </c>
       <c r="O15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P15" t="n">
         <v>92</v>
@@ -1465,16 +1465,16 @@
         <v>15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.399298</v>
+        <v>1.405558</v>
       </c>
       <c r="S15" t="n">
         <v>26</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23623693</v>
+        <v>0.2377839</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26429567</v>
+        <v>0.26565725</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3464591</v>
+        <v>0.3474857</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.44142258</v>
+        <v>0.4432209</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4350533</v>
+        <v>3.4298902</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q16" t="n">
         <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1183274</v>
+        <v>1.1156044</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21389794</v>
+        <v>0.21387696</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2472351</v>
+        <v>0.2505263</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32384565</v>
+        <v>0.32627645</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39207992</v>
+        <v>0.3982456</v>
       </c>
       <c r="K17" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="M17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9759035</v>
+        <v>3.9642856</v>
       </c>
       <c r="O17" t="n">
         <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2409638</v>
+        <v>1.2407408</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22802001</v>
+        <v>0.2272888</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2532374</v>
+        <v>0.2549716</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G18" t="n">
         <v>25</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33733797</v>
+        <v>0.33833176</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39460433</v>
+        <v>0.39701703</v>
       </c>
       <c r="K18" t="n">
         <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>3.400997</v>
+        <v>3.3840644</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1826007</v>
+        <v>1.179051</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21893491</v>
+        <v>0.21864717</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,16 +1685,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24716398</v>
+        <v>0.2465148</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>107</v>
@@ -1703,46 +1703,46 @@
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32137382</v>
+        <v>0.32069173</v>
       </c>
       <c r="I19" t="n">
         <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.41285664</v>
+        <v>0.41074464</v>
       </c>
       <c r="K19" t="n">
         <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="M19" t="n">
         <v>14</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8476734</v>
+        <v>4.8675065</v>
       </c>
       <c r="O19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P19" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q19" t="n">
         <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3985953</v>
+        <v>1.3983493</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2557981</v>
+        <v>0.2557355</v>
       </c>
       <c r="U19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -1752,43 +1752,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23022847</v>
+        <v>0.23002085</v>
       </c>
       <c r="C20" t="n">
         <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G20" t="n">
         <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29873016</v>
+        <v>0.29839975</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37398946</v>
+        <v>0.37456566</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="M20" t="n">
         <v>15</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1045694</v>
+        <v>4.056448</v>
       </c>
       <c r="O20" t="n">
         <v>13</v>
@@ -1797,16 +1797,16 @@
         <v>85</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2759227</v>
+        <v>1.2726878</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23267154</v>
+        <v>0.23243801</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -1819,64 +1819,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23770198</v>
+        <v>0.23650569</v>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3213042</v>
+        <v>0.31986216</v>
       </c>
       <c r="I21" t="n">
         <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>0.42477557</v>
+        <v>0.42258522</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="M21" t="n">
         <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3038995</v>
+        <v>3.360053</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.191394</v>
+        <v>1.1930912</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22694525</v>
+        <v>0.22778963</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1886,43 +1886,43 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23593149</v>
+        <v>0.23722376</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="E22" t="n">
         <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G22" t="n">
         <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30173776</v>
+        <v>0.30305868</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40230688</v>
+        <v>0.40331492</v>
       </c>
       <c r="K22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L22" t="n">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1465135</v>
+        <v>4.0976887</v>
       </c>
       <c r="O22" t="n">
         <v>15</v>
@@ -1931,16 +1931,16 @@
         <v>98</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3040601</v>
+        <v>1.2991714</v>
       </c>
       <c r="S22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25487512</v>
+        <v>0.2538071</v>
       </c>
       <c r="U22" t="n">
         <v>23</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25873178</v>
+        <v>0.25763166</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -1968,49 +1968,49 @@
         <v>108</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>0.337136</v>
+        <v>0.33600712</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.42048153</v>
+        <v>0.41798055</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>796</v>
+        <v>809</v>
       </c>
       <c r="M23" t="n">
         <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.171116</v>
+        <v>4.2213078</v>
       </c>
       <c r="O23" t="n">
+        <v>17</v>
+      </c>
+      <c r="P23" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3044608</v>
+      </c>
+      <c r="S23" t="n">
         <v>16</v>
       </c>
-      <c r="P23" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.2984682</v>
-      </c>
-      <c r="S23" t="n">
-        <v>15</v>
-      </c>
       <c r="T23" t="n">
-        <v>0.23604852</v>
+        <v>0.23732877</v>
       </c>
       <c r="U23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22181146</v>
+        <v>0.2233965</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2979848</v>
+        <v>0.29912025</v>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>0.36524954</v>
+        <v>0.36953354</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="M24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N24" t="n">
-        <v>3.885068</v>
+        <v>3.940018</v>
       </c>
       <c r="O24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P24" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3045249</v>
+        <v>1.316025</v>
       </c>
       <c r="S24" t="n">
         <v>17</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24301778</v>
+        <v>0.24453992</v>
       </c>
       <c r="U24" t="n">
         <v>19</v>
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25573316</v>
+        <v>0.25447044</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E25" t="n">
         <v>26</v>
       </c>
       <c r="F25" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G25" t="n">
         <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3079132</v>
+        <v>0.30669615</v>
       </c>
       <c r="I25" t="n">
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41730368</v>
+        <v>0.41712517</v>
       </c>
       <c r="K25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>657</v>
+      </c>
+      <c r="M25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" t="n">
-        <v>654</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6</v>
-      </c>
       <c r="N25" t="n">
-        <v>4.32</v>
+        <v>4.369942</v>
       </c>
       <c r="O25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P25" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3617977</v>
+        <v>1.3699422</v>
       </c>
       <c r="S25" t="n">
         <v>21</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24723116</v>
+        <v>0.24779385</v>
       </c>
       <c r="U25" t="n">
         <v>20</v>
@@ -2154,16 +2154,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23141655</v>
+        <v>0.23303324</v>
       </c>
       <c r="C26" t="n">
         <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
         <v>105</v>
@@ -2172,28 +2172,28 @@
         <v>10</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31218904</v>
+        <v>0.31336406</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38359046</v>
+        <v>0.3836565</v>
       </c>
       <c r="K26" t="n">
         <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>734</v>
+        <v>750</v>
       </c>
       <c r="M26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6968503</v>
+        <v>3.688716</v>
       </c>
       <c r="O26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
         <v>80</v>
@@ -2202,16 +2202,16 @@
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.191601</v>
+        <v>1.1893644</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24185069</v>
+        <v>0.24116424</v>
       </c>
       <c r="U26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -2221,64 +2221,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24632353</v>
+        <v>0.24563953</v>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E27" t="n">
         <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G27" t="n">
         <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32378784</v>
+        <v>0.3233687</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3930147</v>
+        <v>0.39280522</v>
       </c>
       <c r="K27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L27" t="n">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2598896</v>
+        <v>4.2444344</v>
       </c>
       <c r="O27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P27" t="n">
         <v>89</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3454461</v>
+        <v>1.3466606</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25551936</v>
+        <v>0.2547406</v>
       </c>
       <c r="U27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25916326</v>
+        <v>0.26015368</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G28" t="n">
         <v>29</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3361758</v>
+        <v>0.3388296</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39392817</v>
+        <v>0.39553604</v>
       </c>
       <c r="K28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L28" t="n">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7790055</v>
+        <v>3.781719</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P28" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2002763</v>
+        <v>1.1950886</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23497067</v>
+        <v>0.23442028</v>
       </c>
       <c r="U28" t="n">
         <v>7</v>
@@ -2355,64 +2355,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24435826</v>
+        <v>0.2436389</v>
       </c>
       <c r="C29" t="n">
         <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E29" t="n">
         <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G29" t="n">
         <v>19</v>
       </c>
       <c r="H29" t="n">
-        <v>0.32033953</v>
+        <v>0.31891724</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39210156</v>
+        <v>0.39177415</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="M29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9485688</v>
+        <v>3.9253204</v>
       </c>
       <c r="O29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P29" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q29" t="n">
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2397138</v>
+        <v>1.231551</v>
       </c>
       <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.23686956</v>
+      </c>
+      <c r="U29" t="n">
         <v>9</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.237777</v>
-      </c>
-      <c r="U29" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24728547</v>
+        <v>0.2465374</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
         <v>345</v>
@@ -2437,46 +2437,46 @@
         <v>86</v>
       </c>
       <c r="G30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30954647</v>
+        <v>0.30865747</v>
       </c>
       <c r="I30" t="n">
+        <v>26</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.3874654</v>
+      </c>
+      <c r="K30" t="n">
         <v>25</v>
       </c>
-      <c r="J30" t="n">
-        <v>0.38949212</v>
-      </c>
-      <c r="K30" t="n">
-        <v>23</v>
-      </c>
       <c r="L30" t="n">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="M30" t="n">
         <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1208644</v>
+        <v>4.0959024</v>
       </c>
       <c r="O30" t="n">
         <v>14</v>
       </c>
       <c r="P30" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q30" t="n">
         <v>16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3193648</v>
+        <v>1.3169136</v>
       </c>
       <c r="S30" t="n">
         <v>18</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2422012</v>
+        <v>0.24185725</v>
       </c>
       <c r="U30" t="n">
         <v>18</v>
@@ -2489,43 +2489,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24525101</v>
+        <v>0.24631368</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G31" t="n">
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3180158</v>
+        <v>0.3192065</v>
       </c>
       <c r="I31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42096338</v>
+        <v>0.4219169</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="M31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7118793</v>
+        <v>4.6575575</v>
       </c>
       <c r="O31" t="n">
         <v>25</v>
@@ -2537,13 +2537,13 @@
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3904967</v>
+        <v>1.37959</v>
       </c>
       <c r="S31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25762144</v>
+        <v>0.25629973</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2244898</v>
+        <v>0.24242425</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.29816514</v>
+        <v>0.3167421</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J2" t="n">
-        <v>0.40816328</v>
+        <v>0.44444445</v>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>34</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5882354</v>
+        <v>4.4117646</v>
       </c>
       <c r="O2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q2" t="n">
         <v>23</v>
       </c>
-      <c r="P2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>17</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.2352941</v>
+        <v>1.137255</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25396827</v>
+        <v>0.24064171</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2867,22 +2867,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.22553192</v>
+        <v>0.23849373</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
         <v>0.30152673</v>
@@ -2891,40 +2891,40 @@
         <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2851064</v>
+        <v>0.31380752</v>
       </c>
       <c r="K3" t="n">
+        <v>25</v>
+      </c>
+      <c r="L3" t="n">
+        <v>70</v>
+      </c>
+      <c r="M3" t="n">
+        <v>25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.6373625</v>
+      </c>
+      <c r="O3" t="n">
+        <v>27</v>
+      </c>
+      <c r="P3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4505494</v>
+      </c>
+      <c r="S3" t="n">
         <v>26</v>
       </c>
-      <c r="L3" t="n">
-        <v>62</v>
-      </c>
-      <c r="M3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.8268156</v>
-      </c>
-      <c r="O3" t="n">
-        <v>24</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>20</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.3743017</v>
-      </c>
-      <c r="S3" t="n">
-        <v>21</v>
-      </c>
       <c r="T3" t="n">
-        <v>0.26923078</v>
+        <v>0.2821577</v>
       </c>
       <c r="U3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2934,40 +2934,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1764706</v>
+        <v>0.16666667</v>
       </c>
       <c r="C4" t="n">
         <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>0.23243243</v>
+        <v>0.23756906</v>
       </c>
       <c r="I4" t="n">
         <v>29</v>
       </c>
       <c r="J4" t="n">
-        <v>0.25882354</v>
+        <v>0.22222222</v>
       </c>
       <c r="K4" t="n">
         <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>3.857143</v>
@@ -2976,22 +2976,22 @@
         <v>14</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
         <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3333334</v>
+        <v>1.2857143</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2516129</v>
+        <v>0.23684211</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.185567</v>
+        <v>0.21</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" t="n">
-        <v>0.27272728</v>
+        <v>0.29515418</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J5" t="n">
-        <v>0.28350514</v>
+        <v>0.315</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="M5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9512196</v>
+        <v>4.526946</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3170731</v>
+        <v>1.4371257</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="T5" t="n">
-        <v>0.23831776</v>
+        <v>0.24774775</v>
       </c>
       <c r="U5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2631579</v>
+        <v>0.23766816</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32421875</v>
+        <v>0.2857143</v>
       </c>
       <c r="I6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.41704035</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L6" t="n">
+        <v>54</v>
+      </c>
+      <c r="M6" t="n">
         <v>12</v>
       </c>
-      <c r="J6" t="n">
-        <v>0.4649123</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>45</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8</v>
-      </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.857143</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.0793651</v>
+      </c>
+      <c r="S6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
+        <v>0.21276596</v>
+      </c>
+      <c r="U6" t="n">
         <v>7</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.984127</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.19742489</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.21818182</v>
+        <v>0.23655914</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -3147,52 +3147,52 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32407406</v>
+        <v>0.3353846</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3890909</v>
+        <v>0.4265233</v>
       </c>
       <c r="K7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M7" t="n">
         <v>30</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5753424</v>
+        <v>3.69863</v>
       </c>
       <c r="O7" t="n">
         <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3561643</v>
+        <v>1.3835616</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24542125</v>
+        <v>0.2642857</v>
       </c>
       <c r="U7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2985782</v>
+        <v>0.3198198</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.36864406</v>
+        <v>0.3968254</v>
       </c>
       <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.518018</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.48341233</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
       <c r="L8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M8" t="n">
         <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>1.8</v>
+        <v>2.1272728</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0727273</v>
+        <v>1.1454545</v>
       </c>
       <c r="S8" t="n">
         <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2</v>
+        <v>0.21105528</v>
       </c>
       <c r="U8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.24120604</v>
+        <v>0.25615764</v>
       </c>
       <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.34051725</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.41379312</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16</v>
+      </c>
+      <c r="L9" t="n">
+        <v>54</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.529412</v>
+      </c>
+      <c r="O9" t="n">
+        <v>28</v>
+      </c>
+      <c r="P9" t="n">
         <v>15</v>
       </c>
-      <c r="D9" t="n">
-        <v>27</v>
-      </c>
-      <c r="E9" t="n">
-        <v>16</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>22</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.32599118</v>
-      </c>
-      <c r="I9" t="n">
-        <v>11</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.37185928</v>
-      </c>
-      <c r="K9" t="n">
-        <v>21</v>
-      </c>
-      <c r="L9" t="n">
-        <v>57</v>
-      </c>
-      <c r="M9" t="n">
-        <v>16</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.3653846</v>
-      </c>
-      <c r="O9" t="n">
-        <v>26</v>
-      </c>
-      <c r="P9" t="n">
-        <v>13</v>
-      </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5384616</v>
+        <v>1.7254902</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25980392</v>
+        <v>0.3014354</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.23383084</v>
+        <v>0.22772278</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2764977</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2920792</v>
+      </c>
+      <c r="K10" t="n">
         <v>28</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.29223743</v>
-      </c>
-      <c r="I10" t="n">
-        <v>23</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.3034826</v>
-      </c>
-      <c r="K10" t="n">
-        <v>25</v>
-      </c>
       <c r="L10" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1666667</v>
+        <v>3.2727273</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2962962</v>
+        <v>1.3090909</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T10" t="n">
-        <v>0.24757281</v>
+        <v>0.254717</v>
       </c>
       <c r="U10" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -3403,61 +3403,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2857143</v>
+        <v>0.27570093</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="F11" t="n">
-        <v>9</v>
-      </c>
       <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.34979424</v>
+      </c>
+      <c r="I11" t="n">
         <v>8</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.34710744</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6</v>
-      </c>
       <c r="J11" t="n">
-        <v>0.49308756</v>
+        <v>0.4813084</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N11" t="n">
-        <v>6.1132073</v>
+        <v>7.6415095</v>
       </c>
       <c r="O11" t="n">
         <v>29</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5283018</v>
+        <v>1.6415094</v>
       </c>
       <c r="S11" t="n">
         <v>28</v>
       </c>
       <c r="T11" t="n">
-        <v>0.30593607</v>
+        <v>0.3347826</v>
       </c>
       <c r="U11" t="n">
         <v>29</v>
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24166666</v>
+        <v>0.24796748</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
+        <v>13</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.31501833</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.44715446</v>
+      </c>
+      <c r="K12" t="n">
         <v>8</v>
       </c>
-      <c r="G12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.31598514</v>
-      </c>
-      <c r="I12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.3875</v>
-      </c>
-      <c r="K12" t="n">
-        <v>19</v>
-      </c>
       <c r="L12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.375</v>
+        <v>3.09375</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R12" t="n">
-        <v>0.96875</v>
+        <v>0.875</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0.21008404</v>
+        <v>0.1923077</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.22983871</v>
+        <v>0.21276596</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
         <v>9</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2846154</v>
+      </c>
+      <c r="I13" t="n">
+        <v>23</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.36595744</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" t="n">
+        <v>55</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.857143</v>
+      </c>
+      <c r="O13" t="n">
+        <v>14</v>
+      </c>
+      <c r="P13" t="n">
         <v>12</v>
       </c>
-      <c r="G13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.2930403</v>
-      </c>
-      <c r="I13" t="n">
-        <v>22</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.41532257</v>
-      </c>
-      <c r="K13" t="n">
-        <v>12</v>
-      </c>
-      <c r="L13" t="n">
-        <v>56</v>
-      </c>
-      <c r="M13" t="n">
-        <v>15</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.7384615</v>
-      </c>
-      <c r="O13" t="n">
-        <v>13</v>
-      </c>
-      <c r="P13" t="n">
-        <v>14</v>
-      </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2769231</v>
+        <v>1.1746032</v>
       </c>
       <c r="S13" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>0.22764228</v>
+        <v>0.2112069</v>
       </c>
       <c r="U13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2160804</v>
+        <v>0.18229167</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2685185</v>
+        <v>0.24038461</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>0.35678393</v>
+        <v>0.31770834</v>
       </c>
       <c r="K14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N14" t="n">
-        <v>8.940397000000001</v>
+        <v>9.655628999999999</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9668875</v>
+        <v>2.1059604</v>
       </c>
       <c r="S14" t="n">
         <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3425926</v>
+        <v>0.35514018</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
@@ -3671,46 +3671,46 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.25</v>
+        <v>0.2413793</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31363636</v>
+        <v>0.30941704</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>0.38</v>
+        <v>0.3497537</v>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M15" t="n">
         <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>3.6666667</v>
+        <v>4.924528</v>
       </c>
       <c r="O15" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P15" t="n">
         <v>6</v>
@@ -3719,16 +3719,16 @@
         <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>1.037037</v>
+        <v>1.264151</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>0.19897959</v>
+        <v>0.2413793</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -3738,40 +3738,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.32300884</v>
+        <v>0.3167421</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
+        <v>42</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.37903225</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.51131225</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
         <v>45</v>
       </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="M16" t="n">
         <v>8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.38976377</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.50884956</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>52</v>
-      </c>
-      <c r="M16" t="n">
-        <v>11</v>
       </c>
       <c r="N16" t="n">
         <v>3.5660377</v>
@@ -3780,22 +3780,22 @@
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3773584</v>
+        <v>1.3584906</v>
       </c>
       <c r="S16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T16" t="n">
-        <v>0.24120604</v>
+        <v>0.24242425</v>
       </c>
       <c r="U16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.27860695</v>
+        <v>0.30660376</v>
       </c>
       <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>38</v>
+      </c>
+      <c r="E17" t="n">
         <v>7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>30</v>
-      </c>
-      <c r="E17" t="n">
-        <v>13</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>0.34684685</v>
+        <v>0.36909872</v>
       </c>
       <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>41</v>
+      </c>
+      <c r="M17" t="n">
         <v>7</v>
       </c>
-      <c r="J17" t="n">
-        <v>0.46766168</v>
-      </c>
-      <c r="K17" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" t="n">
-        <v>42</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6</v>
-      </c>
       <c r="N17" t="n">
-        <v>2.7169812</v>
+        <v>2.54717</v>
       </c>
       <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
         <v>5</v>
       </c>
-      <c r="P17" t="n">
-        <v>6</v>
-      </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.018868</v>
+        <v>0.9811321</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0.21989529</v>
+        <v>0.19892474</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.24242425</v>
+        <v>0.2857143</v>
       </c>
       <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>29</v>
+      </c>
+      <c r="E18" t="n">
+        <v>14</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.36123347</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5123153</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>51</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.7636364</v>
+      </c>
+      <c r="O18" t="n">
         <v>13</v>
       </c>
-      <c r="D18" t="n">
-        <v>24</v>
-      </c>
-      <c r="E18" t="n">
-        <v>21</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8</v>
-      </c>
-      <c r="G18" t="n">
-        <v>14</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.3288889</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.44949496</v>
-      </c>
-      <c r="K18" t="n">
-        <v>9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>53</v>
-      </c>
-      <c r="M18" t="n">
-        <v>12</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.4363637</v>
-      </c>
-      <c r="O18" t="n">
-        <v>9</v>
-      </c>
       <c r="P18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>13</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3454546</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.21212122</v>
+      </c>
+      <c r="U18" t="n">
         <v>6</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>10</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.2363636</v>
-      </c>
-      <c r="S18" t="n">
-        <v>12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.19587629</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.26190478</v>
+        <v>0.2596154</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>0.30666667</v>
+        <v>0.3080357</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>0.44761905</v>
+        <v>0.41826922</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>6.0545454</v>
+        <v>5.3333335</v>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P19" t="n">
         <v>11</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5090909</v>
+        <v>1.2962962</v>
       </c>
       <c r="S19" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T19" t="n">
-        <v>0.28636363</v>
+        <v>0.2583732</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.21348314</v>
+        <v>0.21641791</v>
       </c>
       <c r="C20" t="n">
+        <v>22</v>
+      </c>
+      <c r="D20" t="n">
         <v>26</v>
       </c>
-      <c r="D20" t="n">
-        <v>29</v>
-      </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F20" t="n">
         <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>0.31270358</v>
+        <v>0.30491802</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39325842</v>
+        <v>0.39925373</v>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L20" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N20" t="n">
-        <v>4.375</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2361112</v>
+        <v>1.1527778</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>0.22710623</v>
+        <v>0.22262774</v>
       </c>
       <c r="U20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.15555556</v>
+        <v>0.13574661</v>
       </c>
       <c r="C21" t="n">
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
         <v>26</v>
@@ -4091,46 +4091,46 @@
         <v>18</v>
       </c>
       <c r="H21" t="n">
-        <v>0.20502092</v>
+        <v>0.18723404</v>
       </c>
       <c r="I21" t="n">
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>0.28444445</v>
+        <v>0.25791857</v>
       </c>
       <c r="K21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L21" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>2.685083</v>
+        <v>3.4309392</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2762431</v>
+        <v>1.2928177</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T21" t="n">
-        <v>0.24347825</v>
+        <v>0.25</v>
       </c>
       <c r="U21" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.28286853</v>
+        <v>0.27160493</v>
       </c>
       <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>39</v>
+      </c>
+      <c r="E22" t="n">
         <v>6</v>
       </c>
-      <c r="D22" t="n">
-        <v>45</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3</v>
-      </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.33695653</v>
+        <v>0.3283582</v>
       </c>
       <c r="I22" t="n">
+        <v>11</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.44444445</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" t="n">
+        <v>65</v>
+      </c>
+      <c r="M22" t="n">
+        <v>23</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.354839</v>
+      </c>
+      <c r="O22" t="n">
+        <v>19</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>14</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2580645</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.22033899</v>
+      </c>
+      <c r="U22" t="n">
         <v>9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.48207173</v>
-      </c>
-      <c r="K22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>69</v>
-      </c>
-      <c r="M22" t="n">
-        <v>26</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5.080645</v>
-      </c>
-      <c r="O22" t="n">
-        <v>25</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>20</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3225807</v>
-      </c>
-      <c r="S22" t="n">
-        <v>17</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.23012552</v>
-      </c>
-      <c r="U22" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -4207,16 +4207,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.30120483</v>
+        <v>0.28455284</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>14</v>
@@ -4225,46 +4225,46 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3642857</v>
+        <v>0.3501805</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5421686999999999</v>
+        <v>0.5243902</v>
       </c>
       <c r="K23" t="n">
         <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.142857</v>
+        <v>4.935484</v>
       </c>
       <c r="O23" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2222222</v>
+        <v>1.3225807</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23728813</v>
+        <v>0.2542373</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2565445</v>
+        <v>0.2717949</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
         <v>26</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.37004405</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.44615385</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>39</v>
+      </c>
+      <c r="M24" t="n">
         <v>5</v>
       </c>
-      <c r="G24" t="n">
+      <c r="N24" t="n">
+        <v>4.78481</v>
+      </c>
+      <c r="O24" t="n">
         <v>22</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.36160713</v>
-      </c>
-      <c r="I24" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.39267015</v>
-      </c>
-      <c r="K24" t="n">
-        <v>17</v>
-      </c>
-      <c r="L24" t="n">
-        <v>43</v>
-      </c>
-      <c r="M24" t="n">
-        <v>7</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.280488</v>
-      </c>
-      <c r="O24" t="n">
-        <v>19</v>
-      </c>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4085366</v>
+        <v>1.5759493</v>
       </c>
       <c r="S24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2535211</v>
+        <v>0.27751195</v>
       </c>
       <c r="U24" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.23744293</v>
+        <v>0.21559633</v>
       </c>
       <c r="C25" t="n">
+        <v>23</v>
+      </c>
+      <c r="D25" t="n">
+        <v>23</v>
+      </c>
+      <c r="E25" t="n">
+        <v>23</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.26890758</v>
+      </c>
+      <c r="I25" t="n">
+        <v>25</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.39908257</v>
+      </c>
+      <c r="K25" t="n">
+        <v>19</v>
+      </c>
+      <c r="L25" t="n">
+        <v>54</v>
+      </c>
+      <c r="M25" t="n">
+        <v>12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.9836066</v>
+      </c>
+      <c r="O25" t="n">
         <v>16</v>
       </c>
-      <c r="D25" t="n">
-        <v>24</v>
-      </c>
-      <c r="E25" t="n">
-        <v>21</v>
-      </c>
-      <c r="F25" t="n">
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2131147</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.21777777</v>
+      </c>
+      <c r="U25" t="n">
         <v>8</v>
-      </c>
-      <c r="G25" t="n">
-        <v>14</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.29752067</v>
-      </c>
-      <c r="I25" t="n">
-        <v>21</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.40182647</v>
-      </c>
-      <c r="K25" t="n">
-        <v>14</v>
-      </c>
-      <c r="L25" t="n">
-        <v>62</v>
-      </c>
-      <c r="M25" t="n">
-        <v>19</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.7580645</v>
-      </c>
-      <c r="O25" t="n">
-        <v>6</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.048387</v>
-      </c>
-      <c r="S25" t="n">
-        <v>6</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.19090909</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4408,46 +4408,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22689076</v>
+        <v>0.24686192</v>
       </c>
       <c r="C26" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
+        <v>27</v>
+      </c>
+      <c r="E26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>23</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3283582</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.33891213</v>
+      </c>
+      <c r="K26" t="n">
         <v>22</v>
       </c>
-      <c r="E26" t="n">
-        <v>24</v>
-      </c>
-      <c r="F26" t="n">
-        <v>7</v>
-      </c>
-      <c r="G26" t="n">
-        <v>18</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.30827066</v>
-      </c>
-      <c r="I26" t="n">
-        <v>17</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.34453782</v>
-      </c>
-      <c r="K26" t="n">
-        <v>24</v>
-      </c>
       <c r="L26" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="M26" t="n">
+        <v>26</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.881356</v>
+      </c>
+      <c r="O26" t="n">
         <v>23</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.576271</v>
-      </c>
-      <c r="O26" t="n">
-        <v>22</v>
       </c>
       <c r="P26" t="n">
         <v>3</v>
@@ -4456,16 +4456,16 @@
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3559322</v>
+        <v>1.2881356</v>
       </c>
       <c r="S26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T26" t="n">
-        <v>0.27586207</v>
+        <v>0.26086956</v>
       </c>
       <c r="U26" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.19871795</v>
+        <v>0.1923077</v>
       </c>
       <c r="C27" t="n">
         <v>27</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2529412</v>
+        <v>0.25146198</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>0.27564102</v>
+        <v>0.2948718</v>
       </c>
       <c r="K27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M27" t="n">
         <v>2</v>
@@ -4523,16 +4523,16 @@
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4222223</v>
+        <v>1.4444444</v>
       </c>
       <c r="S27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T27" t="n">
         <v>0.25443786</v>
       </c>
       <c r="U27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.30051813</v>
+        <v>0.31413612</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0.37155962</v>
+        <v>0.39819005</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.54404145</v>
+        <v>0.57591623</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>1.8333334</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
         <v>8</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R28" t="n">
-        <v>0.9074074</v>
+        <v>0.7592593</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.21</v>
+        <v>0.1761658</v>
       </c>
       <c r="U28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.26859504</v>
+        <v>0.25523013</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
         <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
         <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>0.34200743</v>
+        <v>0.32061067</v>
       </c>
       <c r="I29" t="n">
+        <v>13</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.42259413</v>
+      </c>
+      <c r="K29" t="n">
+        <v>13</v>
+      </c>
+      <c r="L29" t="n">
+        <v>60</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.483871</v>
+      </c>
+      <c r="O29" t="n">
+        <v>9</v>
+      </c>
+      <c r="P29" t="n">
         <v>8</v>
       </c>
-      <c r="J29" t="n">
-        <v>0.44214877</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="Q29" t="n">
+        <v>14</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.22317597</v>
+      </c>
+      <c r="U29" t="n">
         <v>11</v>
-      </c>
-      <c r="L29" t="n">
-        <v>62</v>
-      </c>
-      <c r="M29" t="n">
-        <v>19</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4.1311474</v>
-      </c>
-      <c r="O29" t="n">
-        <v>16</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>20</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.1803279</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.24894515</v>
-      </c>
-      <c r="U29" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.21757323</v>
+        <v>0.19911504</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
+        <v>27</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="n">
         <v>20</v>
       </c>
-      <c r="F30" t="n">
-        <v>8</v>
-      </c>
-      <c r="G30" t="n">
-        <v>14</v>
-      </c>
       <c r="H30" t="n">
-        <v>0.26744187</v>
+        <v>0.24691358</v>
       </c>
       <c r="I30" t="n">
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.35564855</v>
+        <v>0.30973452</v>
       </c>
       <c r="K30" t="n">
+        <v>26</v>
+      </c>
+      <c r="L30" t="n">
+        <v>61</v>
+      </c>
+      <c r="M30" t="n">
+        <v>21</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.7142856</v>
+      </c>
+      <c r="O30" t="n">
+        <v>12</v>
+      </c>
+      <c r="P30" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>19</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.3968254</v>
+      </c>
+      <c r="S30" t="n">
         <v>23</v>
       </c>
-      <c r="L30" t="n">
-        <v>62</v>
-      </c>
-      <c r="M30" t="n">
-        <v>19</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.292308</v>
-      </c>
-      <c r="O30" t="n">
-        <v>20</v>
-      </c>
-      <c r="P30" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>24</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.4769231</v>
-      </c>
-      <c r="S30" t="n">
-        <v>25</v>
-      </c>
       <c r="T30" t="n">
-        <v>0.25101215</v>
+        <v>0.22978723</v>
       </c>
       <c r="U30" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.22040816</v>
+        <v>0.23577236</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" t="n">
         <v>11</v>
       </c>
-      <c r="F31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6</v>
-      </c>
       <c r="H31" t="n">
-        <v>0.2846442</v>
+        <v>0.29850745</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>0.39591837</v>
+        <v>0.40650406</v>
       </c>
       <c r="K31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L31" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="M31" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N31" t="n">
-        <v>6.096774</v>
+        <v>4.064516</v>
       </c>
       <c r="O31" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="P31" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>14</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.2258065</v>
+      </c>
+      <c r="S31" t="n">
         <v>11</v>
       </c>
-      <c r="Q31" t="n">
-        <v>24</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.483871</v>
-      </c>
-      <c r="S31" t="n">
-        <v>26</v>
-      </c>
       <c r="T31" t="n">
-        <v>0.2734694</v>
+        <v>0.23175965</v>
       </c>
       <c r="U31" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23828125</v>
+        <v>0.23789474</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E2" t="n">
         <v>19</v>
@@ -561,46 +561,46 @@
         <v>78</v>
       </c>
       <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3084436</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3859649</v>
+      </c>
+      <c r="K2" t="n">
         <v>25</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.3093342</v>
-      </c>
-      <c r="I2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.3877841</v>
-      </c>
-      <c r="K2" t="n">
-        <v>24</v>
-      </c>
       <c r="L2" t="n">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2973695</v>
+        <v>4.317621</v>
       </c>
       <c r="O2" t="n">
         <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q2" t="n">
         <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2880071</v>
+        <v>1.2885462</v>
       </c>
       <c r="S2" t="n">
         <v>14</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25026363</v>
+        <v>0.25078043</v>
       </c>
       <c r="U2" t="n">
         <v>21</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24719101</v>
+        <v>0.24831763</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G3" t="n">
         <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32627118</v>
+        <v>0.32684824</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4082397</v>
+        <v>0.41117093</v>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="M3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>5.0208063</v>
+        <v>4.974293</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4486346</v>
+        <v>1.4460155</v>
       </c>
       <c r="S3" t="n">
         <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26492286</v>
+        <v>0.26385662</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,43 +680,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24689165</v>
+        <v>0.24639718</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E4" t="n">
         <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" t="n">
         <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31099713</v>
+        <v>0.3108151</v>
       </c>
       <c r="I4" t="n">
         <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4063943</v>
+        <v>0.4056239</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4254644</v>
+        <v>3.3961504</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -725,16 +725,16 @@
         <v>88</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2111464</v>
+        <v>1.2005371</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22560528</v>
+        <v>0.22395644</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -747,64 +747,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23847213</v>
+        <v>0.23850085</v>
       </c>
       <c r="C5" t="n">
         <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31789088</v>
+        <v>0.3185654</v>
       </c>
       <c r="I5" t="n">
         <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39573297</v>
+        <v>0.39693356</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="M5" t="n">
         <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4319654</v>
+        <v>4.3924</v>
       </c>
       <c r="O5" t="n">
         <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q5" t="n">
         <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3840172</v>
+        <v>1.3744662</v>
       </c>
       <c r="S5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2557983</v>
+        <v>0.2545757</v>
       </c>
       <c r="U5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24269423</v>
+        <v>0.24287222</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E6" t="n">
         <v>29</v>
@@ -832,46 +832,46 @@
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31021196</v>
+        <v>0.31071654</v>
       </c>
       <c r="I6" t="n">
         <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38382038</v>
+        <v>0.38296375</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="M6" t="n">
         <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7392087</v>
+        <v>3.8143048</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2464029</v>
+        <v>1.2621058</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24153902</v>
+        <v>0.24288225</v>
       </c>
       <c r="U6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -881,64 +881,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24293016</v>
+        <v>0.2452133</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33755895</v>
+        <v>0.33972684</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40511075</v>
+        <v>0.41383943</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="M7" t="n">
         <v>18</v>
       </c>
       <c r="N7" t="n">
-        <v>4.245209</v>
+        <v>4.2307363</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q7" t="n">
         <v>30</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2543554</v>
+        <v>1.2578562</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24140327</v>
+        <v>0.24219555</v>
       </c>
       <c r="U7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24296401</v>
+        <v>0.24180472</v>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E8" t="n">
         <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32366845</v>
+        <v>0.3220974</v>
       </c>
       <c r="I8" t="n">
         <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41752762</v>
+        <v>0.41593233</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.205909</v>
+        <v>4.2329497</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P8" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3240824</v>
+        <v>1.3286093</v>
       </c>
       <c r="S8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23942652</v>
+        <v>0.23944661</v>
       </c>
       <c r="U8" t="n">
         <v>13</v>
@@ -1015,43 +1015,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22743426</v>
+        <v>0.22760801</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G9" t="n">
         <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30917114</v>
+        <v>0.30869973</v>
       </c>
       <c r="I9" t="n">
         <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3891258</v>
+        <v>0.38918158</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="M9" t="n">
         <v>27</v>
       </c>
       <c r="N9" t="n">
-        <v>4.620321</v>
+        <v>4.6190476</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
@@ -1060,16 +1060,16 @@
         <v>118</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4639038</v>
+        <v>1.468254</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25113675</v>
+        <v>0.25121108</v>
       </c>
       <c r="U9" t="n">
         <v>22</v>
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22785258</v>
+        <v>0.22891144</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="E10" t="n">
         <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31012857</v>
+        <v>0.31060135</v>
       </c>
       <c r="I10" t="n">
         <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36321756</v>
+        <v>0.3661183</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7657895</v>
+        <v>3.7685306</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q10" t="n">
         <v>19</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2565789</v>
+        <v>1.2600781</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23754387</v>
+        <v>0.23759972</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25427788</v>
+        <v>0.25389302</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E11" t="n">
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G11" t="n">
         <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32464746</v>
+        <v>0.3236187</v>
       </c>
       <c r="I11" t="n">
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41546887</v>
+        <v>0.41740012</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.62649</v>
+        <v>5.5955496</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q11" t="n">
         <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5258278</v>
+        <v>1.5196335</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28874874</v>
+        <v>0.28791857</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23636363</v>
+        <v>0.23533471</v>
       </c>
       <c r="C12" t="n">
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G12" t="n">
         <v>15</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31503877</v>
+        <v>0.3139535</v>
       </c>
       <c r="I12" t="n">
         <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39825174</v>
+        <v>0.39648032</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.763564</v>
+        <v>3.7330434</v>
       </c>
       <c r="O12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q12" t="n">
         <v>7</v>
       </c>
-      <c r="P12" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>9</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.229378</v>
+        <v>1.2234782</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23514938</v>
+        <v>0.23455933</v>
       </c>
       <c r="U12" t="n">
         <v>8</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24147248</v>
+        <v>0.24132176</v>
       </c>
       <c r="C13" t="n">
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
         <v>116</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3156146</v>
+        <v>0.31572664</v>
       </c>
       <c r="I13" t="n">
         <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40999663</v>
+        <v>0.40821093</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>721</v>
+        <v>734</v>
       </c>
       <c r="M13" t="n">
         <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>4.734816</v>
+        <v>4.772093</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
       </c>
       <c r="P13" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3909324</v>
+        <v>1.3928119</v>
       </c>
       <c r="S13" t="n">
         <v>24</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24093087</v>
+        <v>0.24086604</v>
       </c>
       <c r="U13" t="n">
         <v>14</v>
@@ -1350,16 +1350,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24392782</v>
+        <v>0.24330817</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
         <v>361</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
         <v>85</v>
@@ -1368,43 +1368,43 @@
         <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3152679</v>
+        <v>0.3142244</v>
       </c>
       <c r="I14" t="n">
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39208883</v>
+        <v>0.38984215</v>
       </c>
       <c r="K14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L14" t="n">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.875659</v>
+        <v>4.865393</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4380492</v>
+        <v>1.4355189</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2611092</v>
+        <v>0.26165363</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1426,13 +1426,13 @@
         <v>391</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
         <v>101</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" t="n">
         <v>0.31772575</v>
@@ -1444,25 +1444,25 @@
         <v>0.3960396</v>
       </c>
       <c r="K15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L15" t="n">
         <v>820</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N15" t="n">
         <v>4.630916</v>
       </c>
       <c r="O15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>92</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
         <v>1.405558</v>
@@ -1474,7 +1474,7 @@
         <v>0.2377839</v>
       </c>
       <c r="U15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26565725</v>
+        <v>0.26455566</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3474857</v>
+        <v>0.3469327</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4432209</v>
+        <v>0.44194758</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4298902</v>
+        <v>3.476294</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1156044</v>
+        <v>1.1222271</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21387696</v>
+        <v>0.21547157</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2505263</v>
+        <v>0.25008672</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" t="n">
         <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32627645</v>
+        <v>0.32553127</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3982456</v>
+        <v>0.3981963</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L17" t="n">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="M17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9642856</v>
+        <v>3.946335</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2407408</v>
+        <v>1.2369109</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2272888</v>
+        <v>0.2271933</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2549716</v>
+        <v>0.25500527</v>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
         <v>78</v>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33833176</v>
+        <v>0.33909288</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39701703</v>
+        <v>0.39761153</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3840644</v>
+        <v>3.3675365</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.179051</v>
+        <v>1.1769128</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21864717</v>
+        <v>0.21893063</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,43 +1685,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2465148</v>
+        <v>0.24638656</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G19" t="n">
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32069173</v>
+        <v>0.32124662</v>
       </c>
       <c r="I19" t="n">
         <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.41074464</v>
+        <v>0.41210085</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="M19" t="n">
         <v>14</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8675065</v>
+        <v>4.8226705</v>
       </c>
       <c r="O19" t="n">
         <v>27</v>
@@ -1733,16 +1733,16 @@
         <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3983493</v>
+        <v>1.3975955</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2557355</v>
+        <v>0.25541848</v>
       </c>
       <c r="U19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1752,64 +1752,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23002085</v>
+        <v>0.22928841</v>
       </c>
       <c r="C20" t="n">
         <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G20" t="n">
         <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29839975</v>
+        <v>0.29751554</v>
       </c>
       <c r="I20" t="n">
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37456566</v>
+        <v>0.3746992</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="M20" t="n">
         <v>15</v>
       </c>
       <c r="N20" t="n">
-        <v>4.056448</v>
+        <v>4.119037</v>
       </c>
       <c r="O20" t="n">
         <v>13</v>
       </c>
       <c r="P20" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2726878</v>
+        <v>1.2814783</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23243801</v>
+        <v>0.23391216</v>
       </c>
       <c r="U20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1819,64 +1819,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23650569</v>
+        <v>0.23589204</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31986216</v>
+        <v>0.31878674</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J21" t="n">
-        <v>0.42258522</v>
+        <v>0.4209604</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="M21" t="n">
         <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.360053</v>
+        <v>3.3587954</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1930912</v>
+        <v>1.1890004</v>
       </c>
       <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.22685835</v>
+      </c>
+      <c r="U21" t="n">
         <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.22778963</v>
-      </c>
-      <c r="U21" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1886,64 +1886,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23722376</v>
+        <v>0.23806275</v>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30305868</v>
+        <v>0.3043746</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40331492</v>
+        <v>0.40552524</v>
       </c>
       <c r="K22" t="n">
         <v>13</v>
       </c>
       <c r="L22" t="n">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.0976887</v>
+        <v>4.1198277</v>
       </c>
       <c r="O22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P22" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q22" t="n">
         <v>17</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2991714</v>
+        <v>1.3034483</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2538071</v>
+        <v>0.25450903</v>
       </c>
       <c r="U22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25763166</v>
+        <v>0.25827813</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33600712</v>
+        <v>0.3366569</v>
       </c>
       <c r="I23" t="n">
         <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.41798055</v>
+        <v>0.4178808</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>809</v>
+        <v>822</v>
       </c>
       <c r="M23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2213078</v>
+        <v>4.28204</v>
       </c>
       <c r="O23" t="n">
+        <v>19</v>
+      </c>
+      <c r="P23" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.311616</v>
+      </c>
+      <c r="S23" t="n">
         <v>17</v>
       </c>
-      <c r="P23" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3044608</v>
-      </c>
-      <c r="S23" t="n">
-        <v>16</v>
-      </c>
       <c r="T23" t="n">
-        <v>0.23732877</v>
+        <v>0.23815967</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2233965</v>
+        <v>0.22446044</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29912025</v>
+        <v>0.30032155</v>
       </c>
       <c r="I24" t="n">
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>0.36953354</v>
+        <v>0.37194246</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="M24" t="n">
         <v>11</v>
       </c>
       <c r="N24" t="n">
-        <v>3.940018</v>
+        <v>4.161205</v>
       </c>
       <c r="O24" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P24" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.316025</v>
+        <v>1.3339238</v>
       </c>
       <c r="S24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24453992</v>
+        <v>0.24691358</v>
       </c>
       <c r="U24" t="n">
         <v>19</v>
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25447044</v>
+        <v>0.2549219</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E25" t="n">
         <v>26</v>
       </c>
       <c r="F25" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G25" t="n">
         <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30669615</v>
+        <v>0.30670828</v>
       </c>
       <c r="I25" t="n">
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41712517</v>
+        <v>0.41819417</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.369942</v>
+        <v>4.3655534</v>
       </c>
       <c r="O25" t="n">
         <v>21</v>
@@ -2132,16 +2132,16 @@
         <v>85</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3699422</v>
+        <v>1.3642355</v>
       </c>
       <c r="S25" t="n">
         <v>21</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24779385</v>
+        <v>0.24729683</v>
       </c>
       <c r="U25" t="n">
         <v>20</v>
@@ -2163,13 +2163,13 @@
         <v>356</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
         <v>105</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H26" t="n">
         <v>0.31336406</v>
@@ -2181,13 +2181,13 @@
         <v>0.3836565</v>
       </c>
       <c r="K26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L26" t="n">
         <v>750</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N26" t="n">
         <v>3.688716</v>
@@ -2199,19 +2199,19 @@
         <v>80</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>1.1893644</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
         <v>0.24116424</v>
       </c>
       <c r="U26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24563953</v>
+        <v>0.2437972</v>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E27" t="n">
         <v>18</v>
@@ -2236,49 +2236,49 @@
         <v>91</v>
       </c>
       <c r="G27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3233687</v>
+        <v>0.32123527</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39280522</v>
+        <v>0.38978785</v>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L27" t="n">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2444344</v>
+        <v>4.2350564</v>
       </c>
       <c r="O27" t="n">
         <v>18</v>
       </c>
       <c r="P27" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3466606</v>
+        <v>1.3456179</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2547406</v>
+        <v>0.2541593</v>
       </c>
       <c r="U27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -2288,64 +2288,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26015368</v>
+        <v>0.26074395</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3388296</v>
+        <v>0.33865815</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39553604</v>
+        <v>0.39725533</v>
       </c>
       <c r="K28" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L28" t="n">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.781719</v>
+        <v>3.7358491</v>
       </c>
       <c r="O28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
         <v>100</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1950886</v>
+        <v>1.190027</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23442028</v>
+        <v>0.23388252</v>
       </c>
       <c r="U28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2355,64 +2355,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2436389</v>
+        <v>0.24362509</v>
       </c>
       <c r="C29" t="n">
         <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E29" t="n">
         <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31891724</v>
+        <v>0.31960663</v>
       </c>
       <c r="I29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39177415</v>
+        <v>0.39145416</v>
       </c>
       <c r="K29" t="n">
+        <v>20</v>
+      </c>
+      <c r="L29" t="n">
+        <v>734</v>
+      </c>
+      <c r="M29" t="n">
+        <v>16</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.9903805</v>
+      </c>
+      <c r="O29" t="n">
+        <v>11</v>
+      </c>
+      <c r="P29" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q29" t="n">
         <v>22</v>
       </c>
-      <c r="L29" t="n">
-        <v>726</v>
-      </c>
-      <c r="M29" t="n">
-        <v>17</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.9253204</v>
-      </c>
-      <c r="O29" t="n">
-        <v>10</v>
-      </c>
-      <c r="P29" t="n">
-        <v>102</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>21</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.231551</v>
+        <v>1.23568</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23686956</v>
+        <v>0.23780069</v>
       </c>
       <c r="U29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -2422,64 +2422,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2465374</v>
+        <v>0.24786033</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G30" t="n">
         <v>23</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30865747</v>
+        <v>0.31029138</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3874654</v>
+        <v>0.38993496</v>
       </c>
       <c r="K30" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L30" t="n">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="M30" t="n">
         <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.0959024</v>
+        <v>4.0831537</v>
       </c>
       <c r="O30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q30" t="n">
         <v>16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3169136</v>
+        <v>1.3106419</v>
       </c>
       <c r="S30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24185725</v>
+        <v>0.24100102</v>
       </c>
       <c r="U30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -2489,46 +2489,46 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24631368</v>
+        <v>0.2475182</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>117</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3214815</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.425546</v>
+      </c>
+      <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="F31" t="n">
-        <v>114</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.3192065</v>
-      </c>
-      <c r="I31" t="n">
-        <v>13</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.4219169</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3</v>
-      </c>
       <c r="L31" t="n">
-        <v>728</v>
+        <v>738</v>
       </c>
       <c r="M31" t="n">
         <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6575575</v>
+        <v>4.627269</v>
       </c>
       <c r="O31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P31" t="n">
         <v>123</v>
@@ -2537,13 +2537,13 @@
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37959</v>
+        <v>1.3803293</v>
       </c>
       <c r="S31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25629973</v>
+        <v>0.25630942</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24242425</v>
+        <v>0.22279793</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2890995</v>
+      </c>
+      <c r="I2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3834197</v>
+      </c>
+      <c r="K2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L2" t="n">
+        <v>39</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.7647057</v>
+      </c>
+      <c r="O2" t="n">
+        <v>21</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="n">
         <v>26</v>
       </c>
-      <c r="E2" t="n">
-        <v>19</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="R2" t="n">
+        <v>1.1764706</v>
+      </c>
+      <c r="S2" t="n">
         <v>9</v>
       </c>
-      <c r="G2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3167421</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.44444445</v>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" t="n">
-        <v>34</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.4117646</v>
-      </c>
-      <c r="O2" t="n">
-        <v>20</v>
-      </c>
-      <c r="P2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>23</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.137255</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
       <c r="T2" t="n">
-        <v>0.24064171</v>
+        <v>0.2513089</v>
       </c>
       <c r="U2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.23849373</v>
+        <v>0.2682927</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3220974</v>
+      </c>
+      <c r="I3" t="n">
         <v>14</v>
       </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
+        <v>0.3699187</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L3" t="n">
+        <v>68</v>
+      </c>
+      <c r="M3" t="n">
+        <v>26</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.4590163</v>
+      </c>
+      <c r="O3" t="n">
         <v>25</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.30152673</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
         <v>19</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.31380752</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="R3" t="n">
+        <v>1.4754099</v>
+      </c>
+      <c r="S3" t="n">
         <v>25</v>
       </c>
-      <c r="L3" t="n">
-        <v>70</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="T3" t="n">
+        <v>0.2768595</v>
+      </c>
+      <c r="U3" t="n">
         <v>25</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5.6373625</v>
-      </c>
-      <c r="O3" t="n">
-        <v>27</v>
-      </c>
-      <c r="P3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>23</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.4505494</v>
-      </c>
-      <c r="S3" t="n">
-        <v>26</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2821577</v>
-      </c>
-      <c r="U3" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.16666667</v>
+        <v>0.17088607</v>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -2952,46 +2952,46 @@
         <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>0.23756906</v>
+        <v>0.25139666</v>
       </c>
       <c r="I4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>0.22222222</v>
+        <v>0.2278481</v>
       </c>
       <c r="K4" t="n">
         <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.857143</v>
+        <v>2.9302325</v>
       </c>
       <c r="O4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2857143</v>
+        <v>1.0232558</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23684211</v>
+        <v>0.20261438</v>
       </c>
       <c r="U4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21</v>
+        <v>0.20833333</v>
       </c>
       <c r="C5" t="n">
         <v>25</v>
@@ -3010,7 +3010,7 @@
         <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -3019,46 +3019,46 @@
         <v>25</v>
       </c>
       <c r="H5" t="n">
-        <v>0.29515418</v>
+        <v>0.30493274</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
-        <v>0.315</v>
+        <v>0.31770834</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M5" t="n">
         <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>4.526946</v>
+        <v>3.9272728</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
         <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4371257</v>
+        <v>1.2545455</v>
       </c>
       <c r="S5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="T5" t="n">
-        <v>0.24774775</v>
+        <v>0.23584905</v>
       </c>
       <c r="U5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.23766816</v>
+        <v>0.23076923</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.29149798</v>
+      </c>
+      <c r="I6" t="n">
+        <v>21</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.36199096</v>
+      </c>
+      <c r="K6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L6" t="n">
+        <v>56</v>
+      </c>
+      <c r="M6" t="n">
+        <v>16</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.796875</v>
+      </c>
+      <c r="O6" t="n">
+        <v>13</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="S6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.2857143</v>
-      </c>
-      <c r="I6" t="n">
-        <v>22</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.41704035</v>
-      </c>
-      <c r="K6" t="n">
-        <v>15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>54</v>
-      </c>
-      <c r="M6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.857143</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.0793651</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.21276596</v>
+        <v>0.20851064</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.23655914</v>
+        <v>0.25306123</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3353846</v>
+        <v>0.35191637</v>
       </c>
       <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4979592</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>67</v>
+      </c>
+      <c r="M7" t="n">
+        <v>25</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.515625</v>
+      </c>
+      <c r="O7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" t="n">
-        <v>0.4265233</v>
-      </c>
-      <c r="K7" t="n">
-        <v>12</v>
-      </c>
-      <c r="L7" t="n">
-        <v>82</v>
-      </c>
-      <c r="M7" t="n">
-        <v>30</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.69863</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>11</v>
       </c>
-      <c r="P7" t="n">
-        <v>16</v>
-      </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3835616</v>
+        <v>1.453125</v>
       </c>
       <c r="S7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2642857</v>
+        <v>0.28</v>
       </c>
       <c r="U7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3198198</v>
+        <v>0.30092594</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.373444</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.49074075</v>
+      </c>
+      <c r="K8" t="n">
         <v>7</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.3968254</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.8867924</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.518018</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>49</v>
-      </c>
-      <c r="M8" t="n">
-        <v>9</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.1272728</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.1454545</v>
+        <v>1.1886792</v>
       </c>
       <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.21578947</v>
+      </c>
+      <c r="U8" t="n">
         <v>7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.21105528</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.25615764</v>
+        <v>0.245</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>0.34051725</v>
+        <v>0.29816514</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>0.41379312</v>
+        <v>0.395</v>
       </c>
       <c r="K9" t="n">
         <v>16</v>
       </c>
       <c r="L9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>6.529412</v>
+        <v>6.3</v>
       </c>
       <c r="O9" t="n">
+        <v>27</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>27</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S9" t="n">
         <v>28</v>
       </c>
-      <c r="P9" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>29</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.7254902</v>
-      </c>
-      <c r="S9" t="n">
-        <v>29</v>
-      </c>
       <c r="T9" t="n">
-        <v>0.3014354</v>
+        <v>0.2955665</v>
       </c>
       <c r="U9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22772278</v>
+        <v>0.24623115</v>
       </c>
       <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="n">
         <v>21</v>
       </c>
-      <c r="D10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
         <v>25</v>
       </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>29</v>
-      </c>
       <c r="H10" t="n">
-        <v>0.2764977</v>
+        <v>0.2809524</v>
       </c>
       <c r="I10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2920792</v>
+        <v>0.36180905</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M10" t="n">
         <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2727273</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3090909</v>
+        <v>1.3333334</v>
       </c>
       <c r="S10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="T10" t="n">
-        <v>0.254717</v>
+        <v>0.24880382</v>
       </c>
       <c r="U10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -3403,61 +3403,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.27570093</v>
+        <v>0.25</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34979424</v>
+        <v>0.32478634</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4813084</v>
+        <v>0.50961536</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N11" t="n">
-        <v>7.6415095</v>
+        <v>7.1320753</v>
       </c>
       <c r="O11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6415094</v>
+        <v>1.5849056</v>
       </c>
       <c r="S11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3347826</v>
+        <v>0.32300884</v>
       </c>
       <c r="U11" t="n">
         <v>29</v>
@@ -3470,61 +3470,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24796748</v>
+        <v>0.236</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31501833</v>
+        <v>0.3057554</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
-        <v>0.44715446</v>
+        <v>0.44</v>
       </c>
       <c r="K12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" t="n">
+        <v>61</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.7272727</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
         <v>8</v>
       </c>
-      <c r="L12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M12" t="n">
-        <v>22</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.09375</v>
-      </c>
-      <c r="O12" t="n">
-        <v>5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
       <c r="Q12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R12" t="n">
-        <v>0.875</v>
+        <v>0.8939394000000001</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1923077</v>
+        <v>0.19246861</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.21276596</v>
+        <v>0.22594142</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
         <v>30</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2846154</v>
+        <v>0.28735632</v>
       </c>
       <c r="I13" t="n">
         <v>23</v>
       </c>
       <c r="J13" t="n">
-        <v>0.36595744</v>
+        <v>0.36820084</v>
       </c>
       <c r="K13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>3.857143</v>
+        <v>4.857143</v>
       </c>
       <c r="O13" t="n">
+        <v>24</v>
+      </c>
+      <c r="P13" t="n">
         <v>14</v>
       </c>
-      <c r="P13" t="n">
-        <v>12</v>
-      </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1746032</v>
+        <v>1.3015873</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2112069</v>
+        <v>0.22457626</v>
       </c>
       <c r="U13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.18229167</v>
+        <v>0.17989418</v>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>28</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H14" t="n">
-        <v>0.24038461</v>
+        <v>0.23152709</v>
       </c>
       <c r="I14" t="n">
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>0.31770834</v>
+        <v>0.29100528</v>
       </c>
       <c r="K14" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N14" t="n">
-        <v>9.655628999999999</v>
+        <v>9.292208</v>
       </c>
       <c r="O14" t="n">
         <v>30</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1059604</v>
+        <v>2.0064936</v>
       </c>
       <c r="S14" t="n">
         <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>0.35514018</v>
+        <v>0.35159817</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2413793</v>
+        <v>0.24539877</v>
       </c>
       <c r="C15" t="n">
+        <v>17</v>
+      </c>
+      <c r="D15" t="n">
+        <v>17</v>
+      </c>
+      <c r="E15" t="n">
+        <v>26</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.30113637</v>
+      </c>
+      <c r="I15" t="n">
+        <v>18</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.35582823</v>
+      </c>
+      <c r="K15" t="n">
+        <v>24</v>
+      </c>
+      <c r="L15" t="n">
+        <v>38</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.8139534</v>
+      </c>
+      <c r="O15" t="n">
+        <v>22</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2790698</v>
+      </c>
+      <c r="S15" t="n">
         <v>16</v>
       </c>
-      <c r="D15" t="n">
-        <v>24</v>
-      </c>
-      <c r="E15" t="n">
-        <v>22</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>25</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.30941704</v>
-      </c>
-      <c r="I15" t="n">
-        <v>16</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.3497537</v>
-      </c>
-      <c r="K15" t="n">
-        <v>21</v>
-      </c>
-      <c r="L15" t="n">
-        <v>55</v>
-      </c>
-      <c r="M15" t="n">
-        <v>16</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.924528</v>
-      </c>
-      <c r="O15" t="n">
-        <v>24</v>
-      </c>
-      <c r="P15" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>10</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.264151</v>
-      </c>
-      <c r="S15" t="n">
-        <v>13</v>
-      </c>
       <c r="T15" t="n">
-        <v>0.2413793</v>
+        <v>0.24096386</v>
       </c>
       <c r="U15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3738,16 +3738,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3167421</v>
+        <v>0.29953918</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
@@ -3756,46 +3756,46 @@
         <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>0.37903225</v>
+        <v>0.37651822</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.51131225</v>
+        <v>0.49769586</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>45</v>
       </c>
       <c r="M16" t="n">
+        <v>9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>19</v>
+      </c>
+      <c r="P16" t="n">
         <v>8</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.5660377</v>
-      </c>
-      <c r="O16" t="n">
-        <v>10</v>
-      </c>
-      <c r="P16" t="n">
-        <v>5</v>
-      </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3584906</v>
+        <v>1.4230769</v>
       </c>
       <c r="S16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T16" t="n">
-        <v>0.24242425</v>
+        <v>0.26130652</v>
       </c>
       <c r="U16" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -3805,31 +3805,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.30660376</v>
+        <v>0.30414745</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H17" t="n">
-        <v>0.36909872</v>
+        <v>0.3628692</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.49308756</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
@@ -3838,31 +3838,31 @@
         <v>41</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.54717</v>
+        <v>2.5961537</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9811321</v>
+        <v>1.0192307</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
       </c>
       <c r="T17" t="n">
-        <v>0.19892474</v>
+        <v>0.20320855</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2857143</v>
+        <v>0.27918783</v>
       </c>
       <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>27</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.36444443</v>
+      </c>
+      <c r="I18" t="n">
         <v>5</v>
       </c>
-      <c r="D18" t="n">
-        <v>29</v>
-      </c>
-      <c r="E18" t="n">
-        <v>14</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.36123347</v>
-      </c>
-      <c r="I18" t="n">
-        <v>6</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.5123153</v>
+        <v>0.48730963</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M18" t="n">
         <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7636364</v>
+        <v>3.2727273</v>
       </c>
       <c r="O18" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P18" t="n">
         <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3454546</v>
+        <v>1.1090909</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21212122</v>
+        <v>0.2</v>
       </c>
       <c r="U18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3942,61 +3942,61 @@
         <v>0.2596154</v>
       </c>
       <c r="C19" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" t="n">
+        <v>34</v>
+      </c>
+      <c r="E19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" t="n">
         <v>10</v>
       </c>
-      <c r="D19" t="n">
-        <v>29</v>
-      </c>
-      <c r="E19" t="n">
-        <v>14</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>7</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
+        <v>0.3171806</v>
+      </c>
+      <c r="I19" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.46153846</v>
+      </c>
+      <c r="K19" t="n">
+        <v>11</v>
+      </c>
+      <c r="L19" t="n">
+        <v>38</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.8333335</v>
+      </c>
+      <c r="O19" t="n">
+        <v>23</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>19</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3148148</v>
+      </c>
+      <c r="S19" t="n">
         <v>18</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.3080357</v>
-      </c>
-      <c r="I19" t="n">
-        <v>17</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.41826922</v>
-      </c>
-      <c r="K19" t="n">
-        <v>14</v>
-      </c>
-      <c r="L19" t="n">
-        <v>40</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5.3333335</v>
-      </c>
-      <c r="O19" t="n">
-        <v>26</v>
-      </c>
-      <c r="P19" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>23</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.2962962</v>
-      </c>
-      <c r="S19" t="n">
-        <v>17</v>
-      </c>
       <c r="T19" t="n">
-        <v>0.2583732</v>
+        <v>0.24880382</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.21641791</v>
+        <v>0.20600858</v>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.29433963</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.35622317</v>
+      </c>
+      <c r="K20" t="n">
+        <v>23</v>
+      </c>
+      <c r="L20" t="n">
+        <v>61</v>
+      </c>
+      <c r="M20" t="n">
+        <v>21</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.903226</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
         <v>4</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.30491802</v>
-      </c>
-      <c r="I20" t="n">
-        <v>18</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.39925373</v>
-      </c>
-      <c r="K20" t="n">
-        <v>18</v>
-      </c>
-      <c r="L20" t="n">
-        <v>67</v>
-      </c>
-      <c r="M20" t="n">
-        <v>24</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>6</v>
-      </c>
-      <c r="P20" t="n">
-        <v>5</v>
-      </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1527778</v>
+        <v>1.1451613</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>0.22262774</v>
+        <v>0.22510822</v>
       </c>
       <c r="U20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.13574661</v>
+        <v>0.13716814</v>
       </c>
       <c r="C21" t="n">
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
         <v>26</v>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H21" t="n">
-        <v>0.18723404</v>
+        <v>0.19087137</v>
       </c>
       <c r="I21" t="n">
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>0.25791857</v>
+        <v>0.2300885</v>
       </c>
       <c r="K21" t="n">
         <v>29</v>
       </c>
       <c r="L21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4309392</v>
+        <v>3.7540107</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
         <v>19</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2928177</v>
+        <v>1.2352941</v>
       </c>
       <c r="S21" t="n">
+        <v>12</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="U21" t="n">
         <v>16</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.27160493</v>
+        <v>0.28163266</v>
       </c>
       <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>44</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>13</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.34798536</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.47346938</v>
+      </c>
+      <c r="K22" t="n">
         <v>9</v>
       </c>
-      <c r="D22" t="n">
-        <v>39</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="L22" t="n">
+        <v>72</v>
+      </c>
+      <c r="M22" t="n">
+        <v>28</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.645161</v>
+      </c>
+      <c r="O22" t="n">
+        <v>20</v>
+      </c>
+      <c r="P22" t="n">
         <v>6</v>
       </c>
-      <c r="F22" t="n">
-        <v>11</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3283582</v>
-      </c>
-      <c r="I22" t="n">
-        <v>11</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.44444445</v>
-      </c>
-      <c r="K22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" t="n">
-        <v>65</v>
-      </c>
-      <c r="M22" t="n">
-        <v>23</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.354839</v>
-      </c>
-      <c r="O22" t="n">
-        <v>19</v>
-      </c>
-      <c r="P22" t="n">
-        <v>8</v>
-      </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2580645</v>
+        <v>1.3548387</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T22" t="n">
-        <v>0.22033899</v>
+        <v>0.23966943</v>
       </c>
       <c r="U22" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.28455284</v>
+        <v>0.27125505</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3501805</v>
+        <v>0.34408602</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5243902</v>
+        <v>0.49392712</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="M23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>4.935484</v>
+        <v>6.196721</v>
       </c>
       <c r="O23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3225807</v>
+        <v>1.4918033</v>
       </c>
       <c r="S23" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2542373</v>
+        <v>0.26890758</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2717949</v>
+        <v>0.28078818</v>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>0.37004405</v>
+        <v>0.37339056</v>
       </c>
       <c r="I24" t="n">
         <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.44615385</v>
+        <v>0.4679803</v>
       </c>
       <c r="K24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>4.78481</v>
+        <v>8.36129</v>
       </c>
       <c r="O24" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="P24" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5759493</v>
+        <v>1.916129</v>
       </c>
       <c r="S24" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T24" t="n">
-        <v>0.27751195</v>
+        <v>0.31797236</v>
       </c>
       <c r="U24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.21559633</v>
+        <v>0.2300885</v>
       </c>
       <c r="C25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F25" t="n">
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>0.26890758</v>
+        <v>0.27459016</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>0.39908257</v>
+        <v>0.41150442</v>
       </c>
       <c r="K25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L25" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9836066</v>
+        <v>4.4262295</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2131147</v>
+        <v>1.2459016</v>
       </c>
       <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.22943723</v>
+      </c>
+      <c r="U25" t="n">
         <v>10</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.21777777</v>
-      </c>
-      <c r="U25" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.24686192</v>
+        <v>0.25365853</v>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" t="n">
         <v>18</v>
@@ -4426,28 +4426,28 @@
         <v>23</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3283582</v>
+        <v>0.34615386</v>
       </c>
       <c r="I26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3512195</v>
+      </c>
+      <c r="K26" t="n">
+        <v>25</v>
+      </c>
+      <c r="L26" t="n">
+        <v>59</v>
+      </c>
+      <c r="M26" t="n">
+        <v>18</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.7058823</v>
+      </c>
+      <c r="O26" t="n">
         <v>11</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.33891213</v>
-      </c>
-      <c r="K26" t="n">
-        <v>22</v>
-      </c>
-      <c r="L26" t="n">
-        <v>72</v>
-      </c>
-      <c r="M26" t="n">
-        <v>26</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.881356</v>
-      </c>
-      <c r="O26" t="n">
-        <v>23</v>
       </c>
       <c r="P26" t="n">
         <v>3</v>
@@ -4456,16 +4456,16 @@
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2881356</v>
+        <v>1.137255</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T26" t="n">
-        <v>0.26086956</v>
+        <v>0.234375</v>
       </c>
       <c r="U26" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1923077</v>
+        <v>0.1589404</v>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>28</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2195122</v>
+      </c>
+      <c r="I27" t="n">
         <v>29</v>
       </c>
-      <c r="F27" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" t="n">
-        <v>25</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.25146198</v>
-      </c>
-      <c r="I27" t="n">
-        <v>26</v>
-      </c>
       <c r="J27" t="n">
-        <v>0.2948718</v>
+        <v>0.23178808</v>
       </c>
       <c r="K27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L27" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>3.2727273</v>
       </c>
       <c r="O27" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4444444</v>
+        <v>1.3181819</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25443786</v>
+        <v>0.23125</v>
       </c>
       <c r="U27" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -4542,61 +4542,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.31413612</v>
+        <v>0.3112245</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0.39819005</v>
+        <v>0.3828829</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.57591623</v>
+        <v>0.59183675</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.8333334</v>
+        <v>1.6666666</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R28" t="n">
-        <v>0.7592593</v>
+        <v>0.7222222</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1761658</v>
+        <v>0.17368421</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.25523013</v>
+        <v>0.2614108</v>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.34317344</v>
+      </c>
+      <c r="I29" t="n">
         <v>11</v>
       </c>
-      <c r="F29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G29" t="n">
-        <v>7</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.32061067</v>
-      </c>
-      <c r="I29" t="n">
-        <v>13</v>
-      </c>
       <c r="J29" t="n">
-        <v>0.42259413</v>
+        <v>0.41908714</v>
       </c>
       <c r="K29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L29" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>3.483871</v>
+        <v>4.209677</v>
       </c>
       <c r="O29" t="n">
+        <v>17</v>
+      </c>
+      <c r="P29" t="n">
         <v>9</v>
       </c>
-      <c r="P29" t="n">
-        <v>8</v>
-      </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>1.0645162</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>0.22317597</v>
+        <v>0.2375</v>
       </c>
       <c r="U29" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -4676,61 +4676,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.19911504</v>
+        <v>0.23144105</v>
       </c>
       <c r="C30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" t="n">
         <v>26</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>18</v>
       </c>
-      <c r="E30" t="n">
-        <v>27</v>
-      </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
+        <v>17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.28514057</v>
+      </c>
+      <c r="I30" t="n">
+        <v>24</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.3624454</v>
+      </c>
+      <c r="K30" t="n">
         <v>20</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.24691358</v>
-      </c>
-      <c r="I30" t="n">
-        <v>27</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.30973452</v>
-      </c>
-      <c r="K30" t="n">
-        <v>26</v>
-      </c>
       <c r="L30" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N30" t="n">
-        <v>3.7142856</v>
+        <v>3.857143</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q30" t="n">
+        <v>23</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.3174603</v>
+      </c>
+      <c r="S30" t="n">
         <v>19</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.3968254</v>
-      </c>
-      <c r="S30" t="n">
-        <v>23</v>
-      </c>
       <c r="T30" t="n">
-        <v>0.22978723</v>
+        <v>0.23404256</v>
       </c>
       <c r="U30" t="n">
         <v>12</v>
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.23577236</v>
+        <v>0.25896415</v>
       </c>
       <c r="C31" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
         <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H31" t="n">
-        <v>0.29850745</v>
+        <v>0.33093524</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>0.40650406</v>
+        <v>0.43824703</v>
       </c>
       <c r="K31" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L31" t="n">
         <v>72</v>
       </c>
       <c r="M31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N31" t="n">
-        <v>4.064516</v>
+        <v>3.919355</v>
       </c>
       <c r="O31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
+        <v>12</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.2741935</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.23504274</v>
+      </c>
+      <c r="U31" t="n">
         <v>14</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.2258065</v>
-      </c>
-      <c r="S31" t="n">
-        <v>11</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.23175965</v>
-      </c>
-      <c r="U31" t="n">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -549,19 +549,19 @@
         <v>0.23789474</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
         <v>367</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H2" t="n">
         <v>0.3084436</v>
@@ -591,7 +591,7 @@
         <v>106</v>
       </c>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R2" t="n">
         <v>1.2885462</v>
@@ -603,7 +603,7 @@
         <v>0.25078043</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -622,7 +622,7 @@
         <v>401</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
         <v>112</v>
@@ -646,7 +646,7 @@
         <v>754</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
         <v>4.974293</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24639718</v>
+        <v>0.24635163</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>104</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3108151</v>
+        <v>0.31087434</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4056239</v>
+        <v>0.40410006</v>
       </c>
       <c r="K4" t="n">
         <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3961504</v>
+        <v>3.4869528</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2005371</v>
+        <v>1.210084</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22395644</v>
+        <v>0.22611807</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -756,13 +756,13 @@
         <v>403</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
         <v>0.3185654</v>
@@ -780,7 +780,7 @@
         <v>809</v>
       </c>
       <c r="M5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N5" t="n">
         <v>4.3924</v>
@@ -804,7 +804,7 @@
         <v>0.2545757</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -817,13 +817,13 @@
         <v>0.24287222</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
         <v>337</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>73</v>
@@ -835,19 +835,19 @@
         <v>0.31071654</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
         <v>0.38296375</v>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
         <v>698</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
         <v>3.8143048</v>
@@ -859,7 +859,7 @@
         <v>91</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R6" t="n">
         <v>1.2621058</v>
@@ -884,13 +884,13 @@
         <v>0.2452133</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>448</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>112</v>
@@ -914,13 +914,13 @@
         <v>737</v>
       </c>
       <c r="M7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
         <v>4.2307363</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P7" t="n">
         <v>132</v>
@@ -948,61 +948,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24180472</v>
+        <v>0.24217118</v>
       </c>
       <c r="C8" t="n">
         <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3220974</v>
+        <v>0.32192415</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41593233</v>
+        <v>0.41684064</v>
       </c>
       <c r="K8" t="n">
         <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2329497</v>
+        <v>4.257556</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P8" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3286093</v>
+        <v>1.3377135</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23944661</v>
+        <v>0.23991582</v>
       </c>
       <c r="U8" t="n">
         <v>13</v>
@@ -1015,64 +1015,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22760801</v>
+        <v>0.22842288</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30869973</v>
+        <v>0.3091133</v>
       </c>
       <c r="I9" t="n">
         <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>0.38918158</v>
+        <v>0.39098787</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="M9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6190476</v>
+        <v>4.5882354</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.468254</v>
+        <v>1.4588236</v>
       </c>
       <c r="S9" t="n">
         <v>29</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25121108</v>
+        <v>0.25</v>
       </c>
       <c r="U9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22891144</v>
+        <v>0.22949117</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
         <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31060135</v>
+        <v>0.31221303</v>
       </c>
       <c r="I10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3661183</v>
+        <v>0.3679474</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7685306</v>
+        <v>3.7827764</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2600781</v>
+        <v>1.2609254</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23759972</v>
+        <v>0.2380137</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1149,43 +1149,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25389302</v>
+        <v>0.25560388</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3236187</v>
+        <v>0.32584608</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.41740012</v>
+        <v>0.42020744</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="M11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5955496</v>
+        <v>5.576973</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
@@ -1194,16 +1194,16 @@
         <v>119</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5196335</v>
+        <v>1.518758</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28791857</v>
+        <v>0.2872928</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,64 +1216,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23533471</v>
+        <v>0.23603542</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.31429434</v>
+      </c>
+      <c r="I12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.39816076</v>
+      </c>
+      <c r="K12" t="n">
         <v>15</v>
       </c>
-      <c r="H12" t="n">
-        <v>0.3139535</v>
-      </c>
-      <c r="I12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.39648032</v>
-      </c>
-      <c r="K12" t="n">
-        <v>18</v>
-      </c>
       <c r="L12" t="n">
-        <v>750</v>
+        <v>764</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7330434</v>
+        <v>3.8106713</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2234782</v>
+        <v>1.2405335</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23455933</v>
+        <v>0.23785079</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24132176</v>
+        <v>0.24198931</v>
       </c>
       <c r="C13" t="n">
         <v>19</v>
@@ -1292,7 +1292,7 @@
         <v>400</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>116</v>
@@ -1301,13 +1301,13 @@
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31572664</v>
+        <v>0.3163235</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40821093</v>
+        <v>0.4088785</v>
       </c>
       <c r="K13" t="n">
         <v>11</v>
@@ -1328,7 +1328,7 @@
         <v>119</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R13" t="n">
         <v>1.3928119</v>
@@ -1340,7 +1340,7 @@
         <v>0.24086604</v>
       </c>
       <c r="U13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24330817</v>
+        <v>0.24228029</v>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
         <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3142244</v>
+        <v>0.3128034</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>0.38984215</v>
+        <v>0.3895487</v>
       </c>
       <c r="K14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L14" t="n">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>4.865393</v>
+        <v>4.866953</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4355189</v>
+        <v>1.4369098</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26165363</v>
+        <v>0.2621849</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23967224</v>
+        <v>0.23851351</v>
       </c>
       <c r="C15" t="n">
         <v>20</v>
@@ -1432,49 +1432,49 @@
         <v>101</v>
       </c>
       <c r="G15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31772575</v>
+        <v>0.31616983</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3960396</v>
+        <v>0.39324325</v>
       </c>
       <c r="K15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" t="n">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.630916</v>
+        <v>4.594757</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P15" t="n">
         <v>92</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.405558</v>
+        <v>1.3987967</v>
       </c>
       <c r="S15" t="n">
         <v>26</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2377839</v>
+        <v>0.23635744</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26455566</v>
+        <v>0.26689076</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3469327</v>
+        <v>0.34910372</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.44194758</v>
+        <v>0.445042</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.476294</v>
+        <v>3.517197</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1222271</v>
+        <v>1.1285468</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21547157</v>
+        <v>0.21625392</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,13 +1551,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25008672</v>
+        <v>0.24982841</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -1566,46 +1566,46 @@
         <v>79</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32553127</v>
+        <v>0.32562387</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3981963</v>
+        <v>0.39739192</v>
       </c>
       <c r="K17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="M17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N17" t="n">
-        <v>3.946335</v>
+        <v>4.0686526</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P17" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2369109</v>
+        <v>1.2487047</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2271933</v>
+        <v>0.22928177</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25500527</v>
+        <v>0.25373653</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33909288</v>
+        <v>0.33781308</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39761153</v>
+        <v>0.39624608</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="M18" t="n">
         <v>8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3675365</v>
+        <v>3.3631992</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1769128</v>
+        <v>1.1813811</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21893063</v>
+        <v>0.21988596</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1688,7 +1688,7 @@
         <v>0.24638656</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>429</v>
@@ -1700,13 +1700,13 @@
         <v>110</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
         <v>0.32124662</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
         <v>0.41210085</v>
@@ -1730,7 +1730,7 @@
         <v>102</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>1.3975955</v>
@@ -1742,7 +1742,7 @@
         <v>0.25541848</v>
       </c>
       <c r="U19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -1755,19 +1755,19 @@
         <v>0.22928841</v>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>346</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20" t="n">
         <v>98</v>
       </c>
       <c r="G20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
         <v>0.29751554</v>
@@ -1779,7 +1779,7 @@
         <v>0.3746992</v>
       </c>
       <c r="K20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L20" t="n">
         <v>726</v>
@@ -1797,7 +1797,7 @@
         <v>87</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
         <v>1.2814783</v>
@@ -1822,7 +1822,7 @@
         <v>0.23589204</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" t="n">
         <v>417</v>
@@ -1852,7 +1852,7 @@
         <v>766</v>
       </c>
       <c r="M21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N21" t="n">
         <v>3.3587954</v>
@@ -1870,7 +1870,7 @@
         <v>1.1890004</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
         <v>0.22685835</v>
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23806275</v>
+        <v>0.23692204</v>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E22" t="n">
         <v>14</v>
@@ -1904,46 +1904,46 @@
         <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3043746</v>
+        <v>0.3031412</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40552524</v>
+        <v>0.40330747</v>
       </c>
       <c r="K22" t="n">
         <v>13</v>
       </c>
       <c r="L22" t="n">
-        <v>762</v>
+        <v>772</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1198277</v>
+        <v>4.141457</v>
       </c>
       <c r="O22" t="n">
         <v>14</v>
       </c>
       <c r="P22" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q22" t="n">
+        <v>18</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3140179</v>
+      </c>
+      <c r="S22" t="n">
         <v>17</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.3034483</v>
-      </c>
-      <c r="S22" t="n">
-        <v>15</v>
-      </c>
       <c r="T22" t="n">
-        <v>0.25450903</v>
+        <v>0.25593668</v>
       </c>
       <c r="U22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25827813</v>
+        <v>0.25964683</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>111</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3380608</v>
+      </c>
+      <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="F23" t="n">
-        <v>109</v>
-      </c>
-      <c r="G23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.3366569</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5</v>
-      </c>
       <c r="J23" t="n">
-        <v>0.4178808</v>
+        <v>0.4205363</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="M23" t="n">
         <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>4.28204</v>
+        <v>4.2444916</v>
       </c>
       <c r="O23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
         <v>88</v>
@@ -2001,16 +2001,16 @@
         <v>7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.311616</v>
+        <v>1.3042372</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23815967</v>
+        <v>0.23702712</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22446044</v>
+        <v>0.22514205</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.30032155</v>
+        <v>0.30117422</v>
       </c>
       <c r="I24" t="n">
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37194246</v>
+        <v>0.37535512</v>
       </c>
       <c r="K24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L24" t="n">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="M24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N24" t="n">
-        <v>4.161205</v>
+        <v>4.2594213</v>
       </c>
       <c r="O24" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P24" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3339238</v>
+        <v>1.3501314</v>
       </c>
       <c r="S24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24691358</v>
+        <v>0.24956492</v>
       </c>
       <c r="U24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -2096,13 +2096,13 @@
         <v>349</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F25" t="n">
         <v>93</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H25" t="n">
         <v>0.30670828</v>
@@ -2114,7 +2114,7 @@
         <v>0.41819417</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
         <v>663</v>
@@ -2144,7 +2144,7 @@
         <v>0.24729683</v>
       </c>
       <c r="U25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23303324</v>
+        <v>0.23164035</v>
       </c>
       <c r="C26" t="n">
         <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
         <v>105</v>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31336406</v>
+        <v>0.31274718</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3836565</v>
+        <v>0.38126287</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N26" t="n">
-        <v>3.688716</v>
+        <v>3.646154</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -2202,16 +2202,16 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1893644</v>
+        <v>1.1820513</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24116424</v>
+        <v>0.23997258</v>
       </c>
       <c r="U26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2437972</v>
+        <v>0.24565756</v>
       </c>
       <c r="C27" t="n">
         <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="E27" t="n">
         <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.32276297</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.393123</v>
+      </c>
+      <c r="K27" t="n">
         <v>21</v>
       </c>
-      <c r="H27" t="n">
-        <v>0.32123527</v>
-      </c>
-      <c r="I27" t="n">
-        <v>12</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.38978785</v>
-      </c>
-      <c r="K27" t="n">
-        <v>23</v>
-      </c>
       <c r="L27" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2350564</v>
+        <v>4.232238</v>
       </c>
       <c r="O27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P27" t="n">
         <v>90</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3456179</v>
+        <v>1.3441385</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2541593</v>
+        <v>0.2540238</v>
       </c>
       <c r="U27" t="n">
         <v>23</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26074395</v>
+        <v>0.26131907</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33865815</v>
+        <v>0.33890817</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39725533</v>
+        <v>0.39821747</v>
       </c>
       <c r="K28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L28" t="n">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7358491</v>
+        <v>3.7150466</v>
       </c>
       <c r="O28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
-        <v>1.190027</v>
+        <v>1.183755</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23388252</v>
+        <v>0.23292035</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2355,64 +2355,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24362509</v>
+        <v>0.2460911</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F29" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31960663</v>
+        <v>0.3216126</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39145416</v>
+        <v>0.39564922</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L29" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="M29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9903805</v>
+        <v>3.9904926</v>
       </c>
       <c r="O29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P29" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q29" t="n">
         <v>22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.23568</v>
+        <v>1.2394123</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23780069</v>
+        <v>0.23846675</v>
       </c>
       <c r="U29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -2431,7 +2431,7 @@
         <v>354</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
         <v>88</v>
@@ -2449,7 +2449,7 @@
         <v>0.38993496</v>
       </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L30" t="n">
         <v>648</v>
@@ -2479,7 +2479,7 @@
         <v>0.24100102</v>
       </c>
       <c r="U30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -2498,7 +2498,7 @@
         <v>470</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>117</v>
@@ -2510,7 +2510,7 @@
         <v>0.3214815</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
         <v>0.425546</v>
@@ -2528,7 +2528,7 @@
         <v>4.627269</v>
       </c>
       <c r="O31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P31" t="n">
         <v>123</v>
@@ -2809,13 +2809,13 @@
         <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
         <v>0.2890995</v>
@@ -2827,37 +2827,37 @@
         <v>0.3834197</v>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
         <v>39</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
         <v>4.7647057</v>
       </c>
       <c r="O2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
         <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R2" t="n">
         <v>1.1764706</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
         <v>0.2513089</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2682927</v>
+        <v>0.24757281</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3220974</v>
+        <v>0.30044842</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3699187</v>
+        <v>0.3592233</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L3" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="M3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.3653846</v>
+      </c>
+      <c r="O3" t="n">
+        <v>24</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>13</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5576923</v>
+      </c>
+      <c r="S3" t="n">
         <v>26</v>
       </c>
-      <c r="N3" t="n">
-        <v>5.4590163</v>
-      </c>
-      <c r="O3" t="n">
-        <v>25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>19</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.4754099</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
       <c r="T3" t="n">
-        <v>0.2768595</v>
+        <v>0.2952381</v>
       </c>
       <c r="U3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.17088607</v>
+        <v>0.18324608</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -2952,46 +2952,46 @@
         <v>30</v>
       </c>
       <c r="H4" t="n">
-        <v>0.25139666</v>
+        <v>0.2626728</v>
       </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2278481</v>
+        <v>0.2356021</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9302325</v>
+        <v>4.326923</v>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0232558</v>
+        <v>1.1923077</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>0.20261438</v>
+        <v>0.23834197</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3010,55 +3010,55 @@
         <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H5" t="n">
         <v>0.30493274</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>0.31770834</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
         <v>60</v>
       </c>
       <c r="M5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N5" t="n">
         <v>3.9272728</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
         <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
         <v>1.2545455</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T5" t="n">
         <v>0.23584905</v>
       </c>
       <c r="U5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.23076923</v>
+        <v>0.23157895</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.29149798</v>
+        <v>0.2857143</v>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>0.36199096</v>
+        <v>0.3631579</v>
       </c>
       <c r="K6" t="n">
         <v>21</v>
       </c>
       <c r="L6" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.796875</v>
+        <v>3.9272728</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1875</v>
+        <v>1.1818181</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>0.20851064</v>
+        <v>0.205</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3135,16 +3135,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25306123</v>
+        <v>0.26923078</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>17</v>
@@ -3153,43 +3153,43 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.35191637</v>
+        <v>0.375</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4979592</v>
+        <v>0.5480769</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>3.515625</v>
+        <v>3.6666667</v>
       </c>
       <c r="O7" t="n">
         <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
+        <v>17</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4444444</v>
+      </c>
+      <c r="S7" t="n">
         <v>23</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.453125</v>
-      </c>
-      <c r="S7" t="n">
-        <v>24</v>
-      </c>
       <c r="T7" t="n">
-        <v>0.28</v>
+        <v>0.2890995</v>
       </c>
       <c r="U7" t="n">
         <v>26</v>
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.30092594</v>
+        <v>0.2964427</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>0.373444</v>
+        <v>0.3642857</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.49074075</v>
+        <v>0.49011856</v>
       </c>
       <c r="K8" t="n">
         <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8867924</v>
+        <v>3.375</v>
       </c>
       <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1886792</v>
+        <v>1.3206522</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.21578947</v>
+        <v>0.22522523</v>
       </c>
       <c r="U8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.245</v>
+        <v>0.25210086</v>
       </c>
       <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>33</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.30501932</v>
+      </c>
+      <c r="I9" t="n">
         <v>18</v>
       </c>
-      <c r="D9" t="n">
+      <c r="J9" t="n">
+        <v>0.4159664</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15</v>
+      </c>
+      <c r="L9" t="n">
+        <v>71</v>
+      </c>
+      <c r="M9" t="n">
+        <v>28</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.644068</v>
+      </c>
+      <c r="O9" t="n">
         <v>26</v>
       </c>
-      <c r="E9" t="n">
-        <v>18</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>19</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.29816514</v>
-      </c>
-      <c r="I9" t="n">
-        <v>19</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="K9" t="n">
-        <v>16</v>
-      </c>
-      <c r="L9" t="n">
-        <v>58</v>
-      </c>
-      <c r="M9" t="n">
-        <v>17</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>27</v>
-      </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>1.76</v>
+        <v>1.5932204</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2955665</v>
+        <v>0.2746781</v>
       </c>
       <c r="U9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -3336,49 +3336,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24623115</v>
+        <v>0.25108224</v>
       </c>
       <c r="C10" t="n">
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2809524</v>
+        <v>0.30677292</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36180905</v>
+        <v>0.38528138</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L10" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.7142856</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
         <v>8</v>
@@ -3387,13 +3387,13 @@
         <v>1.3333334</v>
       </c>
       <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.25203252</v>
+      </c>
+      <c r="U10" t="n">
         <v>21</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.24880382</v>
-      </c>
-      <c r="U10" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -3403,43 +3403,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25</v>
+        <v>0.27160493</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32478634</v>
+        <v>0.3512545</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.50961536</v>
+        <v>0.5308642</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" t="n">
-        <v>7.1320753</v>
+        <v>6.677419</v>
       </c>
       <c r="O11" t="n">
         <v>28</v>
@@ -3451,16 +3451,16 @@
         <v>19</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5849056</v>
+        <v>1.5645162</v>
       </c>
       <c r="S11" t="n">
         <v>27</v>
       </c>
       <c r="T11" t="n">
-        <v>0.32300884</v>
+        <v>0.31128404</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.236</v>
+        <v>0.25291827</v>
       </c>
       <c r="C12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" t="n">
+        <v>45</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3240418</v>
+      </c>
+      <c r="I12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.47470817</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>62</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.876923</v>
+      </c>
+      <c r="O12" t="n">
+        <v>12</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
         <v>19</v>
       </c>
-      <c r="D12" t="n">
-        <v>42</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>14</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.3057554</v>
-      </c>
-      <c r="I12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="K12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L12" t="n">
-        <v>61</v>
-      </c>
-      <c r="M12" t="n">
-        <v>21</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.7272727</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>16</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.8939394000000001</v>
+        <v>1.1846154</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>0.19246861</v>
+        <v>0.24193548</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.22594142</v>
+        <v>0.2451923</v>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
         <v>14</v>
       </c>
-      <c r="F13" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9</v>
-      </c>
       <c r="H13" t="n">
-        <v>0.28735632</v>
+        <v>0.31441048</v>
       </c>
       <c r="I13" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
-        <v>0.36820084</v>
+        <v>0.39423078</v>
       </c>
       <c r="K13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="M13" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>4.857143</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="n">
         <v>28</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3015873</v>
+        <v>1.4074074</v>
       </c>
       <c r="S13" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="T13" t="n">
-        <v>0.22457626</v>
+        <v>0.23414634</v>
       </c>
       <c r="U13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.17989418</v>
+        <v>0.19587629</v>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2415459</v>
+      </c>
+      <c r="I14" t="n">
+        <v>29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.32474226</v>
+      </c>
+      <c r="K14" t="n">
         <v>25</v>
       </c>
-      <c r="H14" t="n">
-        <v>0.23152709</v>
-      </c>
-      <c r="I14" t="n">
-        <v>28</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.29100528</v>
-      </c>
-      <c r="K14" t="n">
-        <v>27</v>
-      </c>
       <c r="L14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N14" t="n">
-        <v>9.292208</v>
+        <v>7.7388535</v>
       </c>
       <c r="O14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0064936</v>
+        <v>1.9108281</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T14" t="n">
-        <v>0.35159817</v>
+        <v>0.33796296</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.24539877</v>
+        <v>0.22680412</v>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30113637</v>
+        <v>0.27884614</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>0.35582823</v>
+        <v>0.31958762</v>
       </c>
       <c r="K15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L15" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8139534</v>
+        <v>4.2352943</v>
       </c>
       <c r="O15" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
         <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2790698</v>
+        <v>1.1960784</v>
       </c>
       <c r="S15" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T15" t="n">
-        <v>0.24096386</v>
+        <v>0.21875</v>
       </c>
       <c r="U15" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.29953918</v>
+        <v>0.32156864</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>0.37651822</v>
+        <v>0.39726028</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.49769586</v>
+        <v>0.5254902</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>4.8688526</v>
       </c>
       <c r="O16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4230769</v>
+        <v>1.4590164</v>
       </c>
       <c r="S16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T16" t="n">
-        <v>0.26130652</v>
+        <v>0.2638298</v>
       </c>
       <c r="U16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.30414745</v>
+        <v>0.29435483</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>6</v>
       </c>
       <c r="G17" t="n">
+        <v>18</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.35869566</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.4717742</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>44</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="O17" t="n">
         <v>19</v>
       </c>
-      <c r="H17" t="n">
-        <v>0.3628692</v>
-      </c>
-      <c r="I17" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.49308756</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>41</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="P17" t="n">
         <v>8</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.5961537</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>6</v>
-      </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0192307</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>0.20320855</v>
+        <v>0.23423423</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.27918783</v>
+        <v>0.2599119</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>0.36444443</v>
+        <v>0.34496123</v>
       </c>
       <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4581498</v>
+      </c>
+      <c r="K18" t="n">
+        <v>11</v>
+      </c>
+      <c r="L18" t="n">
+        <v>54</v>
+      </c>
+      <c r="M18" t="n">
+        <v>17</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.234375</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>19</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.171875</v>
+      </c>
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="J18" t="n">
-        <v>0.48730963</v>
-      </c>
-      <c r="K18" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>47</v>
-      </c>
-      <c r="M18" t="n">
-        <v>10</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.2727273</v>
-      </c>
-      <c r="O18" t="n">
-        <v>7</v>
-      </c>
-      <c r="P18" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>12</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.1090909</v>
-      </c>
-      <c r="S18" t="n">
-        <v>6</v>
-      </c>
       <c r="T18" t="n">
-        <v>0.2</v>
+        <v>0.21459228</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -3942,43 +3942,43 @@
         <v>0.2596154</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>34</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
         <v>0.3171806</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J19" t="n">
         <v>0.46153846</v>
       </c>
       <c r="K19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
         <v>38</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
         <v>4.8333335</v>
       </c>
       <c r="O19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P19" t="n">
         <v>10</v>
@@ -3996,7 +3996,7 @@
         <v>0.24880382</v>
       </c>
       <c r="U19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.20600858</v>
+        <v>0.20103092</v>
       </c>
       <c r="C20" t="n">
+        <v>27</v>
+      </c>
+      <c r="D20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" t="n">
         <v>26</v>
       </c>
-      <c r="D20" t="n">
-        <v>21</v>
-      </c>
-      <c r="E20" t="n">
-        <v>23</v>
-      </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29433963</v>
+        <v>0.28310502</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>0.35622317</v>
+        <v>0.34536082</v>
       </c>
       <c r="K20" t="n">
         <v>23</v>
       </c>
       <c r="L20" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="M20" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.903226</v>
+        <v>3.4615386</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P20" t="n">
         <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1451613</v>
+        <v>1.2115384</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.22510822</v>
+        <v>0.2371134</v>
       </c>
       <c r="U20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -4073,61 +4073,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.13716814</v>
+        <v>0.12041885</v>
       </c>
       <c r="C21" t="n">
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H21" t="n">
-        <v>0.19087137</v>
+        <v>0.1724138</v>
       </c>
       <c r="I21" t="n">
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2300885</v>
+        <v>0.20942408</v>
       </c>
       <c r="K21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L21" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7540107</v>
+        <v>4.3067484</v>
       </c>
       <c r="O21" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2352941</v>
+        <v>1.2331289</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2375</v>
+        <v>0.23923445</v>
       </c>
       <c r="U21" t="n">
         <v>16</v>
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.28163266</v>
+        <v>0.25316456</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H22" t="n">
-        <v>0.34798536</v>
+        <v>0.31417623</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>0.47346938</v>
+        <v>0.4177215</v>
       </c>
       <c r="K22" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L22" t="n">
         <v>72</v>
       </c>
       <c r="M22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N22" t="n">
-        <v>4.645161</v>
+        <v>4.790323</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3548387</v>
+        <v>1.532258</v>
       </c>
       <c r="S22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T22" t="n">
-        <v>0.23966943</v>
+        <v>0.26229507</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -4207,16 +4207,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.27125505</v>
+        <v>0.28853756</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
         <v>15</v>
@@ -4225,19 +4225,19 @@
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0.34408602</v>
+        <v>0.3676976</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.49392712</v>
+        <v>0.51778656</v>
       </c>
       <c r="K23" t="n">
         <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M23" t="n">
         <v>30</v>
@@ -4246,25 +4246,25 @@
         <v>6.196721</v>
       </c>
       <c r="O23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P23" t="n">
         <v>11</v>
       </c>
       <c r="Q23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4918033</v>
+        <v>1.3934426</v>
       </c>
       <c r="S23" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="T23" t="n">
-        <v>0.26890758</v>
+        <v>0.2616034</v>
       </c>
       <c r="U23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.28078818</v>
+        <v>0.28033474</v>
       </c>
       <c r="C24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>14</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11</v>
+      </c>
+      <c r="G24" t="n">
         <v>6</v>
       </c>
-      <c r="D24" t="n">
-        <v>24</v>
-      </c>
-      <c r="E24" t="n">
-        <v>22</v>
-      </c>
-      <c r="F24" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>14</v>
-      </c>
       <c r="H24" t="n">
-        <v>0.37339056</v>
+        <v>0.37226278</v>
       </c>
       <c r="I24" t="n">
         <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4679803</v>
+        <v>0.49372384</v>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N24" t="n">
-        <v>8.36129</v>
+        <v>9.050280000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q24" t="n">
         <v>30</v>
       </c>
       <c r="R24" t="n">
-        <v>1.916129</v>
+        <v>2.0446928</v>
       </c>
       <c r="S24" t="n">
+        <v>30</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.3372549</v>
+      </c>
+      <c r="U24" t="n">
         <v>29</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.31797236</v>
-      </c>
-      <c r="U24" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2300885</v>
+        <v>0.24226804</v>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E25" t="n">
+        <v>21</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" t="n">
         <v>16</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H25" t="n">
+        <v>0.27884614</v>
+      </c>
+      <c r="I25" t="n">
+        <v>25</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.41237113</v>
+      </c>
+      <c r="K25" t="n">
+        <v>16</v>
+      </c>
+      <c r="L25" t="n">
+        <v>37</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.6346154</v>
+      </c>
+      <c r="O25" t="n">
         <v>9</v>
-      </c>
-      <c r="G25" t="n">
-        <v>9</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.27459016</v>
-      </c>
-      <c r="I25" t="n">
-        <v>26</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.41150442</v>
-      </c>
-      <c r="K25" t="n">
-        <v>15</v>
-      </c>
-      <c r="L25" t="n">
-        <v>47</v>
-      </c>
-      <c r="M25" t="n">
-        <v>10</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.4262295</v>
-      </c>
-      <c r="O25" t="n">
-        <v>18</v>
       </c>
       <c r="P25" t="n">
         <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2459016</v>
+        <v>1.1153846</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>0.22943723</v>
+        <v>0.19895288</v>
       </c>
       <c r="U25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.25365853</v>
+        <v>0.24120604</v>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D26" t="n">
         <v>26</v>
@@ -4423,49 +4423,49 @@
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" t="n">
-        <v>0.34615386</v>
+        <v>0.33480176</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3512195</v>
+        <v>0.34170854</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L26" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M26" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="N26" t="n">
-        <v>3.7058823</v>
+        <v>2.7692308</v>
       </c>
       <c r="O26" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.137255</v>
+        <v>1.0384616</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>0.234375</v>
+        <v>0.21465969</v>
       </c>
       <c r="U26" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -4475,46 +4475,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1589404</v>
+        <v>0.20418848</v>
       </c>
       <c r="C27" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2195122</v>
+        <v>0.26442307</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>0.23178808</v>
+        <v>0.31413612</v>
       </c>
       <c r="K27" t="n">
         <v>28</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2727273</v>
+        <v>3.3962264</v>
       </c>
       <c r="O27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
@@ -4523,16 +4523,16 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3181819</v>
+        <v>1.3018868</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23125</v>
+        <v>0.23316061</v>
       </c>
       <c r="U27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -4542,37 +4542,37 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3112245</v>
+        <v>0.29533678</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.37272727</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.53367877</v>
+      </c>
+      <c r="K28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.3828829</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.59183675</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
       <c r="L28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
@@ -4584,19 +4584,19 @@
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
-        <v>0.7222222</v>
+        <v>0.7777778</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.17368421</v>
+        <v>0.1897436</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2614108</v>
+        <v>0.28225806</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F29" t="n">
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H29" t="n">
-        <v>0.34317344</v>
+        <v>0.3537906</v>
       </c>
       <c r="I29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>0.41908714</v>
+        <v>0.44354838</v>
       </c>
       <c r="K29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L29" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>4.209677</v>
+        <v>4.064516</v>
       </c>
       <c r="O29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R29" t="n">
-        <v>1.0645162</v>
+        <v>1.1774193</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2375</v>
+        <v>0.25101215</v>
       </c>
       <c r="U29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.23144105</v>
+        <v>0.23737374</v>
       </c>
       <c r="C30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
+        <v>21</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="n">
         <v>18</v>
       </c>
-      <c r="F30" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" t="n">
-        <v>17</v>
-      </c>
       <c r="H30" t="n">
-        <v>0.28514057</v>
+        <v>0.2962963</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3624454</v>
+        <v>0.36868685</v>
       </c>
       <c r="K30" t="n">
         <v>20</v>
       </c>
       <c r="L30" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="M30" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="N30" t="n">
-        <v>3.857143</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3174603</v>
+        <v>1.2407408</v>
       </c>
       <c r="S30" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23404256</v>
+        <v>0.22277227</v>
       </c>
       <c r="U30" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.25896415</v>
+        <v>0.26511627</v>
       </c>
       <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>32</v>
+      </c>
+      <c r="E31" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>14</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.34166667</v>
+      </c>
+      <c r="I31" t="n">
+        <v>11</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.45581394</v>
+      </c>
+      <c r="K31" t="n">
         <v>12</v>
       </c>
-      <c r="D31" t="n">
-        <v>37</v>
-      </c>
-      <c r="E31" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" t="n">
-        <v>9</v>
-      </c>
-      <c r="G31" t="n">
-        <v>9</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.33093524</v>
-      </c>
-      <c r="I31" t="n">
-        <v>12</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.43824703</v>
-      </c>
-      <c r="K31" t="n">
-        <v>13</v>
-      </c>
       <c r="L31" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="M31" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="N31" t="n">
-        <v>3.919355</v>
+        <v>2.8867924</v>
       </c>
       <c r="O31" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2741935</v>
+        <v>1.1509434</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>0.23504274</v>
+        <v>0.21538462</v>
       </c>
       <c r="U31" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23789474</v>
+        <v>0.23664384</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
         <v>29</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3084436</v>
+        <v>0.30686364</v>
       </c>
       <c r="I2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.38287672</v>
+      </c>
+      <c r="K2" t="n">
         <v>26</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.3859649</v>
-      </c>
-      <c r="K2" t="n">
-        <v>25</v>
-      </c>
       <c r="L2" t="n">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.317621</v>
+        <v>4.2991414</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2885462</v>
+        <v>1.2952789</v>
       </c>
       <c r="S2" t="n">
         <v>14</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25078043</v>
+        <v>0.2520243</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24831763</v>
+        <v>0.24843699</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="E3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F3" t="n">
+        <v>113</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3266979</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4100033</v>
+      </c>
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="F3" t="n">
-        <v>112</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.32684824</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.41117093</v>
-      </c>
-      <c r="K3" t="n">
-        <v>10</v>
-      </c>
       <c r="L3" t="n">
-        <v>754</v>
+        <v>771</v>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>4.974293</v>
+        <v>5.0653267</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="Q3" t="n">
         <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4460155</v>
+        <v>1.4585427</v>
       </c>
       <c r="S3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26385662</v>
+        <v>0.26489636</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,64 +680,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24635163</v>
+        <v>0.24694294</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31087434</v>
+        <v>0.3124235</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>0.40410006</v>
+        <v>0.4113451</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4869528</v>
+        <v>3.4639308</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q4" t="n">
         <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.210084</v>
+        <v>1.2142549</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22611807</v>
+        <v>0.22725688</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23850085</v>
+        <v>0.23807935</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3185654</v>
+        <v>0.3190925</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39693356</v>
+        <v>0.39646548</v>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>809</v>
+        <v>825</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3924</v>
+        <v>4.3497496</v>
       </c>
       <c r="O5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
         <v>99</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3744662</v>
+        <v>1.3772955</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2545757</v>
+        <v>0.25398892</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
@@ -814,64 +814,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24287222</v>
+        <v>0.2432154</v>
       </c>
       <c r="C6" t="n">
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31071654</v>
+        <v>0.3118047</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38296375</v>
+        <v>0.38543457</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8143048</v>
+        <v>3.7600868</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2621058</v>
+        <v>1.2507592</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24288225</v>
+        <v>0.24156916</v>
       </c>
       <c r="U6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2452133</v>
+        <v>0.24391848</v>
       </c>
       <c r="C7" t="n">
         <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -896,49 +896,49 @@
         <v>112</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33972684</v>
+        <v>0.33798406</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41383943</v>
+        <v>0.41058514</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>737</v>
+        <v>755</v>
       </c>
       <c r="M7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2307363</v>
+        <v>4.3618007</v>
       </c>
       <c r="O7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2578562</v>
+        <v>1.2709298</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24219555</v>
+        <v>0.24448161</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24217118</v>
+        <v>0.24159022</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32192415</v>
+        <v>0.3208798</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41684064</v>
+        <v>0.41522256</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>777</v>
+        <v>795</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.257556</v>
+        <v>4.2053914</v>
       </c>
       <c r="O8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3377135</v>
+        <v>1.3311938</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23991582</v>
+        <v>0.23902607</v>
       </c>
       <c r="U8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22842288</v>
+        <v>0.22839716</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E9" t="n">
         <v>21</v>
@@ -1030,49 +1030,49 @@
         <v>106</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3091133</v>
+        <v>0.30998197</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39098787</v>
+        <v>0.3886818</v>
       </c>
       <c r="K9" t="n">
         <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>816</v>
+        <v>829</v>
       </c>
       <c r="M9" t="n">
         <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5882354</v>
+        <v>4.597701</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4588236</v>
+        <v>1.458493</v>
       </c>
       <c r="S9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.25</v>
+        <v>0.24932976</v>
       </c>
       <c r="U9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -1082,61 +1082,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22949117</v>
+        <v>0.22884224</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E10" t="n">
         <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31221303</v>
+        <v>0.31126422</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3679474</v>
+        <v>0.36594447</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>713</v>
+        <v>740</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7827764</v>
+        <v>3.7603514</v>
       </c>
       <c r="O10" t="n">
         <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2609254</v>
+        <v>1.2572145</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2380137</v>
+        <v>0.23753764</v>
       </c>
       <c r="U10" t="n">
         <v>11</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25560388</v>
+        <v>0.25775892</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32584608</v>
+        <v>0.32836694</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42020744</v>
+        <v>0.42469782</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>772</v>
+        <v>785</v>
       </c>
       <c r="M11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.576973</v>
+        <v>5.541087</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q11" t="n">
         <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.518758</v>
+        <v>1.517067</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2872928</v>
+        <v>0.28743654</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,64 +1216,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23603542</v>
+        <v>0.23535353</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" t="n">
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31429434</v>
+        <v>0.31330344</v>
       </c>
       <c r="I12" t="n">
         <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39816076</v>
+        <v>0.396633</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8106713</v>
+        <v>3.7669077</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
         <v>91</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2405335</v>
+        <v>1.2313908</v>
       </c>
       <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.23644987</v>
+      </c>
+      <c r="U12" t="n">
         <v>8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.23785079</v>
-      </c>
-      <c r="U12" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24198931</v>
+        <v>0.24158221</v>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3163235</v>
+        <v>0.31569716</v>
       </c>
       <c r="I13" t="n">
         <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4088785</v>
+        <v>0.4102648</v>
       </c>
       <c r="K13" t="n">
         <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="M13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>4.772093</v>
+        <v>4.7771807</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
       </c>
       <c r="P13" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3928119</v>
+        <v>1.3902439</v>
       </c>
       <c r="S13" t="n">
         <v>24</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24086604</v>
+        <v>0.24031778</v>
       </c>
       <c r="U13" t="n">
         <v>15</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24228029</v>
+        <v>0.24135616</v>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E14" t="n">
         <v>23</v>
@@ -1368,43 +1368,43 @@
         <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3128034</v>
+        <v>0.31150496</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3895487</v>
+        <v>0.3873783</v>
       </c>
       <c r="K14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L14" t="n">
-        <v>701</v>
+        <v>716</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.866953</v>
+        <v>4.879932</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4369098</v>
+        <v>1.4395417</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2621849</v>
+        <v>0.26286092</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23851351</v>
+        <v>0.23700762</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G15" t="n">
         <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31616983</v>
+        <v>0.3140325</v>
       </c>
       <c r="I15" t="n">
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39324325</v>
+        <v>0.39059913</v>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L15" t="n">
-        <v>830</v>
+        <v>846</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.594757</v>
+        <v>4.637967</v>
       </c>
       <c r="O15" t="n">
         <v>24</v>
       </c>
       <c r="P15" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q15" t="n">
         <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3987967</v>
+        <v>1.4010919</v>
       </c>
       <c r="S15" t="n">
         <v>26</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23635744</v>
+        <v>0.23684211</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26689076</v>
+        <v>0.265259</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34910372</v>
+        <v>0.3480392</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.445042</v>
+        <v>0.44275817</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.517197</v>
+        <v>3.4714286</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1285468</v>
+        <v>1.1243697</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21625392</v>
+        <v>0.21562606</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.24982841</v>
+        <v>0.25158915</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32562387</v>
+        <v>0.32819906</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.39739192</v>
+        <v>0.40414855</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L17" t="n">
-        <v>715</v>
+        <v>734</v>
       </c>
       <c r="M17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N17" t="n">
-        <v>4.0686526</v>
+        <v>4.055696</v>
       </c>
       <c r="O17" t="n">
         <v>11</v>
       </c>
       <c r="P17" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487047</v>
+        <v>1.2481012</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22928177</v>
+        <v>0.22983463</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25373653</v>
+        <v>0.25490198</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33781308</v>
+        <v>0.33838835</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39624608</v>
+        <v>0.39790398</v>
       </c>
       <c r="K18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3631992</v>
+        <v>3.362047</v>
       </c>
       <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" t="n">
-        <v>83</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
+        <v>1.1756929</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.1813811</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
       <c r="T18" t="n">
-        <v>0.21988596</v>
+        <v>0.21905424</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24638656</v>
+        <v>0.24622455</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32124662</v>
+        <v>0.32104185</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.41210085</v>
+        <v>0.41661194</v>
       </c>
       <c r="K19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>719</v>
+        <v>743</v>
       </c>
       <c r="M19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8226705</v>
+        <v>4.821429</v>
       </c>
       <c r="O19" t="n">
         <v>27</v>
       </c>
       <c r="P19" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Q19" t="n">
         <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3975955</v>
+        <v>1.3953782</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25541848</v>
+        <v>0.25457516</v>
       </c>
       <c r="U19" t="n">
         <v>25</v>
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.22928841</v>
+        <v>0.23030506</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E20" t="n">
         <v>28</v>
       </c>
       <c r="F20" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G20" t="n">
         <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29751554</v>
+        <v>0.2983944</v>
       </c>
       <c r="I20" t="n">
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3746992</v>
+        <v>0.37546095</v>
       </c>
       <c r="K20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="M20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N20" t="n">
-        <v>4.119037</v>
+        <v>4.2517896</v>
       </c>
       <c r="O20" t="n">
+        <v>17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q20" t="n">
         <v>13</v>
       </c>
-      <c r="P20" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.2814783</v>
+        <v>1.288421</v>
       </c>
       <c r="S20" t="n">
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23391216</v>
+        <v>0.23476523</v>
       </c>
       <c r="U20" t="n">
         <v>7</v>
@@ -1819,64 +1819,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23589204</v>
+        <v>0.23541524</v>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31878674</v>
+        <v>0.31880108</v>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4209604</v>
+        <v>0.42175704</v>
       </c>
       <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>779</v>
+      </c>
+      <c r="M21" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.3850746</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3</v>
       </c>
-      <c r="L21" t="n">
-        <v>766</v>
-      </c>
-      <c r="M21" t="n">
-        <v>23</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.3587954</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.1890004</v>
+        <v>1.192324</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22685835</v>
+        <v>0.22716387</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23692204</v>
+        <v>0.23792069</v>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3031412</v>
+        <v>0.30391565</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40330747</v>
+        <v>0.40586472</v>
       </c>
       <c r="K22" t="n">
         <v>13</v>
       </c>
       <c r="L22" t="n">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="M22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.141457</v>
+        <v>4.1057286</v>
       </c>
       <c r="O22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P22" t="n">
         <v>101</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3140179</v>
+        <v>1.3053918</v>
       </c>
       <c r="S22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25593668</v>
+        <v>0.25489557</v>
       </c>
       <c r="U22" t="n">
         <v>26</v>
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.25964683</v>
+        <v>0.2610083</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3380608</v>
+        <v>0.33889204</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4205363</v>
+        <v>0.4208679</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>834</v>
+        <v>850</v>
       </c>
       <c r="M23" t="n">
         <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2444916</v>
+        <v>4.2666945</v>
       </c>
       <c r="O23" t="n">
+        <v>18</v>
+      </c>
+      <c r="P23" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3090004</v>
+      </c>
+      <c r="S23" t="n">
         <v>17</v>
       </c>
-      <c r="P23" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3042372</v>
-      </c>
-      <c r="S23" t="n">
-        <v>15</v>
-      </c>
       <c r="T23" t="n">
-        <v>0.23702712</v>
+        <v>0.23779888</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22514205</v>
+        <v>0.22430556</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.30117422</v>
+        <v>0.3</v>
       </c>
       <c r="I24" t="n">
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37535512</v>
+        <v>0.37291667</v>
       </c>
       <c r="K24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>717</v>
+        <v>744</v>
       </c>
       <c r="M24" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.241202</v>
+      </c>
+      <c r="O24" t="n">
+        <v>16</v>
+      </c>
+      <c r="P24" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q24" t="n">
         <v>13</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.2594213</v>
-      </c>
-      <c r="O24" t="n">
-        <v>19</v>
-      </c>
-      <c r="P24" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>14</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.3501314</v>
+        <v>1.3454936</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24956492</v>
+        <v>0.24820758</v>
       </c>
       <c r="U24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -2087,64 +2087,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2549219</v>
+        <v>0.25587553</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30670828</v>
+        <v>0.30745813</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41819417</v>
+        <v>0.41972858</v>
       </c>
       <c r="K25" t="n">
         <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3655534</v>
+        <v>4.4903307</v>
       </c>
       <c r="O25" t="n">
+        <v>22</v>
+      </c>
+      <c r="P25" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3807477</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.24974482</v>
+      </c>
+      <c r="U25" t="n">
         <v>21</v>
-      </c>
-      <c r="P25" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.3642355</v>
-      </c>
-      <c r="S25" t="n">
-        <v>21</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.24729683</v>
-      </c>
-      <c r="U25" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23164035</v>
+        <v>0.23162135</v>
       </c>
       <c r="C26" t="n">
         <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G26" t="n">
         <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31274718</v>
+        <v>0.31238833</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38126287</v>
+        <v>0.3820074</v>
       </c>
       <c r="K26" t="n">
         <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="M26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>3.646154</v>
+        <v>3.586466</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -2202,16 +2202,16 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1820513</v>
+        <v>1.1666666</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23997258</v>
+        <v>0.23732796</v>
       </c>
       <c r="U26" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24565756</v>
+        <v>0.24792817</v>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32276297</v>
+        <v>0.32538956</v>
       </c>
       <c r="I27" t="n">
         <v>9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.393123</v>
+        <v>0.39744475</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L27" t="n">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.232238</v>
+        <v>4.14484</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P27" t="n">
         <v>90</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3441385</v>
+        <v>1.3347788</v>
       </c>
       <c r="S27" t="n">
         <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2540238</v>
+        <v>0.25248033</v>
       </c>
       <c r="U27" t="n">
         <v>23</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26131907</v>
+        <v>0.26027873</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G28" t="n">
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33890817</v>
+        <v>0.33816275</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39821747</v>
+        <v>0.39965156</v>
       </c>
       <c r="K28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7150466</v>
+        <v>3.7617188</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Q28" t="n">
         <v>20</v>
       </c>
       <c r="R28" t="n">
-        <v>1.183755</v>
+        <v>1.1809896</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23292035</v>
+        <v>0.23268698</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2460911</v>
+        <v>0.24427995</v>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" t="n">
         <v>364</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F29" t="n">
         <v>95</v>
       </c>
       <c r="G29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3216126</v>
+        <v>0.3197238</v>
       </c>
       <c r="I29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39564922</v>
+        <v>0.39266488</v>
       </c>
       <c r="K29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="M29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9904926</v>
+        <v>3.9675353</v>
       </c>
       <c r="O29" t="n">
         <v>10</v>
       </c>
       <c r="P29" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q29" t="n">
         <v>22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2394123</v>
+        <v>1.2340881</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23846675</v>
+        <v>0.23775989</v>
       </c>
       <c r="U29" t="n">
         <v>12</v>
@@ -2422,16 +2422,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24786033</v>
+        <v>0.24505532</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
         <v>88</v>
@@ -2440,43 +2440,43 @@
         <v>23</v>
       </c>
       <c r="H30" t="n">
-        <v>0.31029138</v>
+        <v>0.3069909</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38993496</v>
+        <v>0.38484746</v>
       </c>
       <c r="K30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.0831537</v>
+        <v>4.1205735</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P30" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3106419</v>
+        <v>1.3064923</v>
       </c>
       <c r="S30" t="n">
         <v>16</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24100102</v>
+        <v>0.24044265</v>
       </c>
       <c r="U30" t="n">
         <v>16</v>
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2475182</v>
+        <v>0.248057</v>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3214815</v>
+        <v>0.32212237</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>0.425546</v>
+        <v>0.42940414</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>738</v>
+        <v>751</v>
       </c>
       <c r="M31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.627269</v>
+        <v>4.657862</v>
       </c>
       <c r="O31" t="n">
         <v>25</v>
       </c>
       <c r="P31" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3803293</v>
+        <v>1.3867106</v>
       </c>
       <c r="S31" t="n">
         <v>23</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25630942</v>
+        <v>0.25775504</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.22279793</v>
+        <v>0.20812182</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2890995</v>
+        <v>0.28767124</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3834197</v>
+        <v>0.3401015</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7647057</v>
+        <v>4.090909</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1764706</v>
+        <v>1.290909</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2513089</v>
+        <v>0.27102804</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24757281</v>
+        <v>0.25853658</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
       </c>
       <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.30941704</v>
+      </c>
+      <c r="I3" t="n">
         <v>18</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.30044842</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>0.38536584</v>
+      </c>
+      <c r="K3" t="n">
         <v>20</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.3592233</v>
-      </c>
-      <c r="K3" t="n">
-        <v>22</v>
-      </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>5.3653846</v>
+        <v>6.962264</v>
       </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5576923</v>
+        <v>1.754717</v>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2952381</v>
+        <v>0.30414745</v>
       </c>
       <c r="U3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.18324608</v>
+        <v>0.22680412</v>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2626728</v>
+        <v>0.32</v>
       </c>
       <c r="I4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2356021</v>
+        <v>0.4226804</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>4.326923</v>
+        <v>4.075472</v>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
         <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1923077</v>
+        <v>1.3018868</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23834197</v>
+        <v>0.25603864</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.20833333</v>
+        <v>0.20744681</v>
       </c>
       <c r="C5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3122172</v>
+      </c>
+      <c r="I5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.35106382</v>
+      </c>
+      <c r="K5" t="n">
         <v>25</v>
       </c>
-      <c r="D5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>27</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.30493274</v>
-      </c>
-      <c r="I5" t="n">
-        <v>19</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.31770834</v>
-      </c>
-      <c r="K5" t="n">
-        <v>27</v>
-      </c>
       <c r="L5" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="M5" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9272728</v>
+        <v>4.3333335</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2545455</v>
+        <v>1.3888888</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="T5" t="n">
-        <v>0.23584905</v>
+        <v>0.23152709</v>
       </c>
       <c r="U5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.23157895</v>
+        <v>0.23232323</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.30044842</v>
+      </c>
+      <c r="I6" t="n">
         <v>24</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.2857143</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
+        <v>0.36868685</v>
+      </c>
+      <c r="K6" t="n">
         <v>23</v>
       </c>
-      <c r="J6" t="n">
-        <v>0.3631579</v>
-      </c>
-      <c r="K6" t="n">
-        <v>21</v>
-      </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9272728</v>
+        <v>4.090909</v>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
         <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1818181</v>
+        <v>1.2363636</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>0.205</v>
+        <v>0.22772278</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.26923078</v>
+        <v>0.26540285</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>17</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.375</v>
+        <v>0.3580247</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5480769</v>
+        <v>0.49763033</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7" t="n">
+        <v>18</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.5636363</v>
+      </c>
+      <c r="O7" t="n">
+        <v>22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
         <v>19</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.6666667</v>
-      </c>
-      <c r="O7" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>17</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.4444444</v>
+        <v>1.6181818</v>
       </c>
       <c r="S7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2890995</v>
+        <v>0.31390134</v>
       </c>
       <c r="U7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2964427</v>
+        <v>0.23553719</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.30597016</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.40082645</v>
+      </c>
+      <c r="K8" t="n">
+        <v>18</v>
+      </c>
+      <c r="L8" t="n">
+        <v>57</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6684783</v>
+      </c>
+      <c r="O8" t="n">
         <v>8</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.3642857</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.49011856</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>56</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.375</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3206522</v>
+        <v>1.3695652</v>
       </c>
       <c r="S8" t="n">
         <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.22522523</v>
+        <v>0.23348017</v>
       </c>
       <c r="U8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.25210086</v>
+        <v>0.24152543</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30501932</v>
+        <v>0.31153846</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4159664</v>
+        <v>0.37288135</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N9" t="n">
         <v>5.644068</v>
       </c>
       <c r="O9" t="n">
+        <v>24</v>
+      </c>
+      <c r="P9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>23</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.6101695</v>
+      </c>
+      <c r="S9" t="n">
         <v>26</v>
       </c>
-      <c r="P9" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>29</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.5932204</v>
-      </c>
-      <c r="S9" t="n">
-        <v>28</v>
-      </c>
       <c r="T9" t="n">
-        <v>0.2746781</v>
+        <v>0.25777778</v>
       </c>
       <c r="U9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.25108224</v>
+        <v>0.25531915</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
         <v>31</v>
@@ -3348,52 +3348,52 @@
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
-        <v>0.30677292</v>
+        <v>0.32307693</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>0.38528138</v>
+        <v>0.39574468</v>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7142856</v>
+        <v>3.65625</v>
       </c>
       <c r="O10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
         <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3333334</v>
+        <v>1.28125</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>0.25203252</v>
+        <v>0.25301206</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -3403,46 +3403,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.27160493</v>
+        <v>0.28691983</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3512545</v>
+        <v>0.3731884</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5308642</v>
+        <v>0.51898736</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N11" t="n">
-        <v>6.677419</v>
+        <v>5.951613</v>
       </c>
       <c r="O11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P11" t="n">
         <v>10</v>
@@ -3451,16 +3451,16 @@
         <v>19</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5645162</v>
+        <v>1.548387</v>
       </c>
       <c r="S11" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="T11" t="n">
-        <v>0.31128404</v>
+        <v>0.3046875</v>
       </c>
       <c r="U11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.25291827</v>
+        <v>0.24107143</v>
       </c>
       <c r="C12" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" t="n">
+        <v>34</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.30081302</v>
+      </c>
+      <c r="I12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.42857143</v>
+      </c>
+      <c r="K12" t="n">
         <v>14</v>
       </c>
-      <c r="D12" t="n">
-        <v>45</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="L12" t="n">
+        <v>54</v>
+      </c>
+      <c r="M12" t="n">
+        <v>18</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="O12" t="n">
         <v>5</v>
       </c>
-      <c r="F12" t="n">
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="n">
         <v>15</v>
       </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.3240418</v>
-      </c>
-      <c r="I12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.47470817</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M12" t="n">
-        <v>26</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.876923</v>
-      </c>
-      <c r="O12" t="n">
-        <v>12</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>19</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.1846154</v>
+        <v>0.98214287</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0.24193548</v>
+        <v>0.19902913</v>
       </c>
       <c r="U12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2451923</v>
+        <v>0.2160804</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31441048</v>
+        <v>0.29596412</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
-        <v>0.39423078</v>
+        <v>0.41708544</v>
       </c>
       <c r="K13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
-        <v>5.5</v>
+        <v>4.909091</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>13</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4074074</v>
+        <v>1.3272728</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23414634</v>
+        <v>0.22167487</v>
       </c>
       <c r="U13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.19587629</v>
+        <v>0.19879518</v>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2415459</v>
+        <v>0.22988506</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>0.32474226</v>
+        <v>0.3253012</v>
       </c>
       <c r="K14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L14" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>7.7388535</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9108281</v>
+        <v>1.6444445</v>
       </c>
       <c r="S14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T14" t="n">
-        <v>0.33796296</v>
+        <v>0.29885057</v>
       </c>
       <c r="U14" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.22680412</v>
+        <v>0.18716578</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.27884614</v>
+        <v>0.2284264</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.31958762</v>
+        <v>0.26737967</v>
       </c>
       <c r="K15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2352943</v>
+        <v>4.7647057</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1960784</v>
+        <v>1.2941177</v>
       </c>
       <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.23195876</v>
+      </c>
+      <c r="U15" t="n">
         <v>11</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.21875</v>
-      </c>
-      <c r="U15" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.32156864</v>
+        <v>0.28691983</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>0.39726028</v>
+        <v>0.37226278</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5254902</v>
+        <v>0.4556962</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
         <v>49</v>
       </c>
       <c r="M16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.7741935</v>
+      </c>
+      <c r="O16" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>19</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.2419355</v>
+      </c>
+      <c r="S16" t="n">
         <v>11</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.8688526</v>
-      </c>
-      <c r="O16" t="n">
-        <v>23</v>
-      </c>
-      <c r="P16" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>24</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4590164</v>
-      </c>
-      <c r="S16" t="n">
-        <v>24</v>
-      </c>
       <c r="T16" t="n">
-        <v>0.2638298</v>
+        <v>0.2457627</v>
       </c>
       <c r="U16" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.29435483</v>
+        <v>0.2992126</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.37586206</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5551180999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>53</v>
+      </c>
+      <c r="M17" t="n">
+        <v>16</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>21</v>
+      </c>
+      <c r="P17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>15</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3333334</v>
+      </c>
+      <c r="S17" t="n">
         <v>18</v>
       </c>
-      <c r="H17" t="n">
-        <v>0.35869566</v>
-      </c>
-      <c r="I17" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.4717742</v>
-      </c>
-      <c r="K17" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>44</v>
-      </c>
-      <c r="M17" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="O17" t="n">
-        <v>19</v>
-      </c>
-      <c r="P17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>13</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>12</v>
-      </c>
       <c r="T17" t="n">
-        <v>0.23423423</v>
+        <v>0.2599119</v>
       </c>
       <c r="U17" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2599119</v>
+        <v>0.2734694</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
         <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34496123</v>
+        <v>0.3561151</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4581498</v>
+        <v>0.4489796</v>
       </c>
       <c r="K18" t="n">
         <v>11</v>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N18" t="n">
-        <v>3.234375</v>
+        <v>2.7692308</v>
       </c>
       <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.0615385</v>
+      </c>
+      <c r="S18" t="n">
         <v>4</v>
       </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>19</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.171875</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
       <c r="T18" t="n">
-        <v>0.21459228</v>
+        <v>0.21161826</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2596154</v>
+        <v>0.23152709</v>
       </c>
       <c r="C19" t="n">
+        <v>21</v>
+      </c>
+      <c r="D19" t="n">
+        <v>33</v>
+      </c>
+      <c r="E19" t="n">
         <v>12</v>
       </c>
-      <c r="D19" t="n">
-        <v>34</v>
-      </c>
-      <c r="E19" t="n">
-        <v>10</v>
-      </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.30530974</v>
+      </c>
+      <c r="I19" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.49753696</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>54</v>
+      </c>
+      <c r="M19" t="n">
+        <v>18</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.8076923</v>
+      </c>
+      <c r="O19" t="n">
+        <v>11</v>
+      </c>
+      <c r="P19" t="n">
         <v>8</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.3171806</v>
-      </c>
-      <c r="I19" t="n">
-        <v>14</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.46153846</v>
-      </c>
-      <c r="K19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" t="n">
-        <v>38</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.8333335</v>
-      </c>
-      <c r="O19" t="n">
-        <v>22</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3148148</v>
+        <v>1.1923077</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>0.24880382</v>
+        <v>0.21875</v>
       </c>
       <c r="U19" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.20103092</v>
+        <v>0.22330096</v>
       </c>
       <c r="C20" t="n">
+        <v>23</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17</v>
+      </c>
+      <c r="E20" t="n">
         <v>27</v>
       </c>
-      <c r="D20" t="n">
-        <v>18</v>
-      </c>
-      <c r="E20" t="n">
-        <v>26</v>
-      </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>0.28310502</v>
+        <v>0.3030303</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>0.34536082</v>
+        <v>0.38349515</v>
       </c>
       <c r="K20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L20" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M20" t="n">
         <v>14</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4615386</v>
+        <v>6.3</v>
       </c>
       <c r="O20" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2115384</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2371134</v>
+        <v>0.25641027</v>
       </c>
       <c r="U20" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.12041885</v>
+        <v>0.15544042</v>
       </c>
       <c r="C21" t="n">
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1724138</v>
+        <v>0.22274882</v>
       </c>
       <c r="I21" t="n">
         <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>0.20942408</v>
+        <v>0.29533678</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L21" t="n">
         <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3067484</v>
+        <v>3.994083</v>
       </c>
       <c r="O21" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>26</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2248521</v>
+      </c>
+      <c r="S21" t="n">
         <v>9</v>
       </c>
-      <c r="Q21" t="n">
-        <v>17</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.2331289</v>
-      </c>
-      <c r="S21" t="n">
-        <v>14</v>
-      </c>
       <c r="T21" t="n">
-        <v>0.23923445</v>
+        <v>0.23394495</v>
       </c>
       <c r="U21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.25316456</v>
+        <v>0.2761905</v>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.33620688</v>
+      </c>
+      <c r="I22" t="n">
         <v>9</v>
       </c>
-      <c r="F22" t="n">
-        <v>10</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="J22" t="n">
+        <v>0.4904762</v>
+      </c>
+      <c r="K22" t="n">
         <v>8</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.31417623</v>
-      </c>
-      <c r="I22" t="n">
-        <v>16</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.4177215</v>
-      </c>
-      <c r="K22" t="n">
-        <v>14</v>
-      </c>
       <c r="L22" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="M22" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.790323</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P22" t="n">
         <v>7</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.532258</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T22" t="n">
-        <v>0.26229507</v>
+        <v>0.26168224</v>
       </c>
       <c r="U22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.28853756</v>
+        <v>0.29961088</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3676976</v>
+        <v>0.3809524</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.51778656</v>
+        <v>0.49416342</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="M23" t="n">
         <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>6.196721</v>
+        <v>5.7</v>
       </c>
       <c r="O23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3934426</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2616034</v>
+        <v>0.2638298</v>
       </c>
       <c r="U23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.28033474</v>
+        <v>0.2625</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" t="n">
         <v>11</v>
       </c>
-      <c r="G24" t="n">
-        <v>6</v>
-      </c>
       <c r="H24" t="n">
-        <v>0.37226278</v>
+        <v>0.33458647</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>0.49372384</v>
+        <v>0.45416668</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L24" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="M24" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="N24" t="n">
-        <v>9.050280000000001</v>
+        <v>8.583815</v>
       </c>
       <c r="O24" t="n">
         <v>30</v>
       </c>
       <c r="P24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q24" t="n">
         <v>30</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0446928</v>
+        <v>1.8554913</v>
       </c>
       <c r="S24" t="n">
         <v>30</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3372549</v>
+        <v>0.30379745</v>
       </c>
       <c r="U24" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24226804</v>
+        <v>0.26794258</v>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
         <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>0.27884614</v>
+        <v>0.3018018</v>
       </c>
       <c r="I25" t="n">
+        <v>22</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4401914</v>
+      </c>
+      <c r="K25" t="n">
+        <v>13</v>
+      </c>
+      <c r="L25" t="n">
+        <v>42</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6.529412</v>
+      </c>
+      <c r="O25" t="n">
+        <v>28</v>
+      </c>
+      <c r="P25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>11</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5686275</v>
+      </c>
+      <c r="S25" t="n">
         <v>25</v>
       </c>
-      <c r="J25" t="n">
-        <v>0.41237113</v>
-      </c>
-      <c r="K25" t="n">
-        <v>16</v>
-      </c>
-      <c r="L25" t="n">
-        <v>37</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.6346154</v>
-      </c>
-      <c r="O25" t="n">
-        <v>9</v>
-      </c>
-      <c r="P25" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.1153846</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
       <c r="T25" t="n">
-        <v>0.19895288</v>
+        <v>0.27</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -4408,34 +4408,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.24120604</v>
+        <v>0.24747474</v>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H26" t="n">
-        <v>0.33480176</v>
+        <v>0.32579187</v>
       </c>
       <c r="I26" t="n">
         <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>0.34170854</v>
+        <v>0.36868685</v>
       </c>
       <c r="K26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
         <v>62</v>
@@ -4444,7 +4444,7 @@
         <v>26</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7692308</v>
+        <v>2.2075472</v>
       </c>
       <c r="O26" t="n">
         <v>2</v>
@@ -4456,16 +4456,16 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.0384616</v>
+        <v>0.9622642</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>0.21465969</v>
+        <v>0.19270833</v>
       </c>
       <c r="U26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -4475,46 +4475,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.20418848</v>
+        <v>0.2647059</v>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H27" t="n">
-        <v>0.26442307</v>
+        <v>0.33333334</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>0.31413612</v>
+        <v>0.44607842</v>
       </c>
       <c r="K27" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3962264</v>
+        <v>2.037736</v>
       </c>
       <c r="O27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
@@ -4523,16 +4523,16 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3018868</v>
+        <v>1.0943396</v>
       </c>
       <c r="S27" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23316061</v>
+        <v>0.1904762</v>
       </c>
       <c r="U27" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -4542,61 +4542,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.29533678</v>
+        <v>0.285</v>
       </c>
       <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>13</v>
+      </c>
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="D28" t="n">
-        <v>34</v>
-      </c>
-      <c r="E28" t="n">
-        <v>10</v>
-      </c>
-      <c r="F28" t="n">
-        <v>12</v>
-      </c>
-      <c r="G28" t="n">
-        <v>5</v>
-      </c>
       <c r="H28" t="n">
-        <v>0.37272727</v>
+        <v>0.36681223</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.53367877</v>
+        <v>0.515</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.6666666</v>
+        <v>3.0566037</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>0.7777778</v>
+        <v>0.8301887</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1897436</v>
+        <v>0.1875</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.28225806</v>
+        <v>0.25365853</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E29" t="n">
+        <v>18</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>17</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.31858408</v>
+      </c>
+      <c r="I29" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.40487805</v>
+      </c>
+      <c r="K29" t="n">
+        <v>17</v>
+      </c>
+      <c r="L29" t="n">
+        <v>41</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.7358491</v>
+      </c>
+      <c r="O29" t="n">
+        <v>9</v>
+      </c>
+      <c r="P29" t="n">
         <v>8</v>
       </c>
-      <c r="F29" t="n">
-        <v>9</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="Q29" t="n">
         <v>11</v>
       </c>
-      <c r="H29" t="n">
-        <v>0.3537906</v>
-      </c>
-      <c r="I29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.44354838</v>
-      </c>
-      <c r="K29" t="n">
-        <v>13</v>
-      </c>
-      <c r="L29" t="n">
-        <v>59</v>
-      </c>
-      <c r="M29" t="n">
-        <v>21</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4.064516</v>
-      </c>
-      <c r="O29" t="n">
-        <v>15</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>19</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.1774193</v>
+        <v>1.0754716</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>0.25101215</v>
+        <v>0.23444976</v>
       </c>
       <c r="U29" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.23737374</v>
+        <v>0.1861702</v>
       </c>
       <c r="C30" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.24509804</v>
+      </c>
+      <c r="I30" t="n">
+        <v>27</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.27659574</v>
+      </c>
+      <c r="K30" t="n">
+        <v>29</v>
+      </c>
+      <c r="L30" t="n">
+        <v>45</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.3962264</v>
+      </c>
+      <c r="O30" t="n">
         <v>6</v>
       </c>
-      <c r="G30" t="n">
-        <v>18</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.2962963</v>
-      </c>
-      <c r="I30" t="n">
-        <v>21</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.36868685</v>
-      </c>
-      <c r="K30" t="n">
-        <v>20</v>
-      </c>
-      <c r="L30" t="n">
-        <v>54</v>
-      </c>
-      <c r="M30" t="n">
-        <v>17</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>8</v>
-      </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2407408</v>
+        <v>1.0754716</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>0.22277227</v>
+        <v>0.20103092</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.26511627</v>
+        <v>0.27669904</v>
       </c>
       <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>37</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.36864406</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.5388349</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>49</v>
+      </c>
+      <c r="M31" t="n">
         <v>10</v>
       </c>
-      <c r="D31" t="n">
-        <v>32</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="N31" t="n">
+        <v>4.075472</v>
+      </c>
+      <c r="O31" t="n">
         <v>13</v>
       </c>
-      <c r="F31" t="n">
-        <v>8</v>
-      </c>
-      <c r="G31" t="n">
-        <v>14</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.34166667</v>
-      </c>
-      <c r="I31" t="n">
-        <v>11</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.45581394</v>
-      </c>
-      <c r="K31" t="n">
-        <v>12</v>
-      </c>
-      <c r="L31" t="n">
-        <v>60</v>
-      </c>
-      <c r="M31" t="n">
-        <v>23</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.8867924</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3</v>
-      </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
         <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.1509434</v>
+        <v>1.245283</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T31" t="n">
-        <v>0.21538462</v>
+        <v>0.25123152</v>
       </c>
       <c r="U31" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23664384</v>
+        <v>0.23644987</v>
       </c>
       <c r="C2" t="n">
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>79</v>
@@ -564,43 +564,43 @@
         <v>29</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30686364</v>
+        <v>0.30727106</v>
       </c>
       <c r="I2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38287672</v>
+        <v>0.38177508</v>
       </c>
       <c r="K2" t="n">
         <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2991414</v>
+        <v>4.28426</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q2" t="n">
         <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2952789</v>
+        <v>1.2893509</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2520243</v>
+        <v>0.2516689</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24843699</v>
+        <v>0.24804688</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G3" t="n">
         <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3266979</v>
+        <v>0.32618773</v>
       </c>
       <c r="I3" t="n">
         <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4100033</v>
+        <v>0.40950522</v>
       </c>
       <c r="K3" t="n">
         <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>771</v>
+        <v>781</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.0653267</v>
+        <v>5.109317</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4585427</v>
+        <v>1.4708074</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26489636</v>
+        <v>0.26679462</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24694294</v>
+        <v>0.24773718</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G4" t="n">
         <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3124235</v>
+        <v>0.31299093</v>
       </c>
       <c r="I4" t="n">
         <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4113451</v>
+        <v>0.4116661</v>
       </c>
       <c r="K4" t="n">
         <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4639308</v>
+        <v>3.527754</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q4" t="n">
         <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2142549</v>
+        <v>1.2207514</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22725688</v>
+        <v>0.22849277</v>
       </c>
       <c r="U4" t="n">
         <v>4</v>
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23807935</v>
+        <v>0.23779683</v>
       </c>
       <c r="C5" t="n">
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
         <v>104</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3190925</v>
+        <v>0.31876457</v>
       </c>
       <c r="I5" t="n">
         <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39646548</v>
+        <v>0.39478892</v>
       </c>
       <c r="K5" t="n">
         <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3497496</v>
+        <v>4.3400826</v>
       </c>
       <c r="O5" t="n">
         <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="n">
         <v>16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3772955</v>
+        <v>1.3710743</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25398892</v>
+        <v>0.2532258</v>
       </c>
       <c r="U5" t="n">
         <v>24</v>
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2432154</v>
+        <v>0.24355495</v>
       </c>
       <c r="C6" t="n">
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3118047</v>
+        <v>0.3118706</v>
       </c>
       <c r="I6" t="n">
         <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38543457</v>
+        <v>0.38602442</v>
       </c>
       <c r="K6" t="n">
         <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="M6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.7744424</v>
+      </c>
+      <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="N6" t="n">
-        <v>3.7600868</v>
-      </c>
-      <c r="O6" t="n">
-        <v>6</v>
-      </c>
       <c r="P6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q6" t="n">
         <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2507592</v>
+        <v>1.2491424</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24156916</v>
+        <v>0.24159022</v>
       </c>
       <c r="U6" t="n">
         <v>17</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24391848</v>
+        <v>0.2438945</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -896,46 +896,46 @@
         <v>112</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33798406</v>
+        <v>0.3381234</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41058514</v>
+        <v>0.40931293</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="M7" t="n">
         <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3618007</v>
+        <v>4.357737</v>
       </c>
       <c r="O7" t="n">
         <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2709298</v>
+        <v>1.2691348</v>
       </c>
       <c r="S7" t="n">
         <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24448161</v>
+        <v>0.24420913</v>
       </c>
       <c r="U7" t="n">
         <v>18</v>
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24159022</v>
+        <v>0.24169184</v>
       </c>
       <c r="C8" t="n">
         <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3208798</v>
+        <v>0.32133293</v>
       </c>
       <c r="I8" t="n">
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41522256</v>
+        <v>0.41658273</v>
       </c>
       <c r="K8" t="n">
         <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2053914</v>
+        <v>4.214467</v>
       </c>
       <c r="O8" t="n">
         <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q8" t="n">
         <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3311938</v>
+        <v>1.3350254</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23902607</v>
+        <v>0.24001354</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1015,43 +1015,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22839716</v>
+        <v>0.22785234</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E9" t="n">
         <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G9" t="n">
         <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30998197</v>
+        <v>0.3089988</v>
       </c>
       <c r="I9" t="n">
         <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3886818</v>
+        <v>0.38791946</v>
       </c>
       <c r="K9" t="n">
         <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="M9" t="n">
         <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.597701</v>
+        <v>4.568182</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
@@ -1063,13 +1063,13 @@
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.458493</v>
+        <v>1.455808</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24932976</v>
+        <v>0.24892277</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1082,61 +1082,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22884224</v>
+        <v>0.22994652</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E10" t="n">
         <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31126422</v>
+        <v>0.3119266</v>
       </c>
       <c r="I10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36594447</v>
+        <v>0.36764705</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7603514</v>
+        <v>3.796526</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Q10" t="n">
         <v>19</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2572145</v>
+        <v>1.2617866</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23753764</v>
+        <v>0.23768595</v>
       </c>
       <c r="U10" t="n">
         <v>11</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25775892</v>
+        <v>0.25856498</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32836694</v>
+        <v>0.3285136</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42469782</v>
+        <v>0.42598578</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.541087</v>
+        <v>5.535</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.517067</v>
+        <v>1.5175</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28743654</v>
+        <v>0.28732747</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23535353</v>
+        <v>0.23586161</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G12" t="n">
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31330344</v>
+        <v>0.31373706</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
-        <v>0.396633</v>
+        <v>0.39753824</v>
       </c>
       <c r="K12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7669077</v>
+        <v>3.7582002</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2313908</v>
+        <v>1.2275021</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23644987</v>
+        <v>0.2358459</v>
       </c>
       <c r="U12" t="n">
         <v>8</v>
@@ -1283,43 +1283,43 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24158221</v>
+        <v>0.24117838</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31569716</v>
+        <v>0.3148899</v>
       </c>
       <c r="I13" t="n">
         <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4102648</v>
+        <v>0.4101651</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7771807</v>
+        <v>4.724448</v>
       </c>
       <c r="O13" t="n">
         <v>26</v>
@@ -1328,19 +1328,19 @@
         <v>124</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3902439</v>
+        <v>1.3822567</v>
       </c>
       <c r="S13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24031778</v>
+        <v>0.23918742</v>
       </c>
       <c r="U13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24135616</v>
+        <v>0.24152824</v>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E14" t="n">
         <v>23</v>
@@ -1365,28 +1365,28 @@
         <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31150496</v>
+        <v>0.31132916</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3873783</v>
+        <v>0.38704318</v>
       </c>
       <c r="K14" t="n">
         <v>23</v>
       </c>
       <c r="L14" t="n">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="M14" t="n">
         <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.879932</v>
+        <v>4.83599</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
@@ -1398,13 +1398,13 @@
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4395417</v>
+        <v>1.4320469</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26286092</v>
+        <v>0.26191258</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23700762</v>
+        <v>0.23708306</v>
       </c>
       <c r="C15" t="n">
         <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="E15" t="n">
+        <v>17</v>
+      </c>
+      <c r="F15" t="n">
+        <v>104</v>
+      </c>
+      <c r="G15" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3134677</v>
+      </c>
+      <c r="I15" t="n">
         <v>18</v>
       </c>
-      <c r="F15" t="n">
-        <v>103</v>
-      </c>
-      <c r="G15" t="n">
-        <v>16</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.3140325</v>
-      </c>
-      <c r="I15" t="n">
-        <v>17</v>
-      </c>
       <c r="J15" t="n">
-        <v>0.39059913</v>
+        <v>0.39045128</v>
       </c>
       <c r="K15" t="n">
         <v>21</v>
       </c>
       <c r="L15" t="n">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="M15" t="n">
         <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>4.637967</v>
+        <v>4.630814</v>
       </c>
       <c r="O15" t="n">
         <v>24</v>
       </c>
       <c r="P15" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4010919</v>
+        <v>1.4015781</v>
       </c>
       <c r="S15" t="n">
         <v>26</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23684211</v>
+        <v>0.23724909</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.265259</v>
+        <v>0.26396602</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>122</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3480392</v>
+        <v>0.34731734</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.44275817</v>
+        <v>0.43972558</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4714286</v>
+        <v>3.488575</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q16" t="n">
         <v>13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1243697</v>
+        <v>1.1292065</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21562606</v>
+        <v>0.21577883</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25158915</v>
+        <v>0.25371656</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.32819906</v>
+        <v>0.33099824</v>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.40414855</v>
+        <v>0.40997687</v>
       </c>
       <c r="K17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="M17" t="n">
         <v>11</v>
       </c>
       <c r="N17" t="n">
-        <v>4.055696</v>
+        <v>4.088861</v>
       </c>
       <c r="O17" t="n">
         <v>11</v>
       </c>
       <c r="P17" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2481012</v>
+        <v>1.2465582</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22983463</v>
+        <v>0.22963952</v>
       </c>
       <c r="U17" t="n">
         <v>5</v>
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25490198</v>
+        <v>0.25451505</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33838835</v>
+        <v>0.33726066</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39790398</v>
+        <v>0.39765885</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="M18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.362047</v>
+        <v>3.346543</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1666,13 +1666,13 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1756929</v>
+        <v>1.1787521</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21905424</v>
+        <v>0.2190509</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24622455</v>
+        <v>0.24716185</v>
       </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
@@ -1703,25 +1703,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32104185</v>
+        <v>0.3219653</v>
       </c>
       <c r="I19" t="n">
         <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.41661194</v>
+        <v>0.4168018</v>
       </c>
       <c r="K19" t="n">
         <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="M19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N19" t="n">
-        <v>4.821429</v>
+        <v>4.7785625</v>
       </c>
       <c r="O19" t="n">
         <v>27</v>
@@ -1730,16 +1730,16 @@
         <v>106</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3953782</v>
+        <v>1.387204</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25457516</v>
+        <v>0.25372168</v>
       </c>
       <c r="U19" t="n">
         <v>25</v>
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23030506</v>
+        <v>0.23145695</v>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F20" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G20" t="n">
         <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2983944</v>
+        <v>0.29952124</v>
       </c>
       <c r="I20" t="n">
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37546095</v>
+        <v>0.37748346</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="M20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2517896</v>
+        <v>4.293922</v>
       </c>
       <c r="O20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P20" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>1.288421</v>
+        <v>1.2914238</v>
       </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23476523</v>
+        <v>0.23570019</v>
       </c>
       <c r="U20" t="n">
         <v>7</v>
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23541524</v>
+        <v>0.23471467</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
         <v>128</v>
@@ -1837,25 +1837,25 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31880108</v>
+        <v>0.31763646</v>
       </c>
       <c r="I21" t="n">
         <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>0.42175704</v>
+        <v>0.41949728</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="M21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3850746</v>
+        <v>3.392074</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -1867,13 +1867,13 @@
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.192324</v>
+        <v>1.1989882</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22716387</v>
+        <v>0.22837839</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,46 +1886,46 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23792069</v>
+        <v>0.23721544</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
         <v>120</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30391565</v>
+        <v>0.30301222</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40586472</v>
+        <v>0.40448695</v>
       </c>
       <c r="K22" t="n">
+        <v>14</v>
+      </c>
+      <c r="L22" t="n">
+        <v>787</v>
+      </c>
+      <c r="M22" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.120934</v>
+      </c>
+      <c r="O22" t="n">
         <v>13</v>
-      </c>
-      <c r="L22" t="n">
-        <v>780</v>
-      </c>
-      <c r="M22" t="n">
-        <v>23</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.1057286</v>
-      </c>
-      <c r="O22" t="n">
-        <v>12</v>
       </c>
       <c r="P22" t="n">
         <v>101</v>
@@ -1934,13 +1934,13 @@
         <v>17</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3053918</v>
+        <v>1.3048373</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25489557</v>
+        <v>0.2549273</v>
       </c>
       <c r="U22" t="n">
         <v>26</v>
@@ -1953,61 +1953,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2610083</v>
+        <v>0.26189727</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>0.33889204</v>
+        <v>0.3399386</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4208679</v>
+        <v>0.4219981</v>
       </c>
       <c r="K23" t="n">
         <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="M23" t="n">
         <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2666945</v>
+        <v>4.2748156</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q23" t="n">
         <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3090004</v>
+        <v>1.3129615</v>
       </c>
       <c r="S23" t="n">
         <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23779888</v>
+        <v>0.23841918</v>
       </c>
       <c r="U23" t="n">
         <v>13</v>
@@ -2020,43 +2020,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22430556</v>
+        <v>0.22435677</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3</v>
+        <v>0.3005213</v>
       </c>
       <c r="I24" t="n">
         <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37291667</v>
+        <v>0.37255573</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="M24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N24" t="n">
-        <v>4.241202</v>
+        <v>4.215528</v>
       </c>
       <c r="O24" t="n">
         <v>16</v>
@@ -2065,16 +2065,16 @@
         <v>96</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3454936</v>
+        <v>1.3428086</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24820758</v>
+        <v>0.24704292</v>
       </c>
       <c r="U24" t="n">
         <v>19</v>
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25587553</v>
+        <v>0.25613347</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E25" t="n">
         <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30745813</v>
+        <v>0.30817798</v>
       </c>
       <c r="I25" t="n">
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41972858</v>
+        <v>0.42230946</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4903307</v>
+        <v>4.5133986</v>
       </c>
       <c r="O25" t="n">
         <v>22</v>
       </c>
       <c r="P25" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q25" t="n">
         <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3807477</v>
+        <v>1.380689</v>
       </c>
       <c r="S25" t="n">
         <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24974482</v>
+        <v>0.25067294</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23162135</v>
+        <v>0.23130608</v>
       </c>
       <c r="C26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G26" t="n">
         <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31238833</v>
+        <v>0.31170747</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3820074</v>
+        <v>0.3815221</v>
       </c>
       <c r="K26" t="n">
         <v>27</v>
       </c>
       <c r="L26" t="n">
-        <v>781</v>
+        <v>791</v>
       </c>
       <c r="M26" t="n">
         <v>24</v>
       </c>
       <c r="N26" t="n">
-        <v>3.586466</v>
+        <v>3.5464685</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -2202,16 +2202,16 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1666666</v>
+        <v>1.1598513</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23732796</v>
+        <v>0.23603724</v>
       </c>
       <c r="U26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -2221,43 +2221,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24792817</v>
+        <v>0.24760929</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G27" t="n">
         <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32538956</v>
+        <v>0.32487157</v>
       </c>
       <c r="I27" t="n">
         <v>9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39744475</v>
+        <v>0.39651638</v>
       </c>
       <c r="K27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" t="n">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.14484</v>
+        <v>4.13691</v>
       </c>
       <c r="O27" t="n">
         <v>14</v>
@@ -2266,16 +2266,16 @@
         <v>90</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3347788</v>
+        <v>1.332618</v>
       </c>
       <c r="S27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25248033</v>
+        <v>0.25237128</v>
       </c>
       <c r="U27" t="n">
         <v>23</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.26027873</v>
+        <v>0.25887626</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -2297,7 +2297,7 @@
         <v>396</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
         <v>84</v>
@@ -2306,43 +2306,43 @@
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33816275</v>
+        <v>0.33658835</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39965156</v>
+        <v>0.39675975</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L28" t="n">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7617188</v>
+        <v>3.746134</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P28" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1809896</v>
+        <v>1.1778351</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23268698</v>
+        <v>0.23235093</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24427995</v>
+        <v>0.243594</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3197238</v>
+        <v>0.31877598</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39266488</v>
+        <v>0.39301166</v>
       </c>
       <c r="K29" t="n">
         <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="M29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9675353</v>
+        <v>3.9793074</v>
       </c>
       <c r="O29" t="n">
         <v>10</v>
       </c>
       <c r="P29" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2340881</v>
+        <v>1.2377534</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23775989</v>
+        <v>0.23823725</v>
       </c>
       <c r="U29" t="n">
         <v>12</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24505532</v>
+        <v>0.2436919</v>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" t="n">
         <v>356</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F30" t="n">
         <v>88</v>
       </c>
       <c r="G30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3069909</v>
+        <v>0.30563083</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38484746</v>
+        <v>0.38247013</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1205735</v>
+        <v>4.1131053</v>
       </c>
       <c r="O30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3064923</v>
+        <v>1.3034223</v>
       </c>
       <c r="S30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24044265</v>
+        <v>0.24003984</v>
       </c>
       <c r="U30" t="n">
         <v>16</v>
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.248057</v>
+        <v>0.24855861</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32212237</v>
+        <v>0.32272857</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>0.42940414</v>
+        <v>0.43017298</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="M31" t="n">
         <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.657862</v>
+        <v>4.716735</v>
       </c>
       <c r="O31" t="n">
         <v>25</v>
       </c>
       <c r="P31" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3867106</v>
+        <v>1.3946939</v>
       </c>
       <c r="S31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25775504</v>
+        <v>0.25868604</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.20812182</v>
+        <v>0.21827412</v>
       </c>
       <c r="C2" t="n">
         <v>25</v>
       </c>
       <c r="D2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
         <v>26</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
+        <v>0.3063063</v>
+      </c>
+      <c r="I2" t="n">
         <v>20</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>22</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.28767124</v>
-      </c>
-      <c r="I2" t="n">
-        <v>26</v>
       </c>
       <c r="J2" t="n">
         <v>0.3401015</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.090909</v>
+        <v>3.6964285</v>
       </c>
       <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q2" t="n">
         <v>15</v>
       </c>
-      <c r="P2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>23</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.290909</v>
+        <v>1.1785715</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>0.27102804</v>
+        <v>0.25581396</v>
       </c>
       <c r="U2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.25853658</v>
+        <v>0.26213592</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>0.30941704</v>
+        <v>0.31390134</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.38536584</v>
+        <v>0.41262135</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>6.962264</v>
+        <v>7.8333335</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.754717</v>
+        <v>2.0185184</v>
       </c>
       <c r="S3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.30414745</v>
+        <v>0.33777776</v>
       </c>
       <c r="U3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.22680412</v>
+        <v>0.25</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3448276</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.1666665</v>
+      </c>
+      <c r="O4" t="n">
+        <v>21</v>
+      </c>
+      <c r="P4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I4" t="n">
-        <v>14</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.4226804</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="Q4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.3518518</v>
+      </c>
+      <c r="S4" t="n">
         <v>15</v>
       </c>
-      <c r="L4" t="n">
-        <v>42</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.075472</v>
-      </c>
-      <c r="O4" t="n">
-        <v>13</v>
-      </c>
-      <c r="P4" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>11</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.3018868</v>
-      </c>
-      <c r="S4" t="n">
-        <v>16</v>
-      </c>
       <c r="T4" t="n">
-        <v>0.25603864</v>
+        <v>0.25943395</v>
       </c>
       <c r="U4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.20744681</v>
+        <v>0.21578947</v>
       </c>
       <c r="C5" t="n">
         <v>26</v>
       </c>
       <c r="D5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3169643</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.33157894</v>
+      </c>
+      <c r="K5" t="n">
         <v>26</v>
       </c>
-      <c r="E5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>22</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3122172</v>
-      </c>
-      <c r="I5" t="n">
-        <v>16</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.35106382</v>
-      </c>
-      <c r="K5" t="n">
-        <v>25</v>
-      </c>
       <c r="L5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3333335</v>
+        <v>4.075472</v>
       </c>
       <c r="O5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3888888</v>
+        <v>1.3018868</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>0.23152709</v>
+        <v>0.22613065</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.23232323</v>
+        <v>0.24630542</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.30837005</v>
+      </c>
+      <c r="I6" t="n">
         <v>18</v>
       </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>27</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.30044842</v>
-      </c>
-      <c r="I6" t="n">
-        <v>24</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.36868685</v>
+        <v>0.4039409</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L6" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>4.090909</v>
+        <v>4.8333335</v>
       </c>
       <c r="O6" t="n">
+        <v>18</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3518518</v>
+      </c>
+      <c r="S6" t="n">
         <v>15</v>
       </c>
-      <c r="P6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.2363636</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
       <c r="T6" t="n">
-        <v>0.22772278</v>
+        <v>0.25365853</v>
       </c>
       <c r="U6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.26540285</v>
+        <v>0.28640777</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3580247</v>
+        <v>0.37238494</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.49763033</v>
+        <v>0.52427185</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M7" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>5.5636363</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P7" t="n">
         <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6181818</v>
+        <v>1.574074</v>
       </c>
       <c r="S7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T7" t="n">
-        <v>0.31390134</v>
+        <v>0.30875576</v>
       </c>
       <c r="U7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23553719</v>
+        <v>0.2398374</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.31135532</v>
+      </c>
+      <c r="I8" t="n">
+        <v>17</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.42682928</v>
+      </c>
+      <c r="K8" t="n">
+        <v>16</v>
+      </c>
+      <c r="L8" t="n">
+        <v>55</v>
+      </c>
+      <c r="M8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.8152175</v>
+      </c>
+      <c r="O8" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" t="n">
         <v>7</v>
       </c>
-      <c r="G8" t="n">
-        <v>17</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.30597016</v>
-      </c>
-      <c r="I8" t="n">
-        <v>19</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.40082645</v>
-      </c>
-      <c r="K8" t="n">
-        <v>18</v>
-      </c>
-      <c r="L8" t="n">
-        <v>57</v>
-      </c>
-      <c r="M8" t="n">
-        <v>22</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.6684783</v>
-      </c>
-      <c r="O8" t="n">
-        <v>8</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3695652</v>
+        <v>1.402174</v>
       </c>
       <c r="S8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23348017</v>
+        <v>0.23684211</v>
       </c>
       <c r="U8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.24152543</v>
+        <v>0.23275863</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2936508</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K9" t="n">
         <v>23</v>
       </c>
-      <c r="E9" t="n">
-        <v>24</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="L9" t="n">
+        <v>61</v>
+      </c>
+      <c r="M9" t="n">
+        <v>25</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>15</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
         <v>6</v>
       </c>
-      <c r="G9" t="n">
+      <c r="R9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S9" t="n">
         <v>22</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.31153846</v>
-      </c>
-      <c r="I9" t="n">
-        <v>17</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.37288135</v>
-      </c>
-      <c r="K9" t="n">
-        <v>22</v>
-      </c>
-      <c r="L9" t="n">
-        <v>62</v>
-      </c>
-      <c r="M9" t="n">
-        <v>26</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.644068</v>
-      </c>
-      <c r="O9" t="n">
-        <v>24</v>
-      </c>
-      <c r="P9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>23</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.6101695</v>
-      </c>
-      <c r="S9" t="n">
-        <v>26</v>
-      </c>
       <c r="T9" t="n">
-        <v>0.25777778</v>
+        <v>0.24215247</v>
       </c>
       <c r="U9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.25531915</v>
+        <v>0.25104603</v>
       </c>
       <c r="C10" t="n">
         <v>14</v>
@@ -3345,55 +3345,55 @@
         <v>31</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>0.32307693</v>
+        <v>0.31153846</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
-        <v>0.39574468</v>
+        <v>0.41004184</v>
       </c>
       <c r="K10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65625</v>
+        <v>4.21875</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28125</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.25301206</v>
+        <v>0.24180327</v>
       </c>
       <c r="U10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.28691983</v>
+        <v>0.30379745</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.37956205</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5611814000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>49</v>
+      </c>
+      <c r="M11" t="n">
         <v>11</v>
       </c>
-      <c r="G11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.3731884</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.51898736</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>54</v>
-      </c>
-      <c r="M11" t="n">
-        <v>18</v>
-      </c>
       <c r="N11" t="n">
-        <v>5.951613</v>
+        <v>6.285714</v>
       </c>
       <c r="O11" t="n">
         <v>26</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.548387</v>
+        <v>1.6190476</v>
       </c>
       <c r="S11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3046875</v>
+        <v>0.3065134</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -3470,61 +3470,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24107143</v>
+        <v>0.24663678</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" t="n">
         <v>10</v>
       </c>
-      <c r="F12" t="n">
-        <v>11</v>
-      </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>0.30081302</v>
+        <v>0.29752067</v>
       </c>
       <c r="I12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J12" t="n">
-        <v>0.42857143</v>
+        <v>0.4349776</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.375</v>
+        <v>3.2727273</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" t="n">
         <v>9</v>
       </c>
-      <c r="Q12" t="n">
-        <v>15</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.98214287</v>
+        <v>0.92727274</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0.19902913</v>
+        <v>0.19900498</v>
       </c>
       <c r="U12" t="n">
         <v>4</v>
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2160804</v>
+        <v>0.21989529</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2890995</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.40837696</v>
+      </c>
+      <c r="K13" t="n">
+        <v>21</v>
+      </c>
+      <c r="L13" t="n">
+        <v>50</v>
+      </c>
+      <c r="M13" t="n">
+        <v>13</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>15</v>
+      </c>
+      <c r="P13" t="n">
         <v>11</v>
       </c>
-      <c r="G13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.29596412</v>
-      </c>
-      <c r="I13" t="n">
-        <v>25</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.41708544</v>
-      </c>
-      <c r="K13" t="n">
-        <v>16</v>
-      </c>
-      <c r="L13" t="n">
-        <v>51</v>
-      </c>
-      <c r="M13" t="n">
-        <v>12</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.909091</v>
-      </c>
-      <c r="O13" t="n">
-        <v>20</v>
-      </c>
-      <c r="P13" t="n">
-        <v>13</v>
-      </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3272728</v>
+        <v>1.1666666</v>
       </c>
       <c r="S13" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>0.22167487</v>
+        <v>0.20304568</v>
       </c>
       <c r="U13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3604,31 +3604,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.19879518</v>
+        <v>0.1875</v>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H14" t="n">
-        <v>0.22988506</v>
+        <v>0.21556886</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3253012</v>
+        <v>0.325</v>
       </c>
       <c r="K14" t="n">
         <v>27</v>
@@ -3637,31 +3637,31 @@
         <v>47</v>
       </c>
       <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>19</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
         <v>9</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>23</v>
-      </c>
-      <c r="P14" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>15</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.6444445</v>
+        <v>1.5333333</v>
       </c>
       <c r="S14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T14" t="n">
-        <v>0.29885057</v>
+        <v>0.29069766</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.18716578</v>
+        <v>0.19587629</v>
       </c>
       <c r="C15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
         <v>28</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E15" t="n">
-        <v>29</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.23529412</v>
+      </c>
+      <c r="I15" t="n">
+        <v>28</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.28350514</v>
+      </c>
+      <c r="K15" t="n">
         <v>29</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.2284264</v>
-      </c>
-      <c r="I15" t="n">
-        <v>29</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.26737967</v>
-      </c>
-      <c r="K15" t="n">
-        <v>30</v>
-      </c>
       <c r="L15" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7647057</v>
+        <v>5.2941175</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2941177</v>
+        <v>1.372549</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23195876</v>
+        <v>0.24623115</v>
       </c>
       <c r="U15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.28691983</v>
+        <v>0.2838983</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>0.37226278</v>
+        <v>0.36996338</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4556962</v>
+        <v>0.45338982</v>
       </c>
       <c r="K16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7741935</v>
+        <v>4.209677</v>
       </c>
       <c r="O16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P16" t="n">
         <v>10</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2419355</v>
+        <v>1.3225807</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2457627</v>
+        <v>0.24896266</v>
       </c>
       <c r="U16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -3805,46 +3805,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2992126</v>
+        <v>0.33460075</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.37586206</v>
+        <v>0.41558442</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5551180999999999</v>
+        <v>0.6387833000000001</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M17" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
-        <v>5.25</v>
+        <v>5.9016395</v>
       </c>
       <c r="O17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P17" t="n">
         <v>9</v>
@@ -3853,16 +3853,16 @@
         <v>15</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3333334</v>
+        <v>1.3770492</v>
       </c>
       <c r="S17" t="n">
         <v>18</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2599119</v>
+        <v>0.25862068</v>
       </c>
       <c r="U17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -3872,43 +3872,43 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2734694</v>
+        <v>0.26778242</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>31</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
         <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3561151</v>
+        <v>0.3432836</v>
       </c>
       <c r="I18" t="n">
         <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4489796</v>
+        <v>0.44769874</v>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7692308</v>
+        <v>2.671875</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -3917,19 +3917,19 @@
         <v>7</v>
       </c>
       <c r="Q18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.22594142</v>
+      </c>
+      <c r="U18" t="n">
         <v>8</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.0615385</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.21161826</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -3939,61 +3939,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.23152709</v>
+        <v>0.24401914</v>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>13</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3277311</v>
+      </c>
+      <c r="I19" t="n">
         <v>12</v>
       </c>
-      <c r="F19" t="n">
-        <v>15</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.30530974</v>
-      </c>
-      <c r="I19" t="n">
-        <v>20</v>
-      </c>
       <c r="J19" t="n">
-        <v>0.49753696</v>
+        <v>0.4832536</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8076923</v>
+        <v>3.6346154</v>
       </c>
       <c r="O19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P19" t="n">
         <v>8</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1923077</v>
+        <v>1.1538461</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>0.21875</v>
+        <v>0.21164021</v>
       </c>
       <c r="U19" t="n">
         <v>7</v>
@@ -4006,43 +4006,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.22330096</v>
+        <v>0.23671497</v>
       </c>
       <c r="C20" t="n">
+        <v>21</v>
+      </c>
+      <c r="D20" t="n">
         <v>23</v>
       </c>
-      <c r="D20" t="n">
-        <v>17</v>
-      </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>9</v>
       </c>
-      <c r="G20" t="n">
-        <v>14</v>
-      </c>
       <c r="H20" t="n">
-        <v>0.3030303</v>
+        <v>0.29955947</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>0.38349515</v>
+        <v>0.41545895</v>
       </c>
       <c r="K20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L20" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M20" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>6.84</v>
       </c>
       <c r="O20" t="n">
         <v>27</v>
@@ -4054,16 +4054,16 @@
         <v>25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
+        <v>23</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.26262626</v>
+      </c>
+      <c r="U20" t="n">
         <v>21</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.25641027</v>
-      </c>
-      <c r="U20" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.15544042</v>
+        <v>0.16931216</v>
       </c>
       <c r="C21" t="n">
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F21" t="n">
         <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H21" t="n">
-        <v>0.22274882</v>
+        <v>0.23300971</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>0.29533678</v>
+        <v>0.31746033</v>
       </c>
       <c r="K21" t="n">
         <v>28</v>
       </c>
       <c r="L21" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N21" t="n">
-        <v>3.994083</v>
+        <v>4.339286</v>
       </c>
       <c r="O21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P21" t="n">
         <v>13</v>
       </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2248521</v>
+        <v>1.3392857</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T21" t="n">
-        <v>0.23394495</v>
+        <v>0.25560537</v>
       </c>
       <c r="U21" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -4140,61 +4140,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2761905</v>
+        <v>0.25980392</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.33620688</v>
+        <v>0.32599118</v>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4904762</v>
+        <v>0.47058824</v>
       </c>
       <c r="K22" t="n">
         <v>8</v>
       </c>
       <c r="L22" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
         <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>4.754717</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5</v>
+        <v>1.3962264</v>
       </c>
       <c r="S22" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="T22" t="n">
-        <v>0.26168224</v>
+        <v>0.2631579</v>
       </c>
       <c r="U22" t="n">
         <v>22</v>
@@ -4207,61 +4207,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.29961088</v>
+        <v>0.30268198</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3809524</v>
+        <v>0.3762712</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.49416342</v>
+        <v>0.47126436</v>
       </c>
       <c r="K23" t="n">
         <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M23" t="n">
         <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="n">
         <v>28</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2638298</v>
+        <v>0.27118644</v>
       </c>
       <c r="U23" t="n">
         <v>23</v>
@@ -4274,43 +4274,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2625</v>
+        <v>0.26530612</v>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
       </c>
       <c r="G24" t="n">
+        <v>9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.33579335</v>
+      </c>
+      <c r="I24" t="n">
         <v>11</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.33458647</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10</v>
-      </c>
       <c r="J24" t="n">
-        <v>0.45416668</v>
+        <v>0.45306122</v>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M24" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N24" t="n">
-        <v>8.583815</v>
+        <v>8.271675999999999</v>
       </c>
       <c r="O24" t="n">
         <v>30</v>
@@ -4319,16 +4319,16 @@
         <v>16</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8554913</v>
+        <v>1.8728323</v>
       </c>
       <c r="S24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T24" t="n">
-        <v>0.30379745</v>
+        <v>0.30084747</v>
       </c>
       <c r="U24" t="n">
         <v>27</v>
@@ -4341,34 +4341,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.26794258</v>
+        <v>0.26291078</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3018018</v>
+        <v>0.30701753</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4401914</v>
+        <v>0.48826292</v>
       </c>
       <c r="K25" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
         <v>42</v>
@@ -4377,28 +4377,28 @@
         <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>6.529412</v>
+        <v>7.56</v>
       </c>
       <c r="O25" t="n">
         <v>28</v>
       </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5686275</v>
+        <v>1.68</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T25" t="n">
-        <v>0.27</v>
+        <v>0.295</v>
       </c>
       <c r="U25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -4408,46 +4408,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.24747474</v>
+        <v>0.22459893</v>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H26" t="n">
-        <v>0.32579187</v>
+        <v>0.29807693</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>0.36868685</v>
+        <v>0.36898395</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M26" t="n">
         <v>26</v>
       </c>
       <c r="N26" t="n">
-        <v>2.2075472</v>
+        <v>1.1666666</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -4456,16 +4456,16 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9622642</v>
+        <v>0.7037037</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.19270833</v>
+        <v>0.14973262</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4475,46 +4475,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2647059</v>
+        <v>0.26442307</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
         <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>0.33333334</v>
+        <v>0.33898306</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>0.44607842</v>
+        <v>0.44230768</v>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L27" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.037736</v>
+        <v>2.4230769</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
@@ -4523,16 +4523,16 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.0943396</v>
+        <v>1.1538461</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1904762</v>
+        <v>0.20634921</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.285</v>
+        <v>0.255</v>
       </c>
       <c r="C28" t="n">
+        <v>13</v>
+      </c>
+      <c r="D28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.34210527</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="K28" t="n">
+        <v>14</v>
+      </c>
+      <c r="L28" t="n">
+        <v>42</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.2884614</v>
+      </c>
+      <c r="O28" t="n">
         <v>5</v>
       </c>
-      <c r="D28" t="n">
-        <v>35</v>
-      </c>
-      <c r="E28" t="n">
-        <v>9</v>
-      </c>
-      <c r="F28" t="n">
-        <v>13</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.36681223</v>
-      </c>
-      <c r="I28" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" t="n">
-        <v>38</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.0566037</v>
-      </c>
-      <c r="O28" t="n">
-        <v>4</v>
-      </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8301887</v>
+        <v>0.86538464</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1875</v>
+        <v>0.19473684</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.25365853</v>
+        <v>0.24878049</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" t="n">
         <v>27</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31858408</v>
+        <v>0.3018018</v>
       </c>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>0.40487805</v>
+        <v>0.41951218</v>
       </c>
       <c r="K29" t="n">
         <v>17</v>
       </c>
       <c r="L29" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.7358491</v>
+        <v>4.245283</v>
       </c>
       <c r="O29" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P29" t="n">
         <v>8</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.0754716</v>
+        <v>1.2075472</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23444976</v>
+        <v>0.25</v>
       </c>
       <c r="U29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -4676,43 +4676,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1861702</v>
+        <v>0.17391305</v>
       </c>
       <c r="C30" t="n">
         <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
         <v>28</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>30</v>
       </c>
       <c r="H30" t="n">
-        <v>0.24509804</v>
+        <v>0.23880596</v>
       </c>
       <c r="I30" t="n">
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.27659574</v>
+        <v>0.25543478</v>
       </c>
       <c r="K30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L30" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3962264</v>
+        <v>3.4615386</v>
       </c>
       <c r="O30" t="n">
         <v>6</v>
@@ -4724,16 +4724,16 @@
         <v>15</v>
       </c>
       <c r="R30" t="n">
-        <v>1.0754716</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>0.20103092</v>
+        <v>0.19895288</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.27669904</v>
+        <v>0.28985506</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
         <v>13</v>
       </c>
       <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.37815127</v>
+      </c>
+      <c r="I31" t="n">
         <v>3</v>
       </c>
-      <c r="H31" t="n">
-        <v>0.36864406</v>
-      </c>
-      <c r="I31" t="n">
-        <v>5</v>
-      </c>
       <c r="J31" t="n">
-        <v>0.5388349</v>
+        <v>0.5458937</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N31" t="n">
-        <v>4.075472</v>
+        <v>5.09434</v>
       </c>
       <c r="O31" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="P31" t="n">
         <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.245283</v>
+        <v>1.4339622</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25123152</v>
+        <v>0.27962086</v>
       </c>
       <c r="U31" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23644987</v>
+        <v>0.23712374</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G2" t="n">
         <v>29</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30727106</v>
+        <v>0.3074842</v>
       </c>
       <c r="I2" t="n">
         <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38177508</v>
+        <v>0.3846154</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.28426</v>
+        <v>4.2357383</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>110</v>
       </c>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2893509</v>
+        <v>1.2848154</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2516689</v>
+        <v>0.25140217</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -616,19 +616,19 @@
         <v>0.24804688</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>416</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
         <v>114</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
         <v>0.32618773</v>
@@ -649,7 +649,7 @@
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.109317</v>
+        <v>5.0981364</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24773718</v>
+        <v>0.24843079</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G4" t="n">
         <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31299093</v>
+        <v>0.3139881</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4116661</v>
+        <v>0.4132805</v>
       </c>
       <c r="K4" t="n">
         <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.527754</v>
+        <v>3.5514333</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2207514</v>
+        <v>1.225548</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22849277</v>
+        <v>0.22927989</v>
       </c>
       <c r="U4" t="n">
         <v>4</v>
@@ -756,13 +756,13 @@
         <v>416</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
         <v>104</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H5" t="n">
         <v>0.31876457</v>
@@ -774,7 +774,7 @@
         <v>0.39478892</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>832</v>
@@ -835,7 +835,7 @@
         <v>0.3118706</v>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
         <v>0.38602442</v>
@@ -847,7 +847,7 @@
         <v>725</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
         <v>3.7744424</v>
@@ -884,7 +884,7 @@
         <v>0.2438945</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>455</v>
@@ -914,7 +914,7 @@
         <v>762</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
         <v>4.357737</v>
@@ -951,19 +951,19 @@
         <v>0.24169184</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
         <v>428</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
         <v>125</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0.32133293</v>
@@ -981,13 +981,13 @@
         <v>799</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N8" t="n">
         <v>4.214467</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
         <v>96</v>
@@ -1005,7 +1005,7 @@
         <v>0.24001354</v>
       </c>
       <c r="U8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1024,7 +1024,7 @@
         <v>372</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
         <v>107</v>
@@ -1042,7 +1042,7 @@
         <v>0.38791946</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>834</v>
@@ -1091,7 +1091,7 @@
         <v>362</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
         <v>84</v>
@@ -1103,7 +1103,7 @@
         <v>0.3119266</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
         <v>0.36764705</v>
@@ -1115,7 +1115,7 @@
         <v>749</v>
       </c>
       <c r="M10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N10" t="n">
         <v>3.796526</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25856498</v>
+        <v>0.2583839</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3285136</v>
+        <v>0.32924393</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42598578</v>
+        <v>0.42574257</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.535</v>
+        <v>5.5310574</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5175</v>
+        <v>1.5166599</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28732747</v>
+        <v>0.2877943</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1225,7 +1225,7 @@
         <v>379</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
         <v>105</v>
@@ -1237,13 +1237,13 @@
         <v>0.31373706</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
         <v>0.39753824</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
         <v>780</v>
@@ -1255,7 +1255,7 @@
         <v>3.7582002</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
         <v>93</v>
@@ -1273,7 +1273,7 @@
         <v>0.2358459</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1283,64 +1283,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24117838</v>
+        <v>0.24216251</v>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3148899</v>
+        <v>0.31557846</v>
       </c>
       <c r="I13" t="n">
         <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4101651</v>
+        <v>0.41266796</v>
       </c>
       <c r="K13" t="n">
         <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="M13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>4.724448</v>
+        <v>4.7550607</v>
       </c>
       <c r="O13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3822567</v>
+        <v>1.3882592</v>
       </c>
       <c r="S13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T13" t="n">
-        <v>0.23918742</v>
+        <v>0.24060881</v>
       </c>
       <c r="U13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1350,43 +1350,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24152824</v>
+        <v>0.24525213</v>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="E14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" t="n">
+        <v>91</v>
+      </c>
+      <c r="G14" t="n">
         <v>23</v>
       </c>
-      <c r="F14" t="n">
-        <v>87</v>
-      </c>
-      <c r="G14" t="n">
-        <v>25</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.31132916</v>
+        <v>0.31497216</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.38704318</v>
+        <v>0.39325476</v>
       </c>
       <c r="K14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="M14" t="n">
         <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.83599</v>
+        <v>4.793032</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
@@ -1398,13 +1398,13 @@
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4320469</v>
+        <v>1.437163</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26191258</v>
+        <v>0.26209807</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1420,7 +1420,7 @@
         <v>0.23708306</v>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
         <v>399</v>
@@ -1432,19 +1432,19 @@
         <v>104</v>
       </c>
       <c r="G15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H15" t="n">
         <v>0.3134677</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
         <v>0.39045128</v>
       </c>
       <c r="K15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" t="n">
         <v>859</v>
@@ -1462,7 +1462,7 @@
         <v>97</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R15" t="n">
         <v>1.4015781</v>
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26396602</v>
+        <v>0.2647533</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34731734</v>
+        <v>0.3473358</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.43972558</v>
+        <v>0.4398581</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.488575</v>
+        <v>3.507787</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1292065</v>
+        <v>1.1348361</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21577883</v>
+        <v>0.21611722</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1560,7 +1560,7 @@
         <v>418</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
         <v>91</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25451505</v>
+        <v>0.25421488</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
@@ -1636,25 +1636,25 @@
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33726066</v>
+        <v>0.33673173</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39765885</v>
+        <v>0.39636365</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>3.346543</v>
+        <v>3.3201334</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1666,13 +1666,13 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1787521</v>
+        <v>1.1767403</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2190509</v>
+        <v>0.21897314</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1694,7 +1694,7 @@
         <v>448</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>117</v>
@@ -1718,13 +1718,13 @@
         <v>753</v>
       </c>
       <c r="M19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N19" t="n">
         <v>4.7785625</v>
       </c>
       <c r="O19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P19" t="n">
         <v>106</v>
@@ -1736,7 +1736,7 @@
         <v>1.387204</v>
       </c>
       <c r="S19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T19" t="n">
         <v>0.25372168</v>
@@ -1752,64 +1752,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23145695</v>
+        <v>0.2321779</v>
       </c>
       <c r="C20" t="n">
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>0.29952124</v>
+        <v>0.30064973</v>
       </c>
       <c r="I20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37748346</v>
+        <v>0.37900588</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N20" t="n">
-        <v>4.293922</v>
+        <v>4.27426</v>
       </c>
       <c r="O20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P20" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2914238</v>
+        <v>1.2976973</v>
       </c>
       <c r="S20" t="n">
         <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23570019</v>
+        <v>0.23655216</v>
       </c>
       <c r="U20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -1819,43 +1819,43 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23471467</v>
+        <v>0.23335575</v>
       </c>
       <c r="C21" t="n">
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31763646</v>
+        <v>0.3161022</v>
       </c>
       <c r="I21" t="n">
         <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>0.41949728</v>
+        <v>0.41930062</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>790</v>
+        <v>807</v>
       </c>
       <c r="M21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.392074</v>
+        <v>3.3651521</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -1867,13 +1867,13 @@
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1989882</v>
+        <v>1.190496</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22837839</v>
+        <v>0.22734872</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23721544</v>
+        <v>0.23769155</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E22" t="n">
         <v>16</v>
@@ -1904,43 +1904,43 @@
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30301222</v>
+        <v>0.3041814</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40448695</v>
+        <v>0.40365177</v>
       </c>
       <c r="K22" t="n">
         <v>14</v>
       </c>
       <c r="L22" t="n">
-        <v>787</v>
+        <v>800</v>
       </c>
       <c r="M22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N22" t="n">
-        <v>4.120934</v>
+        <v>4.2473164</v>
       </c>
       <c r="O22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Q22" t="n">
+        <v>18</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.325351</v>
+      </c>
+      <c r="S22" t="n">
         <v>17</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.3048373</v>
-      </c>
-      <c r="S22" t="n">
-        <v>16</v>
-      </c>
       <c r="T22" t="n">
-        <v>0.2549273</v>
+        <v>0.25836253</v>
       </c>
       <c r="U22" t="n">
         <v>26</v>
@@ -1968,7 +1968,7 @@
         <v>114</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
         <v>0.3399386</v>
@@ -1992,7 +1992,7 @@
         <v>4.2748156</v>
       </c>
       <c r="O23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P23" t="n">
         <v>96</v>
@@ -2004,7 +2004,7 @@
         <v>1.3129615</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T23" t="n">
         <v>0.23841918</v>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22435677</v>
+        <v>0.22440678</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
@@ -2038,43 +2038,43 @@
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3005213</v>
+        <v>0.29975727</v>
       </c>
       <c r="I24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37255573</v>
+        <v>0.37084746</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="M24" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N24" t="n">
-        <v>4.215528</v>
+        <v>4.2583895</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P24" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3428086</v>
+        <v>1.3427013</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24704292</v>
+        <v>0.24758092</v>
       </c>
       <c r="U24" t="n">
         <v>19</v>
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25613347</v>
+        <v>0.25615284</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G25" t="n">
         <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30817798</v>
+        <v>0.30895033</v>
       </c>
       <c r="I25" t="n">
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>0.42230946</v>
+        <v>0.4232513</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5133986</v>
+        <v>4.473507</v>
       </c>
       <c r="O25" t="n">
         <v>22</v>
       </c>
       <c r="P25" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.380689</v>
+        <v>1.3713204</v>
       </c>
       <c r="S25" t="n">
         <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25067294</v>
+        <v>0.24908425</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2163,7 +2163,7 @@
         <v>372</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
         <v>109</v>
@@ -2175,25 +2175,25 @@
         <v>0.31170747</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
         <v>0.3815221</v>
       </c>
       <c r="K26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L26" t="n">
         <v>791</v>
       </c>
       <c r="M26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N26" t="n">
         <v>3.5464685</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
         <v>80</v>
@@ -2211,7 +2211,7 @@
         <v>0.23603724</v>
       </c>
       <c r="U26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24760929</v>
+        <v>0.24721378</v>
       </c>
       <c r="C27" t="n">
         <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
@@ -2236,31 +2236,31 @@
         <v>99</v>
       </c>
       <c r="G27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32487157</v>
+        <v>0.3241627</v>
       </c>
       <c r="I27" t="n">
         <v>9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39651638</v>
+        <v>0.39513677</v>
       </c>
       <c r="K27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L27" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.13691</v>
+        <v>4.123886</v>
       </c>
       <c r="O27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
         <v>90</v>
@@ -2269,13 +2269,13 @@
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.332618</v>
+        <v>1.3313534</v>
       </c>
       <c r="S27" t="n">
         <v>18</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25237128</v>
+        <v>0.2520924</v>
       </c>
       <c r="U27" t="n">
         <v>23</v>
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25887626</v>
+        <v>0.25750342</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E28" t="n">
         <v>18</v>
@@ -2306,43 +2306,43 @@
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33658835</v>
+        <v>0.33464327</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39675975</v>
+        <v>0.39392906</v>
       </c>
       <c r="K28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L28" t="n">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.746134</v>
+        <v>3.7605095</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1778351</v>
+        <v>1.1707007</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23235093</v>
+        <v>0.23100407</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2364,7 +2364,7 @@
         <v>367</v>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
         <v>97</v>
@@ -2382,13 +2382,13 @@
         <v>0.39301166</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L29" t="n">
         <v>747</v>
       </c>
       <c r="M29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N29" t="n">
         <v>3.9793074</v>
@@ -2422,64 +2422,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2436919</v>
+        <v>0.2421952</v>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30563083</v>
+        <v>0.3041145</v>
       </c>
       <c r="I30" t="n">
+        <v>28</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.38054553</v>
+      </c>
+      <c r="K30" t="n">
         <v>27</v>
       </c>
-      <c r="J30" t="n">
-        <v>0.38247013</v>
-      </c>
-      <c r="K30" t="n">
-        <v>25</v>
-      </c>
       <c r="L30" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1131053</v>
+        <v>4.139256</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P30" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3034223</v>
+        <v>1.3078512</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24003984</v>
+        <v>0.24022347</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24855861</v>
+        <v>0.24984168</v>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32272857</v>
+        <v>0.32360443</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>0.43017298</v>
+        <v>0.4328689</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="M31" t="n">
         <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.716735</v>
+        <v>4.785224</v>
       </c>
       <c r="O31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3946939</v>
+        <v>1.3976585</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25868604</v>
+        <v>0.25944427</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.21827412</v>
+        <v>0.23076923</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3063063</v>
+        <v>0.30131003</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3401015</v>
+        <v>0.3653846</v>
       </c>
       <c r="K2" t="n">
         <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6964285</v>
+        <v>3.0535715</v>
       </c>
       <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
         <v>8</v>
       </c>
-      <c r="P2" t="n">
-        <v>9</v>
-      </c>
       <c r="Q2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.1428572</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U2" t="n">
         <v>15</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.1785715</v>
-      </c>
-      <c r="S2" t="n">
-        <v>9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.25581396</v>
-      </c>
-      <c r="U2" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2867,61 +2867,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.26213592</v>
+        <v>0.2559524</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="n">
-        <v>0.31390134</v>
+        <v>0.30769232</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>0.41262135</v>
+        <v>0.41666666</v>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>7.8333335</v>
+        <v>7.4</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0185184</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.33777776</v>
+        <v>0.32417583</v>
       </c>
       <c r="U3" t="n">
         <v>30</v>
@@ -2934,61 +2934,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25</v>
+        <v>0.2581967</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3448276</v>
+        <v>0.35106382</v>
       </c>
       <c r="I4" t="n">
         <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>0.455</v>
+        <v>0.46721312</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="M4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1666665</v>
+        <v>5.203125</v>
       </c>
       <c r="O4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3518518</v>
+        <v>1.390625</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
-        <v>0.25943395</v>
+        <v>0.264</v>
       </c>
       <c r="U4" t="n">
         <v>20</v>
@@ -3001,46 +3001,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21578947</v>
+        <v>0.22981367</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3169643</v>
+        <v>0.33333334</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>0.33157894</v>
+        <v>0.36024845</v>
       </c>
       <c r="K5" t="n">
         <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="M5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.075472</v>
+        <v>3.6818182</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
@@ -3049,16 +3049,16 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3018868</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>0.22613065</v>
+        <v>0.21472393</v>
       </c>
       <c r="U5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24630542</v>
+        <v>0.23699422</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>0.30837005</v>
+        <v>0.30927834</v>
       </c>
       <c r="I6" t="n">
         <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4039409</v>
+        <v>0.3815029</v>
       </c>
       <c r="K6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8333335</v>
+        <v>5.2</v>
       </c>
       <c r="O6" t="n">
         <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
         <v>9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3518518</v>
+        <v>1.4222223</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T6" t="n">
-        <v>0.25365853</v>
+        <v>0.2616279</v>
       </c>
       <c r="U6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -3135,61 +3135,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.28640777</v>
+        <v>0.2848837</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.37238494</v>
+        <v>0.37185928</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.52427185</v>
+        <v>0.55813956</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="O7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="P7" t="n">
         <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R7" t="n">
-        <v>1.574074</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T7" t="n">
-        <v>0.30875576</v>
+        <v>0.30769232</v>
       </c>
       <c r="U7" t="n">
         <v>29</v>
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2398374</v>
+        <v>0.23333333</v>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31135532</v>
+        <v>0.30172414</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J8" t="n">
-        <v>0.42682928</v>
+        <v>0.42380953</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="M8" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8152175</v>
+        <v>4.1273885</v>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
         <v>7</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.402174</v>
+        <v>1.4904459</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23684211</v>
+        <v>0.2512563</v>
       </c>
       <c r="U8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.23275863</v>
+        <v>0.2284264</v>
       </c>
       <c r="C9" t="n">
+        <v>27</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
         <v>22</v>
       </c>
-      <c r="D9" t="n">
-        <v>22</v>
-      </c>
-      <c r="E9" t="n">
-        <v>26</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>21</v>
-      </c>
       <c r="H9" t="n">
-        <v>0.2936508</v>
+        <v>0.2962963</v>
       </c>
       <c r="I9" t="n">
         <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>0.375</v>
+        <v>0.37055838</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.326923</v>
       </c>
       <c r="O9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.4230769</v>
       </c>
       <c r="S9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24215247</v>
+        <v>0.24226804</v>
       </c>
       <c r="U9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.25104603</v>
+        <v>0.24752475</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31153846</v>
+        <v>0.3153153</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>0.41004184</v>
+        <v>0.41584158</v>
       </c>
       <c r="K10" t="n">
         <v>20</v>
       </c>
       <c r="L10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N10" t="n">
-        <v>4.21875</v>
+        <v>4.090909</v>
       </c>
       <c r="O10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
         <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.2363636</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.24180327</v>
+        <v>0.23076923</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3403,16 +3403,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.30379745</v>
+        <v>0.29583332</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>12</v>
@@ -3421,46 +3421,46 @@
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.37956205</v>
+        <v>0.38078293</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5611814000000001</v>
+        <v>0.5416666999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M11" t="n">
+        <v>16</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.5958548</v>
+      </c>
+      <c r="O11" t="n">
+        <v>21</v>
+      </c>
+      <c r="P11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" t="n">
-        <v>6.285714</v>
-      </c>
-      <c r="O11" t="n">
-        <v>26</v>
-      </c>
-      <c r="P11" t="n">
-        <v>12</v>
-      </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6190476</v>
+        <v>1.5544041</v>
       </c>
       <c r="S11" t="n">
+        <v>24</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.3053435</v>
+      </c>
+      <c r="U11" t="n">
         <v>27</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.3065134</v>
-      </c>
-      <c r="U11" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24663678</v>
+        <v>0.23913044</v>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>0.29752067</v>
+        <v>0.2914573</v>
       </c>
       <c r="I12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4349776</v>
+        <v>0.45108697</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2727273</v>
+        <v>3.326087</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
         <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>0.92727274</v>
+        <v>1.0217391</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0.19900498</v>
+        <v>0.21637426</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.21989529</v>
+        <v>0.24365482</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2890995</v>
+        <v>0.30875576</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>0.40837696</v>
+        <v>0.43654823</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.924528</v>
       </c>
       <c r="O13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P13" t="n">
         <v>11</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1666666</v>
+        <v>1.264151</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>0.20304568</v>
+        <v>0.22727273</v>
       </c>
       <c r="U13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1875</v>
+        <v>0.25490198</v>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.29493088</v>
+      </c>
+      <c r="I14" t="n">
         <v>26</v>
       </c>
-      <c r="H14" t="n">
-        <v>0.21556886</v>
-      </c>
-      <c r="I14" t="n">
-        <v>30</v>
-      </c>
       <c r="J14" t="n">
-        <v>0.325</v>
+        <v>0.43137255</v>
       </c>
       <c r="K14" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L14" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>4.3333335</v>
       </c>
       <c r="O14" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="P14" t="n">
         <v>8</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5333333</v>
+        <v>1.5925926</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
       </c>
       <c r="T14" t="n">
-        <v>0.29069766</v>
+        <v>0.28846154</v>
       </c>
       <c r="U14" t="n">
         <v>25</v>
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.19587629</v>
+        <v>0.18518518</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>0.23529412</v>
+        <v>0.22352941</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J15" t="n">
-        <v>0.28350514</v>
+        <v>0.25308642</v>
       </c>
       <c r="K15" t="n">
         <v>29</v>
       </c>
       <c r="L15" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2941175</v>
+        <v>5.4418607</v>
       </c>
       <c r="O15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.372549</v>
+        <v>1.4418604</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T15" t="n">
-        <v>0.24623115</v>
+        <v>0.25443786</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2838983</v>
+        <v>0.27038628</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
         <v>7</v>
       </c>
-      <c r="F16" t="n">
-        <v>9</v>
-      </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H16" t="n">
-        <v>0.36996338</v>
+        <v>0.35793358</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.45338982</v>
+        <v>0.42060086</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L16" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>4.209677</v>
+        <v>4.359375</v>
       </c>
       <c r="O16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P16" t="n">
         <v>10</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3225807</v>
+        <v>1.328125</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T16" t="n">
-        <v>0.24896266</v>
+        <v>0.24166666</v>
       </c>
       <c r="U16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.33460075</v>
+        <v>0.33482143</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.41558442</v>
+        <v>0.41666666</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6387833000000001</v>
+        <v>0.6339286</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>5.9016395</v>
+        <v>5.7115383</v>
       </c>
       <c r="O17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3770492</v>
+        <v>1.3269231</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T17" t="n">
-        <v>0.25862068</v>
+        <v>0.25252524</v>
       </c>
       <c r="U17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -3872,61 +3872,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.26778242</v>
+        <v>0.26530612</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3432836</v>
+        <v>0.32962963</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>0.44769874</v>
+        <v>0.41632652</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N18" t="n">
-        <v>2.671875</v>
+        <v>2.390625</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q18" t="n">
         <v>7</v>
       </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.125</v>
+        <v>1.109375</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22594142</v>
+        <v>0.21940929</v>
       </c>
       <c r="U18" t="n">
         <v>8</v>
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24401914</v>
+        <v>0.24712643</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>8</v>
       </c>
-      <c r="F19" t="n">
-        <v>13</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2</v>
-      </c>
       <c r="H19" t="n">
-        <v>0.3277311</v>
+        <v>0.3316583</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4832536</v>
+        <v>0.4827586</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6346154</v>
+        <v>3.5581396</v>
       </c>
       <c r="O19" t="n">
         <v>7</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.1860465</v>
+      </c>
+      <c r="S19" t="n">
         <v>9</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.1538461</v>
-      </c>
-      <c r="S19" t="n">
-        <v>6</v>
-      </c>
       <c r="T19" t="n">
-        <v>0.21164021</v>
+        <v>0.21518987</v>
       </c>
       <c r="U19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23671497</v>
+        <v>0.25821596</v>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.32627118</v>
+      </c>
+      <c r="I20" t="n">
+        <v>13</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4460094</v>
+      </c>
+      <c r="K20" t="n">
         <v>9</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.29955947</v>
-      </c>
-      <c r="I20" t="n">
-        <v>22</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.41545895</v>
-      </c>
-      <c r="K20" t="n">
-        <v>18</v>
-      </c>
       <c r="L20" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>6.84</v>
+        <v>6.75</v>
       </c>
       <c r="O20" t="n">
         <v>27</v>
       </c>
       <c r="P20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.5961539</v>
       </c>
       <c r="S20" t="n">
+        <v>26</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.28372094</v>
+      </c>
+      <c r="U20" t="n">
         <v>23</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.26262626</v>
-      </c>
-      <c r="U20" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -4076,61 +4076,61 @@
         <v>0.16931216</v>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
         <v>27</v>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H21" t="n">
-        <v>0.23300971</v>
+        <v>0.23671497</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>0.31746033</v>
+        <v>0.33862433</v>
       </c>
       <c r="K21" t="n">
         <v>28</v>
       </c>
       <c r="L21" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M21" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N21" t="n">
-        <v>4.339286</v>
+        <v>4.178571</v>
       </c>
       <c r="O21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P21" t="n">
         <v>13</v>
       </c>
       <c r="Q21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3392857</v>
+        <v>1.1785715</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>0.25560537</v>
+        <v>0.23255815</v>
       </c>
       <c r="U21" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.25980392</v>
+        <v>0.26213592</v>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H22" t="n">
-        <v>0.32599118</v>
+        <v>0.33766234</v>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>0.47058824</v>
+        <v>0.4223301</v>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L22" t="n">
         <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>4.754717</v>
+        <v>5.7115383</v>
       </c>
       <c r="O22" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3962264</v>
+        <v>1.6346154</v>
       </c>
       <c r="S22" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2631579</v>
+        <v>0.30555555</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.30268198</v>
+        <v>0.30357143</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3762712</v>
+        <v>0.37698412</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.47126436</v>
+        <v>0.4419643</v>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="M23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>5.8235292</v>
       </c>
       <c r="O23" t="n">
         <v>24</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.5294118</v>
       </c>
       <c r="S23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T23" t="n">
-        <v>0.27118644</v>
+        <v>0.27227724</v>
       </c>
       <c r="U23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.26530612</v>
+        <v>0.25306123</v>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
       </c>
       <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3197026</v>
+      </c>
+      <c r="I24" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.43265307</v>
+      </c>
+      <c r="K24" t="n">
+        <v>12</v>
+      </c>
+      <c r="L24" t="n">
+        <v>67</v>
+      </c>
+      <c r="M24" t="n">
+        <v>30</v>
+      </c>
+      <c r="N24" t="n">
         <v>9</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.33579335</v>
-      </c>
-      <c r="I24" t="n">
-        <v>11</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.45306122</v>
-      </c>
-      <c r="K24" t="n">
-        <v>11</v>
-      </c>
-      <c r="L24" t="n">
-        <v>63</v>
-      </c>
-      <c r="M24" t="n">
-        <v>26</v>
-      </c>
-      <c r="N24" t="n">
-        <v>8.271675999999999</v>
       </c>
       <c r="O24" t="n">
         <v>30</v>
       </c>
       <c r="P24" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8728323</v>
+        <v>1.8275862</v>
       </c>
       <c r="S24" t="n">
         <v>29</v>
       </c>
       <c r="T24" t="n">
-        <v>0.30084747</v>
+        <v>0.3</v>
       </c>
       <c r="U24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.26291078</v>
+        <v>0.26190478</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30701753</v>
+        <v>0.3231441</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J25" t="n">
-        <v>0.48826292</v>
+        <v>0.50476193</v>
       </c>
       <c r="K25" t="n">
         <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>7.56</v>
+        <v>6.7058825</v>
       </c>
       <c r="O25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.68</v>
+        <v>1.5098039</v>
       </c>
       <c r="S25" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.295</v>
+        <v>0.27450982</v>
       </c>
       <c r="U25" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -4408,61 +4408,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22459893</v>
+        <v>0.22929937</v>
       </c>
       <c r="C26" t="n">
+        <v>26</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="n">
         <v>23</v>
       </c>
-      <c r="D26" t="n">
-        <v>30</v>
-      </c>
-      <c r="E26" t="n">
-        <v>15</v>
-      </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
+        <v>27</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.30285713</v>
+      </c>
+      <c r="I26" t="n">
         <v>21</v>
       </c>
-      <c r="H26" t="n">
-        <v>0.29807693</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
+        <v>0.34394905</v>
+      </c>
+      <c r="K26" t="n">
+        <v>27</v>
+      </c>
+      <c r="L26" t="n">
+        <v>57</v>
+      </c>
+      <c r="M26" t="n">
         <v>23</v>
       </c>
-      <c r="J26" t="n">
-        <v>0.36898395</v>
-      </c>
-      <c r="K26" t="n">
-        <v>24</v>
-      </c>
-      <c r="L26" t="n">
-        <v>63</v>
-      </c>
-      <c r="M26" t="n">
-        <v>26</v>
-      </c>
       <c r="N26" t="n">
-        <v>1.1666666</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7037037</v>
+        <v>0.62222224</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.14973262</v>
+        <v>0.12903225</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.26442307</v>
+        <v>0.25726143</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
@@ -4490,49 +4490,49 @@
         <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H27" t="n">
-        <v>0.33898306</v>
+        <v>0.32841328</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
-        <v>0.44230768</v>
+        <v>0.41908714</v>
       </c>
       <c r="K27" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L27" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4230769</v>
+        <v>2.5081968</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.1538461</v>
+        <v>1.1639345</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>0.20634921</v>
+        <v>0.20982143</v>
       </c>
       <c r="U27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -4542,61 +4542,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.255</v>
+        <v>0.23809524</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E28" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28" t="n">
-        <v>0.34210527</v>
+        <v>0.31660232</v>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>0.435</v>
+        <v>0.3939394</v>
       </c>
       <c r="K28" t="n">
+        <v>22</v>
+      </c>
+      <c r="L28" t="n">
+        <v>51</v>
+      </c>
+      <c r="M28" t="n">
+        <v>16</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.5409837</v>
+      </c>
+      <c r="O28" t="n">
+        <v>6</v>
+      </c>
+      <c r="P28" t="n">
         <v>14</v>
       </c>
-      <c r="L28" t="n">
-        <v>42</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.2884614</v>
-      </c>
-      <c r="O28" t="n">
-        <v>5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>11</v>
-      </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="R28" t="n">
-        <v>0.86538464</v>
+        <v>0.8196721</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>0.19473684</v>
+        <v>0.18181819</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24878049</v>
+        <v>0.2366864</v>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D29" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3018018</v>
+        <v>0.2972973</v>
       </c>
       <c r="I29" t="n">
+        <v>24</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.41420117</v>
+      </c>
+      <c r="K29" t="n">
         <v>21</v>
       </c>
-      <c r="J29" t="n">
-        <v>0.41951218</v>
-      </c>
-      <c r="K29" t="n">
-        <v>17</v>
-      </c>
       <c r="L29" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>4.245283</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
         <v>9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2075472</v>
+        <v>1.2045455</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>0.25</v>
+        <v>0.24571429</v>
       </c>
       <c r="U29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.17391305</v>
+        <v>0.16489361</v>
       </c>
       <c r="C30" t="n">
+        <v>30</v>
+      </c>
+      <c r="D30" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="n">
-        <v>13</v>
-      </c>
-      <c r="E30" t="n">
-        <v>28</v>
-      </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
+        <v>29</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.21890548</v>
+      </c>
+      <c r="I30" t="n">
         <v>30</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.23880596</v>
-      </c>
-      <c r="I30" t="n">
-        <v>27</v>
-      </c>
       <c r="J30" t="n">
-        <v>0.25543478</v>
+        <v>0.24468085</v>
       </c>
       <c r="K30" t="n">
         <v>30</v>
       </c>
       <c r="L30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.4615386</v>
+        <v>4.4117646</v>
       </c>
       <c r="O30" t="n">
+        <v>15</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>19</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.1568627</v>
+      </c>
+      <c r="S30" t="n">
         <v>6</v>
       </c>
-      <c r="P30" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>15</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4</v>
-      </c>
       <c r="T30" t="n">
-        <v>0.19895288</v>
+        <v>0.21578947</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -4743,61 +4743,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.28985506</v>
+        <v>0.31428573</v>
       </c>
       <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>45</v>
+      </c>
+      <c r="E31" t="n">
         <v>4</v>
       </c>
-      <c r="D31" t="n">
-        <v>36</v>
-      </c>
-      <c r="E31" t="n">
-        <v>8</v>
-      </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.37815127</v>
+        <v>0.39917696</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5458937</v>
+        <v>0.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M31" t="n">
+        <v>6</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.8333335</v>
+      </c>
+      <c r="O31" t="n">
+        <v>25</v>
+      </c>
+      <c r="P31" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q31" t="n">
         <v>7</v>
       </c>
-      <c r="N31" t="n">
-        <v>5.09434</v>
-      </c>
-      <c r="O31" t="n">
-        <v>20</v>
-      </c>
-      <c r="P31" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.4339622</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
         <v>21</v>
       </c>
       <c r="T31" t="n">
-        <v>0.27962086</v>
+        <v>0.28440368</v>
       </c>
       <c r="U31" t="n">
         <v>24</v>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23712374</v>
+        <v>0.23642384</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>82</v>
@@ -564,43 +564,43 @@
         <v>29</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3074842</v>
+        <v>0.30684525</v>
       </c>
       <c r="I2" t="n">
         <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3846154</v>
+        <v>0.38278145</v>
       </c>
       <c r="K2" t="n">
         <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2357383</v>
+        <v>4.2383723</v>
       </c>
       <c r="O2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q2" t="n">
         <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2848154</v>
+        <v>1.2832226</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25140217</v>
+        <v>0.2509804</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24804688</v>
+        <v>0.24758531</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E3" t="n">
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32618773</v>
+        <v>0.32578796</v>
       </c>
       <c r="I3" t="n">
         <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40950522</v>
+        <v>0.40856406</v>
       </c>
       <c r="K3" t="n">
         <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.0981364</v>
+        <v>5.1143913</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4708074</v>
+        <v>1.4710947</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26679462</v>
+        <v>0.26662445</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24843079</v>
+        <v>0.24910219</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
@@ -695,49 +695,49 @@
         <v>116</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3139881</v>
+        <v>0.31410068</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4132805</v>
+        <v>0.41332027</v>
       </c>
       <c r="K4" t="n">
         <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5514333</v>
+        <v>3.6510851</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.225548</v>
+        <v>1.239566</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22927989</v>
+        <v>0.2311305</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23779683</v>
+        <v>0.23727155</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
@@ -765,25 +765,25 @@
         <v>17</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31876457</v>
+        <v>0.3183391</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39478892</v>
+        <v>0.39262402</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3400826</v>
+        <v>4.347364</v>
       </c>
       <c r="O5" t="n">
         <v>20</v>
@@ -792,19 +792,19 @@
         <v>100</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3710743</v>
+        <v>1.3718839</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2532258</v>
+        <v>0.25358853</v>
       </c>
       <c r="U5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -814,64 +814,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24355495</v>
+        <v>0.24438484</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="E6" t="n">
         <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3118706</v>
+        <v>0.31355423</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38602442</v>
+        <v>0.3881998</v>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="M6" t="n">
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7744424</v>
+        <v>3.7426875</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
         <v>94</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2491424</v>
+        <v>1.2424756</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24159022</v>
+        <v>0.24041694</v>
       </c>
       <c r="U6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -881,16 +881,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2438945</v>
+        <v>0.24436574</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>112</v>
@@ -899,28 +899,28 @@
         <v>11</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3381234</v>
+        <v>0.33807135</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40931293</v>
+        <v>0.40856406</v>
       </c>
       <c r="K7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="M7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
-        <v>4.357737</v>
+        <v>4.3315506</v>
       </c>
       <c r="O7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P7" t="n">
         <v>137</v>
@@ -929,13 +929,13 @@
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2691348</v>
+        <v>1.2661457</v>
       </c>
       <c r="S7" t="n">
         <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24420913</v>
+        <v>0.24361493</v>
       </c>
       <c r="U7" t="n">
         <v>18</v>
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24169184</v>
+        <v>0.24053156</v>
       </c>
       <c r="C8" t="n">
         <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
         <v>125</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32133293</v>
+        <v>0.31997642</v>
       </c>
       <c r="I8" t="n">
         <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41658273</v>
+        <v>0.41362128</v>
       </c>
       <c r="K8" t="n">
         <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="M8" t="n">
         <v>23</v>
       </c>
       <c r="N8" t="n">
-        <v>4.214467</v>
+        <v>4.2572145</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P8" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3350254</v>
+        <v>1.3425345</v>
       </c>
       <c r="S8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24001354</v>
+        <v>0.24088323</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22785234</v>
+        <v>0.22709164</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G9" t="n">
         <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3089988</v>
+        <v>0.30816868</v>
       </c>
       <c r="I9" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3864542</v>
+      </c>
+      <c r="K9" t="n">
         <v>24</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.38791946</v>
-      </c>
-      <c r="K9" t="n">
-        <v>23</v>
-      </c>
       <c r="L9" t="n">
-        <v>834</v>
+        <v>852</v>
       </c>
       <c r="M9" t="n">
         <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.568182</v>
+        <v>4.5617976</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.455808</v>
+        <v>1.451935</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24892277</v>
+        <v>0.2487709</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1082,43 +1082,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22994652</v>
+        <v>0.22865652</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E10" t="n">
+        <v>29</v>
+      </c>
+      <c r="F10" t="n">
+        <v>85</v>
+      </c>
+      <c r="G10" t="n">
         <v>27</v>
       </c>
-      <c r="F10" t="n">
-        <v>84</v>
-      </c>
-      <c r="G10" t="n">
-        <v>26</v>
-      </c>
       <c r="H10" t="n">
-        <v>0.3119266</v>
+        <v>0.31026393</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36764705</v>
+        <v>0.3663137</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="M10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.796526</v>
+        <v>3.7702703</v>
       </c>
       <c r="O10" t="n">
         <v>9</v>
@@ -1127,19 +1127,19 @@
         <v>106</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2617866</v>
+        <v>1.2653563</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23768595</v>
+        <v>0.23831317</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2583839</v>
+        <v>0.25821745</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
@@ -1164,46 +1164,46 @@
         <v>105</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32924393</v>
+        <v>0.32919255</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42574257</v>
+        <v>0.42414665</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>801</v>
+        <v>812</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5310574</v>
+        <v>5.49227</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q11" t="n">
         <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5166599</v>
+        <v>1.514646</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2877943</v>
+        <v>0.28715906</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23586161</v>
+        <v>0.23601054</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31373706</v>
+        <v>0.31414378</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39753824</v>
+        <v>0.39763</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7582002</v>
+        <v>3.7272348</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q12" t="n">
         <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2275021</v>
+        <v>1.224948</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2358459</v>
+        <v>0.23550844</v>
       </c>
       <c r="U12" t="n">
         <v>7</v>
@@ -1283,64 +1283,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24216251</v>
+        <v>0.24176173</v>
       </c>
       <c r="C13" t="n">
         <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31557846</v>
+        <v>0.3161619</v>
       </c>
       <c r="I13" t="n">
         <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41266796</v>
+        <v>0.41159695</v>
       </c>
       <c r="K13" t="n">
         <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="M13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7550607</v>
+        <v>4.7360835</v>
       </c>
       <c r="O13" t="n">
         <v>25</v>
       </c>
       <c r="P13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q13" t="n">
         <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3882592</v>
+        <v>1.3912696</v>
       </c>
       <c r="S13" t="n">
         <v>24</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24060881</v>
+        <v>0.24135724</v>
       </c>
       <c r="U13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24525213</v>
+        <v>0.24790187</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31497216</v>
+        <v>0.31882387</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39325476</v>
+        <v>0.3983215</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L14" t="n">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="M14" t="n">
         <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.793032</v>
+        <v>4.8396225</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.437163</v>
+        <v>1.4433962</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26209807</v>
+        <v>0.2629891</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23708306</v>
+        <v>0.23738681</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
         <v>104</v>
@@ -1435,46 +1435,46 @@
         <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3134677</v>
+        <v>0.31338537</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39045128</v>
+        <v>0.389392</v>
       </c>
       <c r="K15" t="n">
         <v>22</v>
       </c>
       <c r="L15" t="n">
-        <v>859</v>
+        <v>870</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.630814</v>
+        <v>4.673931</v>
       </c>
       <c r="O15" t="n">
         <v>24</v>
       </c>
       <c r="P15" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4015781</v>
+        <v>1.4037828</v>
       </c>
       <c r="S15" t="n">
         <v>26</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23724909</v>
+        <v>0.2382037</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1484,43 +1484,43 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2647533</v>
+        <v>0.2643495</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G16" t="n">
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3473358</v>
+        <v>0.34690464</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4398581</v>
+        <v>0.43845662</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.507787</v>
+        <v>3.4803405</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -1529,16 +1529,16 @@
         <v>98</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1348361</v>
+        <v>1.1357925</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21611722</v>
+        <v>0.21640316</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25371656</v>
+        <v>0.2542428</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33099824</v>
+        <v>0.3313149</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.40997687</v>
+        <v>0.41090077</v>
       </c>
       <c r="K17" t="n">
         <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="M17" t="n">
         <v>11</v>
       </c>
       <c r="N17" t="n">
-        <v>4.088861</v>
+        <v>4.093943</v>
       </c>
       <c r="O17" t="n">
         <v>11</v>
       </c>
       <c r="P17" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.2459826</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.22955145</v>
+      </c>
+      <c r="U17" t="n">
         <v>4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.2465582</v>
-      </c>
-      <c r="S17" t="n">
-        <v>9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.22963952</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25421488</v>
+        <v>0.25459826</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33673173</v>
+        <v>0.33740762</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39636365</v>
+        <v>0.3975476</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L18" t="n">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="M18" t="n">
         <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3201334</v>
+        <v>3.3020792</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1767403</v>
+        <v>1.1642886</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21897314</v>
+        <v>0.21737683</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24716185</v>
+        <v>0.24767405</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E19" t="n">
         <v>7</v>
@@ -1703,46 +1703,46 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3219653</v>
+        <v>0.32218412</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4168018</v>
+        <v>0.41642606</v>
       </c>
       <c r="K19" t="n">
         <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="M19" t="n">
         <v>14</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7785625</v>
+        <v>4.7366476</v>
       </c>
       <c r="O19" t="n">
         <v>26</v>
       </c>
       <c r="P19" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>1.387204</v>
+        <v>1.3767462</v>
       </c>
       <c r="S19" t="n">
         <v>23</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25372168</v>
+        <v>0.25224358</v>
       </c>
       <c r="U19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -1752,64 +1752,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2321779</v>
+        <v>0.23345172</v>
       </c>
       <c r="C20" t="n">
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G20" t="n">
         <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30064973</v>
+        <v>0.30195278</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.37900588</v>
+        <v>0.38101387</v>
       </c>
       <c r="K20" t="n">
         <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="M20" t="n">
+        <v>13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.4030094</v>
+      </c>
+      <c r="O20" t="n">
+        <v>21</v>
+      </c>
+      <c r="P20" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q20" t="n">
         <v>15</v>
       </c>
-      <c r="N20" t="n">
-        <v>4.27426</v>
-      </c>
-      <c r="O20" t="n">
-        <v>18</v>
-      </c>
-      <c r="P20" t="n">
-        <v>99</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>14</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.2976973</v>
+        <v>1.3200488</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23655216</v>
+        <v>0.23929712</v>
       </c>
       <c r="U20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23335575</v>
+        <v>0.23421927</v>
       </c>
       <c r="C21" t="n">
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E21" t="n">
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3161022</v>
+        <v>0.31589773</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>0.41930062</v>
+        <v>0.4192691</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>807</v>
+        <v>824</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3651521</v>
+        <v>3.3986793</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Q21" t="n">
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.190496</v>
+        <v>1.1923236</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22734872</v>
+        <v>0.22758849</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23769155</v>
+        <v>0.23766527</v>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E22" t="n">
         <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3041814</v>
+        <v>0.3038159</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40365177</v>
+        <v>0.40309578</v>
       </c>
       <c r="K22" t="n">
         <v>14</v>
       </c>
       <c r="L22" t="n">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="M22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2473164</v>
+        <v>4.211515</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P22" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q22" t="n">
         <v>18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.325351</v>
+        <v>1.320539</v>
       </c>
       <c r="S22" t="n">
         <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25836253</v>
+        <v>0.2573321</v>
       </c>
       <c r="U22" t="n">
         <v>26</v>
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.26189727</v>
+        <v>0.26323986</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3399386</v>
+        <v>0.34178612</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4219981</v>
+        <v>0.42429906</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="M23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2748156</v>
+        <v>4.2718053</v>
       </c>
       <c r="O23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P23" t="n">
         <v>96</v>
@@ -2001,16 +2001,16 @@
         <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3129615</v>
+        <v>1.3131845</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23841918</v>
+        <v>0.23919308</v>
       </c>
       <c r="U23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22440678</v>
+        <v>0.22423632</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29975727</v>
+        <v>0.29957932</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37084746</v>
+        <v>0.37059417</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="M24" t="n">
         <v>18</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2583895</v>
+        <v>4.210701</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P24" t="n">
         <v>99</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3427013</v>
+        <v>1.3376192</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24758092</v>
+        <v>0.246779</v>
       </c>
       <c r="U24" t="n">
         <v>19</v>
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25615284</v>
+        <v>0.25616395</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
         <v>101</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30895033</v>
+        <v>0.30841672</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4232513</v>
+        <v>0.4217099</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.473507</v>
+        <v>4.5243244</v>
       </c>
       <c r="O25" t="n">
         <v>22</v>
       </c>
       <c r="P25" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q25" t="n">
         <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3713204</v>
+        <v>1.3746362</v>
       </c>
       <c r="S25" t="n">
         <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24908425</v>
+        <v>0.25032896</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,61 +2154,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23130608</v>
+        <v>0.23119868</v>
       </c>
       <c r="C26" t="n">
         <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E26" t="n">
         <v>23</v>
       </c>
       <c r="F26" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G26" t="n">
         <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31170747</v>
+        <v>0.31168073</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3815221</v>
+        <v>0.3816092</v>
       </c>
       <c r="K26" t="n">
         <v>26</v>
       </c>
       <c r="L26" t="n">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="M26" t="n">
         <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5464685</v>
+        <v>3.5500205</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1598513</v>
+        <v>1.1649653</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23603724</v>
+        <v>0.23678161</v>
       </c>
       <c r="U26" t="n">
         <v>8</v>
@@ -2221,64 +2221,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24721378</v>
+        <v>0.24503969</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G27" t="n">
+        <v>19</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.32160658</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.39318782</v>
+      </c>
+      <c r="K27" t="n">
         <v>20</v>
       </c>
-      <c r="H27" t="n">
-        <v>0.3241627</v>
-      </c>
-      <c r="I27" t="n">
-        <v>9</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.39513677</v>
-      </c>
-      <c r="K27" t="n">
-        <v>17</v>
-      </c>
       <c r="L27" t="n">
-        <v>677</v>
+        <v>695</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.123886</v>
+        <v>4.1883035</v>
       </c>
       <c r="O27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P27" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q27" t="n">
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3313534</v>
+        <v>1.3401078</v>
       </c>
       <c r="S27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2520924</v>
+        <v>0.25253186</v>
       </c>
       <c r="U27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25750342</v>
+        <v>0.2574224</v>
       </c>
       <c r="C28" t="n">
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G28" t="n">
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33464327</v>
+        <v>0.33443016</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39392906</v>
+        <v>0.395749</v>
       </c>
       <c r="K28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L28" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7605095</v>
+        <v>3.7632241</v>
       </c>
       <c r="O28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" t="n">
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1707007</v>
+        <v>1.1712847</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23100407</v>
+        <v>0.23190348</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2355,43 +2355,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.243594</v>
+        <v>0.24448831</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G29" t="n">
         <v>21</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31877598</v>
+        <v>0.31942403</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39301166</v>
+        <v>0.3942086</v>
       </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L29" t="n">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="M29" t="n">
         <v>12</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9793074</v>
+        <v>3.9682672</v>
       </c>
       <c r="O29" t="n">
         <v>10</v>
@@ -2403,16 +2403,16 @@
         <v>21</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2377534</v>
+        <v>1.2375783</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="n">
-        <v>0.23823725</v>
+        <v>0.23853211</v>
       </c>
       <c r="U29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -2422,46 +2422,46 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2421952</v>
+        <v>0.24350649</v>
       </c>
       <c r="C30" t="n">
         <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="E30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F30" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3041145</v>
+        <v>0.3049499</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38054553</v>
+        <v>0.3814935</v>
       </c>
       <c r="K30" t="n">
         <v>27</v>
       </c>
       <c r="L30" t="n">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.139256</v>
+        <v>4.1266856</v>
       </c>
       <c r="O30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
         <v>104</v>
@@ -2470,16 +2470,16 @@
         <v>17</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3078512</v>
+        <v>1.3044544</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24022347</v>
+        <v>0.24041586</v>
       </c>
       <c r="U30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.24984168</v>
+        <v>0.25046962</v>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32360443</v>
+        <v>0.32408965</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4328689</v>
+        <v>0.43362555</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N31" t="n">
-        <v>4.785224</v>
+        <v>4.7983227</v>
       </c>
       <c r="O31" t="n">
         <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q31" t="n">
         <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3976585</v>
+        <v>1.398163</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25944427</v>
+        <v>0.25889266</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23076923</v>
+        <v>0.21078432</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.27149323</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3137255</v>
+      </c>
+      <c r="K2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L2" t="n">
+        <v>49</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.4363637</v>
+      </c>
+      <c r="O2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" t="n">
-        <v>22</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.30131003</v>
-      </c>
-      <c r="I2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.3653846</v>
-      </c>
-      <c r="K2" t="n">
-        <v>25</v>
-      </c>
-      <c r="L2" t="n">
-        <v>46</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
         <v>9</v>
       </c>
-      <c r="N2" t="n">
-        <v>3.0535715</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>14</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.1428572</v>
+        <v>1.2181818</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25</v>
+        <v>0.26046512</v>
       </c>
       <c r="U2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2559524</v>
+        <v>0.25443786</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>0.30769232</v>
+        <v>0.3172043</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
-        <v>0.41666666</v>
+        <v>0.41420117</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>7.4</v>
+        <v>6.9545455</v>
       </c>
       <c r="O3" t="n">
+        <v>28</v>
+      </c>
+      <c r="P3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>28</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.8863636</v>
+      </c>
+      <c r="S3" t="n">
         <v>29</v>
       </c>
-      <c r="P3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>29</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>30</v>
-      </c>
       <c r="T3" t="n">
-        <v>0.32417583</v>
+        <v>0.30113637</v>
       </c>
       <c r="U3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2581967</v>
+        <v>0.27419356</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>13</v>
@@ -2952,46 +2952,46 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.35106382</v>
+        <v>0.34892085</v>
       </c>
       <c r="I4" t="n">
         <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>0.46721312</v>
+        <v>0.4919355</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N4" t="n">
-        <v>5.203125</v>
+        <v>6.285714</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
+        <v>26</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.5714285</v>
+      </c>
+      <c r="S4" t="n">
         <v>24</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.390625</v>
-      </c>
-      <c r="S4" t="n">
-        <v>16</v>
-      </c>
       <c r="T4" t="n">
-        <v>0.264</v>
+        <v>0.2901961</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -3001,16 +3001,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.22981367</v>
+        <v>0.21518987</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -3019,46 +3019,46 @@
         <v>27</v>
       </c>
       <c r="H5" t="n">
-        <v>0.33333334</v>
+        <v>0.3262032</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.36024845</v>
+        <v>0.33544305</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6818182</v>
+        <v>2.8636363</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.1590909</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>0.21472393</v>
+        <v>0.2125</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.23699422</v>
+        <v>0.27118644</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>0.30927834</v>
+        <v>0.36407766</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3815029</v>
+        <v>0.45762712</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1777778</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.22155689</v>
+      </c>
+      <c r="U6" t="n">
         <v>7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>9</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4222223</v>
-      </c>
-      <c r="S6" t="n">
-        <v>17</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.2616279</v>
-      </c>
-      <c r="U6" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2848837</v>
+        <v>0.26900584</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
         <v>13</v>
       </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.37185928</v>
+        <v>0.3469388</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>0.55813956</v>
+        <v>0.46783626</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
         <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="O7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.4666667</v>
       </c>
       <c r="S7" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T7" t="n">
-        <v>0.30769232</v>
+        <v>0.28</v>
       </c>
       <c r="U7" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23333333</v>
+        <v>0.20689656</v>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" t="n">
         <v>28</v>
       </c>
-      <c r="E8" t="n">
-        <v>16</v>
-      </c>
       <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.26696834</v>
+      </c>
+      <c r="I8" t="n">
+        <v>27</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3596059</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24</v>
+      </c>
+      <c r="L8" t="n">
+        <v>44</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.9872613</v>
+      </c>
+      <c r="O8" t="n">
+        <v>19</v>
+      </c>
+      <c r="P8" t="n">
         <v>9</v>
       </c>
-      <c r="G8" t="n">
-        <v>14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.30172414</v>
-      </c>
-      <c r="I8" t="n">
-        <v>22</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.42380953</v>
-      </c>
-      <c r="K8" t="n">
-        <v>14</v>
-      </c>
-      <c r="L8" t="n">
-        <v>47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>10</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.1273885</v>
-      </c>
-      <c r="O8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P8" t="n">
-        <v>7</v>
-      </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4904459</v>
+        <v>1.6050956</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2512563</v>
+        <v>0.26130652</v>
       </c>
       <c r="U8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2284264</v>
+        <v>0.22222222</v>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2962963</v>
+        <v>0.29357797</v>
       </c>
       <c r="I9" t="n">
+        <v>23</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.34848484</v>
+      </c>
+      <c r="K9" t="n">
         <v>25</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.37055838</v>
-      </c>
-      <c r="K9" t="n">
-        <v>24</v>
-      </c>
       <c r="L9" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
-        <v>4.326923</v>
+        <v>3.7358491</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4230769</v>
+        <v>1.2830188</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24226804</v>
+        <v>0.21354167</v>
       </c>
       <c r="U9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -3336,13 +3336,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24752475</v>
+        <v>0.24</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
         <v>16</v>
@@ -3351,49 +3351,49 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3153153</v>
+        <v>0.3122172</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>0.41584158</v>
+        <v>0.41</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N10" t="n">
-        <v>4.090909</v>
+        <v>3.8333333</v>
       </c>
       <c r="O10" t="n">
+        <v>11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
         <v>9</v>
       </c>
-      <c r="P10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>1.3888888</v>
+      </c>
+      <c r="S10" t="n">
         <v>18</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.2363636</v>
-      </c>
-      <c r="S10" t="n">
-        <v>11</v>
-      </c>
       <c r="T10" t="n">
-        <v>0.23076923</v>
+        <v>0.24880382</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.29583332</v>
+        <v>0.30578512</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.38214287</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5289256</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>50</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.9170985</v>
+      </c>
+      <c r="O11" t="n">
         <v>12</v>
       </c>
-      <c r="G11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.38078293</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.5416666999999999</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>51</v>
-      </c>
-      <c r="M11" t="n">
-        <v>16</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.5958548</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>20</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.3834196</v>
+      </c>
+      <c r="S11" t="n">
+        <v>17</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="U11" t="n">
         <v>21</v>
-      </c>
-      <c r="P11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>22</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.5544041</v>
-      </c>
-      <c r="S11" t="n">
-        <v>24</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.3053435</v>
-      </c>
-      <c r="U11" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -3470,43 +3470,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23913044</v>
+        <v>0.23033708</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2914573</v>
+        <v>0.2994924</v>
       </c>
       <c r="I12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J12" t="n">
-        <v>0.45108697</v>
+        <v>0.38764045</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N12" t="n">
-        <v>3.326087</v>
+        <v>3.1304348</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
@@ -3518,16 +3518,16 @@
         <v>9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0217391</v>
+        <v>1.1086956</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.21637426</v>
+        <v>0.22988506</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -3537,16 +3537,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24365482</v>
+        <v>0.23589744</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
         <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
@@ -3555,46 +3555,46 @@
         <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>0.30875576</v>
+        <v>0.3153153</v>
       </c>
       <c r="I13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.42564103</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13</v>
+      </c>
+      <c r="L13" t="n">
+        <v>47</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.754717</v>
+      </c>
+      <c r="O13" t="n">
+        <v>18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>26</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3962264</v>
+      </c>
+      <c r="S13" t="n">
         <v>19</v>
       </c>
-      <c r="J13" t="n">
-        <v>0.43654823</v>
-      </c>
-      <c r="K13" t="n">
-        <v>11</v>
-      </c>
-      <c r="L13" t="n">
-        <v>48</v>
-      </c>
-      <c r="M13" t="n">
-        <v>13</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.924528</v>
-      </c>
-      <c r="O13" t="n">
-        <v>17</v>
-      </c>
-      <c r="P13" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>22</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.264151</v>
-      </c>
-      <c r="S13" t="n">
-        <v>13</v>
-      </c>
       <c r="T13" t="n">
-        <v>0.22727273</v>
+        <v>0.24752475</v>
       </c>
       <c r="U13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.25490198</v>
+        <v>0.30092594</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>0.29493088</v>
+        <v>0.36666667</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.43137255</v>
+        <v>0.4814815</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N14" t="n">
         <v>4.3333335</v>
       </c>
       <c r="O14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P14" t="n">
         <v>8</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5925926</v>
+        <v>1.5185186</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T14" t="n">
-        <v>0.28846154</v>
+        <v>0.2883721</v>
       </c>
       <c r="U14" t="n">
         <v>25</v>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.18518518</v>
+        <v>0.20245399</v>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
@@ -3686,49 +3686,49 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H15" t="n">
-        <v>0.22352941</v>
+        <v>0.23529412</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>0.25308642</v>
+        <v>0.2760736</v>
       </c>
       <c r="K15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L15" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N15" t="n">
         <v>5.4418607</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4418604</v>
+        <v>1.3720931</v>
       </c>
       <c r="S15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T15" t="n">
-        <v>0.25443786</v>
+        <v>0.24550898</v>
       </c>
       <c r="U15" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.27038628</v>
+        <v>0.24782608</v>
       </c>
       <c r="C16" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" t="n">
+        <v>33</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
         <v>6</v>
       </c>
-      <c r="D16" t="n">
-        <v>39</v>
-      </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" t="n">
-        <v>7</v>
-      </c>
       <c r="G16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H16" t="n">
-        <v>0.35793358</v>
+        <v>0.33962265</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42060086</v>
+        <v>0.37826088</v>
       </c>
       <c r="K16" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L16" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N16" t="n">
-        <v>4.359375</v>
+        <v>4.078125</v>
       </c>
       <c r="O16" t="n">
         <v>14</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>1.328125</v>
+        <v>1.375</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T16" t="n">
-        <v>0.24166666</v>
+        <v>0.24583334</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -3805,61 +3805,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.33482143</v>
+        <v>0.30373833</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>15</v>
+      </c>
+      <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
-        <v>16</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
       <c r="H17" t="n">
-        <v>0.41666666</v>
+        <v>0.39453125</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6339286</v>
+        <v>0.5794392</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7115383</v>
+        <v>5.943396</v>
       </c>
       <c r="O17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P17" t="n">
         <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3269231</v>
+        <v>1.3207548</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>0.25252524</v>
+        <v>0.26108375</v>
       </c>
       <c r="U17" t="n">
         <v>17</v>
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.26530612</v>
+        <v>0.2508834</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" t="n">
-        <v>0.32962963</v>
+        <v>0.3280757</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
-        <v>0.41632652</v>
+        <v>0.40282685</v>
       </c>
       <c r="K18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N18" t="n">
-        <v>2.390625</v>
+        <v>2.4657533</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
-        <v>1.109375</v>
+        <v>1.0136986</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21940929</v>
+        <v>0.20446096</v>
       </c>
       <c r="U18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24712643</v>
+        <v>0.26704547</v>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -3957,46 +3957,46 @@
         <v>8</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3316583</v>
+        <v>0.34653464</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4827586</v>
+        <v>0.5113636</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5581396</v>
+        <v>2.4545455</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
         <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1860465</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0.21518987</v>
+        <v>0.18589744</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.25821596</v>
+        <v>0.27853882</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>0.32627118</v>
+        <v>0.34836066</v>
       </c>
       <c r="I20" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4460094</v>
+        <v>0.46575344</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9.519231</v>
+      </c>
+      <c r="O20" t="n">
+        <v>30</v>
+      </c>
+      <c r="P20" t="n">
         <v>16</v>
       </c>
-      <c r="N20" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="O20" t="n">
-        <v>27</v>
-      </c>
-      <c r="P20" t="n">
-        <v>14</v>
-      </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5961539</v>
+        <v>2.0192308</v>
       </c>
       <c r="S20" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>0.28372094</v>
+        <v>0.32743362</v>
       </c>
       <c r="U20" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.16931216</v>
+        <v>0.20103092</v>
       </c>
       <c r="C21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H21" t="n">
-        <v>0.23671497</v>
+        <v>0.25592417</v>
       </c>
       <c r="I21" t="n">
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>0.33862433</v>
+        <v>0.371134</v>
       </c>
       <c r="K21" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L21" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N21" t="n">
-        <v>4.178571</v>
+        <v>3.9272728</v>
       </c>
       <c r="O21" t="n">
+        <v>13</v>
+      </c>
+      <c r="P21" t="n">
         <v>11</v>
       </c>
-      <c r="P21" t="n">
-        <v>13</v>
-      </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1785715</v>
+        <v>1.1818181</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>0.23255815</v>
+        <v>0.22488038</v>
       </c>
       <c r="U21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.26213592</v>
+        <v>0.24390244</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
         <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H22" t="n">
-        <v>0.33766234</v>
+        <v>0.31441048</v>
       </c>
       <c r="I22" t="n">
+        <v>18</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>17</v>
+      </c>
+      <c r="L22" t="n">
+        <v>60</v>
+      </c>
+      <c r="M22" t="n">
+        <v>26</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.8846154</v>
+      </c>
+      <c r="O22" t="n">
+        <v>23</v>
+      </c>
+      <c r="P22" t="n">
         <v>8</v>
       </c>
-      <c r="J22" t="n">
-        <v>0.4223301</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="Q22" t="n">
         <v>15</v>
-      </c>
-      <c r="L22" t="n">
-        <v>59</v>
-      </c>
-      <c r="M22" t="n">
-        <v>25</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5.7115383</v>
-      </c>
-      <c r="O22" t="n">
-        <v>22</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>9</v>
       </c>
       <c r="R22" t="n">
         <v>1.6346154</v>
       </c>
       <c r="S22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T22" t="n">
         <v>0.30555555</v>
       </c>
       <c r="U22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.30357143</v>
+        <v>0.33624455</v>
       </c>
       <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>47</v>
+      </c>
+      <c r="E23" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="n">
-        <v>35</v>
-      </c>
-      <c r="E23" t="n">
-        <v>8</v>
-      </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H23" t="n">
-        <v>0.37698412</v>
+        <v>0.41603053</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4419643</v>
+        <v>0.5065502</v>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="M23" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8235292</v>
+        <v>5.019231</v>
       </c>
       <c r="O23" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5294118</v>
+        <v>1.4423077</v>
       </c>
       <c r="S23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="T23" t="n">
-        <v>0.27227724</v>
+        <v>0.26600984</v>
       </c>
       <c r="U23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.25306123</v>
+        <v>0.23404256</v>
       </c>
       <c r="C24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
+        <v>23</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" t="n">
+        <v>17</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.30501932</v>
+      </c>
+      <c r="I24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.38297874</v>
+      </c>
+      <c r="K24" t="n">
         <v>21</v>
       </c>
-      <c r="F24" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" t="n">
-        <v>8</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.3197026</v>
-      </c>
-      <c r="I24" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.43265307</v>
-      </c>
-      <c r="K24" t="n">
-        <v>12</v>
-      </c>
       <c r="L24" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>7.6271186</v>
       </c>
       <c r="O24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P24" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8275862</v>
+        <v>1.6101695</v>
       </c>
       <c r="S24" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3</v>
+        <v>0.2735043</v>
       </c>
       <c r="U24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.26190478</v>
+        <v>0.27906978</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3231441</v>
+        <v>0.33189654</v>
       </c>
       <c r="I25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
-        <v>0.50476193</v>
+        <v>0.48372093</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L25" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N25" t="n">
-        <v>6.7058825</v>
+        <v>6.75</v>
       </c>
       <c r="O25" t="n">
         <v>26</v>
       </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5098039</v>
+        <v>1.4423077</v>
       </c>
       <c r="S25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T25" t="n">
-        <v>0.27450982</v>
+        <v>0.28502417</v>
       </c>
       <c r="U25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -4408,61 +4408,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22929937</v>
+        <v>0.19745223</v>
       </c>
       <c r="C26" t="n">
+        <v>30</v>
+      </c>
+      <c r="D26" t="n">
+        <v>21</v>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
         <v>26</v>
       </c>
-      <c r="D26" t="n">
+      <c r="H26" t="n">
+        <v>0.28089887</v>
+      </c>
+      <c r="I26" t="n">
         <v>24</v>
-      </c>
-      <c r="E26" t="n">
-        <v>23</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4</v>
-      </c>
-      <c r="G26" t="n">
-        <v>27</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.30285713</v>
-      </c>
-      <c r="I26" t="n">
-        <v>21</v>
       </c>
       <c r="J26" t="n">
         <v>0.34394905</v>
       </c>
       <c r="K26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L26" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>1.1911764</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0.62222224</v>
+        <v>0.75</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.12903225</v>
+        <v>0.1572327</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.25726143</v>
+        <v>0.2389706</v>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
         <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
+        <v>11</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.30333334</v>
+      </c>
+      <c r="I27" t="n">
+        <v>21</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3970588</v>
+      </c>
+      <c r="K27" t="n">
+        <v>19</v>
+      </c>
+      <c r="L27" t="n">
+        <v>64</v>
+      </c>
+      <c r="M27" t="n">
+        <v>28</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O27" t="n">
+        <v>8</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.2714286</v>
+      </c>
+      <c r="S27" t="n">
+        <v>11</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.22932331</v>
+      </c>
+      <c r="U27" t="n">
         <v>10</v>
-      </c>
-      <c r="G27" t="n">
-        <v>8</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.32841328</v>
-      </c>
-      <c r="I27" t="n">
-        <v>12</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.41908714</v>
-      </c>
-      <c r="K27" t="n">
-        <v>17</v>
-      </c>
-      <c r="L27" t="n">
-        <v>52</v>
-      </c>
-      <c r="M27" t="n">
-        <v>20</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.5081968</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.1639345</v>
-      </c>
-      <c r="S27" t="n">
-        <v>7</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.20982143</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.23809524</v>
+        <v>0.22510822</v>
       </c>
       <c r="C28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D28" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16</v>
+      </c>
+      <c r="F28" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I28" t="n">
+        <v>25</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.3982684</v>
+      </c>
+      <c r="K28" t="n">
+        <v>18</v>
+      </c>
+      <c r="L28" t="n">
+        <v>55</v>
+      </c>
+      <c r="M28" t="n">
         <v>20</v>
-      </c>
-      <c r="D28" t="n">
-        <v>31</v>
-      </c>
-      <c r="E28" t="n">
-        <v>11</v>
-      </c>
-      <c r="F28" t="n">
-        <v>10</v>
-      </c>
-      <c r="G28" t="n">
-        <v>8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.31660232</v>
-      </c>
-      <c r="I28" t="n">
-        <v>16</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.3939394</v>
-      </c>
-      <c r="K28" t="n">
-        <v>22</v>
-      </c>
-      <c r="L28" t="n">
-        <v>51</v>
-      </c>
-      <c r="M28" t="n">
-        <v>16</v>
       </c>
       <c r="N28" t="n">
         <v>3.5409837</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8196721</v>
+        <v>0.8852459</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>0.18181819</v>
+        <v>0.20089285</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2366864</v>
+        <v>0.2647059</v>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2972973</v>
+        <v>0.33333334</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>0.41420117</v>
+        <v>0.44117647</v>
       </c>
       <c r="K29" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="L29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>4.5</v>
+        <v>4.7045455</v>
       </c>
       <c r="O29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2045455</v>
+        <v>1.3409091</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24571429</v>
+        <v>0.26553673</v>
       </c>
       <c r="U29" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.16489361</v>
+        <v>0.19791667</v>
       </c>
       <c r="C30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>27</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.24757281</v>
+      </c>
+      <c r="I30" t="n">
         <v>29</v>
       </c>
-      <c r="F30" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="J30" t="n">
+        <v>0.29166666</v>
+      </c>
+      <c r="K30" t="n">
         <v>29</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.21890548</v>
-      </c>
-      <c r="I30" t="n">
-        <v>30</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.24468085</v>
-      </c>
-      <c r="K30" t="n">
-        <v>30</v>
-      </c>
       <c r="L30" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4117646</v>
+        <v>4.5882354</v>
       </c>
       <c r="O30" t="n">
+        <v>16</v>
+      </c>
+      <c r="P30" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q30" t="n">
         <v>15</v>
       </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>19</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.1568627</v>
+        <v>1.137255</v>
       </c>
       <c r="S30" t="n">
         <v>6</v>
       </c>
       <c r="T30" t="n">
-        <v>0.21578947</v>
+        <v>0.22395833</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.31428573</v>
+        <v>0.30952382</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.39917696</v>
+        <v>0.3909465</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8333335</v>
+        <v>6.8333335</v>
       </c>
       <c r="O31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.6666666</v>
       </c>
       <c r="S31" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>0.28440368</v>
+        <v>0.29493088</v>
       </c>
       <c r="U31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23642384</v>
+        <v>0.23698854</v>
       </c>
       <c r="C2" t="n">
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" t="n">
         <v>29</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30684525</v>
+        <v>0.30703562</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38278145</v>
+        <v>0.38330606</v>
       </c>
       <c r="K2" t="n">
         <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2383723</v>
+        <v>4.296464</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q2" t="n">
         <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2832226</v>
+        <v>1.2890625</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2509804</v>
+        <v>0.25217953</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24758531</v>
+        <v>0.24705508</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>115</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32578796</v>
+        <v>0.32492203</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40856406</v>
+        <v>0.4068768</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1143913</v>
+        <v>5.1303287</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4710947</v>
+        <v>1.4725944</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26662445</v>
+        <v>0.26622766</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,43 +680,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24910219</v>
+        <v>0.24814217</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31410068</v>
+        <v>0.31262758</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41332027</v>
+        <v>0.41227788</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6510851</v>
+        <v>3.6104004</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -725,16 +725,16 @@
         <v>101</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.239566</v>
+        <v>1.233182</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2311305</v>
+        <v>0.23007968</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23727155</v>
+        <v>0.23887815</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.31927025</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.39684075</v>
+      </c>
+      <c r="K5" t="n">
         <v>17</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.3183391</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.39262402</v>
-      </c>
-      <c r="K5" t="n">
-        <v>21</v>
-      </c>
       <c r="L5" t="n">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.347364</v>
+        <v>4.3981404</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3718839</v>
+        <v>1.3714632</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25358853</v>
+        <v>0.25339225</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24438484</v>
+        <v>0.24486415</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E6" t="n">
         <v>28</v>
@@ -832,25 +832,25 @@
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31355423</v>
+        <v>0.31428573</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3881998</v>
+        <v>0.38800532</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="M6" t="n">
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7426875</v>
+        <v>3.7003353</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -859,19 +859,19 @@
         <v>94</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2424756</v>
+        <v>1.2347025</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>0.24041694</v>
+        <v>0.23934753</v>
       </c>
       <c r="U6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24436574</v>
+        <v>0.24426752</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33807135</v>
+        <v>0.33774468</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40856406</v>
+        <v>0.41146496</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="M7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3315506</v>
+        <v>4.3608623</v>
       </c>
       <c r="O7" t="n">
         <v>19</v>
       </c>
       <c r="P7" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2661457</v>
+        <v>1.2717657</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24361493</v>
+        <v>0.24514878</v>
       </c>
       <c r="U7" t="n">
         <v>18</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24053156</v>
+        <v>0.23947369</v>
       </c>
       <c r="C8" t="n">
         <v>19</v>
@@ -966,28 +966,28 @@
         <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31997642</v>
+        <v>0.31854016</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41362128</v>
+        <v>0.41085526</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="M8" t="n">
         <v>23</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2572145</v>
+        <v>4.2543426</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P8" t="n">
         <v>98</v>
@@ -996,13 +996,13 @@
         <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3425345</v>
+        <v>1.3436725</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24088323</v>
+        <v>0.24140212</v>
       </c>
       <c r="U8" t="n">
         <v>16</v>
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22709164</v>
+        <v>0.2280932</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30816868</v>
+        <v>0.30964172</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3864542</v>
+        <v>0.39218903</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="M9" t="n">
         <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5617976</v>
+        <v>4.5666666</v>
       </c>
       <c r="O9" t="n">
         <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q9" t="n">
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.451935</v>
+        <v>1.4555556</v>
       </c>
       <c r="S9" t="n">
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2487709</v>
+        <v>0.24878365</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1082,43 +1082,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22865652</v>
+        <v>0.22865555</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E10" t="n">
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31026393</v>
+        <v>0.3106346</v>
       </c>
       <c r="I10" t="n">
         <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3663137</v>
+        <v>0.36669937</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>762</v>
+        <v>775</v>
       </c>
       <c r="M10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7702703</v>
+        <v>3.7961912</v>
       </c>
       <c r="O10" t="n">
         <v>9</v>
@@ -1130,16 +1130,16 @@
         <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2653563</v>
+        <v>1.2751216</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23831317</v>
+        <v>0.2391726</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1149,43 +1149,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25821745</v>
+        <v>0.2571965</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32919255</v>
+        <v>0.32792842</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42414665</v>
+        <v>0.42396745</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>812</v>
+        <v>822</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.49227</v>
+        <v>5.482675</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
@@ -1197,13 +1197,13 @@
         <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.514646</v>
+        <v>1.5108783</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28715906</v>
+        <v>0.28658167</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,43 +1216,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23601054</v>
+        <v>0.23590747</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3145418</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.39784947</v>
+      </c>
+      <c r="K12" t="n">
         <v>15</v>
       </c>
-      <c r="H12" t="n">
-        <v>0.31414378</v>
-      </c>
-      <c r="I12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.39763</v>
-      </c>
-      <c r="K12" t="n">
-        <v>16</v>
-      </c>
       <c r="L12" t="n">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7272348</v>
+        <v>3.6858552</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1261,16 +1261,16 @@
         <v>94</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.224948</v>
+        <v>1.2224506</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23550844</v>
+        <v>0.2351015</v>
       </c>
       <c r="U12" t="n">
         <v>7</v>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24176173</v>
+        <v>0.2413793</v>
       </c>
       <c r="C13" t="n">
         <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
@@ -1301,43 +1301,43 @@
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3161619</v>
+        <v>0.31511074</v>
       </c>
       <c r="I13" t="n">
         <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41159695</v>
+        <v>0.41034484</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L13" t="n">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="M13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7360835</v>
+        <v>4.7766757</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3912696</v>
+        <v>1.4006346</v>
       </c>
       <c r="S13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24135724</v>
+        <v>0.24183835</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24790187</v>
+        <v>0.24768592</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E14" t="n">
         <v>19</v>
@@ -1365,46 +1365,46 @@
         <v>93</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31882387</v>
+        <v>0.31850585</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3983215</v>
+        <v>0.3977019</v>
       </c>
       <c r="K14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" t="n">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="M14" t="n">
         <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8396225</v>
+        <v>4.8582454</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4433962</v>
+        <v>1.446385</v>
       </c>
       <c r="S14" t="n">
         <v>27</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2629891</v>
+        <v>0.2630911</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23738681</v>
+        <v>0.23914431</v>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G15" t="n">
         <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31338537</v>
+        <v>0.3145875</v>
       </c>
       <c r="I15" t="n">
+        <v>18</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3933589</v>
+      </c>
+      <c r="K15" t="n">
         <v>21</v>
       </c>
-      <c r="J15" t="n">
-        <v>0.389392</v>
-      </c>
-      <c r="K15" t="n">
-        <v>22</v>
-      </c>
       <c r="L15" t="n">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.673931</v>
+        <v>4.6335907</v>
       </c>
       <c r="O15" t="n">
         <v>24</v>
       </c>
       <c r="P15" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4037828</v>
+        <v>1.3981293</v>
       </c>
       <c r="S15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2382037</v>
+        <v>0.2369439</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2643495</v>
+        <v>0.26397222</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -1502,43 +1502,43 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34690464</v>
+        <v>0.34622824</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.43845662</v>
+        <v>0.43700662</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4803405</v>
+        <v>3.4751403</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1357925</v>
+        <v>1.1319166</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21640316</v>
+        <v>0.21577574</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,46 +1551,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2542428</v>
+        <v>0.2543633</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3313149</v>
+        <v>0.33076045</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.41090077</v>
+        <v>0.41208792</v>
       </c>
       <c r="K17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="M17" t="n">
         <v>11</v>
       </c>
       <c r="N17" t="n">
-        <v>4.093943</v>
+        <v>4.0488997</v>
       </c>
       <c r="O17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
         <v>90</v>
@@ -1599,13 +1599,13 @@
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2459826</v>
+        <v>1.2408313</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22955145</v>
+        <v>0.22886059</v>
       </c>
       <c r="U17" t="n">
         <v>4</v>
@@ -1618,16 +1618,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25459826</v>
+        <v>0.25455126</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
         <v>84</v>
@@ -1636,43 +1636,43 @@
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33740762</v>
+        <v>0.3368984</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3975476</v>
+        <v>0.3966784</v>
       </c>
       <c r="K18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="M18" t="n">
         <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3020792</v>
+        <v>3.3245862</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1642886</v>
+        <v>1.1614857</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21737683</v>
+        <v>0.2173913</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,16 +1685,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24767405</v>
+        <v>0.24841371</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>117</v>
@@ -1703,46 +1703,46 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32218412</v>
+        <v>0.32354602</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.41642606</v>
+        <v>0.4159264</v>
       </c>
       <c r="K19" t="n">
         <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="M19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7366476</v>
+        <v>4.67371</v>
       </c>
       <c r="O19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3767462</v>
+        <v>1.3774889</v>
       </c>
       <c r="S19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25224358</v>
+        <v>0.251664</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23345172</v>
+        <v>0.23386581</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20" t="n">
         <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30195278</v>
+        <v>0.30288184</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.38101387</v>
+        <v>0.38115016</v>
       </c>
       <c r="K20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L20" t="n">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="M20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4030094</v>
+        <v>4.3769107</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
         <v>101</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3200488</v>
+        <v>1.3189863</v>
       </c>
       <c r="S20" t="n">
         <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23929712</v>
+        <v>0.23917851</v>
       </c>
       <c r="U20" t="n">
         <v>13</v>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23421927</v>
+        <v>0.23372781</v>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
         <v>436</v>
@@ -1837,25 +1837,25 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31589773</v>
+        <v>0.3147016</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4192691</v>
+        <v>0.41683105</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3986793</v>
+        <v>3.398447</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
@@ -1867,13 +1867,13 @@
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1923236</v>
+        <v>1.1916633</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22758849</v>
+        <v>0.22789784</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23766527</v>
+        <v>0.23779126</v>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3038159</v>
+        <v>0.30483592</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40309578</v>
+        <v>0.40440473</v>
       </c>
       <c r="K22" t="n">
         <v>14</v>
       </c>
       <c r="L22" t="n">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="M22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N22" t="n">
-        <v>4.211515</v>
+        <v>4.29074</v>
       </c>
       <c r="O22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P22" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.320539</v>
+        <v>1.3295593</v>
       </c>
       <c r="S22" t="n">
         <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2573321</v>
+        <v>0.25795382</v>
       </c>
       <c r="U22" t="n">
         <v>26</v>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.26323986</v>
+        <v>0.2619562</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
@@ -1971,46 +1971,46 @@
         <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>0.34178612</v>
+        <v>0.34052432</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.42429906</v>
+        <v>0.42147484</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="M23" t="n">
         <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2718053</v>
+        <v>4.2580256</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q23" t="n">
         <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3131845</v>
+        <v>1.3049759</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23919308</v>
+        <v>0.23835182</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22423632</v>
+        <v>0.22579576</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.29957932</v>
+        <v>0.30097952</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37059417</v>
+        <v>0.37267905</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="M24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N24" t="n">
-        <v>4.210701</v>
+        <v>4.2083673</v>
       </c>
       <c r="O24" t="n">
         <v>14</v>
       </c>
       <c r="P24" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3376192</v>
+        <v>1.3375717</v>
       </c>
       <c r="S24" t="n">
         <v>18</v>
       </c>
       <c r="T24" t="n">
-        <v>0.246779</v>
+        <v>0.24722403</v>
       </c>
       <c r="U24" t="n">
         <v>19</v>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25616395</v>
+        <v>0.25420502</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>377</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
         <v>101</v>
@@ -2105,43 +2105,43 @@
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30841672</v>
+        <v>0.30679497</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4217099</v>
+        <v>0.41827992</v>
       </c>
       <c r="K25" t="n">
         <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5243244</v>
+        <v>4.562911</v>
       </c>
       <c r="O25" t="n">
         <v>22</v>
       </c>
       <c r="P25" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3746362</v>
+        <v>1.3778783</v>
       </c>
       <c r="S25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25032896</v>
+        <v>0.25064936</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23119868</v>
+        <v>0.23049414</v>
       </c>
       <c r="C26" t="n">
         <v>27</v>
@@ -2163,55 +2163,55 @@
         <v>377</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
         <v>110</v>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31168073</v>
+        <v>0.31093165</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3816092</v>
+        <v>0.3793888</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="M26" t="n">
         <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5500205</v>
+        <v>3.537404</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1649653</v>
+        <v>1.1633644</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23678161</v>
+        <v>0.23707317</v>
       </c>
       <c r="U26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -2221,43 +2221,43 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24503969</v>
+        <v>0.2447644</v>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G27" t="n">
         <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>0.32160658</v>
+        <v>0.3206506</v>
       </c>
       <c r="I27" t="n">
         <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39318782</v>
+        <v>0.39430627</v>
       </c>
       <c r="K27" t="n">
         <v>20</v>
       </c>
       <c r="L27" t="n">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1883035</v>
+        <v>4.152994</v>
       </c>
       <c r="O27" t="n">
         <v>13</v>
@@ -2269,13 +2269,13 @@
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3401078</v>
+        <v>1.3375717</v>
       </c>
       <c r="S27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25253186</v>
+        <v>0.25250566</v>
       </c>
       <c r="U27" t="n">
         <v>24</v>
@@ -2288,16 +2288,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2574224</v>
+        <v>0.25742903</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
         <v>87</v>
@@ -2306,25 +2306,25 @@
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33443016</v>
+        <v>0.33382702</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.395749</v>
+        <v>0.39499167</v>
       </c>
       <c r="K28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L28" t="n">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7632241</v>
+        <v>3.721046</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
@@ -2333,16 +2333,16 @@
         <v>112</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1712847</v>
+        <v>1.1656289</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23190348</v>
+        <v>0.23143236</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2355,64 +2355,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24448831</v>
+        <v>0.24315515</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
         <v>21</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31942403</v>
+        <v>0.3185918</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3942086</v>
+        <v>0.39243808</v>
       </c>
       <c r="K29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>754</v>
+        <v>768</v>
       </c>
       <c r="M29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9682672</v>
+        <v>4.068951</v>
       </c>
       <c r="O29" t="n">
+        <v>11</v>
+      </c>
+      <c r="P29" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>20</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.244839</v>
+      </c>
+      <c r="S29" t="n">
         <v>10</v>
       </c>
-      <c r="P29" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>21</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.2375783</v>
-      </c>
-      <c r="S29" t="n">
-        <v>7</v>
-      </c>
       <c r="T29" t="n">
-        <v>0.23853211</v>
+        <v>0.24029754</v>
       </c>
       <c r="U29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -2422,43 +2422,43 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24350649</v>
+        <v>0.24391025</v>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3049499</v>
+        <v>0.30541012</v>
       </c>
       <c r="I30" t="n">
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3814935</v>
+        <v>0.38301283</v>
       </c>
       <c r="K30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1266856</v>
+        <v>4.0816493</v>
       </c>
       <c r="O30" t="n">
         <v>12</v>
@@ -2467,19 +2467,19 @@
         <v>104</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3044544</v>
+        <v>1.2950687</v>
       </c>
       <c r="S30" t="n">
         <v>14</v>
       </c>
       <c r="T30" t="n">
-        <v>0.24041586</v>
+        <v>0.23857051</v>
       </c>
       <c r="U30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.25046962</v>
+        <v>0.2508527</v>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32408965</v>
+        <v>0.32549128</v>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.43362555</v>
+        <v>0.43472868</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="M31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7983227</v>
+        <v>4.7578034</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
         <v>130</v>
       </c>
       <c r="Q31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.398163</v>
+        <v>1.3927301</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25889266</v>
+        <v>0.25864708</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.21078432</v>
+        <v>0.22439024</v>
       </c>
       <c r="C2" t="n">
         <v>25</v>
@@ -2809,55 +2809,55 @@
         <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.28699553</v>
+      </c>
+      <c r="I2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.34634146</v>
+      </c>
+      <c r="K2" t="n">
+        <v>26</v>
+      </c>
+      <c r="L2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N2" t="n">
         <v>4</v>
       </c>
-      <c r="G2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.27149323</v>
-      </c>
-      <c r="I2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.3137255</v>
-      </c>
-      <c r="K2" t="n">
-        <v>28</v>
-      </c>
-      <c r="L2" t="n">
-        <v>49</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>12</v>
       </c>
-      <c r="N2" t="n">
-        <v>3.4363637</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>6</v>
       </c>
-      <c r="P2" t="n">
-        <v>7</v>
-      </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2181818</v>
+        <v>1.2962962</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T2" t="n">
-        <v>0.26046512</v>
+        <v>0.27102804</v>
       </c>
       <c r="U2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -2867,64 +2867,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.25443786</v>
+        <v>0.22485207</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3172043</v>
+        <v>0.29032257</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>0.41420117</v>
+        <v>0.33136094</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>6.9545455</v>
+        <v>8.162789999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8863636</v>
+        <v>1.9767442</v>
       </c>
       <c r="S3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.30113637</v>
+        <v>0.3125</v>
       </c>
       <c r="U3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.27419356</v>
+        <v>0.268</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>13</v>
@@ -2952,43 +2952,43 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.34892085</v>
+        <v>0.33333334</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4919355</v>
+        <v>0.488</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="M4" t="n">
+        <v>27</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6.142857</v>
+      </c>
+      <c r="O4" t="n">
         <v>24</v>
-      </c>
-      <c r="N4" t="n">
-        <v>6.285714</v>
-      </c>
-      <c r="O4" t="n">
-        <v>25</v>
       </c>
       <c r="P4" t="n">
         <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5714285</v>
+        <v>1.6190476</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2901961</v>
+        <v>0.29571983</v>
       </c>
       <c r="U4" t="n">
         <v>26</v>
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21518987</v>
+        <v>0.24550898</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.33157894</v>
+      </c>
+      <c r="I5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.39520958</v>
+      </c>
+      <c r="K5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39</v>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>27</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3262032</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.33544305</v>
-      </c>
-      <c r="K5" t="n">
-        <v>27</v>
-      </c>
-      <c r="L5" t="n">
-        <v>47</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.3181819</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.23170732</v>
+      </c>
+      <c r="U5" t="n">
         <v>10</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.8636363</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.1590909</v>
-      </c>
-      <c r="S5" t="n">
-        <v>7</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.2125</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3068,64 +3068,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.27118644</v>
+        <v>0.27683616</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>0.36407766</v>
+        <v>0.36893204</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.45762712</v>
+        <v>0.46892655</v>
       </c>
       <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>46</v>
+      </c>
+      <c r="M6" t="n">
         <v>11</v>
       </c>
-      <c r="L6" t="n">
-        <v>45</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7</v>
-      </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1777778</v>
+        <v>0.7777778</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.22155689</v>
+        <v>0.17610063</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.26900584</v>
+        <v>0.22699386</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3469388</v>
+        <v>0.30107528</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
-        <v>0.46783626</v>
+        <v>0.36809817</v>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M7" t="n">
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="O7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4666667</v>
+        <v>1.5111111</v>
       </c>
       <c r="S7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T7" t="n">
-        <v>0.28</v>
+        <v>0.2937853</v>
       </c>
       <c r="U7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -3205,61 +3205,61 @@
         <v>0.20689656</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>27</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
         <v>20</v>
-      </c>
-      <c r="E8" t="n">
-        <v>28</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>17</v>
       </c>
       <c r="H8" t="n">
         <v>0.26696834</v>
       </c>
       <c r="I8" t="n">
+        <v>28</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.33990148</v>
+      </c>
+      <c r="K8" t="n">
         <v>27</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.3596059</v>
-      </c>
-      <c r="K8" t="n">
-        <v>24</v>
       </c>
       <c r="L8" t="n">
         <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>4.9872613</v>
+        <v>4.725</v>
       </c>
       <c r="O8" t="n">
+        <v>18</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5562501</v>
+      </c>
+      <c r="S8" t="n">
+        <v>23</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.2682927</v>
+      </c>
+      <c r="U8" t="n">
         <v>19</v>
-      </c>
-      <c r="P8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>20</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.6050956</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.26130652</v>
-      </c>
-      <c r="U8" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22222222</v>
+        <v>0.235</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.29357797</v>
+        <v>0.32300884</v>
       </c>
       <c r="I9" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>0.34848484</v>
+        <v>0.435</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7358491</v>
+        <v>3.8333333</v>
       </c>
       <c r="O9" t="n">
         <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2830188</v>
+        <v>1.2777778</v>
       </c>
       <c r="S9" t="n">
         <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>0.21354167</v>
+        <v>0.21243523</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24</v>
+        <v>0.225</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3122172</v>
+        <v>0.31111112</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>0.41</v>
+        <v>0.375</v>
       </c>
       <c r="K10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" t="n">
+        <v>66</v>
+      </c>
+      <c r="M10" t="n">
+        <v>29</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1925464</v>
+      </c>
+      <c r="O10" t="n">
         <v>15</v>
       </c>
-      <c r="L10" t="n">
-        <v>61</v>
-      </c>
-      <c r="M10" t="n">
-        <v>27</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.8333333</v>
-      </c>
-      <c r="O10" t="n">
-        <v>11</v>
-      </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3888888</v>
+        <v>1.4906832</v>
       </c>
       <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.2606635</v>
+      </c>
+      <c r="U10" t="n">
         <v>18</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.24880382</v>
-      </c>
-      <c r="U10" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.30578512</v>
+        <v>0.29752067</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.38214287</v>
+        <v>0.37809187</v>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5289256</v>
+        <v>0.5041322</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9170985</v>
+        <v>4.1210527</v>
       </c>
       <c r="O11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
+        <v>17</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4052632</v>
+      </c>
+      <c r="S11" t="n">
+        <v>19</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.2701613</v>
+      </c>
+      <c r="U11" t="n">
         <v>20</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3834196</v>
-      </c>
-      <c r="S11" t="n">
-        <v>17</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="U11" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23033708</v>
+        <v>0.24561404</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>25</v>
@@ -3482,49 +3482,49 @@
         <v>18</v>
       </c>
       <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.32460734</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.42105263</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L12" t="n">
+        <v>49</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.8636363</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="G12" t="n">
-        <v>21</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.2994924</v>
-      </c>
-      <c r="I12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.38764045</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L12" t="n">
-        <v>51</v>
-      </c>
-      <c r="M12" t="n">
-        <v>18</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.1304348</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
+        <v>1.1590909</v>
+      </c>
+      <c r="S12" t="n">
         <v>7</v>
       </c>
-      <c r="Q12" t="n">
-        <v>9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.1086956</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
       <c r="T12" t="n">
-        <v>0.22988506</v>
+        <v>0.23255815</v>
       </c>
       <c r="U12" t="n">
         <v>11</v>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.23589744</v>
+        <v>0.2371134</v>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -3552,49 +3552,49 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3153153</v>
+        <v>0.30092594</v>
       </c>
       <c r="I13" t="n">
+        <v>22</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.43814433</v>
+      </c>
+      <c r="K13" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>44</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.8461537</v>
+      </c>
+      <c r="O13" t="n">
+        <v>21</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>25</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5192307</v>
+      </c>
+      <c r="S13" t="n">
+        <v>22</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.2562814</v>
+      </c>
+      <c r="U13" t="n">
         <v>17</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.42564103</v>
-      </c>
-      <c r="K13" t="n">
-        <v>13</v>
-      </c>
-      <c r="L13" t="n">
-        <v>47</v>
-      </c>
-      <c r="M13" t="n">
-        <v>10</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.754717</v>
-      </c>
-      <c r="O13" t="n">
-        <v>18</v>
-      </c>
-      <c r="P13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>26</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3962264</v>
-      </c>
-      <c r="S13" t="n">
-        <v>19</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.24752475</v>
-      </c>
-      <c r="U13" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.30092594</v>
+        <v>0.30593607</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36666667</v>
+        <v>0.37551022</v>
       </c>
       <c r="I14" t="n">
         <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4814815</v>
+        <v>0.5022831</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>56</v>
       </c>
       <c r="M14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3333335</v>
+        <v>4.754717</v>
       </c>
       <c r="O14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5185186</v>
+        <v>1.6037736</v>
       </c>
       <c r="S14" t="n">
+        <v>26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.28301886</v>
+      </c>
+      <c r="U14" t="n">
         <v>23</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2883721</v>
-      </c>
-      <c r="U14" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.20245399</v>
+        <v>0.2364532</v>
       </c>
       <c r="C15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.27102804</v>
+      </c>
+      <c r="I15" t="n">
         <v>27</v>
       </c>
-      <c r="D15" t="n">
-        <v>11</v>
-      </c>
-      <c r="E15" t="n">
-        <v>30</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.23529412</v>
-      </c>
-      <c r="I15" t="n">
-        <v>30</v>
-      </c>
       <c r="J15" t="n">
-        <v>0.2760736</v>
+        <v>0.3596059</v>
       </c>
       <c r="K15" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4418607</v>
+        <v>4.673077</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
+        <v>17</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2884616</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.2244898</v>
+      </c>
+      <c r="U15" t="n">
         <v>9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3720931</v>
-      </c>
-      <c r="S15" t="n">
-        <v>15</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.24550898</v>
-      </c>
-      <c r="U15" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.24782608</v>
+        <v>0.25652173</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
+        <v>25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.33716476</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.37391305</v>
+      </c>
+      <c r="K16" t="n">
         <v>21</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.33962265</v>
-      </c>
-      <c r="I16" t="n">
-        <v>11</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.37826088</v>
-      </c>
-      <c r="K16" t="n">
-        <v>22</v>
-      </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M16" t="n">
         <v>12</v>
       </c>
       <c r="N16" t="n">
-        <v>4.078125</v>
+        <v>3.4615386</v>
       </c>
       <c r="O16" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R16" t="n">
-        <v>1.375</v>
+        <v>1.2461538</v>
       </c>
       <c r="S16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>0.24583334</v>
+        <v>0.21940929</v>
       </c>
       <c r="U16" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.30373833</v>
+        <v>0.3127962</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.39453125</v>
+        <v>0.3984064</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5794392</v>
+        <v>0.60189575</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M17" t="n">
         <v>7</v>
       </c>
       <c r="N17" t="n">
-        <v>5.943396</v>
+        <v>5.5</v>
       </c>
       <c r="O17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3207548</v>
+        <v>1.2962962</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T17" t="n">
-        <v>0.26108375</v>
+        <v>0.25247526</v>
       </c>
       <c r="U17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2508834</v>
+        <v>0.25</v>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3280757</v>
+        <v>0.31410256</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40282685</v>
+        <v>0.38732395</v>
       </c>
       <c r="K18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="N18" t="n">
-        <v>2.4657533</v>
+        <v>2.875</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0136986</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.20446096</v>
+        <v>0.20149253</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.26704547</v>
+        <v>0.28248587</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
         <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.36097562</v>
+      </c>
+      <c r="I19" t="n">
         <v>8</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.34653464</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10</v>
-      </c>
       <c r="J19" t="n">
-        <v>0.5113636</v>
+        <v>0.48022598</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M19" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.4545455</v>
+        <v>3.2727273</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>11</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.0454545</v>
+      </c>
+      <c r="S19" t="n">
         <v>5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
       </c>
       <c r="T19" t="n">
         <v>0.18589744</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.27853882</v>
+        <v>0.29411766</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.34836066</v>
+        <v>0.372</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.46575344</v>
+        <v>0.46606335</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M20" t="n">
         <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>9.519231</v>
+        <v>8.150944000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0192308</v>
+        <v>1.8679246</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>0.32743362</v>
+        <v>0.30701753</v>
       </c>
       <c r="U20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.20103092</v>
+        <v>0.2010582</v>
       </c>
       <c r="C21" t="n">
         <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>0.25592417</v>
+        <v>0.25</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>0.371134</v>
+        <v>0.35449734</v>
       </c>
       <c r="K21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L21" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M21" t="n">
         <v>30</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9272728</v>
+        <v>3.9807692</v>
       </c>
       <c r="O21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
         <v>23</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1818181</v>
+        <v>1.2307693</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22488038</v>
+        <v>0.24257426</v>
       </c>
       <c r="U21" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.24390244</v>
+        <v>0.23383084</v>
       </c>
       <c r="C22" t="n">
+        <v>21</v>
+      </c>
+      <c r="D22" t="n">
+        <v>19</v>
+      </c>
+      <c r="E22" t="n">
+        <v>27</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3114035</v>
+      </c>
+      <c r="I22" t="n">
         <v>16</v>
       </c>
-      <c r="D22" t="n">
-        <v>24</v>
-      </c>
-      <c r="E22" t="n">
-        <v>20</v>
-      </c>
-      <c r="F22" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" t="n">
-        <v>17</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.31441048</v>
-      </c>
-      <c r="I22" t="n">
-        <v>18</v>
-      </c>
       <c r="J22" t="n">
-        <v>0.4</v>
+        <v>0.3880597</v>
       </c>
       <c r="K22" t="n">
         <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M22" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8846154</v>
+        <v>6.882353</v>
       </c>
       <c r="O22" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6346154</v>
+        <v>1.7254902</v>
       </c>
       <c r="S22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T22" t="n">
-        <v>0.30555555</v>
+        <v>0.30660376</v>
       </c>
       <c r="U22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.33624455</v>
+        <v>0.3122172</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.39285713</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.47058824</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>53</v>
+      </c>
+      <c r="M23" t="n">
+        <v>17</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.9056604</v>
+      </c>
+      <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" t="n">
         <v>9</v>
       </c>
-      <c r="G23" t="n">
-        <v>11</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.41603053</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.5065502</v>
-      </c>
-      <c r="K23" t="n">
-        <v>5</v>
-      </c>
-      <c r="L23" t="n">
-        <v>55</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="Q23" t="n">
         <v>20</v>
       </c>
-      <c r="N23" t="n">
-        <v>5.019231</v>
-      </c>
-      <c r="O23" t="n">
-        <v>20</v>
-      </c>
-      <c r="P23" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>23</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.4423077</v>
+        <v>1.2075472</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>0.26600984</v>
+        <v>0.24120604</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.23404256</v>
+        <v>0.24152543</v>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F24" t="n">
         <v>7</v>
       </c>
       <c r="G24" t="n">
+        <v>16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3088803</v>
+      </c>
+      <c r="I24" t="n">
+        <v>18</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.38135594</v>
+      </c>
+      <c r="K24" t="n">
+        <v>19</v>
+      </c>
+      <c r="L24" t="n">
+        <v>65</v>
+      </c>
+      <c r="M24" t="n">
+        <v>27</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>20</v>
+      </c>
+      <c r="P24" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>11</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3833333</v>
+      </c>
+      <c r="S24" t="n">
         <v>17</v>
       </c>
-      <c r="H24" t="n">
-        <v>0.30501932</v>
-      </c>
-      <c r="I24" t="n">
-        <v>20</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.38297874</v>
-      </c>
-      <c r="K24" t="n">
-        <v>21</v>
-      </c>
-      <c r="L24" t="n">
-        <v>68</v>
-      </c>
-      <c r="M24" t="n">
-        <v>29</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7.6271186</v>
-      </c>
-      <c r="O24" t="n">
-        <v>29</v>
-      </c>
-      <c r="P24" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>28</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.6101695</v>
-      </c>
-      <c r="S24" t="n">
-        <v>26</v>
-      </c>
       <c r="T24" t="n">
-        <v>0.2735043</v>
+        <v>0.25110132</v>
       </c>
       <c r="U24" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.27906978</v>
+        <v>0.24390244</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" t="n">
         <v>10</v>
       </c>
-      <c r="G25" t="n">
-        <v>8</v>
-      </c>
       <c r="H25" t="n">
-        <v>0.33189654</v>
+        <v>0.3080357</v>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>0.48372093</v>
+        <v>0.41951218</v>
       </c>
       <c r="K25" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N25" t="n">
-        <v>6.75</v>
+        <v>7.4423075</v>
       </c>
       <c r="O25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4423077</v>
+        <v>1.5769231</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="n">
-        <v>0.28502417</v>
+        <v>0.29577464</v>
       </c>
       <c r="U25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
@@ -4408,61 +4408,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.19745223</v>
+        <v>0.19148937</v>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="n">
         <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H26" t="n">
-        <v>0.28089887</v>
+        <v>0.2735849</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>0.34394905</v>
+        <v>0.31382978</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L26" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1911764</v>
+        <v>1.35</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
       <c r="P26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
       <c r="R26" t="n">
-        <v>0.75</v>
+        <v>0.7875</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1572327</v>
+        <v>0.17460318</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2389706</v>
+        <v>0.25454545</v>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>0.30333334</v>
+        <v>0.31456953</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3970588</v>
+        <v>0.44</v>
       </c>
       <c r="K27" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L27" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="M27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>3.4225352</v>
       </c>
       <c r="O27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2714286</v>
+        <v>1.2535211</v>
       </c>
       <c r="S27" t="n">
         <v>11</v>
       </c>
       <c r="T27" t="n">
-        <v>0.22932331</v>
+        <v>0.23507462</v>
       </c>
       <c r="U27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -4542,46 +4542,46 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.22510822</v>
+        <v>0.21681416</v>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" t="n">
+        <v>17</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.27235773</v>
+      </c>
+      <c r="I28" t="n">
+        <v>26</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.36725664</v>
+      </c>
+      <c r="K28" t="n">
+        <v>23</v>
+      </c>
+      <c r="L28" t="n">
+        <v>52</v>
+      </c>
+      <c r="M28" t="n">
         <v>16</v>
-      </c>
-      <c r="F28" t="n">
-        <v>11</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I28" t="n">
-        <v>25</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.3982684</v>
-      </c>
-      <c r="K28" t="n">
-        <v>18</v>
-      </c>
-      <c r="L28" t="n">
-        <v>55</v>
-      </c>
-      <c r="M28" t="n">
-        <v>20</v>
       </c>
       <c r="N28" t="n">
         <v>3.5409837</v>
       </c>
       <c r="O28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
         <v>12</v>
@@ -4590,16 +4590,16 @@
         <v>25</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8852459</v>
+        <v>0.8688524399999999</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
         <v>0.20089285</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2647059</v>
+        <v>0.24096386</v>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H29" t="n">
-        <v>0.33333334</v>
+        <v>0.30601093</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>0.44117647</v>
+        <v>0.41566265</v>
       </c>
       <c r="K29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L29" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7045455</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3409091</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T29" t="n">
-        <v>0.26553673</v>
+        <v>0.2802198</v>
       </c>
       <c r="U29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.19791667</v>
+        <v>0.18592964</v>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>0.24757281</v>
+        <v>0.23113208</v>
       </c>
       <c r="I30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>0.29166666</v>
+        <v>0.28140703</v>
       </c>
       <c r="K30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L30" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5882354</v>
+        <v>4.0588236</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.137255</v>
+        <v>1.0784314</v>
       </c>
       <c r="S30" t="n">
         <v>6</v>
       </c>
       <c r="T30" t="n">
-        <v>0.22395833</v>
+        <v>0.20634921</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.30952382</v>
+        <v>0.3004926</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3909465</v>
+        <v>0.38235295</v>
       </c>
       <c r="I31" t="n">
         <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6</v>
+        <v>0.5714286</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>6.8333335</v>
+        <v>6.6666665</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
         <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R31" t="n">
-        <v>1.6666666</v>
+        <v>1.574074</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.29493088</v>
+        <v>0.29166666</v>
       </c>
       <c r="U31" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23698854</v>
+        <v>0.23704663</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G2" t="n">
         <v>29</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30703562</v>
+        <v>0.3068182</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38330606</v>
+        <v>0.38277203</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.296464</v>
+        <v>4.260268</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q2" t="n">
         <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2890625</v>
+        <v>1.2822285</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25217953</v>
+        <v>0.25096032</v>
       </c>
       <c r="U2" t="n">
         <v>23</v>
@@ -613,16 +613,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24705508</v>
+        <v>0.24590164</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>115</v>
@@ -631,43 +631,43 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32492203</v>
+        <v>0.32378545</v>
       </c>
       <c r="I3" t="n">
         <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4068768</v>
+        <v>0.40416142</v>
       </c>
       <c r="K3" t="n">
         <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="M3" t="n">
         <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1303287</v>
+        <v>5.124246</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4725944</v>
+        <v>1.4692401</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26622766</v>
+        <v>0.26561043</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24814217</v>
+        <v>0.24864347</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31262758</v>
+        <v>0.31395683</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41227788</v>
+        <v>0.41398022</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6104004</v>
+        <v>3.6146939</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.233182</v>
+        <v>1.2355102</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23007968</v>
+        <v>0.23013788</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23887815</v>
+        <v>0.23785166</v>
       </c>
       <c r="C5" t="n">
         <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31927025</v>
+        <v>0.31950325</v>
       </c>
       <c r="I5" t="n">
         <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39684075</v>
+        <v>0.39578006</v>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3981404</v>
+        <v>4.372251</v>
       </c>
       <c r="O5" t="n">
         <v>21</v>
       </c>
       <c r="P5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q5" t="n">
         <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3714632</v>
+        <v>1.3698521</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25339225</v>
+        <v>0.25351232</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,43 +814,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24486415</v>
+        <v>0.24392647</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31428573</v>
+        <v>0.31388152</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38800532</v>
+        <v>0.3867367</v>
       </c>
       <c r="K6" t="n">
         <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="M6" t="n">
         <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7003353</v>
+        <v>3.6701202</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -862,16 +862,16 @@
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2347025</v>
+        <v>1.230833</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>0.23934753</v>
+        <v>0.238973</v>
       </c>
       <c r="U6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24426752</v>
+        <v>0.24448645</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33774468</v>
+        <v>0.33742833</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41146496</v>
+        <v>0.41178325</v>
       </c>
       <c r="K7" t="n">
         <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="M7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3608623</v>
+        <v>4.35133</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P7" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2717657</v>
+        <v>1.2715552</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24514878</v>
+        <v>0.24406672</v>
       </c>
       <c r="U7" t="n">
         <v>18</v>
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23947369</v>
+        <v>0.23910214</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
         <v>125</v>
@@ -966,46 +966,46 @@
         <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31854016</v>
+        <v>0.31763005</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41085526</v>
+        <v>0.40858817</v>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="M8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2543426</v>
+        <v>4.229448</v>
       </c>
       <c r="O8" t="n">
         <v>15</v>
       </c>
       <c r="P8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3436725</v>
+        <v>1.3386503</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24140212</v>
+        <v>0.24049804</v>
       </c>
       <c r="U8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2280932</v>
+        <v>0.22684433</v>
       </c>
       <c r="C9" t="n">
         <v>29</v>
@@ -1024,7 +1024,7 @@
         <v>384</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
         <v>113</v>
@@ -1033,28 +1033,28 @@
         <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30964172</v>
+        <v>0.30862418</v>
       </c>
       <c r="I9" t="n">
         <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.39218903</v>
+        <v>0.38934025</v>
       </c>
       <c r="K9" t="n">
         <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="M9" t="n">
         <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5666666</v>
+        <v>4.5274725</v>
       </c>
       <c r="O9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P9" t="n">
         <v>124</v>
@@ -1063,13 +1063,13 @@
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4555556</v>
+        <v>1.4468864</v>
       </c>
       <c r="S9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24878365</v>
+        <v>0.24791265</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22865555</v>
+        <v>0.22815534</v>
       </c>
       <c r="C10" t="n">
         <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G10" t="n">
         <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3106346</v>
+        <v>0.3102064</v>
       </c>
       <c r="I10" t="n">
         <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36669937</v>
+        <v>0.36860842</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7961912</v>
+        <v>3.7767534</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q10" t="n">
         <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2751216</v>
+        <v>1.2661322</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2391726</v>
+        <v>0.23783611</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2571965</v>
+        <v>0.25627518</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G11" t="n">
         <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32792842</v>
+        <v>0.32724252</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42396745</v>
+        <v>0.4226836</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.482675</v>
+        <v>5.4948125</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q11" t="n">
         <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5108783</v>
+        <v>1.517957</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28658167</v>
+        <v>0.2870009</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,43 +1216,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23590747</v>
+        <v>0.23555985</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E12" t="n">
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G12" t="n">
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3145418</v>
+        <v>0.31434298</v>
       </c>
       <c r="I12" t="n">
         <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39784947</v>
+        <v>0.39883834</v>
       </c>
       <c r="K12" t="n">
         <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6858552</v>
+        <v>3.6563644</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1264,13 +1264,13 @@
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2224506</v>
+        <v>1.216348</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2351015</v>
+        <v>0.2343598</v>
       </c>
       <c r="U12" t="n">
         <v>7</v>
@@ -1292,7 +1292,7 @@
         <v>432</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
         <v>126</v>
@@ -1304,19 +1304,19 @@
         <v>0.31511074</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
         <v>0.41034484</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>778</v>
       </c>
       <c r="M13" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
         <v>4.7766757</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24768592</v>
+        <v>0.24739337</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E14" t="n">
         <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31850585</v>
+        <v>0.31779662</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3977019</v>
+        <v>0.39810428</v>
       </c>
       <c r="K14" t="n">
         <v>16</v>
       </c>
       <c r="L14" t="n">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="M14" t="n">
         <v>9</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8582454</v>
+        <v>4.887369</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.446385</v>
+        <v>1.4493161</v>
       </c>
       <c r="S14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2630911</v>
+        <v>0.26367065</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,61 +1417,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23914431</v>
+        <v>0.23950773</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
         <v>107</v>
       </c>
       <c r="G15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3145875</v>
+        <v>0.31489843</v>
       </c>
       <c r="I15" t="n">
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3933589</v>
+        <v>0.39255285</v>
       </c>
       <c r="K15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" t="n">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6335907</v>
+        <v>4.6630435</v>
       </c>
       <c r="O15" t="n">
         <v>24</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3981293</v>
+        <v>1.3985507</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2369439</v>
+        <v>0.23780683</v>
       </c>
       <c r="U15" t="n">
         <v>8</v>
@@ -1517,7 +1517,7 @@
         <v>736</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
         <v>3.4751403</v>
@@ -1529,7 +1529,7 @@
         <v>100</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
         <v>1.1319166</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2543633</v>
+        <v>0.25503355</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33076045</v>
+        <v>0.33154324</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.41208792</v>
+        <v>0.41323107</v>
       </c>
       <c r="K17" t="n">
         <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="M17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
-        <v>4.0488997</v>
+        <v>4.0266023</v>
       </c>
       <c r="O17" t="n">
         <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2408313</v>
+        <v>1.241838</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22886059</v>
+        <v>0.22835918</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25455126</v>
+        <v>0.2550505</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G18" t="n">
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3368984</v>
+        <v>0.33695048</v>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3966784</v>
+        <v>0.39772728</v>
       </c>
       <c r="K18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L18" t="n">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="M18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3245862</v>
+        <v>3.3318691</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1614857</v>
+        <v>1.1585463</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2173913</v>
+        <v>0.21675359</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24841371</v>
+        <v>0.24701446</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32354602</v>
+        <v>0.32204813</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4159264</v>
+        <v>0.41389063</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="M19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
-        <v>4.67371</v>
+        <v>4.677251</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3774889</v>
+        <v>1.3745981</v>
       </c>
       <c r="S19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T19" t="n">
-        <v>0.251664</v>
+        <v>0.25094104</v>
       </c>
       <c r="U19" t="n">
         <v>22</v>
@@ -1752,64 +1752,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23386581</v>
+        <v>0.23473585</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30288184</v>
+        <v>0.3039635</v>
       </c>
       <c r="I20" t="n">
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.38115016</v>
+        <v>0.38342297</v>
       </c>
       <c r="K20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L20" t="n">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="M20" t="n">
         <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3769107</v>
+        <v>4.3191404</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P20" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3189863</v>
+        <v>1.3131715</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23917851</v>
+        <v>0.23866124</v>
       </c>
       <c r="U20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -1819,64 +1819,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23372781</v>
+        <v>0.2353896</v>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="E21" t="n">
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3147016</v>
+        <v>0.31618282</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>0.41683105</v>
+        <v>0.42045453</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.398447</v>
+        <v>3.4050121</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q21" t="n">
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1916633</v>
+        <v>1.1932093</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22789784</v>
+        <v>0.22847897</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23779126</v>
+        <v>0.23704173</v>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E22" t="n">
         <v>17</v>
@@ -1904,43 +1904,43 @@
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30483592</v>
+        <v>0.3041619</v>
       </c>
       <c r="I22" t="n">
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40440473</v>
+        <v>0.4023388</v>
       </c>
       <c r="K22" t="n">
         <v>14</v>
       </c>
       <c r="L22" t="n">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="M22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.29074</v>
+        <v>4.2444</v>
       </c>
       <c r="O22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
         <v>111</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3295593</v>
+        <v>1.3212</v>
       </c>
       <c r="S22" t="n">
         <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25795382</v>
+        <v>0.2564895</v>
       </c>
       <c r="U22" t="n">
         <v>26</v>
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2619562</v>
+        <v>0.26167938</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G23" t="n">
         <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>0.34052432</v>
+        <v>0.34044853</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.42147484</v>
+        <v>0.42290077</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="M23" t="n">
         <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2580256</v>
+        <v>4.3195715</v>
       </c>
       <c r="O23" t="n">
+        <v>19</v>
+      </c>
+      <c r="P23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3136165</v>
+      </c>
+      <c r="S23" t="n">
         <v>16</v>
       </c>
-      <c r="P23" t="n">
-        <v>97</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3049759</v>
-      </c>
-      <c r="S23" t="n">
-        <v>15</v>
-      </c>
       <c r="T23" t="n">
-        <v>0.23835182</v>
+        <v>0.23903508</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22579576</v>
+        <v>0.22477818</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.30097952</v>
+        <v>0.30008826</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37267905</v>
+        <v>0.37134406</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="M24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2083673</v>
+        <v>4.195132</v>
       </c>
       <c r="O24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P24" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3375717</v>
+        <v>1.3350912</v>
       </c>
       <c r="S24" t="n">
         <v>18</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24722403</v>
+        <v>0.24717286</v>
       </c>
       <c r="U24" t="n">
         <v>19</v>
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25420502</v>
+        <v>0.2553325</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G25" t="n">
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30679497</v>
+        <v>0.30846775</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41827992</v>
+        <v>0.42158094</v>
       </c>
       <c r="K25" t="n">
         <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.562911</v>
+        <v>4.53477</v>
       </c>
       <c r="O25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q25" t="n">
         <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3778783</v>
+        <v>1.3737291</v>
       </c>
       <c r="S25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25064936</v>
+        <v>0.24975891</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,64 +2154,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23049414</v>
+        <v>0.23029913</v>
       </c>
       <c r="C26" t="n">
         <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G26" t="n">
         <v>13</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31093165</v>
+        <v>0.31118083</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3793888</v>
+        <v>0.37954327</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="M26" t="n">
         <v>22</v>
       </c>
       <c r="N26" t="n">
-        <v>3.537404</v>
+        <v>3.568282</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1633644</v>
+        <v>1.1726072</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23707317</v>
+        <v>0.23826367</v>
       </c>
       <c r="U26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2447644</v>
+        <v>0.24384715</v>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G27" t="n">
         <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3206506</v>
+        <v>0.31991953</v>
       </c>
       <c r="I27" t="n">
         <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39430627</v>
+        <v>0.39345855</v>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L27" t="n">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.152994</v>
+        <v>4.206085</v>
       </c>
       <c r="O27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P27" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q27" t="n">
         <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3375717</v>
+        <v>1.3411764</v>
       </c>
       <c r="S27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25250566</v>
+        <v>0.25327373</v>
       </c>
       <c r="U27" t="n">
         <v>24</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25742903</v>
+        <v>0.25767073</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E28" t="n">
         <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33382702</v>
+        <v>0.3338214</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39499167</v>
+        <v>0.39623886</v>
       </c>
       <c r="K28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L28" t="n">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.721046</v>
+        <v>3.8128078</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P28" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1656289</v>
+        <v>1.1748768</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23143236</v>
+        <v>0.23313686</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2355,43 +2355,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24315515</v>
+        <v>0.24395746</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G29" t="n">
         <v>21</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3185918</v>
+        <v>0.3189407</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39243808</v>
+        <v>0.39510152</v>
       </c>
       <c r="K29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="M29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N29" t="n">
-        <v>4.068951</v>
+        <v>4.079216</v>
       </c>
       <c r="O29" t="n">
         <v>11</v>
@@ -2400,19 +2400,19 @@
         <v>111</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R29" t="n">
-        <v>1.244839</v>
+        <v>1.2482647</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24029754</v>
+        <v>0.24065197</v>
       </c>
       <c r="U29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -2431,13 +2431,13 @@
         <v>376</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F30" t="n">
         <v>93</v>
       </c>
       <c r="G30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H30" t="n">
         <v>0.30541012</v>
@@ -2467,7 +2467,7 @@
         <v>104</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R30" t="n">
         <v>1.2950687</v>
@@ -2504,7 +2504,7 @@
         <v>132</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>0.32549128</v>
@@ -2522,7 +2522,7 @@
         <v>777</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N31" t="n">
         <v>4.7578034</v>
@@ -2534,7 +2534,7 @@
         <v>130</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R31" t="n">
         <v>1.3927301</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.22439024</v>
+        <v>0.22689076</v>
       </c>
       <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2868217</v>
+      </c>
+      <c r="I2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.34453782</v>
+      </c>
+      <c r="K2" t="n">
         <v>25</v>
       </c>
-      <c r="D2" t="n">
-        <v>23</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.28699553</v>
-      </c>
-      <c r="I2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.34634146</v>
-      </c>
-      <c r="K2" t="n">
-        <v>26</v>
-      </c>
       <c r="L2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.5714285</v>
       </c>
       <c r="O2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
         <v>12</v>
       </c>
-      <c r="P2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.2962962</v>
+        <v>1.2063493</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.27102804</v>
+        <v>0.25311205</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2867,16 +2867,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.22485207</v>
+        <v>0.21</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -2885,43 +2885,43 @@
         <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>0.29032257</v>
+        <v>0.27727273</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>0.33136094</v>
+        <v>0.3</v>
       </c>
       <c r="K3" t="n">
         <v>28</v>
       </c>
       <c r="L3" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>8.162789999999999</v>
+        <v>7.5882354</v>
       </c>
       <c r="O3" t="n">
         <v>30</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9767442</v>
+        <v>1.8431373</v>
       </c>
       <c r="S3" t="n">
         <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3125</v>
+        <v>0.2961165</v>
       </c>
       <c r="U3" t="n">
         <v>30</v>
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.268</v>
+        <v>0.27165353</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.34628975</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.52362204</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>13</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
       <c r="L4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N4" t="n">
-        <v>6.142857</v>
+        <v>5.142857</v>
       </c>
       <c r="O4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P4" t="n">
         <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6190476</v>
+        <v>1.5396825</v>
       </c>
       <c r="S4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T4" t="n">
-        <v>0.29571983</v>
+        <v>0.2749004</v>
       </c>
       <c r="U4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.24550898</v>
+        <v>0.22797927</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.33333334</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.37823835</v>
+      </c>
+      <c r="K5" t="n">
         <v>20</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.33157894</v>
-      </c>
-      <c r="I5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.39520958</v>
-      </c>
-      <c r="K5" t="n">
-        <v>16</v>
-      </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.075472</v>
       </c>
       <c r="O5" t="n">
         <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3181819</v>
+        <v>1.3018868</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T5" t="n">
-        <v>0.23170732</v>
+        <v>0.23737374</v>
       </c>
       <c r="U5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -3068,43 +3068,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.27683616</v>
+        <v>0.25853658</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6" t="n">
         <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>0.36893204</v>
+        <v>0.35564855</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.46892655</v>
+        <v>0.4390244</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>1.6666666</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -3113,16 +3113,16 @@
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7777778</v>
+        <v>0.7962963</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.17610063</v>
+        <v>0.18134715</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.22699386</v>
+        <v>0.23350254</v>
       </c>
       <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>23</v>
+      </c>
+      <c r="E7" t="n">
         <v>22</v>
       </c>
-      <c r="D7" t="n">
-        <v>21</v>
-      </c>
-      <c r="E7" t="n">
-        <v>25</v>
-      </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>0.30107528</v>
+        <v>0.3018018</v>
       </c>
       <c r="I7" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>0.36809817</v>
+        <v>0.38071066</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>6.6</v>
+        <v>6.1132073</v>
       </c>
       <c r="O7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5111111</v>
+        <v>1.4716982</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2937853</v>
+        <v>0.27093595</v>
       </c>
       <c r="U7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.20689656</v>
+        <v>0.195</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.25345623</v>
+      </c>
+      <c r="I8" t="n">
+        <v>29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K8" t="n">
+        <v>29</v>
+      </c>
+      <c r="L8" t="n">
+        <v>47</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>14</v>
+      </c>
+      <c r="P8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.26696834</v>
-      </c>
-      <c r="I8" t="n">
-        <v>28</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.33990148</v>
-      </c>
-      <c r="K8" t="n">
-        <v>27</v>
-      </c>
-      <c r="L8" t="n">
-        <v>44</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>9</v>
       </c>
-      <c r="N8" t="n">
-        <v>4.725</v>
-      </c>
-      <c r="O8" t="n">
-        <v>18</v>
-      </c>
-      <c r="P8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>11</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.5562501</v>
+        <v>1.3518518</v>
       </c>
       <c r="S8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2682927</v>
+        <v>0.24875621</v>
       </c>
       <c r="U8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -3269,49 +3269,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.235</v>
+        <v>0.203125</v>
       </c>
       <c r="C9" t="n">
+        <v>28</v>
+      </c>
+      <c r="D9" t="n">
         <v>20</v>
       </c>
-      <c r="D9" t="n">
-        <v>27</v>
-      </c>
       <c r="E9" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.30136988</v>
+      </c>
+      <c r="I9" t="n">
         <v>16</v>
       </c>
-      <c r="F9" t="n">
+      <c r="J9" t="n">
+        <v>0.36458334</v>
+      </c>
+      <c r="K9" t="n">
+        <v>23</v>
+      </c>
+      <c r="L9" t="n">
+        <v>60</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.6666667</v>
+      </c>
+      <c r="O9" t="n">
         <v>10</v>
       </c>
-      <c r="G9" t="n">
+      <c r="P9" t="n">
         <v>5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.32300884</v>
-      </c>
-      <c r="I9" t="n">
-        <v>13</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="K9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L9" t="n">
-        <v>59</v>
-      </c>
-      <c r="M9" t="n">
-        <v>23</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.8333333</v>
-      </c>
-      <c r="O9" t="n">
-        <v>9</v>
-      </c>
-      <c r="P9" t="n">
-        <v>6</v>
       </c>
       <c r="Q9" t="n">
         <v>5</v>
@@ -3320,13 +3320,13 @@
         <v>1.2777778</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>0.21243523</v>
+        <v>0.21649484</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.225</v>
+        <v>0.20895523</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31111112</v>
+        <v>0.280543</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>0.375</v>
+        <v>0.37810946</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M10" t="n">
         <v>29</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1925464</v>
+        <v>3.689441</v>
       </c>
       <c r="O10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P10" t="n">
         <v>6</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4906832</v>
+        <v>1.3416148</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2606635</v>
+        <v>0.23529412</v>
       </c>
       <c r="U10" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.29752067</v>
+        <v>0.2647059</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>0.37809187</v>
+        <v>0.34432235</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5041322</v>
+        <v>0.45378152</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1210527</v>
+        <v>4.7647057</v>
       </c>
       <c r="O11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4052632</v>
+        <v>1.5240642</v>
       </c>
       <c r="S11" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2701613</v>
+        <v>0.2874016</v>
       </c>
       <c r="U11" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.24561404</v>
+        <v>0.22699386</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
         <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3152174</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.41104296</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>44</v>
+      </c>
+      <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="G12" t="n">
-        <v>16</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.32460734</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.42105263</v>
-      </c>
-      <c r="K12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L12" t="n">
-        <v>49</v>
-      </c>
-      <c r="M12" t="n">
-        <v>13</v>
-      </c>
       <c r="N12" t="n">
-        <v>2.8636363</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
         <v>3</v>
       </c>
-      <c r="P12" t="n">
-        <v>6</v>
-      </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1590909</v>
+        <v>0.8</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23255815</v>
+        <v>0.17177914</v>
       </c>
       <c r="U12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -3540,7 +3540,7 @@
         <v>0.2371134</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
         <v>32</v>
@@ -3552,13 +3552,13 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
         <v>0.30092594</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
         <v>0.43814433</v>
@@ -3570,13 +3570,13 @@
         <v>44</v>
       </c>
       <c r="M13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N13" t="n">
         <v>4.8461537</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P13" t="n">
         <v>12</v>
@@ -3588,13 +3588,13 @@
         <v>1.5192307</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T13" t="n">
         <v>0.2562814</v>
       </c>
       <c r="U13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.30593607</v>
+        <v>0.31651375</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -3619,49 +3619,49 @@
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>0.37551022</v>
+        <v>0.3852459</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5022831</v>
+        <v>0.51376146</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M14" t="n">
+        <v>16</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.1923075</v>
+      </c>
+      <c r="O14" t="n">
         <v>21</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.754717</v>
-      </c>
-      <c r="O14" t="n">
-        <v>19</v>
-      </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6037736</v>
+        <v>1.6346154</v>
       </c>
       <c r="S14" t="n">
+        <v>28</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.28502417</v>
+      </c>
+      <c r="U14" t="n">
         <v>26</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.28301886</v>
-      </c>
-      <c r="U14" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2364532</v>
+        <v>0.2583732</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>0.27102804</v>
+        <v>0.30044842</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3596059</v>
+        <v>0.3875598</v>
       </c>
       <c r="K15" t="n">
+        <v>18</v>
+      </c>
+      <c r="L15" t="n">
+        <v>64</v>
+      </c>
+      <c r="M15" t="n">
+        <v>25</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.6751595</v>
+      </c>
+      <c r="O15" t="n">
         <v>24</v>
       </c>
-      <c r="L15" t="n">
-        <v>59</v>
-      </c>
-      <c r="M15" t="n">
-        <v>23</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.673077</v>
-      </c>
-      <c r="O15" t="n">
-        <v>17</v>
-      </c>
       <c r="P15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2884616</v>
+        <v>1.3949045</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2244898</v>
+        <v>0.25853658</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25652173</v>
+        <v>0.21875</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>29</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.30092594</v>
+      </c>
+      <c r="I16" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="K16" t="n">
+        <v>27</v>
+      </c>
+      <c r="L16" t="n">
+        <v>43</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.892857</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="n">
-        <v>25</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.33716476</v>
-      </c>
-      <c r="I16" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.37391305</v>
-      </c>
-      <c r="K16" t="n">
-        <v>21</v>
-      </c>
-      <c r="L16" t="n">
-        <v>47</v>
-      </c>
-      <c r="M16" t="n">
-        <v>12</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.4615386</v>
-      </c>
-      <c r="O16" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" t="n">
-        <v>8</v>
-      </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2461538</v>
+        <v>1.1785715</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21940929</v>
+        <v>0.20895523</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3127962</v>
+        <v>0.33023256</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3984064</v>
+        <v>0.41269842</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.60189575</v>
+        <v>0.63255817</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.4363637</v>
+      </c>
+      <c r="O17" t="n">
         <v>7</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>23</v>
       </c>
       <c r="P17" t="n">
         <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2962962</v>
+        <v>1.1454545</v>
       </c>
       <c r="S17" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>0.25247526</v>
+        <v>0.215</v>
       </c>
       <c r="U17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25</v>
+        <v>0.26804122</v>
       </c>
       <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>40</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.328125</v>
+      </c>
+      <c r="I18" t="n">
         <v>12</v>
       </c>
-      <c r="D18" t="n">
-        <v>34</v>
-      </c>
-      <c r="E18" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>20</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.31410256</v>
-      </c>
-      <c r="I18" t="n">
-        <v>15</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.38732395</v>
+        <v>0.41237113</v>
       </c>
       <c r="K18" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N18" t="n">
-        <v>2.875</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0.9166666999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0.20149253</v>
+        <v>0.18320611</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.28248587</v>
+        <v>0.25603864</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
         <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
-        <v>0.36097562</v>
+        <v>0.33333334</v>
       </c>
       <c r="I19" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.43961352</v>
+      </c>
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>63</v>
+      </c>
+      <c r="M19" t="n">
+        <v>23</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.5660377</v>
+      </c>
+      <c r="O19" t="n">
         <v>8</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.48022598</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6</v>
-      </c>
-      <c r="L19" t="n">
-        <v>49</v>
-      </c>
-      <c r="M19" t="n">
-        <v>13</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.2727273</v>
-      </c>
-      <c r="O19" t="n">
-        <v>5</v>
-      </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0454545</v>
+        <v>1.0566038</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>0.18589744</v>
+        <v>0.18518518</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -4006,61 +4006,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.29411766</v>
+        <v>0.29761904</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" t="n">
         <v>4</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
+        <v>0.37630662</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.48412699</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>46</v>
+      </c>
+      <c r="M20" t="n">
         <v>10</v>
       </c>
-      <c r="G20" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.46606335</v>
-      </c>
-      <c r="K20" t="n">
-        <v>9</v>
-      </c>
-      <c r="L20" t="n">
-        <v>39</v>
-      </c>
-      <c r="M20" t="n">
-        <v>4</v>
-      </c>
       <c r="N20" t="n">
-        <v>8.150944000000001</v>
+        <v>6.822581</v>
       </c>
       <c r="O20" t="n">
         <v>29</v>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="n">
         <v>29</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8679246</v>
+        <v>1.7096775</v>
       </c>
       <c r="S20" t="n">
         <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>0.30701753</v>
+        <v>0.2923077</v>
       </c>
       <c r="U20" t="n">
         <v>29</v>
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2010582</v>
+        <v>0.2290749</v>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>0.25</v>
+        <v>0.28225806</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>0.35449734</v>
+        <v>0.41409692</v>
       </c>
       <c r="K21" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="L21" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="M21" t="n">
         <v>30</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9807692</v>
+        <v>3.9836066</v>
       </c>
       <c r="O21" t="n">
+        <v>13</v>
+      </c>
+      <c r="P21" t="n">
         <v>11</v>
       </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
       <c r="Q21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2307693</v>
+        <v>1.2459016</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T21" t="n">
-        <v>0.24257426</v>
+        <v>0.24789916</v>
       </c>
       <c r="U21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -4140,10 +4140,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23383084</v>
+        <v>0.23880596</v>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
         <v>19</v>
@@ -4155,13 +4155,13 @@
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3114035</v>
+        <v>0.3187773</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
         <v>0.3880597</v>
@@ -4170,34 +4170,34 @@
         <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
+        <v>13</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.8235292</v>
+      </c>
+      <c r="O22" t="n">
+        <v>25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q22" t="n">
         <v>18</v>
       </c>
-      <c r="N22" t="n">
-        <v>6.882353</v>
-      </c>
-      <c r="O22" t="n">
-        <v>27</v>
-      </c>
-      <c r="P22" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>25</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.7254902</v>
+        <v>1.4313725</v>
       </c>
       <c r="S22" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="T22" t="n">
-        <v>0.30660376</v>
+        <v>0.2647059</v>
       </c>
       <c r="U22" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3122172</v>
+        <v>0.29032257</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>0.39285713</v>
+        <v>0.37398374</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.47058824</v>
+        <v>0.4562212</v>
       </c>
       <c r="K23" t="n">
         <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M23" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9056604</v>
+        <v>5.4339623</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2075472</v>
+        <v>1.4528302</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="T23" t="n">
-        <v>0.24120604</v>
+        <v>0.2682927</v>
       </c>
       <c r="U23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -4274,34 +4274,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24152543</v>
+        <v>0.22026432</v>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3088803</v>
+        <v>0.28629032</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>0.38135594</v>
+        <v>0.3215859</v>
       </c>
       <c r="K24" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L24" t="n">
         <v>65</v>
@@ -4310,28 +4310,28 @@
         <v>27</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>3.3934426</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="P24" t="n">
         <v>7</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3833333</v>
+        <v>1.1475409</v>
       </c>
       <c r="S24" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T24" t="n">
-        <v>0.25110132</v>
+        <v>0.21621622</v>
       </c>
       <c r="U24" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.24390244</v>
+        <v>0.2603306</v>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3080357</v>
+        <v>0.32958803</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>0.41951218</v>
+        <v>0.46280992</v>
       </c>
       <c r="K25" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>7.4423075</v>
+        <v>6.639344</v>
       </c>
       <c r="O25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q25" t="n">
+        <v>21</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4918033</v>
+      </c>
+      <c r="S25" t="n">
         <v>23</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.5769231</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
+        <v>0.27868852</v>
+      </c>
+      <c r="U25" t="n">
         <v>25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.29577464</v>
-      </c>
-      <c r="U25" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.19148937</v>
+        <v>0.21025641</v>
       </c>
       <c r="C26" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7</v>
+      </c>
+      <c r="G26" t="n">
+        <v>18</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.28767124</v>
+      </c>
+      <c r="I26" t="n">
         <v>21</v>
       </c>
-      <c r="E26" t="n">
-        <v>25</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>25</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.2735849</v>
-      </c>
-      <c r="I26" t="n">
-        <v>25</v>
-      </c>
       <c r="J26" t="n">
-        <v>0.31382978</v>
+        <v>0.35384616</v>
       </c>
       <c r="K26" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L26" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M26" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>1.35</v>
+        <v>2.4076433</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7875</v>
+        <v>1.0318471</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.17460318</v>
+        <v>0.21243523</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -4475,64 +4475,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.25454545</v>
+        <v>0.2247191</v>
       </c>
       <c r="C27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" t="n">
+        <v>41</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
         <v>11</v>
       </c>
-      <c r="D27" t="n">
-        <v>48</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>13</v>
-      </c>
       <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.28911564</v>
+      </c>
+      <c r="I27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.39700374</v>
+      </c>
+      <c r="K27" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" t="n">
+        <v>63</v>
+      </c>
+      <c r="M27" t="n">
+        <v>23</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.8028169</v>
+      </c>
+      <c r="O27" t="n">
+        <v>12</v>
+      </c>
+      <c r="P27" t="n">
         <v>3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.31456953</v>
-      </c>
-      <c r="I27" t="n">
-        <v>14</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="K27" t="n">
-        <v>10</v>
-      </c>
-      <c r="L27" t="n">
-        <v>60</v>
-      </c>
-      <c r="M27" t="n">
-        <v>25</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.4225352</v>
-      </c>
-      <c r="O27" t="n">
-        <v>6</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2535211</v>
+        <v>1.2957747</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23507462</v>
+        <v>0.24264705</v>
       </c>
       <c r="U27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.21681416</v>
+        <v>0.21238938</v>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
@@ -4560,46 +4560,46 @@
         <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.27235773</v>
+        <v>0.2682927</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>0.36725664</v>
+        <v>0.37168142</v>
       </c>
       <c r="K28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L28" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5409837</v>
+        <v>5.0163937</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="P28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>27</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.0655738</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.23580787</v>
+      </c>
+      <c r="U28" t="n">
         <v>12</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>25</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.8688524399999999</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.20089285</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24096386</v>
+        <v>0.21118012</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H29" t="n">
-        <v>0.30601093</v>
+        <v>0.2742857</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>0.41566265</v>
+        <v>0.39130434</v>
       </c>
       <c r="K29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L29" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
         <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2802198</v>
+        <v>0.2762431</v>
       </c>
       <c r="U29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -4685,13 +4685,13 @@
         <v>22</v>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H30" t="n">
         <v>0.23113208</v>
@@ -4715,25 +4715,25 @@
         <v>4.0588236</v>
       </c>
       <c r="O30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P30" t="n">
         <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R30" t="n">
         <v>1.0784314</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T30" t="n">
         <v>0.20634921</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -4746,19 +4746,19 @@
         <v>0.3004926</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>38</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" t="n">
         <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
         <v>0.38235295</v>
@@ -4776,31 +4776,31 @@
         <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
         <v>6.6666665</v>
       </c>
       <c r="O31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P31" t="n">
         <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R31" t="n">
         <v>1.574074</v>
       </c>
       <c r="S31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T31" t="n">
         <v>0.29166666</v>
       </c>
       <c r="U31" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,64 +546,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23704663</v>
+        <v>0.23712</v>
       </c>
       <c r="C2" t="n">
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" t="n">
         <v>29</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3068182</v>
+        <v>0.30713874</v>
       </c>
       <c r="I2" t="n">
         <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38277203</v>
+        <v>0.3824</v>
       </c>
       <c r="K2" t="n">
         <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.260268</v>
+        <v>4.246581</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q2" t="n">
         <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2822285</v>
+        <v>1.28037</v>
       </c>
       <c r="S2" t="n">
         <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25096032</v>
+        <v>0.2510288</v>
       </c>
       <c r="U2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24590164</v>
+        <v>0.24523586</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" t="n">
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32378545</v>
+        <v>0.32293987</v>
       </c>
       <c r="I3" t="n">
         <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40416142</v>
+        <v>0.40299907</v>
       </c>
       <c r="K3" t="n">
         <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>816</v>
+        <v>827</v>
       </c>
       <c r="M3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>5.124246</v>
+        <v>5.2150536</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4692401</v>
+        <v>1.4778973</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26561043</v>
+        <v>0.267117</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24864347</v>
+        <v>0.24723364</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
@@ -698,43 +698,43 @@
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31395683</v>
+        <v>0.31251782</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41398022</v>
+        <v>0.41131836</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="M4" t="n">
         <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6146939</v>
+        <v>3.6014552</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2355102</v>
+        <v>1.2332255</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>0.23013788</v>
+        <v>0.22974293</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
@@ -747,61 +747,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23785166</v>
+        <v>0.23829114</v>
       </c>
       <c r="C5" t="n">
         <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>0.31950325</v>
+        <v>0.31973168</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39578006</v>
+        <v>0.39651898</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.372251</v>
+        <v>4.357595</v>
       </c>
       <c r="O5" t="n">
         <v>21</v>
       </c>
       <c r="P5" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q5" t="n">
         <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3698521</v>
+        <v>1.3670886</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25351232</v>
+        <v>0.25370827</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,61 +814,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24392647</v>
+        <v>0.24456698</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31388152</v>
+        <v>0.31490105</v>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3867367</v>
+        <v>0.38858256</v>
       </c>
       <c r="K6" t="n">
         <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>750</v>
+        <v>760</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6701202</v>
+        <v>3.6516395</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.230833</v>
+        <v>1.2307377</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>0.238973</v>
+        <v>0.23958333</v>
       </c>
       <c r="U6" t="n">
         <v>13</v>
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24448645</v>
+        <v>0.24336973</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
         <v>471</v>
@@ -899,43 +899,43 @@
         <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33742833</v>
+        <v>0.33585927</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41178325</v>
+        <v>0.40936038</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>778</v>
+        <v>794</v>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>4.35133</v>
+        <v>4.352753</v>
       </c>
       <c r="O7" t="n">
         <v>20</v>
       </c>
       <c r="P7" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2715552</v>
+        <v>1.2761374</v>
       </c>
       <c r="S7" t="n">
         <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24406672</v>
+        <v>0.2454805</v>
       </c>
       <c r="U7" t="n">
         <v>18</v>
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23910214</v>
+        <v>0.24100257</v>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G8" t="n">
         <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31763005</v>
+        <v>0.319155</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>0.40858817</v>
+        <v>0.41323906</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="M8" t="n">
         <v>24</v>
       </c>
       <c r="N8" t="n">
-        <v>4.229448</v>
+        <v>4.194175</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="n">
         <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3386503</v>
+        <v>1.3313106</v>
       </c>
       <c r="S8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.24049804</v>
+        <v>0.23985718</v>
       </c>
       <c r="U8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1015,43 +1015,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22684433</v>
+        <v>0.22847043</v>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G9" t="n">
         <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30862418</v>
+        <v>0.30936074</v>
       </c>
       <c r="I9" t="n">
         <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.38934025</v>
+        <v>0.3917095</v>
       </c>
       <c r="K9" t="n">
         <v>23</v>
       </c>
       <c r="L9" t="n">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="M9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5274725</v>
+        <v>4.478261</v>
       </c>
       <c r="O9" t="n">
         <v>22</v>
@@ -1063,16 +1063,16 @@
         <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4468864</v>
+        <v>1.437198</v>
       </c>
       <c r="S9" t="n">
         <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24791265</v>
+        <v>0.24674086</v>
       </c>
       <c r="U9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -1082,64 +1082,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22815534</v>
+        <v>0.22749119</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3102064</v>
+        <v>0.3088068</v>
       </c>
       <c r="I10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>0.36860842</v>
+        <v>0.3675104</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="M10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7767534</v>
+        <v>3.757732</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q10" t="n">
         <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2661322</v>
+        <v>1.2632831</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23783611</v>
+        <v>0.23691723</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25627518</v>
+        <v>0.25666973</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
@@ -1167,43 +1167,43 @@
         <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32724252</v>
+        <v>0.32813355</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4226836</v>
+        <v>0.42195645</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4948125</v>
+        <v>5.4682193</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q11" t="n">
         <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.517957</v>
+        <v>1.5219108</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2870009</v>
+        <v>0.2872846</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23555985</v>
+        <v>0.23570745</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="E12" t="n">
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31434298</v>
+        <v>0.31473088</v>
       </c>
       <c r="I12" t="n">
         <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39883834</v>
+        <v>0.40114978</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L12" t="n">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6563644</v>
+        <v>3.6383748</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q12" t="n">
         <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.216348</v>
+        <v>1.2115848</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2343598</v>
+        <v>0.23323709</v>
       </c>
       <c r="U12" t="n">
         <v>7</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2413793</v>
+        <v>0.24139</v>
       </c>
       <c r="C13" t="n">
         <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31511074</v>
+        <v>0.31463483</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41034484</v>
+        <v>0.41048712</v>
       </c>
       <c r="K13" t="n">
         <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7766757</v>
+        <v>4.805894</v>
       </c>
       <c r="O13" t="n">
         <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4006346</v>
+        <v>1.4039294</v>
       </c>
       <c r="S13" t="n">
         <v>26</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24183835</v>
+        <v>0.24207221</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24739337</v>
+        <v>0.24765478</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E14" t="n">
         <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G14" t="n">
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31779662</v>
+        <v>0.31757134</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39810428</v>
+        <v>0.39962476</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L14" t="n">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N14" t="n">
-        <v>4.887369</v>
+        <v>4.8944225</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="Q14" t="n">
         <v>24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4493161</v>
+        <v>1.4498007</v>
       </c>
       <c r="S14" t="n">
         <v>28</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26367065</v>
+        <v>0.26384568</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,43 +1417,43 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.23950773</v>
+        <v>0.2401624</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31489843</v>
+        <v>0.3150838</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39255285</v>
+        <v>0.39287946</v>
       </c>
       <c r="K15" t="n">
         <v>22</v>
       </c>
       <c r="L15" t="n">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6630435</v>
+        <v>4.645161</v>
       </c>
       <c r="O15" t="n">
         <v>24</v>
@@ -1465,16 +1465,16 @@
         <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3985507</v>
+        <v>1.3978494</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
       </c>
       <c r="T15" t="n">
-        <v>0.23780683</v>
+        <v>0.23809524</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26397222</v>
+        <v>0.26389757</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G16" t="n">
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34622824</v>
+        <v>0.34555402</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.43700662</v>
+        <v>0.43753904</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="M16" t="n">
         <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4751403</v>
+        <v>3.5021818</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1319166</v>
+        <v>1.1364539</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21577574</v>
+        <v>0.21610306</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,61 +1551,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.25503355</v>
+        <v>0.2539582</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33154324</v>
+        <v>0.33090705</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.41323107</v>
+        <v>0.4126029</v>
       </c>
       <c r="K17" t="n">
         <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="M17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N17" t="n">
-        <v>4.0266023</v>
+        <v>4.01555</v>
       </c>
       <c r="O17" t="n">
         <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.241838</v>
+        <v>1.2344497</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22835918</v>
+        <v>0.22769427</v>
       </c>
       <c r="U17" t="n">
         <v>3</v>
@@ -1639,19 +1639,19 @@
         <v>0.33695048</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0.39772728</v>
       </c>
       <c r="K18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
         <v>759</v>
       </c>
       <c r="M18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N18" t="n">
         <v>3.3318691</v>
@@ -1685,16 +1685,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24701446</v>
+        <v>0.24720149</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>118</v>
@@ -1703,46 +1703,46 @@
         <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.32204813</v>
+        <v>0.32216993</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>0.41389063</v>
+        <v>0.41449004</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N19" t="n">
-        <v>4.677251</v>
+        <v>4.66998</v>
       </c>
       <c r="O19" t="n">
         <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3745981</v>
+        <v>1.374155</v>
       </c>
       <c r="S19" t="n">
+        <v>22</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.2514747</v>
+      </c>
+      <c r="U19" t="n">
         <v>23</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.25094104</v>
-      </c>
-      <c r="U19" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1752,61 +1752,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23473585</v>
+        <v>0.23536776</v>
       </c>
       <c r="C20" t="n">
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G20" t="n">
         <v>15</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3039635</v>
+        <v>0.30397967</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>0.38342297</v>
+        <v>0.38372457</v>
       </c>
       <c r="K20" t="n">
         <v>25</v>
       </c>
       <c r="L20" t="n">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="M20" t="n">
         <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3191404</v>
+        <v>4.315748</v>
       </c>
       <c r="O20" t="n">
         <v>18</v>
       </c>
       <c r="P20" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3131715</v>
+        <v>1.3181102</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23866124</v>
+        <v>0.2393321</v>
       </c>
       <c r="U20" t="n">
         <v>12</v>
@@ -1819,61 +1819,61 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2353896</v>
+        <v>0.23676611</v>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E21" t="n">
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31618282</v>
+        <v>0.31713554</v>
       </c>
       <c r="I21" t="n">
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>0.42045453</v>
+        <v>0.42348412</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4050121</v>
+        <v>3.4006398</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q21" t="n">
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1932093</v>
+        <v>1.189924</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22847897</v>
+        <v>0.2284069</v>
       </c>
       <c r="U21" t="n">
         <v>4</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23704173</v>
+        <v>0.2359199</v>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F22" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3041619</v>
+        <v>0.30332956</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4023388</v>
+        <v>0.40050063</v>
       </c>
       <c r="K22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L22" t="n">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="M22" t="n">
         <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2444</v>
+        <v>4.300317</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P22" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3212</v>
+        <v>1.3240888</v>
       </c>
       <c r="S22" t="n">
         <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2564895</v>
+        <v>0.25642595</v>
       </c>
       <c r="U22" t="n">
         <v>26</v>
@@ -1980,13 +1980,13 @@
         <v>0.42290077</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
         <v>882</v>
       </c>
       <c r="M23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N23" t="n">
         <v>4.3195715</v>
@@ -1998,19 +1998,19 @@
         <v>100</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
         <v>1.3136165</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T23" t="n">
         <v>0.23903508</v>
       </c>
       <c r="U23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -2020,64 +2020,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22477818</v>
+        <v>0.22539786</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.30008826</v>
+        <v>0.30046538</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37134406</v>
+        <v>0.37154922</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="M24" t="n">
         <v>17</v>
       </c>
       <c r="N24" t="n">
-        <v>4.195132</v>
+        <v>4.203852</v>
       </c>
       <c r="O24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P24" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q24" t="n">
         <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3350912</v>
+        <v>1.3338684</v>
       </c>
       <c r="S24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24717286</v>
+        <v>0.24728434</v>
       </c>
       <c r="U24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -2087,43 +2087,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2553325</v>
+        <v>0.25597268</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>105</v>
+      </c>
+      <c r="G25" t="n">
+        <v>21</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.30961868</v>
+      </c>
+      <c r="I25" t="n">
         <v>23</v>
       </c>
-      <c r="F25" t="n">
-        <v>104</v>
-      </c>
-      <c r="G25" t="n">
-        <v>20</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.30846775</v>
-      </c>
-      <c r="I25" t="n">
-        <v>25</v>
-      </c>
       <c r="J25" t="n">
-        <v>0.42158094</v>
+        <v>0.42165685</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.53477</v>
+        <v>4.528962</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
@@ -2135,13 +2135,13 @@
         <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3737291</v>
+        <v>1.3793242</v>
       </c>
       <c r="S25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24975891</v>
+        <v>0.25023848</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,64 +2154,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.23029913</v>
+        <v>0.22961783</v>
       </c>
       <c r="C26" t="n">
         <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E26" t="n">
         <v>26</v>
       </c>
       <c r="F26" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31118083</v>
+        <v>0.31006217</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37954327</v>
+        <v>0.3786624</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="M26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N26" t="n">
-        <v>3.568282</v>
+        <v>3.609282</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1726072</v>
+        <v>1.179294</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23826367</v>
+        <v>0.23991102</v>
       </c>
       <c r="U26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -2221,61 +2221,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24384715</v>
+        <v>0.24333869</v>
       </c>
       <c r="C27" t="n">
         <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G27" t="n">
         <v>19</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31991953</v>
+        <v>0.31946424</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39345855</v>
+        <v>0.3929374</v>
       </c>
       <c r="K27" t="n">
         <v>21</v>
       </c>
       <c r="L27" t="n">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.206085</v>
+        <v>4.171348</v>
       </c>
       <c r="O27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P27" t="n">
         <v>93</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3411764</v>
+        <v>1.3314606</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25327373</v>
+        <v>0.25181904</v>
       </c>
       <c r="U27" t="n">
         <v>24</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25767073</v>
+        <v>0.25912645</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3338214</v>
+        <v>0.3343949</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.39623886</v>
+        <v>0.4005867</v>
       </c>
       <c r="K28" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8128078</v>
+        <v>3.7929354</v>
       </c>
       <c r="O28" t="n">
         <v>9</v>
       </c>
       <c r="P28" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q28" t="n">
         <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1748768</v>
+        <v>1.1693057</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23313686</v>
+        <v>0.23241492</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24395746</v>
+        <v>0.24417491</v>
       </c>
       <c r="C29" t="n">
         <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3189407</v>
+        <v>0.31965813</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39510152</v>
+        <v>0.3973827</v>
       </c>
       <c r="K29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L29" t="n">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="M29" t="n">
         <v>14</v>
       </c>
       <c r="N29" t="n">
-        <v>4.079216</v>
+        <v>4.0674477</v>
       </c>
       <c r="O29" t="n">
         <v>11</v>
       </c>
       <c r="P29" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q29" t="n">
         <v>19</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2482647</v>
+        <v>1.2455574</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24065197</v>
+        <v>0.24067046</v>
       </c>
       <c r="U29" t="n">
         <v>16</v>
@@ -2422,64 +2422,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24391025</v>
+        <v>0.24405706</v>
       </c>
       <c r="C30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D30" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E30" t="n">
         <v>27</v>
       </c>
       <c r="F30" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30541012</v>
+        <v>0.30532375</v>
       </c>
       <c r="I30" t="n">
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38301283</v>
+        <v>0.38288432</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.0816493</v>
+        <v>4.069972</v>
       </c>
       <c r="O30" t="n">
         <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2950687</v>
+        <v>1.2966813</v>
       </c>
       <c r="S30" t="n">
         <v>14</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23857051</v>
+        <v>0.23901974</v>
       </c>
       <c r="U30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2508527</v>
+        <v>0.25053665</v>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32549128</v>
+        <v>0.32465753</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.43472868</v>
+        <v>0.43483594</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="M31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7578034</v>
+        <v>4.76036</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3927301</v>
+        <v>1.3967943</v>
       </c>
       <c r="S31" t="n">
         <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25864708</v>
+        <v>0.25968522</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.22689076</v>
+        <v>0.23175965</v>
       </c>
       <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="n">
         <v>19</v>
       </c>
-      <c r="D2" t="n">
-        <v>26</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>22</v>
-      </c>
       <c r="H2" t="n">
-        <v>0.2868217</v>
+        <v>0.29803923</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J2" t="n">
-        <v>0.34453782</v>
+        <v>0.36480686</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5714285</v>
+        <v>3.3934426</v>
       </c>
       <c r="O2" t="n">
         <v>9</v>
       </c>
       <c r="P2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.1311475</v>
+      </c>
+      <c r="S2" t="n">
         <v>7</v>
       </c>
-      <c r="Q2" t="n">
-        <v>12</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.2063493</v>
-      </c>
-      <c r="S2" t="n">
-        <v>11</v>
-      </c>
       <c r="T2" t="n">
-        <v>0.25311205</v>
+        <v>0.24892704</v>
       </c>
       <c r="U2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2867,16 +2867,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.21</v>
+        <v>0.19587629</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -2885,43 +2885,43 @@
         <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>0.27727273</v>
+        <v>0.25943395</v>
       </c>
       <c r="I3" t="n">
+        <v>27</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2783505</v>
+      </c>
+      <c r="K3" t="n">
+        <v>30</v>
+      </c>
+      <c r="L3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M3" t="n">
         <v>26</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L3" t="n">
-        <v>62</v>
-      </c>
-      <c r="M3" t="n">
-        <v>21</v>
-      </c>
       <c r="N3" t="n">
-        <v>7.5882354</v>
+        <v>7.92</v>
       </c>
       <c r="O3" t="n">
         <v>30</v>
       </c>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8431373</v>
+        <v>1.9</v>
       </c>
       <c r="S3" t="n">
         <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2961165</v>
+        <v>0.31400967</v>
       </c>
       <c r="U3" t="n">
         <v>30</v>
@@ -2934,61 +2934,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.27165353</v>
+        <v>0.2627451</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.34628975</v>
+        <v>0.33333334</v>
       </c>
       <c r="I4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.47058824</v>
+      </c>
+      <c r="K4" t="n">
         <v>7</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.52362204</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
       <c r="L4" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N4" t="n">
-        <v>5.142857</v>
+        <v>5.225806</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P4" t="n">
         <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5396825</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2749004</v>
+        <v>0.26666668</v>
       </c>
       <c r="U4" t="n">
         <v>23</v>
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.22797927</v>
+        <v>0.24873096</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>0.33333334</v>
+        <v>0.34361234</v>
       </c>
       <c r="I5" t="n">
         <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>0.37823835</v>
+        <v>0.40609136</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>4.075472</v>
+        <v>4.5849056</v>
       </c>
       <c r="O5" t="n">
         <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R5" t="n">
         <v>1.3018868</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T5" t="n">
-        <v>0.23737374</v>
+        <v>0.26</v>
       </c>
       <c r="U5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -3068,40 +3068,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.25853658</v>
+        <v>0.25603864</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>0.35564855</v>
+        <v>0.3621399</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4390244</v>
+        <v>0.44444445</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
         <v>52</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N6" t="n">
         <v>1.6666666</v>
@@ -3116,16 +3116,16 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7962963</v>
+        <v>0.8703704</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>0.18134715</v>
+        <v>0.19587629</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3135,16 +3135,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.23350254</v>
+        <v>0.22279793</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
@@ -3153,46 +3153,46 @@
         <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3018018</v>
+        <v>0.29357797</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J7" t="n">
-        <v>0.38071066</v>
+        <v>0.3523316</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>6.1132073</v>
+        <v>3.9807692</v>
       </c>
       <c r="O7" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4716982</v>
+        <v>1.3653846</v>
       </c>
       <c r="S7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T7" t="n">
-        <v>0.27093595</v>
+        <v>0.26153848</v>
       </c>
       <c r="U7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.195</v>
+        <v>0.23529412</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.29464287</v>
+      </c>
+      <c r="I8" t="n">
+        <v>22</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3872549</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" t="n">
+        <v>45</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6666667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.2592592</v>
+      </c>
+      <c r="S8" t="n">
         <v>15</v>
       </c>
-      <c r="E8" t="n">
-        <v>30</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>26</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.25345623</v>
-      </c>
-      <c r="I8" t="n">
-        <v>29</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="K8" t="n">
-        <v>29</v>
-      </c>
-      <c r="L8" t="n">
-        <v>47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>14</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.3518518</v>
-      </c>
-      <c r="S8" t="n">
-        <v>17</v>
-      </c>
       <c r="T8" t="n">
-        <v>0.24875621</v>
+        <v>0.24747474</v>
       </c>
       <c r="U8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.203125</v>
+        <v>0.24489796</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3196347</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.44387755</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L9" t="n">
+        <v>61</v>
+      </c>
+      <c r="M9" t="n">
+        <v>22</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.3333333</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2037038</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.21319798</v>
+      </c>
+      <c r="U9" t="n">
         <v>7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>18</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.30136988</v>
-      </c>
-      <c r="I9" t="n">
-        <v>16</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.36458334</v>
-      </c>
-      <c r="K9" t="n">
-        <v>23</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.6666667</v>
-      </c>
-      <c r="O9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.2777778</v>
-      </c>
-      <c r="S9" t="n">
-        <v>13</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.21649484</v>
-      </c>
-      <c r="U9" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.20895523</v>
+        <v>0.205</v>
       </c>
       <c r="C10" t="n">
         <v>27</v>
       </c>
       <c r="D10" t="n">
+        <v>21</v>
+      </c>
+      <c r="E10" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.25925925</v>
+      </c>
+      <c r="I10" t="n">
+        <v>28</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L10" t="n">
+        <v>67</v>
+      </c>
+      <c r="M10" t="n">
+        <v>28</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.5886075</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.386076</v>
+      </c>
+      <c r="S10" t="n">
         <v>22</v>
       </c>
-      <c r="E10" t="n">
-        <v>24</v>
-      </c>
-      <c r="F10" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.280543</v>
-      </c>
-      <c r="I10" t="n">
-        <v>25</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.37810946</v>
-      </c>
-      <c r="K10" t="n">
-        <v>21</v>
-      </c>
-      <c r="L10" t="n">
-        <v>71</v>
-      </c>
-      <c r="M10" t="n">
-        <v>29</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.689441</v>
-      </c>
-      <c r="O10" t="n">
-        <v>11</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3416148</v>
-      </c>
-      <c r="S10" t="n">
-        <v>16</v>
-      </c>
       <c r="T10" t="n">
-        <v>0.23529412</v>
+        <v>0.23115578</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2647059</v>
+        <v>0.23706897</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34432235</v>
+        <v>0.3220974</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>0.45378152</v>
+        <v>0.37068966</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L11" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M11" t="n">
+        <v>23</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.909091</v>
+      </c>
+      <c r="O11" t="n">
         <v>19</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.7647057</v>
-      </c>
-      <c r="O11" t="n">
-        <v>17</v>
       </c>
       <c r="P11" t="n">
         <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5240642</v>
+        <v>1.6524065</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2874016</v>
+        <v>0.29803923</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -3470,61 +3470,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.22699386</v>
+        <v>0.23076923</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3152174</v>
+        <v>0.32126698</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>0.41104296</v>
+        <v>0.44615385</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>1.1666666</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
       <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
+        <v>0.7962963</v>
+      </c>
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
       <c r="T12" t="n">
-        <v>0.17177914</v>
+        <v>0.16410257</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2371134</v>
+        <v>0.25888324</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.30092594</v>
+        <v>0.31651375</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.43814433</v>
+        <v>0.4720812</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8461537</v>
+        <v>5.647059</v>
       </c>
       <c r="O13" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="n">
         <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5192307</v>
+        <v>1.7058823</v>
       </c>
       <c r="S13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2562814</v>
+        <v>0.2713568</v>
       </c>
       <c r="U13" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -3604,61 +3604,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.31651375</v>
+        <v>0.31075698</v>
       </c>
       <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.37410071</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5179283</v>
+      </c>
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="n">
-        <v>42</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>13</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.3852459</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.51376146</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
       <c r="L14" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="M14" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1923075</v>
+        <v>5.25</v>
       </c>
       <c r="O14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6346154</v>
+        <v>1.6166667</v>
       </c>
       <c r="S14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T14" t="n">
-        <v>0.28502417</v>
+        <v>0.28451884</v>
       </c>
       <c r="U14" t="n">
         <v>26</v>
@@ -3671,16 +3671,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2583732</v>
+        <v>0.27272728</v>
       </c>
       <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>32</v>
+      </c>
+      <c r="E15" t="n">
         <v>11</v>
-      </c>
-      <c r="D15" t="n">
-        <v>30</v>
-      </c>
-      <c r="E15" t="n">
-        <v>14</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
@@ -3689,46 +3689,46 @@
         <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>0.30044842</v>
+        <v>0.31858408</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3875598</v>
+        <v>0.40669855</v>
       </c>
       <c r="K15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M15" t="n">
         <v>25</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6751595</v>
+        <v>5.33121</v>
       </c>
       <c r="O15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3949045</v>
+        <v>1.3566879</v>
       </c>
       <c r="S15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T15" t="n">
-        <v>0.25853658</v>
+        <v>0.25</v>
       </c>
       <c r="U15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -3738,46 +3738,46 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.21875</v>
+        <v>0.23232323</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H16" t="n">
-        <v>0.30092594</v>
+        <v>0.29816514</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3125</v>
+        <v>0.34343433</v>
       </c>
       <c r="K16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L16" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N16" t="n">
-        <v>2.892857</v>
+        <v>3.375</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
         <v>5</v>
@@ -3786,13 +3786,13 @@
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1785715</v>
+        <v>1.2321428</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>0.20895523</v>
+        <v>0.21078432</v>
       </c>
       <c r="U16" t="n">
         <v>6</v>
@@ -3805,46 +3805,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.33023256</v>
+        <v>0.30917874</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.41269842</v>
+        <v>0.39166668</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.63255817</v>
+        <v>0.5797101</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4363637</v>
+        <v>3.1090908</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
         <v>5</v>
@@ -3853,16 +3853,16 @@
         <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1454545</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>0.215</v>
+        <v>0.19897959</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.26804122</v>
+        <v>0.26612905</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>0.328125</v>
+        <v>0.3210332</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
-        <v>0.41237113</v>
+        <v>0.41935483</v>
       </c>
       <c r="K18" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" t="n">
+        <v>52</v>
+      </c>
+      <c r="M18" t="n">
         <v>13</v>
       </c>
-      <c r="L18" t="n">
-        <v>62</v>
-      </c>
-      <c r="M18" t="n">
-        <v>21</v>
-      </c>
       <c r="N18" t="n">
+        <v>3.0983605</v>
+      </c>
+      <c r="O18" t="n">
         <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>5</v>
       </c>
       <c r="P18" t="n">
         <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9166666999999999</v>
+        <v>0.8852459</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0.18320611</v>
+        <v>0.17727272</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25603864</v>
+        <v>0.26923078</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.34854773</v>
+      </c>
+      <c r="I19" t="n">
         <v>8</v>
       </c>
-      <c r="G19" t="n">
-        <v>13</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
+        <v>0.45673078</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>53</v>
+      </c>
+      <c r="M19" t="n">
+        <v>15</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.3333333</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6</v>
+      </c>
+      <c r="P19" t="n">
         <v>9</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.43961352</v>
-      </c>
-      <c r="K19" t="n">
-        <v>9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>63</v>
-      </c>
-      <c r="M19" t="n">
-        <v>23</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.5660377</v>
-      </c>
-      <c r="O19" t="n">
-        <v>8</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0566038</v>
+        <v>1.0925926</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>0.18518518</v>
+        <v>0.20103092</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -4006,61 +4006,61 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.29761904</v>
+        <v>0.30241936</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>12</v>
       </c>
       <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.37809187</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4919355</v>
+      </c>
+      <c r="K20" t="n">
         <v>4</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.37630662</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.48412699</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
+        <v>44</v>
+      </c>
+      <c r="M20" t="n">
         <v>5</v>
       </c>
-      <c r="L20" t="n">
-        <v>46</v>
-      </c>
-      <c r="M20" t="n">
-        <v>10</v>
-      </c>
       <c r="N20" t="n">
-        <v>6.822581</v>
+        <v>6.571429</v>
       </c>
       <c r="O20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
         <v>29</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7096775</v>
+        <v>1.7936507</v>
       </c>
       <c r="S20" t="n">
         <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2923077</v>
+        <v>0.30597016</v>
       </c>
       <c r="U20" t="n">
         <v>29</v>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2290749</v>
+        <v>0.25</v>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
         <v>31</v>
@@ -4085,52 +4085,52 @@
         <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.28225806</v>
+        <v>0.30078125</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>0.41409692</v>
+        <v>0.44915253</v>
       </c>
       <c r="K21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M21" t="n">
         <v>30</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9836066</v>
+        <v>4.1311474</v>
       </c>
       <c r="O21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R21" t="n">
         <v>1.2459016</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T21" t="n">
-        <v>0.24789916</v>
+        <v>0.25311205</v>
       </c>
       <c r="U21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23880596</v>
+        <v>0.22317597</v>
       </c>
       <c r="C22" t="n">
+        <v>23</v>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
+        <v>28</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>19</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.30566037</v>
+      </c>
+      <c r="I22" t="n">
+        <v>17</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.36480686</v>
+      </c>
+      <c r="K22" t="n">
+        <v>23</v>
+      </c>
+      <c r="L22" t="n">
+        <v>58</v>
+      </c>
+      <c r="M22" t="n">
+        <v>19</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.40678</v>
+      </c>
+      <c r="O22" t="n">
+        <v>27</v>
+      </c>
+      <c r="P22" t="n">
         <v>13</v>
       </c>
-      <c r="D22" t="n">
-        <v>19</v>
-      </c>
-      <c r="E22" t="n">
-        <v>27</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="Q22" t="n">
+        <v>25</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4576272</v>
+      </c>
+      <c r="S22" t="n">
+        <v>23</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.26271185</v>
+      </c>
+      <c r="U22" t="n">
         <v>22</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3187773</v>
-      </c>
-      <c r="I22" t="n">
-        <v>13</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.3880597</v>
-      </c>
-      <c r="K22" t="n">
-        <v>17</v>
-      </c>
-      <c r="L22" t="n">
-        <v>51</v>
-      </c>
-      <c r="M22" t="n">
-        <v>13</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5.8235292</v>
-      </c>
-      <c r="O22" t="n">
-        <v>25</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>18</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4313725</v>
-      </c>
-      <c r="S22" t="n">
-        <v>20</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.2647059</v>
-      </c>
-      <c r="U22" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -4207,64 +4207,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.29032257</v>
+        <v>0.28248587</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>16</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.37438422</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.43502825</v>
+      </c>
+      <c r="K23" t="n">
+        <v>13</v>
+      </c>
+      <c r="L23" t="n">
+        <v>41</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>18</v>
+      </c>
+      <c r="P23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" t="n">
-        <v>9</v>
-      </c>
-      <c r="G23" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.37398374</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.4562212</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="Q23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" t="n">
-        <v>48</v>
-      </c>
-      <c r="M23" t="n">
-        <v>12</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5.4339623</v>
-      </c>
-      <c r="O23" t="n">
-        <v>22</v>
-      </c>
-      <c r="P23" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>25</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.4528302</v>
+        <v>1.3777778</v>
       </c>
       <c r="S23" t="n">
         <v>21</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2682927</v>
+        <v>0.25443786</v>
       </c>
       <c r="U23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22026432</v>
+        <v>0.22707424</v>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
         <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H24" t="n">
-        <v>0.28629032</v>
+        <v>0.292</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3215859</v>
+        <v>0.32751092</v>
       </c>
       <c r="K24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L24" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M24" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3934426</v>
+        <v>3.6290324</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P24" t="n">
         <v>7</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1475409</v>
+        <v>1.1451613</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>0.21621622</v>
+        <v>0.22807017</v>
       </c>
       <c r="U24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2603306</v>
+        <v>0.27160493</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
       </c>
       <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.35036495</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.47325101</v>
+      </c>
+      <c r="K25" t="n">
         <v>5</v>
       </c>
-      <c r="H25" t="n">
-        <v>0.32958803</v>
-      </c>
-      <c r="I25" t="n">
-        <v>11</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.46280992</v>
-      </c>
-      <c r="K25" t="n">
-        <v>6</v>
-      </c>
       <c r="L25" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N25" t="n">
-        <v>6.639344</v>
+        <v>4.935484</v>
       </c>
       <c r="O25" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="P25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4918033</v>
+        <v>1.3387097</v>
       </c>
       <c r="S25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="T25" t="n">
-        <v>0.27868852</v>
+        <v>0.25210086</v>
       </c>
       <c r="U25" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.21025641</v>
+        <v>0.21428572</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H26" t="n">
         <v>0.28767124</v>
       </c>
       <c r="I26" t="n">
+        <v>26</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.37244898</v>
+      </c>
+      <c r="K26" t="n">
         <v>21</v>
       </c>
-      <c r="J26" t="n">
-        <v>0.35384616</v>
-      </c>
-      <c r="K26" t="n">
-        <v>24</v>
-      </c>
       <c r="L26" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M26" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4076433</v>
+        <v>3.331169</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R26" t="n">
-        <v>1.0318471</v>
+        <v>1.1883117</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T26" t="n">
-        <v>0.21243523</v>
+        <v>0.25</v>
       </c>
       <c r="U26" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -4475,46 +4475,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2247191</v>
+        <v>0.19123507</v>
       </c>
       <c r="C27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H27" t="n">
-        <v>0.28911564</v>
+        <v>0.25274727</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39700374</v>
+        <v>0.3426295</v>
       </c>
       <c r="K27" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L27" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M27" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="N27" t="n">
         <v>3.8028169</v>
       </c>
       <c r="O27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
@@ -4523,16 +4523,16 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2957747</v>
+        <v>1.2394366</v>
       </c>
       <c r="S27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>0.24264705</v>
+        <v>0.23220974</v>
       </c>
       <c r="U27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -4542,61 +4542,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.21238938</v>
+        <v>0.2446352</v>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2682927</v>
+        <v>0.2952756</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>0.37168142</v>
+        <v>0.42918456</v>
       </c>
       <c r="K28" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N28" t="n">
-        <v>5.0163937</v>
+        <v>5.163934</v>
       </c>
       <c r="O28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P28" t="n">
         <v>13</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.0655738</v>
+        <v>1.0983607</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23580787</v>
+        <v>0.24347825</v>
       </c>
       <c r="U28" t="n">
         <v>12</v>
@@ -4609,61 +4609,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.21118012</v>
+        <v>0.21989529</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D29" t="n">
+        <v>26</v>
+      </c>
+      <c r="E29" t="n">
         <v>19</v>
       </c>
-      <c r="E29" t="n">
-        <v>27</v>
-      </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2742857</v>
+        <v>0.29383886</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39130434</v>
+        <v>0.42931938</v>
       </c>
       <c r="K29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L29" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N29" t="n">
-        <v>5.6</v>
+        <v>5.1666665</v>
       </c>
       <c r="O29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.3333334</v>
       </c>
       <c r="S29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2762431</v>
+        <v>0.27102804</v>
       </c>
       <c r="U29" t="n">
         <v>24</v>
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.18592964</v>
+        <v>0.2</v>
       </c>
       <c r="C30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D30" t="n">
+        <v>25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>23</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="n">
         <v>22</v>
       </c>
-      <c r="E30" t="n">
-        <v>24</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5</v>
-      </c>
-      <c r="G30" t="n">
-        <v>26</v>
-      </c>
       <c r="H30" t="n">
-        <v>0.23113208</v>
+        <v>0.24413146</v>
       </c>
       <c r="I30" t="n">
         <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>0.28140703</v>
+        <v>0.305</v>
       </c>
       <c r="K30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L30" t="n">
         <v>34</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.0588236</v>
+        <v>4.5882354</v>
       </c>
       <c r="O30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
+        <v>7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.2156863</v>
+      </c>
+      <c r="S30" t="n">
+        <v>11</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.23076923</v>
+      </c>
+      <c r="U30" t="n">
         <v>9</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.0784314</v>
-      </c>
-      <c r="S30" t="n">
-        <v>7</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.20634921</v>
-      </c>
-      <c r="U30" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3004926</v>
+        <v>0.28078818</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>0.38235295</v>
+        <v>0.3601695</v>
       </c>
       <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.49753696</v>
+      </c>
+      <c r="K31" t="n">
         <v>3</v>
       </c>
-      <c r="J31" t="n">
-        <v>0.5714286</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
       <c r="L31" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N31" t="n">
         <v>6.6666665</v>
       </c>
       <c r="O31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="R31" t="n">
         <v>1.574074</v>
       </c>
       <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.29577464</v>
+      </c>
+      <c r="U31" t="n">
         <v>27</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.29166666</v>
-      </c>
-      <c r="U31" t="n">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23712</v>
+        <v>0.23741691</v>
       </c>
       <c r="C2" t="n">
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30713874</v>
+        <v>0.30793288</v>
       </c>
       <c r="I2" t="n">
         <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3824</v>
+        <v>0.3846154</v>
       </c>
       <c r="K2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>4.246581</v>
+        <v>4.222443</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>115</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28037</v>
+        <v>1.2737763</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2510288</v>
+        <v>0.25031328</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24523586</v>
+        <v>0.24412128</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
@@ -622,34 +622,34 @@
         <v>421</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
         <v>116</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32293987</v>
+        <v>0.32202923</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>0.40299907</v>
+        <v>0.4012995</v>
       </c>
       <c r="K3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="M3" t="n">
         <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2150536</v>
+        <v>5.1763315</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
@@ -661,13 +661,13 @@
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4778973</v>
+        <v>1.4721893</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.267117</v>
+        <v>0.26636225</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,61 +680,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24723364</v>
+        <v>0.24663536</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>121</v>
+      </c>
+      <c r="G4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" t="n">
-        <v>120</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.31251782</v>
+        <v>0.31197065</v>
       </c>
       <c r="I4" t="n">
         <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41131836</v>
+        <v>0.41032863</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="M4" t="n">
         <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6014552</v>
+        <v>3.610088</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q4" t="n">
         <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2332255</v>
+        <v>1.2285829</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22974293</v>
+        <v>0.22920696</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
@@ -747,46 +747,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23829114</v>
+        <v>0.23800564</v>
       </c>
       <c r="C5" t="n">
         <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>115</v>
+      </c>
+      <c r="G5" t="n">
         <v>13</v>
       </c>
-      <c r="F5" t="n">
-        <v>111</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.31973168</v>
+        <v>0.319202</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39651898</v>
+        <v>0.39887112</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.357595</v>
+        <v>4.3221135</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
         <v>108</v>
@@ -795,13 +795,13 @@
         <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3670886</v>
+        <v>1.3573385</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.25370827</v>
+        <v>0.2520674</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,64 +814,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24456698</v>
+        <v>0.24398074</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E6" t="n">
         <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.31490105</v>
+        <v>0.3147135</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38858256</v>
+        <v>0.38940609</v>
       </c>
       <c r="K6" t="n">
         <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="M6" t="n">
         <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6516395</v>
+        <v>3.611674</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
         <v>95</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2307377</v>
+        <v>1.2294285</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>0.23958333</v>
+        <v>0.23831022</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24336973</v>
+        <v>0.24359371</v>
       </c>
       <c r="C7" t="n">
         <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G7" t="n">
         <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33585927</v>
+        <v>0.3361007</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40936038</v>
+        <v>0.41031182</v>
       </c>
       <c r="K7" t="n">
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="M7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N7" t="n">
-        <v>4.352753</v>
+        <v>4.338334</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2761374</v>
+        <v>1.2791157</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2454805</v>
+        <v>0.24623588</v>
       </c>
       <c r="U7" t="n">
         <v>18</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24100257</v>
+        <v>0.24044587</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
@@ -966,25 +966,25 @@
         <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.319155</v>
+        <v>0.31861913</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41323906</v>
+        <v>0.41210192</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>833</v>
+        <v>844</v>
       </c>
       <c r="M8" t="n">
         <v>24</v>
       </c>
       <c r="N8" t="n">
-        <v>4.194175</v>
+        <v>4.1488595</v>
       </c>
       <c r="O8" t="n">
         <v>14</v>
@@ -996,16 +996,16 @@
         <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3313106</v>
+        <v>1.3265306</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23985718</v>
+        <v>0.23875321</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22847043</v>
+        <v>0.22942485</v>
       </c>
       <c r="C9" t="n">
+        <v>27</v>
+      </c>
+      <c r="D9" t="n">
+        <v>391</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>118</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.30999434</v>
+      </c>
+      <c r="I9" t="n">
+        <v>22</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3937083</v>
+      </c>
+      <c r="K9" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" t="n">
+        <v>892</v>
+      </c>
+      <c r="M9" t="n">
         <v>28</v>
       </c>
-      <c r="D9" t="n">
-        <v>388</v>
-      </c>
-      <c r="E9" t="n">
-        <v>24</v>
-      </c>
-      <c r="F9" t="n">
-        <v>115</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.30936074</v>
-      </c>
-      <c r="I9" t="n">
-        <v>24</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.3917095</v>
-      </c>
-      <c r="K9" t="n">
-        <v>23</v>
-      </c>
-      <c r="L9" t="n">
-        <v>884</v>
-      </c>
-      <c r="M9" t="n">
-        <v>29</v>
-      </c>
       <c r="N9" t="n">
-        <v>4.478261</v>
+        <v>4.483871</v>
       </c>
       <c r="O9" t="n">
         <v>22</v>
       </c>
       <c r="P9" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R9" t="n">
-        <v>1.437198</v>
+        <v>1.4384707</v>
       </c>
       <c r="S9" t="n">
         <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>0.24674086</v>
+        <v>0.246933</v>
       </c>
       <c r="U9" t="n">
         <v>19</v>
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22749119</v>
+        <v>0.22838138</v>
       </c>
       <c r="C10" t="n">
         <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E10" t="n">
         <v>29</v>
@@ -1100,25 +1100,25 @@
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3088068</v>
+        <v>0.30935657</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3675104</v>
+        <v>0.3677542</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>793</v>
+        <v>804</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>3.757732</v>
+        <v>3.7285209</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
@@ -1130,13 +1130,13 @@
         <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2632831</v>
+        <v>1.2628481</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23691723</v>
+        <v>0.23673469</v>
       </c>
       <c r="U10" t="n">
         <v>8</v>
@@ -1149,61 +1149,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25666973</v>
+        <v>0.25591984</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G11" t="n">
         <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32813355</v>
+        <v>0.32737127</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42195645</v>
+        <v>0.4210686</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="M11" t="n">
         <v>25</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4682193</v>
+        <v>5.4591317</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q11" t="n">
         <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5219108</v>
+        <v>1.5170121</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2872846</v>
+        <v>0.28672358</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,61 +1216,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23570745</v>
+        <v>0.2364096</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G12" t="n">
         <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31473088</v>
+        <v>0.3151991</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>0.40114978</v>
+        <v>0.4010746</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6383748</v>
+        <v>3.6315162</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
         <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2115848</v>
+        <v>1.2093116</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23323709</v>
+        <v>0.23308986</v>
       </c>
       <c r="U12" t="n">
         <v>7</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24139</v>
+        <v>0.24179196</v>
       </c>
       <c r="C13" t="n">
         <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31463483</v>
+        <v>0.3151249</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41048712</v>
+        <v>0.41301012</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.805894</v>
+        <v>4.7869363</v>
       </c>
       <c r="O13" t="n">
         <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q13" t="n">
         <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4039294</v>
+        <v>1.399689</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24207221</v>
+        <v>0.24176507</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
@@ -1350,16 +1350,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24765478</v>
+        <v>0.24604896</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
         <v>97</v>
@@ -1368,43 +1368,43 @@
         <v>23</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31757134</v>
+        <v>0.31586245</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39962476</v>
+        <v>0.39665323</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="M14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8944225</v>
+        <v>4.911997</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4498007</v>
+        <v>1.4455407</v>
       </c>
       <c r="S14" t="n">
         <v>28</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26384568</v>
+        <v>0.26333642</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2401624</v>
+        <v>0.24050634</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -1432,49 +1432,49 @@
         <v>108</v>
       </c>
       <c r="G15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3150838</v>
+        <v>0.31538248</v>
       </c>
       <c r="I15" t="n">
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>0.39287946</v>
+        <v>0.39271381</v>
       </c>
       <c r="K15" t="n">
         <v>22</v>
       </c>
       <c r="L15" t="n">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.645161</v>
+        <v>4.654438</v>
       </c>
       <c r="O15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q15" t="n">
+        <v>11</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>26</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.2388993</v>
+      </c>
+      <c r="U15" t="n">
         <v>13</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3978494</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.23809524</v>
-      </c>
-      <c r="U15" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26389757</v>
+        <v>0.26306027</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -1502,43 +1502,43 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34555402</v>
+        <v>0.34408894</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.43753904</v>
+        <v>0.43523955</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="M16" t="n">
         <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5021818</v>
+        <v>3.5604396</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q16" t="n">
         <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1364539</v>
+        <v>1.1420722</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.21610306</v>
+        <v>0.2166295</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2539582</v>
+        <v>0.253605</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
         <v>97</v>
@@ -1569,25 +1569,25 @@
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33090705</v>
+        <v>0.3306541</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4126029</v>
+        <v>0.41128528</v>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="M17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N17" t="n">
-        <v>4.01555</v>
+        <v>4.0153847</v>
       </c>
       <c r="O17" t="n">
         <v>10</v>
@@ -1596,19 +1596,19 @@
         <v>93</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2344497</v>
+        <v>1.2366863</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22769427</v>
+        <v>0.22858046</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2550505</v>
+        <v>0.2545567</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G18" t="n">
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33695048</v>
+        <v>0.33714285</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39772728</v>
+        <v>0.3978993</v>
       </c>
       <c r="K18" t="n">
         <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>759</v>
+        <v>776</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3318691</v>
+        <v>3.3644202</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1585463</v>
+        <v>1.1579154</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21675359</v>
+        <v>0.21707161</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,46 +1685,46 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24720149</v>
+        <v>0.24791859</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3229081</v>
+      </c>
+      <c r="I19" t="n">
         <v>9</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.32216993</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10</v>
-      </c>
       <c r="J19" t="n">
-        <v>0.41449004</v>
+        <v>0.4156645</v>
       </c>
       <c r="K19" t="n">
         <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="M19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N19" t="n">
-        <v>4.66998</v>
+        <v>4.652242</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P19" t="n">
         <v>113</v>
@@ -1733,16 +1733,16 @@
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.374155</v>
+        <v>1.3760818</v>
       </c>
       <c r="S19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2514747</v>
+        <v>0.25168815</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23536776</v>
+        <v>0.23418114</v>
       </c>
       <c r="C20" t="n">
         <v>26</v>
@@ -1767,49 +1767,49 @@
         <v>111</v>
       </c>
       <c r="G20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30397967</v>
+        <v>0.30371612</v>
       </c>
       <c r="I20" t="n">
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>0.38372457</v>
+        <v>0.38120347</v>
       </c>
       <c r="K20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L20" t="n">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="M20" t="n">
         <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>4.315748</v>
+        <v>4.312427</v>
       </c>
       <c r="O20" t="n">
         <v>18</v>
       </c>
       <c r="P20" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3181102</v>
+        <v>1.3171016</v>
       </c>
       <c r="S20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2393321</v>
+        <v>0.23882425</v>
       </c>
       <c r="U20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -1819,64 +1819,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.23676611</v>
+        <v>0.2370676</v>
       </c>
       <c r="C21" t="n">
         <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.31713554</v>
+        <v>0.3174023</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>0.42348412</v>
+        <v>0.42494446</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4006398</v>
+        <v>3.3856804</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.189924</v>
+        <v>1.1914557</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2284069</v>
+        <v>0.22823678</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2359199</v>
+        <v>0.23574969</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E22" t="n">
         <v>18</v>
@@ -1904,43 +1904,43 @@
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30332956</v>
+        <v>0.3028779</v>
       </c>
       <c r="I22" t="n">
         <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>0.40050063</v>
+        <v>0.39931846</v>
       </c>
       <c r="K22" t="n">
         <v>16</v>
       </c>
       <c r="L22" t="n">
-        <v>830</v>
+        <v>839</v>
       </c>
       <c r="M22" t="n">
         <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.300317</v>
+        <v>4.27597</v>
       </c>
       <c r="O22" t="n">
         <v>17</v>
       </c>
       <c r="P22" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3240888</v>
+        <v>1.3241867</v>
       </c>
       <c r="S22" t="n">
         <v>17</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25642595</v>
+        <v>0.25689185</v>
       </c>
       <c r="U22" t="n">
         <v>26</v>
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.26167938</v>
+        <v>0.2611694</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G23" t="n">
         <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>0.34044853</v>
+        <v>0.34014326</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.42290077</v>
+        <v>0.42278862</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="M23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3195715</v>
+        <v>4.3128643</v>
       </c>
       <c r="O23" t="n">
         <v>19</v>
       </c>
       <c r="P23" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3136165</v>
+        <v>1.3175281</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23903508</v>
+        <v>0.23888378</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -2020,61 +2020,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22539786</v>
+        <v>0.22586873</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G24" t="n">
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.30046538</v>
+        <v>0.3025862</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.37154922</v>
+        <v>0.3716216</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="M24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N24" t="n">
-        <v>4.203852</v>
+        <v>4.233823</v>
       </c>
       <c r="O24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3338684</v>
+        <v>1.3362445</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>0.24728434</v>
+        <v>0.2471555</v>
       </c>
       <c r="U24" t="n">
         <v>20</v>
@@ -2087,61 +2087,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25597268</v>
+        <v>0.2556853</v>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G25" t="n">
         <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30961868</v>
+        <v>0.30908066</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>0.42165685</v>
+        <v>0.4213276</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.528962</v>
+        <v>4.5017905</v>
       </c>
       <c r="O25" t="n">
         <v>23</v>
       </c>
       <c r="P25" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q25" t="n">
         <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3793242</v>
+        <v>1.3752487</v>
       </c>
       <c r="S25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.25023848</v>
+        <v>0.249528</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,61 +2154,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22961783</v>
+        <v>0.22933754</v>
       </c>
       <c r="C26" t="n">
+        <v>28</v>
+      </c>
+      <c r="D26" t="n">
+        <v>384</v>
+      </c>
+      <c r="E26" t="n">
         <v>27</v>
-      </c>
-      <c r="D26" t="n">
-        <v>383</v>
-      </c>
-      <c r="E26" t="n">
-        <v>26</v>
       </c>
       <c r="F26" t="n">
         <v>113</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" t="n">
-        <v>0.31006217</v>
+        <v>0.3098237</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3786624</v>
+        <v>0.37791798</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>822</v>
+        <v>832</v>
       </c>
       <c r="M26" t="n">
         <v>21</v>
       </c>
       <c r="N26" t="n">
-        <v>3.609282</v>
+        <v>3.6282907</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.179294</v>
+        <v>1.1846758</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.23991102</v>
+        <v>0.24104337</v>
       </c>
       <c r="U26" t="n">
         <v>15</v>
@@ -2221,64 +2221,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24333869</v>
+        <v>0.24268448</v>
       </c>
       <c r="C27" t="n">
         <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31946424</v>
+        <v>0.31845155</v>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3929374</v>
+        <v>0.39249364</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L27" t="n">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.171348</v>
+        <v>4.1373563</v>
       </c>
       <c r="O27" t="n">
         <v>13</v>
       </c>
       <c r="P27" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3314606</v>
+        <v>1.3267169</v>
       </c>
       <c r="S27" t="n">
         <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25181904</v>
+        <v>0.25117445</v>
       </c>
       <c r="U27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -2288,43 +2288,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.25912645</v>
+        <v>0.2600709</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" t="n">
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3343949</v>
+        <v>0.33486107</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4005867</v>
+        <v>0.40251368</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7929354</v>
+        <v>3.7626505</v>
       </c>
       <c r="O28" t="n">
         <v>9</v>
@@ -2333,16 +2333,16 @@
         <v>116</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1693057</v>
+        <v>1.1686747</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23241492</v>
+        <v>0.23210272</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24417491</v>
+        <v>0.24384081</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E29" t="n">
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31965813</v>
+        <v>0.31923294</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3973827</v>
+        <v>0.39734682</v>
       </c>
       <c r="K29" t="n">
         <v>19</v>
       </c>
       <c r="L29" t="n">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="M29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N29" t="n">
-        <v>4.0674477</v>
+        <v>4.120655</v>
       </c>
       <c r="O29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2455574</v>
+        <v>1.2489014</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24067046</v>
+        <v>0.24108818</v>
       </c>
       <c r="U29" t="n">
         <v>16</v>
@@ -2422,64 +2422,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24405706</v>
+        <v>0.24396363</v>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D30" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>0.30532375</v>
+        <v>0.3060296</v>
       </c>
       <c r="I30" t="n">
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.38288432</v>
+        <v>0.3835058</v>
       </c>
       <c r="K30" t="n">
         <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="M30" t="n">
         <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.069972</v>
+        <v>4.116832</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P30" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q30" t="n">
         <v>14</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2966813</v>
+        <v>1.3069307</v>
       </c>
       <c r="S30" t="n">
         <v>14</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23901974</v>
+        <v>0.23935667</v>
       </c>
       <c r="U30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -2489,61 +2489,61 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.25053665</v>
+        <v>0.25015178</v>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32465753</v>
+        <v>0.32456616</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.43483594</v>
+        <v>0.43442622</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="M31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>4.76036</v>
+        <v>4.7524176</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3967943</v>
+        <v>1.397292</v>
       </c>
       <c r="S31" t="n">
         <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25968522</v>
+        <v>0.25973636</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,64 +2800,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23175965</v>
+        <v>0.24686192</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" t="n">
         <v>13</v>
       </c>
-      <c r="F2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" t="n">
-        <v>19</v>
-      </c>
       <c r="H2" t="n">
-        <v>0.29803923</v>
+        <v>0.32089552</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J2" t="n">
-        <v>0.36480686</v>
+        <v>0.40585774</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M2" t="n">
         <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3934426</v>
+        <v>3.2459016</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1311475</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0.24892704</v>
+        <v>0.22807017</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.19587629</v>
+        <v>0.18134715</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>30</v>
@@ -2882,49 +2882,49 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>0.25943395</v>
+        <v>0.25118482</v>
       </c>
       <c r="I3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2783505</v>
+        <v>0.26943004</v>
       </c>
       <c r="K3" t="n">
         <v>30</v>
       </c>
       <c r="L3" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
-        <v>7.92</v>
+        <v>6.979592</v>
       </c>
       <c r="O3" t="n">
         <v>30</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9</v>
+        <v>1.6938776</v>
       </c>
       <c r="S3" t="n">
         <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0.31400967</v>
+        <v>0.2893401</v>
       </c>
       <c r="U3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2627451</v>
+        <v>0.244</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.30769232</v>
+      </c>
+      <c r="I4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" t="n">
+        <v>71</v>
+      </c>
+      <c r="M4" t="n">
+        <v>29</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.4590163</v>
+      </c>
+      <c r="O4" t="n">
+        <v>25</v>
+      </c>
+      <c r="P4" t="n">
         <v>12</v>
       </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.33333334</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.47058824</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>65</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>26</v>
       </c>
-      <c r="N4" t="n">
-        <v>5.225806</v>
-      </c>
-      <c r="O4" t="n">
-        <v>23</v>
-      </c>
-      <c r="P4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.409836</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T4" t="n">
-        <v>0.26666668</v>
+        <v>0.2532189</v>
       </c>
       <c r="U4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.24873096</v>
+        <v>0.23684211</v>
       </c>
       <c r="C5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.32093024</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4368421</v>
+      </c>
+      <c r="K5" t="n">
         <v>14</v>
       </c>
-      <c r="D5" t="n">
-        <v>27</v>
-      </c>
-      <c r="E5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.34361234</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.40609136</v>
-      </c>
-      <c r="K5" t="n">
-        <v>18</v>
-      </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5849056</v>
+        <v>3.9056604</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P5" t="n">
         <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3018868</v>
+        <v>1.0566038</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>0.26</v>
+        <v>0.22164948</v>
       </c>
       <c r="U5" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3068,16 +3068,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.25603864</v>
+        <v>0.25490198</v>
       </c>
       <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" t="n">
         <v>12</v>
-      </c>
-      <c r="D6" t="n">
-        <v>36</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>9</v>
@@ -3086,46 +3086,46 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3621399</v>
+        <v>0.35443038</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.44444445</v>
+        <v>0.44607842</v>
       </c>
       <c r="K6" t="n">
         <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6666666</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8703704</v>
+        <v>0.9259259</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>0.19587629</v>
+        <v>0.1897436</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3135,40 +3135,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.22279793</v>
+        <v>0.23857868</v>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3063063</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.40609136</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16</v>
+      </c>
+      <c r="L7" t="n">
+        <v>46</v>
+      </c>
+      <c r="M7" t="n">
         <v>6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>22</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.29357797</v>
-      </c>
-      <c r="I7" t="n">
-        <v>24</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.3523316</v>
-      </c>
-      <c r="K7" t="n">
-        <v>25</v>
-      </c>
-      <c r="L7" t="n">
-        <v>51</v>
-      </c>
-      <c r="M7" t="n">
-        <v>12</v>
       </c>
       <c r="N7" t="n">
         <v>3.9807692</v>
@@ -3177,22 +3177,22 @@
         <v>14</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3653846</v>
+        <v>1.4038461</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T7" t="n">
-        <v>0.26153848</v>
+        <v>0.27272728</v>
       </c>
       <c r="U7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -3202,49 +3202,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.23529412</v>
+        <v>0.22335026</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.28372094</v>
+      </c>
+      <c r="I8" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.36548224</v>
+      </c>
+      <c r="K8" t="n">
+        <v>23</v>
+      </c>
+      <c r="L8" t="n">
+        <v>49</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" t="n">
         <v>6</v>
-      </c>
-      <c r="G8" t="n">
-        <v>22</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.29464287</v>
-      </c>
-      <c r="I8" t="n">
-        <v>22</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.3872549</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20</v>
-      </c>
-      <c r="L8" t="n">
-        <v>45</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.6666667</v>
-      </c>
-      <c r="O8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P8" t="n">
-        <v>7</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -3253,13 +3253,13 @@
         <v>1.2592592</v>
       </c>
       <c r="S8" t="n">
+        <v>13</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.23469388</v>
+      </c>
+      <c r="U8" t="n">
         <v>15</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.24747474</v>
-      </c>
-      <c r="U8" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -3272,61 +3272,61 @@
         <v>0.24489796</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3101852</v>
+      </c>
+      <c r="I9" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.46938777</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>63</v>
+      </c>
+      <c r="M9" t="n">
+        <v>26</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.8333333</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.1481482</v>
+      </c>
+      <c r="S9" t="n">
         <v>9</v>
       </c>
-      <c r="G9" t="n">
-        <v>13</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.3196347</v>
-      </c>
-      <c r="I9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.44387755</v>
-      </c>
-      <c r="K9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L9" t="n">
-        <v>61</v>
-      </c>
-      <c r="M9" t="n">
-        <v>22</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.3333333</v>
-      </c>
-      <c r="O9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>0.21025641</v>
+      </c>
+      <c r="U9" t="n">
         <v>4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.2037038</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.21319798</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3336,64 +3336,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.205</v>
+        <v>0.22167487</v>
       </c>
       <c r="C10" t="n">
+        <v>26</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.280543</v>
+      </c>
+      <c r="I10" t="n">
         <v>27</v>
       </c>
-      <c r="D10" t="n">
+      <c r="J10" t="n">
+        <v>0.39408866</v>
+      </c>
+      <c r="K10" t="n">
         <v>21</v>
       </c>
-      <c r="E10" t="n">
-        <v>28</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.25925925</v>
-      </c>
-      <c r="I10" t="n">
-        <v>28</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K10" t="n">
-        <v>19</v>
-      </c>
       <c r="L10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M10" t="n">
         <v>28</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5886075</v>
+        <v>3.2468355</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q10" t="n">
         <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.386076</v>
+        <v>1.3481013</v>
       </c>
       <c r="S10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23115578</v>
+        <v>0.2244898</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -3403,43 +3403,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.23706897</v>
+        <v>0.23175965</v>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3220974</v>
+        <v>0.31460676</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>0.37068966</v>
+        <v>0.37339056</v>
       </c>
       <c r="K11" t="n">
         <v>22</v>
       </c>
       <c r="L11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>4.909091</v>
+        <v>4.695652</v>
       </c>
       <c r="O11" t="n">
         <v>19</v>
@@ -3448,19 +3448,19 @@
         <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6524065</v>
+        <v>1.5326087</v>
       </c>
       <c r="S11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T11" t="n">
-        <v>0.29803923</v>
+        <v>0.28163266</v>
       </c>
       <c r="U11" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.23076923</v>
+        <v>0.2525773</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -3485,46 +3485,46 @@
         <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.32126698</v>
+        <v>0.3438914</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.44615385</v>
+        <v>0.46907216</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M12" t="n">
         <v>15</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1666666</v>
+        <v>1.6666666</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7962963</v>
+        <v>0.8888889</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.16410257</v>
+        <v>0.18274112</v>
       </c>
       <c r="U12" t="n">
         <v>1</v>
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.25888324</v>
+        <v>0.25</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31651375</v>
+        <v>0.3108108</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4720812</v>
+        <v>0.46</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>5.647059</v>
+        <v>4.9411764</v>
       </c>
       <c r="O13" t="n">
+        <v>22</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="n">
         <v>26</v>
       </c>
-      <c r="P13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>25</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.7058823</v>
+        <v>1.5490196</v>
       </c>
       <c r="S13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2713568</v>
+        <v>0.26395938</v>
       </c>
       <c r="U13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.31075698</v>
+        <v>0.30241936</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -3613,55 +3613,55 @@
         <v>45</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.37410071</v>
+        <v>0.36823106</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5179283</v>
+        <v>0.5080645</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M14" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>5.25</v>
+        <v>5.338983</v>
       </c>
       <c r="O14" t="n">
         <v>24</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6166667</v>
+        <v>1.5254238</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="T14" t="n">
-        <v>0.28451884</v>
+        <v>0.26956522</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -3671,64 +3671,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.27272728</v>
+        <v>0.28899083</v>
       </c>
       <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>34</v>
+      </c>
+      <c r="E15" t="n">
         <v>6</v>
       </c>
-      <c r="D15" t="n">
-        <v>32</v>
-      </c>
-      <c r="E15" t="n">
-        <v>11</v>
-      </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31858408</v>
+        <v>0.33474576</v>
       </c>
       <c r="I15" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.42201835</v>
+      </c>
+      <c r="K15" t="n">
         <v>15</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.40669855</v>
-      </c>
-      <c r="K15" t="n">
-        <v>17</v>
       </c>
       <c r="L15" t="n">
         <v>63</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N15" t="n">
-        <v>5.33121</v>
+        <v>4.909091</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3566879</v>
+        <v>1.383117</v>
       </c>
       <c r="S15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
-        <v>0.25</v>
+        <v>0.27040815</v>
       </c>
       <c r="U15" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.23232323</v>
+        <v>0.23039216</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H16" t="n">
-        <v>0.29816514</v>
+        <v>0.28181818</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>0.34343433</v>
+        <v>0.32352942</v>
       </c>
       <c r="K16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.375</v>
+        <v>4.821429</v>
       </c>
       <c r="O16" t="n">
+        <v>20</v>
+      </c>
+      <c r="P16" t="n">
         <v>8</v>
       </c>
-      <c r="P16" t="n">
-        <v>5</v>
-      </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2321428</v>
+        <v>1.3928572</v>
       </c>
       <c r="S16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.23076923</v>
+      </c>
+      <c r="U16" t="n">
         <v>12</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.21078432</v>
-      </c>
-      <c r="U16" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.30917874</v>
+        <v>0.2885572</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>0.39166668</v>
+        <v>0.37068966</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5797101</v>
+        <v>0.5223880400000001</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1090908</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
         <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>1.0909091</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>0.19897959</v>
+        <v>0.215</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.26612905</v>
+        <v>0.25089607</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3210332</v>
+        <v>0.32371795</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>0.41935483</v>
+        <v>0.39784947</v>
       </c>
       <c r="K18" t="n">
+        <v>20</v>
+      </c>
+      <c r="L18" t="n">
+        <v>59</v>
+      </c>
+      <c r="M18" t="n">
+        <v>21</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.3913043</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" t="n">
         <v>16</v>
       </c>
-      <c r="L18" t="n">
-        <v>52</v>
-      </c>
-      <c r="M18" t="n">
-        <v>13</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.0983605</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.8852459</v>
+        <v>0.9565217499999999</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>0.17727272</v>
+        <v>0.19444445</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3939,61 +3939,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.26923078</v>
+        <v>0.2741117</v>
       </c>
       <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3508772</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.40101522</v>
+      </c>
+      <c r="K19" t="n">
+        <v>19</v>
+      </c>
+      <c r="L19" t="n">
+        <v>47</v>
+      </c>
+      <c r="M19" t="n">
         <v>8</v>
       </c>
-      <c r="D19" t="n">
-        <v>31</v>
-      </c>
-      <c r="E19" t="n">
-        <v>13</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="N19" t="n">
+        <v>3.1666667</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
         <v>7</v>
       </c>
-      <c r="G19" t="n">
-        <v>19</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.34854773</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.1111112</v>
+      </c>
+      <c r="S19" t="n">
         <v>8</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.45673078</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8</v>
-      </c>
-      <c r="L19" t="n">
-        <v>53</v>
-      </c>
-      <c r="M19" t="n">
-        <v>15</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.3333333</v>
-      </c>
-      <c r="O19" t="n">
-        <v>6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>17</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.0925926</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
       <c r="T19" t="n">
-        <v>0.20103092</v>
+        <v>0.21212122</v>
       </c>
       <c r="U19" t="n">
         <v>5</v>
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.30241936</v>
+        <v>0.2821577</v>
       </c>
       <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>44</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.36690646</v>
+      </c>
+      <c r="I20" t="n">
         <v>3</v>
       </c>
-      <c r="D20" t="n">
-        <v>47</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>12</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="J20" t="n">
+        <v>0.45228216</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="n">
+        <v>42</v>
+      </c>
+      <c r="M20" t="n">
         <v>3</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.37809187</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.4919355</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>44</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
       <c r="N20" t="n">
-        <v>6.571429</v>
+        <v>5.484375</v>
       </c>
       <c r="O20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7936507</v>
+        <v>1.6875</v>
       </c>
       <c r="S20" t="n">
         <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>0.30597016</v>
+        <v>0.2889734</v>
       </c>
       <c r="U20" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.25</v>
+        <v>0.25738397</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.30078125</v>
+        <v>0.2992126</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>0.44915253</v>
+        <v>0.46413502</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M21" t="n">
         <v>30</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1311474</v>
+        <v>3.3934426</v>
       </c>
       <c r="O21" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2459016</v>
+        <v>1.1803279</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>0.25311205</v>
+        <v>0.24152543</v>
       </c>
       <c r="U21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.22317597</v>
+        <v>0.20704846</v>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
         <v>28</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H22" t="n">
-        <v>0.30566037</v>
+        <v>0.28957528</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>0.36480686</v>
+        <v>0.31277534</v>
       </c>
       <c r="K22" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L22" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>6.40678</v>
+        <v>6.559322</v>
       </c>
       <c r="O22" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q22" t="n">
+        <v>30</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.5762712</v>
+      </c>
+      <c r="S22" t="n">
+        <v>28</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.28270042</v>
+      </c>
+      <c r="U22" t="n">
         <v>25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4576272</v>
-      </c>
-      <c r="S22" t="n">
-        <v>23</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.26271185</v>
-      </c>
-      <c r="U22" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -4207,61 +4207,61 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.28248587</v>
+        <v>0.2636816</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
+        <v>11</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.35930735</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.45273632</v>
+      </c>
+      <c r="K23" t="n">
+        <v>9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>47</v>
+      </c>
+      <c r="M23" t="n">
         <v>8</v>
       </c>
-      <c r="G23" t="n">
-        <v>16</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.37438422</v>
-      </c>
-      <c r="I23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.43502825</v>
-      </c>
-      <c r="K23" t="n">
-        <v>13</v>
-      </c>
-      <c r="L23" t="n">
-        <v>41</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="P23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3777778</v>
+        <v>1.4444444</v>
       </c>
       <c r="S23" t="n">
         <v>21</v>
       </c>
       <c r="T23" t="n">
-        <v>0.25443786</v>
+        <v>0.25480768</v>
       </c>
       <c r="U23" t="n">
         <v>19</v>
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22707424</v>
+        <v>0.24561404</v>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E24" t="n">
+        <v>14</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>21</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.33461538</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.35526314</v>
+      </c>
+      <c r="K24" t="n">
         <v>25</v>
       </c>
-      <c r="F24" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>28</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="I24" t="n">
-        <v>25</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.32751092</v>
-      </c>
-      <c r="K24" t="n">
-        <v>28</v>
-      </c>
       <c r="L24" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M24" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="N24" t="n">
-        <v>3.6290324</v>
+        <v>4.142857</v>
       </c>
       <c r="O24" t="n">
+        <v>16</v>
+      </c>
+      <c r="P24" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q24" t="n">
         <v>11</v>
       </c>
-      <c r="P24" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>7</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.1451613</v>
+        <v>1.2222222</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>0.22807017</v>
+        <v>0.23404256</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -4341,61 +4341,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.27160493</v>
+        <v>0.2532189</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>0.35036495</v>
+        <v>0.32950193</v>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>0.47325101</v>
+        <v>0.44206008</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L25" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M25" t="n">
+        <v>20</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.645161</v>
+      </c>
+      <c r="O25" t="n">
         <v>18</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.935484</v>
-      </c>
-      <c r="O25" t="n">
-        <v>20</v>
       </c>
       <c r="P25" t="n">
         <v>8</v>
       </c>
       <c r="Q25" t="n">
+        <v>11</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3064516</v>
+      </c>
+      <c r="S25" t="n">
         <v>14</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.3387097</v>
-      </c>
-      <c r="S25" t="n">
-        <v>18</v>
-      </c>
       <c r="T25" t="n">
-        <v>0.25210086</v>
+        <v>0.24686192</v>
       </c>
       <c r="U25" t="n">
         <v>17</v>
@@ -4408,64 +4408,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.21428572</v>
+        <v>0.19371727</v>
       </c>
       <c r="C26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
+        <v>24</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.26976743</v>
+      </c>
+      <c r="I26" t="n">
+        <v>28</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.31413612</v>
+      </c>
+      <c r="K26" t="n">
+        <v>28</v>
+      </c>
+      <c r="L26" t="n">
+        <v>51</v>
+      </c>
+      <c r="M26" t="n">
+        <v>12</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.291391</v>
+      </c>
+      <c r="O26" t="n">
+        <v>17</v>
+      </c>
+      <c r="P26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q26" t="n">
         <v>16</v>
       </c>
-      <c r="H26" t="n">
-        <v>0.28767124</v>
-      </c>
-      <c r="I26" t="n">
-        <v>26</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.37244898</v>
-      </c>
-      <c r="K26" t="n">
-        <v>21</v>
-      </c>
-      <c r="L26" t="n">
-        <v>50</v>
-      </c>
-      <c r="M26" t="n">
-        <v>11</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.331169</v>
-      </c>
-      <c r="O26" t="n">
-        <v>5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>14</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.1883117</v>
+        <v>1.4701988</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="T26" t="n">
-        <v>0.25</v>
+        <v>0.2955665</v>
       </c>
       <c r="U26" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.19123507</v>
+        <v>0.18145162</v>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
@@ -4493,46 +4493,46 @@
         <v>13</v>
       </c>
       <c r="H27" t="n">
-        <v>0.25274727</v>
+        <v>0.23308271</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3426295</v>
+        <v>0.33467743</v>
       </c>
       <c r="K27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L27" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M27" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8028169</v>
+        <v>3.9295774</v>
       </c>
       <c r="O27" t="n">
         <v>13</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2394366</v>
+        <v>1.2253522</v>
       </c>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23220974</v>
+        <v>0.23420075</v>
       </c>
       <c r="U27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -4542,64 +4542,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2446352</v>
+        <v>0.25751072</v>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.29149798</v>
+      </c>
+      <c r="I28" t="n">
+        <v>23</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.43776825</v>
+      </c>
+      <c r="K28" t="n">
+        <v>13</v>
+      </c>
+      <c r="L28" t="n">
+        <v>51</v>
+      </c>
+      <c r="M28" t="n">
+        <v>12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.7741935</v>
+      </c>
+      <c r="O28" t="n">
         <v>11</v>
       </c>
-      <c r="G28" t="n">
-        <v>6</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.2952756</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="n">
         <v>21</v>
       </c>
-      <c r="J28" t="n">
-        <v>0.42918456</v>
-      </c>
-      <c r="K28" t="n">
-        <v>15</v>
-      </c>
-      <c r="L28" t="n">
-        <v>56</v>
-      </c>
-      <c r="M28" t="n">
-        <v>17</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.163934</v>
-      </c>
-      <c r="O28" t="n">
-        <v>21</v>
-      </c>
-      <c r="P28" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>25</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.0983607</v>
+        <v>1.016129</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>0.24347825</v>
+        <v>0.2246696</v>
       </c>
       <c r="U28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -4609,64 +4609,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.21989529</v>
+        <v>0.2371134</v>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D29" t="n">
+        <v>29</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16</v>
+      </c>
+      <c r="F29" t="n">
+        <v>13</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3116279</v>
+      </c>
+      <c r="I29" t="n">
+        <v>16</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.46907216</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>55</v>
+      </c>
+      <c r="M29" t="n">
+        <v>16</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6.3333335</v>
+      </c>
+      <c r="O29" t="n">
+        <v>28</v>
+      </c>
+      <c r="P29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>16</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.462963</v>
+      </c>
+      <c r="S29" t="n">
+        <v>22</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.28703704</v>
+      </c>
+      <c r="U29" t="n">
         <v>26</v>
-      </c>
-      <c r="E29" t="n">
-        <v>19</v>
-      </c>
-      <c r="F29" t="n">
-        <v>11</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.29383886</v>
-      </c>
-      <c r="I29" t="n">
-        <v>23</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.42931938</v>
-      </c>
-      <c r="K29" t="n">
-        <v>14</v>
-      </c>
-      <c r="L29" t="n">
-        <v>48</v>
-      </c>
-      <c r="M29" t="n">
-        <v>10</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5.1666665</v>
-      </c>
-      <c r="O29" t="n">
-        <v>22</v>
-      </c>
-      <c r="P29" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>7</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.3333334</v>
-      </c>
-      <c r="S29" t="n">
-        <v>17</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.27102804</v>
-      </c>
-      <c r="U29" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2</v>
+        <v>0.22815534</v>
       </c>
       <c r="C30" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
+        <v>18</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2920354</v>
+      </c>
+      <c r="I30" t="n">
         <v>22</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.24413146</v>
-      </c>
-      <c r="I30" t="n">
-        <v>30</v>
-      </c>
       <c r="J30" t="n">
-        <v>0.305</v>
+        <v>0.36407766</v>
       </c>
       <c r="K30" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5882354</v>
+        <v>4.0588236</v>
       </c>
       <c r="O30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2156863</v>
+        <v>1.3137255</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23076923</v>
+        <v>0.22222222</v>
       </c>
       <c r="U30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -4743,64 +4743,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.28078818</v>
+        <v>0.2815534</v>
       </c>
       <c r="C31" t="n">
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.35983264</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.50970876</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>42</v>
+      </c>
+      <c r="M31" t="n">
         <v>3</v>
       </c>
-      <c r="H31" t="n">
-        <v>0.3601695</v>
-      </c>
-      <c r="I31" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.49753696</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>45</v>
-      </c>
-      <c r="M31" t="n">
-        <v>7</v>
-      </c>
       <c r="N31" t="n">
-        <v>6.6666665</v>
+        <v>6.1666665</v>
       </c>
       <c r="O31" t="n">
+        <v>27</v>
+      </c>
+      <c r="P31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q31" t="n">
         <v>29</v>
       </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>20</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.574074</v>
+        <v>1.5555556</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T31" t="n">
-        <v>0.29577464</v>
+        <v>0.2890995</v>
       </c>
       <c r="U31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -546,61 +546,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23741691</v>
+        <v>0.23660295</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E2" t="n">
         <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30793288</v>
+        <v>0.30706444</v>
       </c>
       <c r="I2" t="n">
         <v>26</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3846154</v>
+        <v>0.3838922</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>4.222443</v>
+        <v>4.209449</v>
       </c>
       <c r="O2" t="n">
         <v>15</v>
       </c>
       <c r="P2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2737763</v>
+        <v>1.269685</v>
       </c>
       <c r="S2" t="n">
         <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>0.25031328</v>
+        <v>0.248991</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
@@ -613,61 +613,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.24412128</v>
+        <v>0.24349158</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" t="n">
         <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32202923</v>
+        <v>0.32095057</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4012995</v>
+        <v>0.40030628</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1763315</v>
+        <v>5.212192</v>
       </c>
       <c r="O3" t="n">
         <v>29</v>
       </c>
       <c r="P3" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4721893</v>
+        <v>1.4724501</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
       </c>
       <c r="T3" t="n">
-        <v>0.26636225</v>
+        <v>0.26642555</v>
       </c>
       <c r="U3" t="n">
         <v>29</v>
@@ -680,13 +680,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24663536</v>
+        <v>0.24620625</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
@@ -698,46 +698,46 @@
         <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.31197065</v>
+        <v>0.3125</v>
       </c>
       <c r="I4" t="n">
         <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41032863</v>
+        <v>0.40910497</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="M4" t="n">
         <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>3.610088</v>
+        <v>3.6035643</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
         <v>106</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2285829</v>
+        <v>1.2261386</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>0.22920696</v>
+        <v>0.22821577</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -747,46 +747,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23800564</v>
+        <v>0.23921812</v>
       </c>
       <c r="C5" t="n">
         <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="E5" t="n">
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>0.319202</v>
+        <v>0.3208219</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.39887112</v>
+        <v>0.40055847</v>
       </c>
       <c r="K5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="M5" t="n">
         <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3221135</v>
+        <v>4.287374</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
         <v>108</v>
@@ -795,13 +795,13 @@
         <v>17</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3573385</v>
+        <v>1.3536018</v>
       </c>
       <c r="S5" t="n">
         <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2520674</v>
+        <v>0.2518922</v>
       </c>
       <c r="U5" t="n">
         <v>25</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.24398074</v>
+        <v>0.24284807</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E6" t="n">
         <v>28</v>
@@ -832,43 +832,43 @@
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3147135</v>
+        <v>0.3137646</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>0.38940609</v>
+        <v>0.3871583</v>
       </c>
       <c r="K6" t="n">
         <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.611674</v>
+        <v>3.589908</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2294285</v>
+        <v>1.2230678</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>0.23831022</v>
+        <v>0.23756377</v>
       </c>
       <c r="U6" t="n">
         <v>9</v>
@@ -881,61 +881,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24359371</v>
+        <v>0.24373855</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3361007</v>
+        <v>0.336248</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.41031182</v>
+        <v>0.41081247</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="M7" t="n">
         <v>18</v>
       </c>
       <c r="N7" t="n">
-        <v>4.338334</v>
+        <v>4.3347654</v>
       </c>
       <c r="O7" t="n">
         <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q7" t="n">
         <v>29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2791157</v>
+        <v>1.2773438</v>
       </c>
       <c r="S7" t="n">
         <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>0.24623588</v>
+        <v>0.24627791</v>
       </c>
       <c r="U7" t="n">
         <v>18</v>
@@ -948,64 +948,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.24044587</v>
+        <v>0.24078159</v>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G8" t="n">
         <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31861913</v>
+        <v>0.31895828</v>
       </c>
       <c r="I8" t="n">
         <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>0.41210192</v>
+        <v>0.4128585</v>
       </c>
       <c r="K8" t="n">
         <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="M8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1488595</v>
+        <v>4.115202</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q8" t="n">
         <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3265306</v>
+        <v>1.3194774</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23875321</v>
+        <v>0.2381558</v>
       </c>
       <c r="U8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -1015,61 +1015,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.22942485</v>
+        <v>0.22965756</v>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G9" t="n">
         <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>0.30999434</v>
+        <v>0.30996928</v>
       </c>
       <c r="I9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3937083</v>
+        <v>0.3933396</v>
       </c>
       <c r="K9" t="n">
         <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="M9" t="n">
         <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>4.483871</v>
+        <v>4.5212765</v>
       </c>
       <c r="O9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q9" t="n">
         <v>24</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4384707</v>
+        <v>1.4397163</v>
       </c>
       <c r="S9" t="n">
         <v>27</v>
       </c>
       <c r="T9" t="n">
-        <v>0.246933</v>
+        <v>0.24704418</v>
       </c>
       <c r="U9" t="n">
         <v>19</v>
@@ -1082,61 +1082,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22838138</v>
+        <v>0.22925149</v>
       </c>
       <c r="C10" t="n">
         <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G10" t="n">
         <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>0.30935657</v>
+        <v>0.31008613</v>
       </c>
       <c r="I10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3677542</v>
+        <v>0.36893204</v>
       </c>
       <c r="K10" t="n">
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="M10" t="n">
         <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7285209</v>
+        <v>3.7104037</v>
       </c>
       <c r="O10" t="n">
         <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q10" t="n">
         <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2628481</v>
+        <v>1.2612578</v>
       </c>
       <c r="S10" t="n">
         <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>0.23673469</v>
+        <v>0.23671947</v>
       </c>
       <c r="U10" t="n">
         <v>8</v>
@@ -1149,43 +1149,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25591984</v>
+        <v>0.2548135</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G11" t="n">
         <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>0.32737127</v>
+        <v>0.3263497</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4210686</v>
+        <v>0.41937426</v>
       </c>
       <c r="K11" t="n">
         <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="M11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4591317</v>
+        <v>5.439752</v>
       </c>
       <c r="O11" t="n">
         <v>30</v>
@@ -1197,13 +1197,13 @@
         <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5170121</v>
+        <v>1.5180163</v>
       </c>
       <c r="S11" t="n">
         <v>30</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28672358</v>
+        <v>0.28646442</v>
       </c>
       <c r="U11" t="n">
         <v>30</v>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2364096</v>
+        <v>0.23488882</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
         <v>407</v>
@@ -1231,28 +1231,28 @@
         <v>115</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3151991</v>
+        <v>0.31359467</v>
       </c>
       <c r="I12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.39805827</v>
+      </c>
+      <c r="K12" t="n">
         <v>18</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.4010746</v>
-      </c>
-      <c r="K12" t="n">
-        <v>15</v>
-      </c>
       <c r="L12" t="n">
-        <v>824</v>
+        <v>838</v>
       </c>
       <c r="M12" t="n">
         <v>20</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6315162</v>
+        <v>3.646063</v>
       </c>
       <c r="O12" t="n">
         <v>7</v>
@@ -1261,16 +1261,16 @@
         <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2093116</v>
+        <v>1.2106299</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>0.23308986</v>
+        <v>0.23335427</v>
       </c>
       <c r="U12" t="n">
         <v>7</v>
@@ -1283,61 +1283,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.24179196</v>
+        <v>0.2417983</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E13" t="n">
         <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3151249</v>
+        <v>0.31531775</v>
       </c>
       <c r="I13" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.41301012</v>
+        <v>0.4131227</v>
       </c>
       <c r="K13" t="n">
         <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7869363</v>
+        <v>4.8050847</v>
       </c>
       <c r="O13" t="n">
         <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q13" t="n">
         <v>27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.399689</v>
+        <v>1.4052389</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T13" t="n">
-        <v>0.24176507</v>
+        <v>0.24254534</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.24604896</v>
+        <v>0.2459418</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E14" t="n">
         <v>20</v>
@@ -1365,46 +1365,46 @@
         <v>97</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31586245</v>
+        <v>0.3150384</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.39665323</v>
+        <v>0.39632466</v>
       </c>
       <c r="K14" t="n">
         <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="M14" t="n">
         <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>4.911997</v>
+        <v>4.9503517</v>
       </c>
       <c r="O14" t="n">
         <v>28</v>
       </c>
       <c r="P14" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q14" t="n">
         <v>25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4455407</v>
+        <v>1.4507427</v>
       </c>
       <c r="S14" t="n">
         <v>28</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26333642</v>
+        <v>0.2642661</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -1417,64 +1417,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.24050634</v>
+        <v>0.24022005</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G15" t="n">
+        <v>17</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3150123</v>
+      </c>
+      <c r="I15" t="n">
         <v>18</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.31538248</v>
-      </c>
-      <c r="I15" t="n">
-        <v>17</v>
-      </c>
       <c r="J15" t="n">
-        <v>0.39271381</v>
+        <v>0.39272615</v>
       </c>
       <c r="K15" t="n">
         <v>22</v>
       </c>
       <c r="L15" t="n">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>4.654438</v>
+        <v>4.6529894</v>
       </c>
       <c r="O15" t="n">
         <v>25</v>
       </c>
       <c r="P15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q15" t="n">
         <v>11</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.3974209</v>
       </c>
       <c r="S15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2388993</v>
+        <v>0.23868568</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1484,61 +1484,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26306027</v>
+        <v>0.26164216</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G16" t="n">
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34408894</v>
+        <v>0.34309512</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.43523955</v>
+        <v>0.43351716</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="M16" t="n">
         <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5604396</v>
+        <v>3.554563</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q16" t="n">
         <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1420722</v>
+        <v>1.1394175</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2166295</v>
+        <v>0.21602018</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1551,64 +1551,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.253605</v>
+        <v>0.25341192</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E17" t="n">
         <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G17" t="n">
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3306541</v>
+        <v>0.3303155</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.41128528</v>
+        <v>0.41066998</v>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N17" t="n">
-        <v>4.0153847</v>
+        <v>4.0152225</v>
       </c>
       <c r="O17" t="n">
         <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2366863</v>
+        <v>1.2400469</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.22858046</v>
+        <v>0.22944671</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1618,61 +1618,61 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2545567</v>
+        <v>0.25435647</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G18" t="n">
         <v>28</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33714285</v>
+        <v>0.3369243</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3978993</v>
+        <v>0.39804342</v>
       </c>
       <c r="K18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L18" t="n">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="M18" t="n">
         <v>11</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3644202</v>
+        <v>3.4798136</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1579154</v>
+        <v>1.16809</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.21707161</v>
+        <v>0.21920404</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
@@ -1685,61 +1685,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.24791859</v>
+        <v>0.2476307</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G19" t="n">
         <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3229081</v>
+        <v>0.3226333</v>
       </c>
       <c r="I19" t="n">
         <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4156645</v>
+        <v>0.41516355</v>
       </c>
       <c r="K19" t="n">
         <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="M19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N19" t="n">
-        <v>4.652242</v>
+        <v>4.624367</v>
       </c>
       <c r="O19" t="n">
         <v>24</v>
       </c>
       <c r="P19" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q19" t="n">
         <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3760818</v>
+        <v>1.373297</v>
       </c>
       <c r="S19" t="n">
         <v>23</v>
       </c>
       <c r="T19" t="n">
-        <v>0.25168815</v>
+        <v>0.2512914</v>
       </c>
       <c r="U19" t="n">
         <v>24</v>
@@ -1752,43 +1752,43 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.23418114</v>
+        <v>0.23350722</v>
       </c>
       <c r="C20" t="n">
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G20" t="n">
         <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>0.30371612</v>
+        <v>0.30262795</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>0.38120347</v>
+        <v>0.38079166</v>
       </c>
       <c r="K20" t="n">
         <v>27</v>
       </c>
       <c r="L20" t="n">
-        <v>783</v>
+        <v>797</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N20" t="n">
-        <v>4.312427</v>
+        <v>4.2730074</v>
       </c>
       <c r="O20" t="n">
         <v>18</v>
@@ -1800,16 +1800,16 @@
         <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3171016</v>
+        <v>1.3111281</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
       </c>
       <c r="T20" t="n">
-        <v>0.23882425</v>
+        <v>0.23779193</v>
       </c>
       <c r="U20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2370676</v>
+        <v>0.23719761</v>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E21" t="n">
         <v>8</v>
@@ -1837,43 +1837,43 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3174023</v>
+        <v>0.3172836</v>
       </c>
       <c r="I21" t="n">
         <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>0.42494446</v>
+        <v>0.42444235</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="M21" t="n">
         <v>26</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3856804</v>
+        <v>3.3710372</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1914557</v>
+        <v>1.1894325</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22823678</v>
+        <v>0.22789969</v>
       </c>
       <c r="U21" t="n">
         <v>3</v>
@@ -1886,61 +1886,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.23574969</v>
+        <v>0.23597915</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" t="n">
         <v>124</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3028779</v>
+        <v>0.3032062</v>
       </c>
       <c r="I22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.39931846</v>
+        <v>0.3984064</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" t="n">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="M22" t="n">
         <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>4.27597</v>
+        <v>4.231187</v>
       </c>
       <c r="O22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
         <v>115</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3241867</v>
+        <v>1.3149729</v>
       </c>
       <c r="S22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25689185</v>
+        <v>0.25525525</v>
       </c>
       <c r="U22" t="n">
         <v>26</v>
@@ -1953,64 +1953,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2611694</v>
+        <v>0.26267418</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>0.34014326</v>
+        <v>0.34172568</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.42278862</v>
+        <v>0.42603025</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>897</v>
+        <v>907</v>
       </c>
       <c r="M23" t="n">
         <v>29</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3128643</v>
+        <v>4.32</v>
       </c>
       <c r="O23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P23" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q23" t="n">
         <v>10</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3175281</v>
+        <v>1.3176923</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T23" t="n">
-        <v>0.23888378</v>
+        <v>0.23884673</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.22586873</v>
+        <v>0.2258681</v>
       </c>
       <c r="C24" t="n">
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
@@ -2038,43 +2038,43 @@
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3025862</v>
+        <v>0.3024182</v>
       </c>
       <c r="I24" t="n">
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3716216</v>
+        <v>0.3701816</v>
       </c>
       <c r="K24" t="n">
         <v>29</v>
       </c>
       <c r="L24" t="n">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="M24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N24" t="n">
-        <v>4.233823</v>
+        <v>4.2313433</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P24" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3362445</v>
+        <v>1.3362136</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2471555</v>
+        <v>0.2471875</v>
       </c>
       <c r="U24" t="n">
         <v>20</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2556853</v>
+        <v>0.25570777</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E25" t="n">
         <v>24</v>
@@ -2105,43 +2105,43 @@
         <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>0.30908066</v>
+        <v>0.30960357</v>
       </c>
       <c r="I25" t="n">
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4213276</v>
+        <v>0.4197869</v>
       </c>
       <c r="K25" t="n">
         <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5017905</v>
+        <v>4.4645667</v>
       </c>
       <c r="O25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P25" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q25" t="n">
         <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3752487</v>
+        <v>1.3677166</v>
       </c>
       <c r="S25" t="n">
         <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0.249528</v>
+        <v>0.2484414</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -2154,61 +2154,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.22933754</v>
+        <v>0.22971286</v>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3098237</v>
+        <v>0.31045932</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>0.37791798</v>
+        <v>0.3795256</v>
       </c>
       <c r="K26" t="n">
         <v>28</v>
       </c>
       <c r="L26" t="n">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="M26" t="n">
         <v>21</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6282907</v>
+        <v>3.6111975</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1846758</v>
+        <v>1.1815708</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24104337</v>
+        <v>0.23996265</v>
       </c>
       <c r="U26" t="n">
         <v>15</v>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.24268448</v>
+        <v>0.24157481</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
@@ -2239,43 +2239,43 @@
         <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>0.31845155</v>
+        <v>0.31776223</v>
       </c>
       <c r="I27" t="n">
         <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.39249364</v>
+        <v>0.39023623</v>
       </c>
       <c r="K27" t="n">
         <v>23</v>
       </c>
       <c r="L27" t="n">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="M27" t="n">
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1373563</v>
+        <v>4.1252947</v>
       </c>
       <c r="O27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
         <v>94</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3267169</v>
+        <v>1.3279654</v>
       </c>
       <c r="S27" t="n">
         <v>19</v>
       </c>
       <c r="T27" t="n">
-        <v>0.25117445</v>
+        <v>0.25069726</v>
       </c>
       <c r="U27" t="n">
         <v>23</v>
@@ -2288,61 +2288,61 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2600709</v>
+        <v>0.25877473</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G28" t="n">
         <v>26</v>
       </c>
       <c r="H28" t="n">
-        <v>0.33486107</v>
+        <v>0.3339949</v>
       </c>
       <c r="I28" t="n">
         <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>0.40251368</v>
+        <v>0.4007658</v>
       </c>
       <c r="K28" t="n">
         <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7626505</v>
+        <v>3.7973778</v>
       </c>
       <c r="O28" t="n">
         <v>9</v>
       </c>
       <c r="P28" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q28" t="n">
         <v>22</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1686747</v>
+        <v>1.1728247</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0.23210272</v>
+        <v>0.23245475</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
@@ -2355,61 +2355,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.24384081</v>
+        <v>0.24461105</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H29" t="n">
-        <v>0.31923294</v>
+        <v>0.32013386</v>
       </c>
       <c r="I29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>0.39734682</v>
+        <v>0.39925024</v>
       </c>
       <c r="K29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L29" t="n">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="M29" t="n">
         <v>16</v>
       </c>
       <c r="N29" t="n">
-        <v>4.120655</v>
+        <v>4.1300397</v>
       </c>
       <c r="O29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P29" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q29" t="n">
         <v>22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2489014</v>
+        <v>1.2509881</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>0.24108818</v>
+        <v>0.24110183</v>
       </c>
       <c r="U29" t="n">
         <v>16</v>
@@ -2422,61 +2422,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.24396363</v>
+        <v>0.24403101</v>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E30" t="n">
         <v>26</v>
       </c>
       <c r="F30" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3060296</v>
+        <v>0.30604783</v>
       </c>
       <c r="I30" t="n">
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3835058</v>
+        <v>0.38449612</v>
       </c>
       <c r="K30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.116832</v>
+        <v>4.131032</v>
       </c>
       <c r="O30" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P30" t="n">
         <v>106</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3069307</v>
+        <v>1.3063946</v>
       </c>
       <c r="S30" t="n">
         <v>14</v>
       </c>
       <c r="T30" t="n">
-        <v>0.23935667</v>
+        <v>0.23922548</v>
       </c>
       <c r="U30" t="n">
         <v>14</v>
@@ -2489,43 +2489,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.25015178</v>
+        <v>0.24962406</v>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.32456616</v>
+        <v>0.3242009</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.43442622</v>
+        <v>0.43458647</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="M31" t="n">
         <v>15</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7524176</v>
+        <v>4.754977</v>
       </c>
       <c r="O31" t="n">
         <v>26</v>
@@ -2534,16 +2534,16 @@
         <v>137</v>
       </c>
       <c r="Q31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
-        <v>1.397292</v>
+        <v>1.3954823</v>
       </c>
       <c r="S31" t="n">
         <v>24</v>
       </c>
       <c r="T31" t="n">
-        <v>0.25973636</v>
+        <v>0.2596439</v>
       </c>
       <c r="U31" t="n">
         <v>27</v>
@@ -2800,46 +2800,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24686192</v>
+        <v>0.23849373</v>
       </c>
       <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.30451128</v>
+      </c>
+      <c r="I2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.41004184</v>
+      </c>
+      <c r="K2" t="n">
         <v>15</v>
       </c>
-      <c r="D2" t="n">
-        <v>36</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.32089552</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.40585774</v>
-      </c>
-      <c r="K2" t="n">
-        <v>17</v>
-      </c>
       <c r="L2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N2" t="n">
         <v>3.2459016</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
@@ -2848,16 +2848,16 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>1.0163934</v>
       </c>
       <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.21333334</v>
+      </c>
+      <c r="U2" t="n">
         <v>4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.22807017</v>
-      </c>
-      <c r="U2" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.18134715</v>
+        <v>0.1761658</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>30</v>
@@ -2885,46 +2885,46 @@
         <v>29</v>
       </c>
       <c r="H3" t="n">
-        <v>0.25118482</v>
+        <v>0.23923445</v>
       </c>
       <c r="I3" t="n">
         <v>29</v>
       </c>
       <c r="J3" t="n">
-        <v>0.26943004</v>
+        <v>0.25906736</v>
       </c>
       <c r="K3" t="n">
         <v>30</v>
       </c>
       <c r="L3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>6.979592</v>
+        <v>7.125</v>
       </c>
       <c r="O3" t="n">
         <v>30</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6938776</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2893401</v>
+        <v>0.26041666</v>
       </c>
       <c r="U3" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2934,22 +2934,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.244</v>
+        <v>0.22857143</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
         <v>0.30769232</v>
@@ -2958,40 +2958,40 @@
         <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>0.404</v>
+        <v>0.38367346</v>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L4" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="M4" t="n">
         <v>29</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4590163</v>
+        <v>4.5737705</v>
       </c>
       <c r="O4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.295082</v>
+      </c>
+      <c r="S4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2246696</v>
+      </c>
+      <c r="U4" t="n">
         <v>12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>26</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.409836</v>
-      </c>
-      <c r="S4" t="n">
-        <v>20</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2532189</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -3001,64 +3001,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.23684211</v>
+        <v>0.2617801</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32093024</v>
+        <v>0.35321102</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4368421</v>
+        <v>0.4921466</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9056604</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
+        <v>9</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q5" t="n">
         <v>12</v>
       </c>
-      <c r="P5" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>16</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.0566038</v>
+        <v>1.0925926</v>
       </c>
       <c r="S5" t="n">
         <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>0.22164948</v>
+        <v>0.23152709</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -3068,43 +3068,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.25490198</v>
+        <v>0.23232323</v>
       </c>
       <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.34051725</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4040404</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M6" t="n">
         <v>10</v>
       </c>
-      <c r="D6" t="n">
-        <v>32</v>
-      </c>
-      <c r="E6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>13</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.35443038</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.44607842</v>
-      </c>
-      <c r="K6" t="n">
-        <v>11</v>
-      </c>
-      <c r="L6" t="n">
-        <v>55</v>
-      </c>
-      <c r="M6" t="n">
-        <v>16</v>
-      </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>0.9818182</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -3116,16 +3116,16 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9259259</v>
+        <v>0.8545455</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1897436</v>
+        <v>0.1761658</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3135,64 +3135,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.23857868</v>
+        <v>0.2413793</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3063063</v>
+        <v>0.30666667</v>
       </c>
       <c r="I7" t="n">
         <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>0.40609136</v>
+        <v>0.43349755</v>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>46</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
         <v>3.9807692</v>
       </c>
       <c r="O7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
         <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R7" t="n">
         <v>1.4038461</v>
       </c>
       <c r="S7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T7" t="n">
-        <v>0.27272728</v>
+        <v>0.27722773</v>
       </c>
       <c r="U7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -3202,64 +3202,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.22335026</v>
+        <v>0.22680412</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H8" t="n">
-        <v>0.28372094</v>
+        <v>0.2809524</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J8" t="n">
-        <v>0.36548224</v>
+        <v>0.3556701</v>
       </c>
       <c r="K8" t="n">
         <v>23</v>
       </c>
       <c r="L8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>2.8333333</v>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.2592592</v>
+        <v>1.0925926</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>0.23469388</v>
+        <v>0.20942408</v>
       </c>
       <c r="U8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3269,16 +3269,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.24489796</v>
+        <v>0.25615764</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" t="n">
         <v>22</v>
-      </c>
-      <c r="E9" t="n">
-        <v>26</v>
       </c>
       <c r="F9" t="n">
         <v>12</v>
@@ -3287,46 +3287,46 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3101852</v>
+        <v>0.32444444</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>0.46938777</v>
+        <v>0.4729064</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M9" t="n">
         <v>26</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8333333</v>
+        <v>3.8333333</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.2037038</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.21827412</v>
+      </c>
+      <c r="U9" t="n">
         <v>5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.1481482</v>
-      </c>
-      <c r="S9" t="n">
-        <v>9</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.21025641</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3336,16 +3336,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.22167487</v>
+        <v>0.21890548</v>
       </c>
       <c r="C10" t="n">
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
@@ -3354,46 +3354,46 @@
         <v>13</v>
       </c>
       <c r="H10" t="n">
-        <v>0.280543</v>
+        <v>0.28181818</v>
       </c>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J10" t="n">
-        <v>0.39408866</v>
+        <v>0.3880597</v>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="M10" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2468355</v>
+        <v>2.392405</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3481013</v>
+        <v>1.2531645</v>
       </c>
       <c r="S10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2244898</v>
+        <v>0.22164948</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3403,16 +3403,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.23175965</v>
+        <v>0.20434782</v>
       </c>
       <c r="C11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" t="n">
         <v>22</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
@@ -3421,46 +3421,46 @@
         <v>21</v>
       </c>
       <c r="H11" t="n">
-        <v>0.31460676</v>
+        <v>0.2981132</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J11" t="n">
-        <v>0.37339056</v>
+        <v>0.33043477</v>
       </c>
       <c r="K11" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="M11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
-        <v>4.695652</v>
+        <v>4.475138</v>
       </c>
       <c r="O11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5326087</v>
+        <v>1.5414366</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T11" t="n">
-        <v>0.28163266</v>
+        <v>0.27916667</v>
       </c>
       <c r="U11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -3470,64 +3470,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2525773</v>
+        <v>0.21925133</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3438914</v>
+        <v>0.31132075</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>0.46907216</v>
+        <v>0.4064171</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N12" t="n">
-        <v>1.6666666</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.962963</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>0.8888889</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
       <c r="T12" t="n">
-        <v>0.18274112</v>
+        <v>0.1959799</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.25</v>
+        <v>0.25615764</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3108108</v>
+        <v>0.32608697</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
-        <v>0.46</v>
+        <v>0.46305418</v>
       </c>
       <c r="K13" t="n">
         <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.9411764</v>
+        <v>6.12</v>
       </c>
       <c r="O13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5490196</v>
+        <v>1.78</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T13" t="n">
-        <v>0.26395938</v>
+        <v>0.29353234</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.30241936</v>
+        <v>0.29803923</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -3619,49 +3619,49 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36823106</v>
+        <v>0.3594306</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5080645</v>
+        <v>0.5058824</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
-        <v>5.338983</v>
+        <v>6.5172415</v>
       </c>
       <c r="O14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5254238</v>
+        <v>1.7068965</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="T14" t="n">
-        <v>0.26956522</v>
+        <v>0.2948718</v>
       </c>
       <c r="U14" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -3671,61 +3671,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.28899083</v>
+        <v>0.28504673</v>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
         <v>6</v>
       </c>
-      <c r="F15" t="n">
-        <v>5</v>
-      </c>
       <c r="G15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H15" t="n">
-        <v>0.33474576</v>
+        <v>0.33760685</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.42201835</v>
+        <v>0.42523363</v>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="N15" t="n">
-        <v>4.909091</v>
+        <v>5.0066223</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.383117</v>
+        <v>1.3311259</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T15" t="n">
-        <v>0.27040815</v>
+        <v>0.2620321</v>
       </c>
       <c r="U15" t="n">
         <v>22</v>
@@ -3738,64 +3738,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.23039216</v>
+        <v>0.22660099</v>
       </c>
       <c r="C16" t="n">
         <v>23</v>
       </c>
       <c r="D16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E16" t="n">
         <v>22</v>
       </c>
-      <c r="E16" t="n">
-        <v>26</v>
-      </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H16" t="n">
-        <v>0.28181818</v>
+        <v>0.27522936</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>0.32352942</v>
+        <v>0.33990148</v>
       </c>
       <c r="K16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.821429</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P16" t="n">
         <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3928572</v>
+        <v>1.2857143</v>
       </c>
       <c r="S16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="T16" t="n">
-        <v>0.23076923</v>
+        <v>0.2195122</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3805,64 +3805,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2885572</v>
+        <v>0.2538071</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
+        <v>21</v>
+      </c>
+      <c r="E17" t="n">
         <v>28</v>
       </c>
-      <c r="E17" t="n">
-        <v>18</v>
-      </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H17" t="n">
-        <v>0.37068966</v>
+        <v>0.3242009</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5223880400000001</v>
+        <v>0.42639595</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>3.1090908</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0909091</v>
+        <v>1.1636363</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0.215</v>
+        <v>0.23152709</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25089607</v>
+        <v>0.25266904</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
@@ -3890,46 +3890,46 @@
         <v>21</v>
       </c>
       <c r="H18" t="n">
-        <v>0.32371795</v>
+        <v>0.33333334</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.39784947</v>
+        <v>0.40213522</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L18" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3913043</v>
+        <v>5.029412</v>
       </c>
       <c r="O18" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="P18" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.0441177</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.22093023</v>
+      </c>
+      <c r="U18" t="n">
         <v>9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>16</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.9565217499999999</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.19444445</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3939,64 +3939,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2741117</v>
+        <v>0.25531915</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
         <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3508772</v>
+        <v>0.33333334</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.40101522</v>
+        <v>0.3882979</v>
       </c>
       <c r="K19" t="n">
         <v>19</v>
       </c>
       <c r="L19" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.3333333</v>
+      </c>
+      <c r="O19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.1666667</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q19" t="n">
+        <v>16</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.1851852</v>
+      </c>
+      <c r="S19" t="n">
         <v>10</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.1111112</v>
-      </c>
-      <c r="S19" t="n">
-        <v>8</v>
-      </c>
       <c r="T19" t="n">
-        <v>0.21212122</v>
+        <v>0.21890548</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2821577</v>
+        <v>0.25941423</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.34065935</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.42259413</v>
+      </c>
+      <c r="K20" t="n">
+        <v>13</v>
+      </c>
+      <c r="L20" t="n">
+        <v>51</v>
+      </c>
+      <c r="M20" t="n">
+        <v>14</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.4307694</v>
+      </c>
+      <c r="O20" t="n">
+        <v>17</v>
+      </c>
+      <c r="P20" t="n">
         <v>10</v>
       </c>
-      <c r="G20" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.36690646</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.45228216</v>
-      </c>
-      <c r="K20" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" t="n">
-        <v>42</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.484375</v>
-      </c>
-      <c r="O20" t="n">
-        <v>26</v>
-      </c>
-      <c r="P20" t="n">
-        <v>11</v>
-      </c>
       <c r="Q20" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6875</v>
+        <v>1.5692308</v>
       </c>
       <c r="S20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2889734</v>
+        <v>0.26666668</v>
       </c>
       <c r="U20" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -4073,16 +4073,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.25738397</v>
+        <v>0.26778242</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
         <v>14</v>
@@ -4091,46 +4091,46 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2992126</v>
+        <v>0.3127413</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>0.46413502</v>
+        <v>0.48535565</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M21" t="n">
         <v>30</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3934426</v>
+        <v>3.0983605</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
+        <v>17</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.0655738</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.22173913</v>
+      </c>
+      <c r="U21" t="n">
         <v>11</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.1803279</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.24152543</v>
-      </c>
-      <c r="U21" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -4140,16 +4140,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.20704846</v>
+        <v>0.21982759</v>
       </c>
       <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>22</v>
+      </c>
+      <c r="E22" t="n">
         <v>27</v>
-      </c>
-      <c r="D22" t="n">
-        <v>19</v>
-      </c>
-      <c r="E22" t="n">
-        <v>28</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -4158,28 +4158,28 @@
         <v>27</v>
       </c>
       <c r="H22" t="n">
-        <v>0.28957528</v>
+        <v>0.30566037</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>0.31277534</v>
+        <v>0.31896552</v>
       </c>
       <c r="K22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L22" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N22" t="n">
-        <v>6.559322</v>
+        <v>5.7</v>
       </c>
       <c r="O22" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P22" t="n">
         <v>14</v>
@@ -4188,16 +4188,16 @@
         <v>30</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5762712</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="T22" t="n">
-        <v>0.28270042</v>
+        <v>0.25957447</v>
       </c>
       <c r="U22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -4207,34 +4207,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2636816</v>
+        <v>0.275</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
       </c>
       <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.36956522</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K23" t="n">
         <v>5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.35930735</v>
-      </c>
-      <c r="I23" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.45273632</v>
-      </c>
-      <c r="K23" t="n">
-        <v>9</v>
       </c>
       <c r="L23" t="n">
         <v>47</v>
@@ -4246,25 +4246,25 @@
         <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4444444</v>
+        <v>1.3888888</v>
       </c>
       <c r="S23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T23" t="n">
-        <v>0.25480768</v>
+        <v>0.2451923</v>
       </c>
       <c r="U23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24561404</v>
+        <v>0.24553572</v>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
         <v>31</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H24" t="n">
-        <v>0.33461538</v>
+        <v>0.32677165</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>0.35526314</v>
+        <v>0.3392857</v>
       </c>
       <c r="K24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L24" t="n">
         <v>53</v>
       </c>
       <c r="M24" t="n">
+        <v>15</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.428571</v>
+      </c>
+      <c r="O24" t="n">
+        <v>15</v>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>17</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.2539682</v>
+      </c>
+      <c r="S24" t="n">
         <v>14</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.142857</v>
-      </c>
-      <c r="O24" t="n">
-        <v>16</v>
-      </c>
-      <c r="P24" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>11</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.2222222</v>
-      </c>
-      <c r="S24" t="n">
-        <v>11</v>
-      </c>
       <c r="T24" t="n">
-        <v>0.23404256</v>
+        <v>0.24896266</v>
       </c>
       <c r="U24" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2532189</v>
+        <v>0.25</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>0.32950193</v>
+        <v>0.328125</v>
       </c>
       <c r="I25" t="n">
         <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>0.44206008</v>
+        <v>0.3859649</v>
       </c>
       <c r="K25" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L25" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>4.645161</v>
+        <v>3.857143</v>
       </c>
       <c r="O25" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P25" t="n">
         <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3064516</v>
+        <v>1.2063493</v>
       </c>
       <c r="S25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>0.24686192</v>
+        <v>0.22033899</v>
       </c>
       <c r="U25" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -4408,61 +4408,61 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.19371727</v>
+        <v>0.20512821</v>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
         <v>29</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
+        <v>21</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.29147983</v>
+      </c>
+      <c r="I26" t="n">
+        <v>25</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.34871796</v>
+      </c>
+      <c r="K26" t="n">
         <v>24</v>
       </c>
-      <c r="H26" t="n">
-        <v>0.26976743</v>
-      </c>
-      <c r="I26" t="n">
-        <v>28</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.31413612</v>
-      </c>
-      <c r="K26" t="n">
-        <v>28</v>
-      </c>
       <c r="L26" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N26" t="n">
-        <v>4.291391</v>
+        <v>4.649007</v>
       </c>
       <c r="O26" t="n">
+        <v>21</v>
+      </c>
+      <c r="P26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q26" t="n">
         <v>17</v>
       </c>
-      <c r="P26" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>16</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.4701988</v>
+        <v>1.5298014</v>
       </c>
       <c r="S26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2955665</v>
+        <v>0.297561</v>
       </c>
       <c r="U26" t="n">
         <v>30</v>
@@ -4475,61 +4475,61 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.18145162</v>
+        <v>0.17004049</v>
       </c>
       <c r="C27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H27" t="n">
-        <v>0.23308271</v>
+        <v>0.22932331</v>
       </c>
       <c r="I27" t="n">
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>0.33467743</v>
+        <v>0.31578946</v>
       </c>
       <c r="K27" t="n">
+        <v>29</v>
+      </c>
+      <c r="L27" t="n">
+        <v>64</v>
+      </c>
+      <c r="M27" t="n">
         <v>26</v>
       </c>
-      <c r="L27" t="n">
-        <v>60</v>
-      </c>
-      <c r="M27" t="n">
-        <v>23</v>
-      </c>
       <c r="N27" t="n">
-        <v>3.9295774</v>
+        <v>3.875</v>
       </c>
       <c r="O27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
         <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2253522</v>
+        <v>1.2638888</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T27" t="n">
-        <v>0.23420075</v>
+        <v>0.229927</v>
       </c>
       <c r="U27" t="n">
         <v>14</v>
@@ -4545,61 +4545,61 @@
         <v>0.25751072</v>
       </c>
       <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="n">
         <v>8</v>
       </c>
-      <c r="D28" t="n">
-        <v>27</v>
-      </c>
-      <c r="E28" t="n">
-        <v>19</v>
-      </c>
-      <c r="F28" t="n">
-        <v>9</v>
-      </c>
-      <c r="G28" t="n">
-        <v>13</v>
-      </c>
       <c r="H28" t="n">
-        <v>0.29149798</v>
+        <v>0.3</v>
       </c>
       <c r="I28" t="n">
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>0.43776825</v>
+        <v>0.45064378</v>
       </c>
       <c r="K28" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7741935</v>
+        <v>4.428571</v>
       </c>
       <c r="O28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P28" t="n">
         <v>10</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R28" t="n">
-        <v>1.016129</v>
+        <v>1.1111112</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2246696</v>
+        <v>0.23376623</v>
       </c>
       <c r="U28" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
@@ -4609,40 +4609,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2371134</v>
+        <v>0.26020408</v>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3116279</v>
+        <v>0.3409091</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>0.46907216</v>
+        <v>0.49489796</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N29" t="n">
         <v>6.3333335</v>
@@ -4651,22 +4651,22 @@
         <v>28</v>
       </c>
       <c r="P29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R29" t="n">
-        <v>1.462963</v>
+        <v>1.4444444</v>
       </c>
       <c r="S29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T29" t="n">
-        <v>0.28703704</v>
+        <v>0.28169015</v>
       </c>
       <c r="U29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -4676,64 +4676,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.22815534</v>
+        <v>0.2488263</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" t="n">
         <v>8</v>
       </c>
-      <c r="G30" t="n">
-        <v>18</v>
-      </c>
       <c r="H30" t="n">
-        <v>0.2920354</v>
+        <v>0.31196582</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>0.36407766</v>
+        <v>0.41314554</v>
       </c>
       <c r="K30" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L30" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>4.0588236</v>
+        <v>4.4117646</v>
       </c>
       <c r="O30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3137255</v>
+        <v>1.3529412</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T30" t="n">
-        <v>0.22222222</v>
+        <v>0.2263158</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -4743,13 +4743,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2815534</v>
+        <v>0.26600984</v>
       </c>
       <c r="C31" t="n">
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
         <v>10</v>
@@ -4761,46 +4761,46 @@
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.35983264</v>
+        <v>0.34615386</v>
       </c>
       <c r="I31" t="n">
         <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>0.50970876</v>
+        <v>0.50246304</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>6.1666665</v>
+        <v>5.3333335</v>
       </c>
       <c r="O31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5555556</v>
+        <v>1.4074074</v>
       </c>
       <c r="S31" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2890995</v>
+        <v>0.27450982</v>
       </c>
       <c r="U31" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/mlb_team_stats.xlsx
+++ b/docs/data/mlb_team_stats.xlsx
@@ -2800,46 +2800,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.23849373</v>
+        <v>0.22885571</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H2" t="n">
-        <v>0.30451128</v>
+        <v>0.30088496</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J2" t="n">
-        <v>0.41004184</v>
+        <v>0.37313432</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="M2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2459016</v>
+        <v>3.8076923</v>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P2" t="n">
         <v>6</v>
@@ -2848,16 +2848,16 @@
         <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0163934</v>
+        <v>1.0384616</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0.21333334</v>
+        <v>0.21052632</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2900,19 +2900,19 @@
         <v>60</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="N3" t="n">
         <v>7.125</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P3" t="n">
         <v>10</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
@@ -2934,64 +2934,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.22857143</v>
+        <v>0.21393035</v>
       </c>
       <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.29147983</v>
+      </c>
+      <c r="I4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.35323384</v>
+      </c>
+      <c r="K4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L4" t="n">
+        <v>53</v>
+      </c>
+      <c r="M4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.4117646</v>
+      </c>
+      <c r="O4" t="n">
         <v>21</v>
       </c>
-      <c r="D4" t="n">
-        <v>29</v>
-      </c>
-      <c r="E4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.30769232</v>
-      </c>
-      <c r="I4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.38367346</v>
-      </c>
-      <c r="K4" t="n">
-        <v>22</v>
-      </c>
-      <c r="L4" t="n">
-        <v>66</v>
-      </c>
-      <c r="M4" t="n">
-        <v>29</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.5737705</v>
-      </c>
-      <c r="O4" t="n">
-        <v>20</v>
-      </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>1.295082</v>
+        <v>1.2352941</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2246696</v>
+        <v>0.21164021</v>
       </c>
       <c r="U4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -3010,19 +3010,19 @@
         <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0.35321102</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0.4921466</v>
@@ -3034,31 +3034,31 @@
         <v>48</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N5" t="n">
         <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
         <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R5" t="n">
         <v>1.0925926</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
         <v>0.23152709</v>
       </c>
       <c r="U5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -3071,25 +3071,25 @@
         <v>0.23232323</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
         <v>0.34051725</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>0.4040404</v>
@@ -3101,7 +3101,7 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>0.9818182</v>
@@ -3138,19 +3138,19 @@
         <v>0.2413793</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
         <v>0.30666667</v>
@@ -3168,7 +3168,7 @@
         <v>46</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
         <v>3.9807692</v>
@@ -3180,19 +3180,19 @@
         <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R7" t="n">
         <v>1.4038461</v>
       </c>
       <c r="S7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T7" t="n">
         <v>0.27722773</v>
       </c>
       <c r="U7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -3205,25 +3205,25 @@
         <v>0.22680412</v>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" t="n">
         <v>0.2809524</v>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J8" t="n">
         <v>0.3556701</v>
@@ -3235,7 +3235,7 @@
         <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N8" t="n">
         <v>2.8333333</v>
@@ -3253,13 +3253,13 @@
         <v>1.0925926</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
         <v>0.20942408</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3272,37 +3272,37 @@
         <v>0.25615764</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0.32444444</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
         <v>0.4729064</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>64</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N9" t="n">
         <v>3.8333333</v>
@@ -3326,7 +3326,7 @@
         <v>0.21827412</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -3339,37 +3339,37 @@
         <v>0.21890548</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
         <v>0.28181818</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
         <v>0.3880597</v>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
         <v>61</v>
       </c>
       <c r="M10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="N10" t="n">
         <v>2.392405</v>
@@ -3381,19 +3381,19 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
         <v>1.2531645</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T10" t="n">
         <v>0.22164948</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -3403,64 +3403,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.20434782</v>
+        <v>0.19689119</v>
       </c>
       <c r="C11" t="n">
         <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
+        <v>28</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
         <v>22</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
+        <v>0.2798165</v>
+      </c>
+      <c r="I11" t="n">
+        <v>27</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.31606218</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28</v>
+      </c>
+      <c r="L11" t="n">
+        <v>51</v>
+      </c>
+      <c r="M11" t="n">
+        <v>16</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="O11" t="n">
+        <v>17</v>
+      </c>
+      <c r="P11" t="n">
         <v>6</v>
       </c>
-      <c r="G11" t="n">
-        <v>21</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.2981132</v>
-      </c>
-      <c r="I11" t="n">
-        <v>24</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.33043477</v>
-      </c>
-      <c r="K11" t="n">
-        <v>27</v>
-      </c>
-      <c r="L11" t="n">
-        <v>58</v>
-      </c>
-      <c r="M11" t="n">
-        <v>17</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.475138</v>
-      </c>
-      <c r="O11" t="n">
-        <v>18</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>7</v>
       </c>
-      <c r="Q11" t="n">
-        <v>10</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.5414366</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T11" t="n">
-        <v>0.27916667</v>
+        <v>0.27</v>
       </c>
       <c r="U11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -3473,25 +3473,25 @@
         <v>0.21925133</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
         <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
         <v>0.31132075</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
         <v>0.4064171</v>
@@ -3503,7 +3503,7 @@
         <v>58</v>
       </c>
       <c r="M12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -3537,64 +3537,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.25615764</v>
+        <v>0.24096386</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.31578946</v>
+      </c>
+      <c r="I13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.42771083</v>
+      </c>
+      <c r="K13" t="n">
         <v>11</v>
       </c>
-      <c r="G13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.32608697</v>
-      </c>
-      <c r="I13" t="n">
-        <v>13</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.46305418</v>
-      </c>
-      <c r="K13" t="n">
-        <v>8</v>
-      </c>
       <c r="L13" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>6.12</v>
+        <v>5.785714</v>
       </c>
       <c r="O13" t="n">
         <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.78</v>
+        <v>1.7380953</v>
       </c>
       <c r="S13" t="n">
         <v>30</v>
       </c>
       <c r="T13" t="n">
-        <v>0.29353234</v>
+        <v>0.27878788</v>
       </c>
       <c r="U13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -3604,64 +3604,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.29803923</v>
+        <v>0.25592417</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3594306</v>
+        <v>0.31601733</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5058824</v>
+        <v>0.4407583</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M14" t="n">
         <v>21</v>
       </c>
       <c r="N14" t="n">
-        <v>6.5172415</v>
+        <v>7.5306125</v>
       </c>
       <c r="O14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P14" t="n">
         <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7068965</v>
+        <v>1.6734694</v>
       </c>
       <c r="S14" t="n">
         <v>29</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2948718</v>
+        <v>0.2979798</v>
       </c>
       <c r="U14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -3680,13 +3680,13 @@
         <v>31</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H15" t="n">
         <v>0.33760685</v>
@@ -3698,37 +3698,37 @@
         <v>0.42523363</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
         <v>58</v>
       </c>
       <c r="M15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N15" t="n">
         <v>5.0066223</v>
       </c>
       <c r="O15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
         <v>1.3311259</v>
       </c>
       <c r="S15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T15" t="n">
         <v>0.2620321</v>
       </c>
       <c r="U15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -3738,61 +3738,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.22660099</v>
+        <v>0.20245399</v>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H16" t="n">
-        <v>0.27522936</v>
+        <v>0.25714287</v>
       </c>
       <c r="I16" t="n">
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>0.33990148</v>
+        <v>0.31288344</v>
       </c>
       <c r="K16" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2857143</v>
+        <v>1.2222222</v>
       </c>
       <c r="S16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2195122</v>
+        <v>0.21428572</v>
       </c>
       <c r="U16" t="n">
         <v>7</v>
@@ -3808,43 +3808,43 @@
         <v>0.2538071</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
         <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H17" t="n">
         <v>0.3242009</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J17" t="n">
         <v>0.42639595</v>
       </c>
       <c r="K17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
         <v>40</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
         <v>3.1090908</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
         <v>6</v>
@@ -3856,13 +3856,13 @@
         <v>1.1636363</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
         <v>0.23152709</v>
       </c>
       <c r="U17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.25266904</v>
+        <v>0.25609756</v>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33333334</v>
+        <v>0.3392857</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.40213522</v>
+        <v>0.41869918</v>
       </c>
       <c r="K18" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L18" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>5.029412</v>
+        <v>5.644068</v>
       </c>
       <c r="O18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P18" t="n">
         <v>11</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0441177</v>
+        <v>1.0508474</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0.22093023</v>
+        <v>0.22222222</v>
       </c>
       <c r="U18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -3942,13 +3942,13 @@
         <v>0.25531915</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>23</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
@@ -3960,31 +3960,31 @@
         <v>0.33333334</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
         <v>0.3882979</v>
       </c>
       <c r="K19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L19" t="n">
         <v>43</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
         <v>3.3333333</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
         <v>9</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R19" t="n">
         <v>1.1851852</v>
@@ -3996,7 +3996,7 @@
         <v>0.21890548</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -4006,64 +4006,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.25941423</v>
+        <v>0.25373134</v>
       </c>
       <c r="C20" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" t="n">
+        <v>29</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.33187774</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4079602</v>
+      </c>
+      <c r="K20" t="n">
+        <v>15</v>
+      </c>
+      <c r="L20" t="n">
+        <v>42</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.7454543</v>
+      </c>
+      <c r="O20" t="n">
+        <v>23</v>
+      </c>
+      <c r="P20" t="n">
         <v>8</v>
       </c>
-      <c r="D20" t="n">
-        <v>36</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F20" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" t="n">
-        <v>13</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.34065935</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.42259413</v>
-      </c>
-      <c r="K20" t="n">
-        <v>13</v>
-      </c>
-      <c r="L20" t="n">
-        <v>51</v>
-      </c>
-      <c r="M20" t="n">
-        <v>14</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.4307694</v>
-      </c>
-      <c r="O20" t="n">
-        <v>17</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5692308</v>
+        <v>1.5272727</v>
       </c>
       <c r="S20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T20" t="n">
-        <v>0.26666668</v>
+        <v>0.2606635</v>
       </c>
       <c r="U20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -4073,64 +4073,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.26778242</v>
+        <v>0.29186603</v>
       </c>
       <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>30</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" t="n">
         <v>4</v>
       </c>
-      <c r="D21" t="n">
-        <v>35</v>
-      </c>
-      <c r="E21" t="n">
-        <v>8</v>
-      </c>
-      <c r="F21" t="n">
-        <v>14</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.3127413</v>
+        <v>0.33480176</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>0.48535565</v>
+        <v>0.49760765</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N21" t="n">
-        <v>3.0983605</v>
+        <v>3.4615386</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P21" t="n">
         <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0655738</v>
+        <v>1.1730769</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>0.22173913</v>
+        <v>0.2361809</v>
       </c>
       <c r="U21" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -4140,64 +4140,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.21982759</v>
+        <v>0.20918368</v>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
+        <v>26</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2882883</v>
+      </c>
+      <c r="I22" t="n">
+        <v>24</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.31632653</v>
+      </c>
+      <c r="K22" t="n">
         <v>27</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.30566037</v>
-      </c>
-      <c r="I22" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.31896552</v>
-      </c>
-      <c r="K22" t="n">
-        <v>28</v>
-      </c>
       <c r="L22" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N22" t="n">
-        <v>5.7</v>
+        <v>3.9807692</v>
       </c>
       <c r="O22" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.1538461</v>
       </c>
       <c r="S22" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>0.25957447</v>
+        <v>0.20418848</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4210,19 +4210,19 @@
         <v>0.275</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>41</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
         <v>0.36956522</v>
@@ -4240,31 +4240,31 @@
         <v>47</v>
       </c>
       <c r="M23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N23" t="n">
         <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P23" t="n">
         <v>7</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R23" t="n">
         <v>1.3888888</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T23" t="n">
         <v>0.2451923</v>
       </c>
       <c r="U23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -4274,64 +4274,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.24553572</v>
+        <v>0.24867725</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
         <v>31</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>0.32677165</v>
+        <v>0.34246576</v>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3392857</v>
+        <v>0.35978836</v>
       </c>
       <c r="K24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L24" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M24" t="n">
+        <v>7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.8333333</v>
+      </c>
+      <c r="O24" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>11</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.2407408</v>
+      </c>
+      <c r="S24" t="n">
         <v>15</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.428571</v>
-      </c>
-      <c r="O24" t="n">
-        <v>15</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>17</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.2539682</v>
-      </c>
-      <c r="S24" t="n">
-        <v>14</v>
-      </c>
       <c r="T24" t="n">
-        <v>0.24896266</v>
+        <v>0.2413793</v>
       </c>
       <c r="U24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -4341,64 +4341,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.25</v>
+        <v>0.24873096</v>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H25" t="n">
-        <v>0.328125</v>
+        <v>0.3196347</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3859649</v>
+        <v>0.36548224</v>
       </c>
       <c r="K25" t="n">
         <v>21</v>
       </c>
       <c r="L25" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.857143</v>
+        <v>4.3333335</v>
       </c>
       <c r="O25" t="n">
+        <v>18</v>
+      </c>
+      <c r="P25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q25" t="n">
         <v>11</v>
       </c>
-      <c r="P25" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" t="n">
